--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1899,7 +1899,7 @@
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
@@ -1915,237 +1915,263 @@
         <v>1</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr"/>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="n">
+      <c r="C52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H52" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr"/>
-      <c r="C52" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="9" t="n">
+      <c r="B53" s="8" t="inlineStr"/>
+      <c r="C53" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G52" s="9" t="inlineStr"/>
-      <c r="H52" s="9" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="D53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr"/>
+      <c r="H53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="5" t="n">
+      <c r="C54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr"/>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="5" t="n">
+      <c r="C56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr"/>
-      <c r="C56" s="9" t="n">
+      <c r="B57" s="8" t="inlineStr"/>
+      <c r="C57" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="9" t="n">
+      <c r="D57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G56" s="9" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="n">
+      <c r="C58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H58" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr"/>
-      <c r="C58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="9" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr"/>
+      <c r="C59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr"/>
+      <c r="H59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B59" s="10" t="inlineStr"/>
-      <c r="C59" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="D59" s="11" t="n">
+      <c r="B60" s="10" t="inlineStr"/>
+      <c r="C60" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D60" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E60" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="11" t="n">
-        <v>59</v>
-      </c>
-      <c r="G59" s="11" t="inlineStr"/>
-      <c r="H59" s="11" t="inlineStr"/>
+      <c r="F60" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="G60" s="11" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2161,7 +2187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5222,11 +5248,61 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>3811</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Reverse Degree of a String</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Simulation</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="J64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v>46285.42987268518</v>
+      </c>
+      <c r="L64" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F63">
+  <conditionalFormatting sqref="F5:F64">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5297,6 +5373,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5308,7 +5385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I169"/>
+  <dimension ref="A1:I172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8356,7 +8433,7 @@
     <row r="139">
       <c r="A139" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B139" s="2" t="n"/>
@@ -8566,7 +8643,7 @@
     <row r="149">
       <c r="A149" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B149" s="18" t="n"/>
@@ -8597,11 +8674,11 @@
       <c r="A151" s="5" t="inlineStr"/>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Reverse Degree of a String</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>125</v>
+        <v>3811</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
@@ -8609,18 +8686,18 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H151" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46285.42987268518</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -8631,7 +8708,7 @@
     <row r="152">
       <c r="A152" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B152" s="18" t="n"/>
@@ -8662,121 +8739,121 @@
       <c r="A154" s="5" t="inlineStr"/>
       <c r="B154" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H154" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B155" s="18" t="n"/>
+      <c r="C155" s="18" t="n"/>
+      <c r="D155" s="18" t="n"/>
+      <c r="E155" s="18" t="n"/>
+      <c r="F155" s="18" t="n"/>
+      <c r="G155" s="18" t="n"/>
+      <c r="H155" s="18" t="n"/>
+      <c r="I155" s="18" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="21" t="n"/>
+      <c r="B156" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C156" s="21" t="n"/>
+      <c r="D156" s="21" t="n"/>
+      <c r="E156" s="21" t="n"/>
+      <c r="F156" s="21" t="n"/>
+      <c r="G156" s="21" t="n"/>
+      <c r="H156" s="21" t="n"/>
+      <c r="I156" s="21" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr"/>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C154" s="5" t="n">
+      <c r="C157" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E154" s="5" t="n">
+      <c r="E157" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F154" s="5" t="n">
+      <c r="F157" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G154" s="5" t="inlineStr">
+      <c r="G157" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H154" s="12" t="n">
+      <c r="H157" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I154" s="13" t="inlineStr">
+      <c r="I157" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="16" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="n"/>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" s="2" t="n"/>
-      <c r="F155" s="2" t="n"/>
-      <c r="G155" s="2" t="n"/>
-      <c r="H155" s="2" t="n"/>
-      <c r="I155" s="2" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B156" s="18" t="n"/>
-      <c r="C156" s="18" t="n"/>
-      <c r="D156" s="18" t="n"/>
-      <c r="E156" s="18" t="n"/>
-      <c r="F156" s="18" t="n"/>
-      <c r="G156" s="18" t="n"/>
-      <c r="H156" s="18" t="n"/>
-      <c r="I156" s="18" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="21" t="n"/>
-      <c r="B157" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C157" s="21" t="n"/>
-      <c r="D157" s="21" t="n"/>
-      <c r="E157" s="21" t="n"/>
-      <c r="F157" s="21" t="n"/>
-      <c r="G157" s="21" t="n"/>
-      <c r="H157" s="21" t="n"/>
-      <c r="I157" s="21" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="5" t="inlineStr"/>
-      <c r="B158" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C158" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D158" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H158" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I158" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="n"/>
+      <c r="I158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B159" s="18" t="n"/>
@@ -8792,7 +8869,7 @@
       <c r="A160" s="21" t="n"/>
       <c r="B160" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C160" s="21" t="n"/>
@@ -8807,227 +8884,292 @@
       <c r="A161" s="5" t="inlineStr"/>
       <c r="B161" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="n"/>
+      <c r="C162" s="18" t="n"/>
+      <c r="D162" s="18" t="n"/>
+      <c r="E162" s="18" t="n"/>
+      <c r="F162" s="18" t="n"/>
+      <c r="G162" s="18" t="n"/>
+      <c r="H162" s="18" t="n"/>
+      <c r="I162" s="18" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="21" t="n"/>
+      <c r="B163" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C163" s="21" t="n"/>
+      <c r="D163" s="21" t="n"/>
+      <c r="E163" s="21" t="n"/>
+      <c r="F163" s="21" t="n"/>
+      <c r="G163" s="21" t="n"/>
+      <c r="H163" s="21" t="n"/>
+      <c r="I163" s="21" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr"/>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C161" s="5" t="n">
+      <c r="C164" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D161" s="5" t="inlineStr">
+      <c r="D164" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E161" s="5" t="n">
+      <c r="E164" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F161" s="5" t="n">
+      <c r="F164" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G161" s="5" t="inlineStr">
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H161" s="12" t="n">
+      <c r="H164" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I161" s="13" t="inlineStr">
+      <c r="I164" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="7" t="inlineStr"/>
-      <c r="B162" s="6" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr"/>
+      <c r="B165" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C162" s="7" t="n">
+      <c r="C165" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D162" s="7" t="inlineStr">
+      <c r="D165" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E162" s="7" t="n">
+      <c r="E165" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F162" s="7" t="n">
+      <c r="F165" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H162" s="14" t="n">
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H165" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I162" s="15" t="inlineStr">
+      <c r="I165" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="17" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B163" s="18" t="n"/>
-      <c r="C163" s="18" t="n"/>
-      <c r="D163" s="18" t="n"/>
-      <c r="E163" s="18" t="n"/>
-      <c r="F163" s="18" t="n"/>
-      <c r="G163" s="18" t="n"/>
-      <c r="H163" s="18" t="n"/>
-      <c r="I163" s="18" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="21" t="n"/>
-      <c r="B164" s="22" t="inlineStr">
+      <c r="B166" s="18" t="n"/>
+      <c r="C166" s="18" t="n"/>
+      <c r="D166" s="18" t="n"/>
+      <c r="E166" s="18" t="n"/>
+      <c r="F166" s="18" t="n"/>
+      <c r="G166" s="18" t="n"/>
+      <c r="H166" s="18" t="n"/>
+      <c r="I166" s="18" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="21" t="n"/>
+      <c r="B167" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C164" s="21" t="n"/>
-      <c r="D164" s="21" t="n"/>
-      <c r="E164" s="21" t="n"/>
-      <c r="F164" s="21" t="n"/>
-      <c r="G164" s="21" t="n"/>
-      <c r="H164" s="21" t="n"/>
-      <c r="I164" s="21" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr"/>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="C167" s="21" t="n"/>
+      <c r="D167" s="21" t="n"/>
+      <c r="E167" s="21" t="n"/>
+      <c r="F167" s="21" t="n"/>
+      <c r="G167" s="21" t="n"/>
+      <c r="H167" s="21" t="n"/>
+      <c r="I167" s="21" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr"/>
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C165" s="5" t="n">
+      <c r="C168" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D165" s="5" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E165" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F165" s="5" t="n">
+      <c r="E168" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G165" s="5" t="inlineStr">
+      <c r="G168" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H165" s="12" t="n">
+      <c r="H168" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I165" s="13" t="inlineStr">
+      <c r="I168" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="16" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B166" s="2" t="n"/>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" s="2" t="n"/>
-      <c r="F166" s="2" t="n"/>
-      <c r="G166" s="2" t="n"/>
-      <c r="H166" s="2" t="n"/>
-      <c r="I166" s="2" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="17" t="inlineStr">
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="2" t="n"/>
+      <c r="I169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B167" s="18" t="n"/>
-      <c r="C167" s="18" t="n"/>
-      <c r="D167" s="18" t="n"/>
-      <c r="E167" s="18" t="n"/>
-      <c r="F167" s="18" t="n"/>
-      <c r="G167" s="18" t="n"/>
-      <c r="H167" s="18" t="n"/>
-      <c r="I167" s="18" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="21" t="n"/>
-      <c r="B168" s="22" t="inlineStr">
+      <c r="B170" s="18" t="n"/>
+      <c r="C170" s="18" t="n"/>
+      <c r="D170" s="18" t="n"/>
+      <c r="E170" s="18" t="n"/>
+      <c r="F170" s="18" t="n"/>
+      <c r="G170" s="18" t="n"/>
+      <c r="H170" s="18" t="n"/>
+      <c r="I170" s="18" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="21" t="n"/>
+      <c r="B171" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C168" s="21" t="n"/>
-      <c r="D168" s="21" t="n"/>
-      <c r="E168" s="21" t="n"/>
-      <c r="F168" s="21" t="n"/>
-      <c r="G168" s="21" t="n"/>
-      <c r="H168" s="21" t="n"/>
-      <c r="I168" s="21" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="inlineStr"/>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="C171" s="21" t="n"/>
+      <c r="D171" s="21" t="n"/>
+      <c r="E171" s="21" t="n"/>
+      <c r="F171" s="21" t="n"/>
+      <c r="G171" s="21" t="n"/>
+      <c r="H171" s="21" t="n"/>
+      <c r="I171" s="21" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr"/>
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C169" s="5" t="n">
+      <c r="C172" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D169" s="5" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E169" s="5" t="n">
+      <c r="E172" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F169" s="5" t="n">
+      <c r="F172" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G169" s="5" t="inlineStr">
+      <c r="G172" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H169" s="12" t="n">
+      <c r="H172" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I169" s="13" t="inlineStr">
+      <c r="I172" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="108">
+  <mergeCells count="110">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B144:I144"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="A108:I108"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="B134:I134"/>
-    <mergeCell ref="A163:I163"/>
     <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B167:I167"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A85:I85"/>
@@ -9044,10 +9186,10 @@
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="B137:I137"/>
-    <mergeCell ref="A167:I167"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B83:I83"/>
+    <mergeCell ref="A169:I169"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
@@ -9071,11 +9213,12 @@
     <mergeCell ref="A166:I166"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B164:I164"/>
     <mergeCell ref="A94:I94"/>
     <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B163:I163"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A133:I133"/>
+    <mergeCell ref="B156:I156"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="A120:I120"/>
     <mergeCell ref="B27:I27"/>
@@ -9087,10 +9230,9 @@
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A156:I156"/>
     <mergeCell ref="B116:I116"/>
+    <mergeCell ref="A170:I170"/>
     <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B168:I168"/>
     <mergeCell ref="B118:I118"/>
     <mergeCell ref="A130:I130"/>
     <mergeCell ref="A82:I82"/>
@@ -9103,6 +9245,7 @@
     <mergeCell ref="B153:I153"/>
     <mergeCell ref="A149:I149"/>
     <mergeCell ref="B121:I121"/>
+    <mergeCell ref="A158:I158"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
     <mergeCell ref="B131:I131"/>
@@ -9114,8 +9257,8 @@
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="B157:I157"/>
     <mergeCell ref="A112:I112"/>
+    <mergeCell ref="B171:I171"/>
     <mergeCell ref="A152:I152"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A127:I127"/>
@@ -9128,6 +9271,7 @@
     <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B80:I80"/>
+    <mergeCell ref="A162:I162"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -9184,11 +9328,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I169" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9200,7 +9345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11754,24 +11899,59 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="238" customHeight="1">
+    <row r="59" ht="196" customHeight="1">
       <c r="A59" s="5" t="n">
         <v>55</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
+          <t>Reverse Degree of a String</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>3811</v>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int reverseDegree(String s) {
+    int sum =0;
+    int i =1;
+    char[] arr = s.toCharArray();
+     for(char c:arr){
+        int value = (26 - (c -'a'))*i;
+        sum+=value;
+        i++;
+     }  
+     return sum; 
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="238" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -11791,24 +11971,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="252" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="252" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -11831,24 +12011,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="140" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="140" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -11862,24 +12042,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="294" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="294" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -11905,24 +12085,24 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="252" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="252" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -12020,7 +12200,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>23</v>
@@ -12029,7 +12209,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -12058,7 +12238,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>23</v>
@@ -12067,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1587,37 +1587,37 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>43.4</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>1</v>
@@ -1626,261 +1626,261 @@
         <v>0</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>46.8</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Linked List — TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr"/>
-      <c r="C42" s="9" t="n">
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D43" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9" t="n">
+      <c r="E43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Bit Manipulation, Primality Test</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Math</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Bit Manipulation, Primality Test</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H43" s="5" t="n">
+      <c r="H44" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr"/>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
+      <c r="D46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="G46" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H46" s="7" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
-      <c r="C46" s="9" t="n">
+      <c r="B47" s="8" t="inlineStr"/>
+      <c r="C47" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="D47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="9" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="5" t="n">
+      <c r="C48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr"/>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
@@ -1889,17 +1889,17 @@
         <v>1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C50" s="7" t="n">
@@ -1915,17 +1915,17 @@
         <v>1</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="7" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
@@ -1941,237 +1941,263 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="7" t="n">
+      <c r="C53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H52" s="7" t="n">
+      <c r="H53" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr"/>
-      <c r="C53" s="9" t="n">
+      <c r="B54" s="8" t="inlineStr"/>
+      <c r="C54" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="9" t="n">
+      <c r="D54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G53" s="9" t="inlineStr"/>
-      <c r="H53" s="9" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="7" t="n">
+      <c r="C55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr"/>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="7" t="n">
+      <c r="C57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr"/>
-      <c r="C57" s="9" t="n">
+      <c r="B58" s="8" t="inlineStr"/>
+      <c r="C58" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="9" t="n">
+      <c r="D58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G57" s="9" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="7" t="n">
+      <c r="C59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H58" s="7" t="n">
+      <c r="H59" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr"/>
-      <c r="C59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr"/>
+      <c r="C60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr"/>
-      <c r="C60" s="11" t="n">
+      <c r="B61" s="10" t="inlineStr"/>
+      <c r="C61" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D61" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="E60" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F60" s="11" t="n">
-        <v>60</v>
-      </c>
-      <c r="G60" s="11" t="inlineStr"/>
-      <c r="H60" s="11" t="inlineStr"/>
+      <c r="E61" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="G61" s="11" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2187,7 +2213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5298,11 +5324,61 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Merge k Sorted Lists</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Linked List</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="12" t="n">
+        <v>46286.43949074074</v>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F64">
+  <conditionalFormatting sqref="F5:F65">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5374,6 +5450,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5385,7 +5462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I172"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7813,7 +7890,7 @@
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: LINKED LIST   —   5 solved   (Low: 3 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
         </is>
       </c>
       <c r="B111" s="2" t="n"/>
@@ -7828,7 +7905,7 @@
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B112" s="18" t="n"/>
@@ -7841,40 +7918,40 @@
       <c r="I112" s="18" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="19" t="n"/>
-      <c r="B113" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C113" s="19" t="n"/>
-      <c r="D113" s="19" t="n"/>
-      <c r="E113" s="19" t="n"/>
-      <c r="F113" s="19" t="n"/>
-      <c r="G113" s="19" t="n"/>
-      <c r="H113" s="19" t="n"/>
-      <c r="I113" s="19" t="n"/>
+      <c r="A113" s="23" t="n"/>
+      <c r="B113" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C113" s="23" t="n"/>
+      <c r="D113" s="23" t="n"/>
+      <c r="E113" s="23" t="n"/>
+      <c r="F113" s="23" t="n"/>
+      <c r="G113" s="23" t="n"/>
+      <c r="H113" s="23" t="n"/>
+      <c r="I113" s="23" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr"/>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List II</t>
+          <t>Merge k Sorted Lists</t>
         </is>
       </c>
       <c r="C114" s="5" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>43.4</v>
+        <v>45.9</v>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
@@ -7882,7 +7959,7 @@
         </is>
       </c>
       <c r="H114" s="12" t="n">
-        <v>46275.41266203704</v>
+        <v>46286.43949074074</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -7893,7 +7970,7 @@
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B115" s="18" t="n"/>
@@ -7906,155 +7983,155 @@
       <c r="I115" s="18" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="21" t="n"/>
-      <c r="B116" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C116" s="21" t="n"/>
-      <c r="D116" s="21" t="n"/>
-      <c r="E116" s="21" t="n"/>
-      <c r="F116" s="21" t="n"/>
-      <c r="G116" s="21" t="n"/>
-      <c r="H116" s="21" t="n"/>
-      <c r="I116" s="21" t="n"/>
+      <c r="A116" s="19" t="n"/>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C116" s="19" t="n"/>
+      <c r="D116" s="19" t="n"/>
+      <c r="E116" s="19" t="n"/>
+      <c r="F116" s="19" t="n"/>
+      <c r="G116" s="19" t="n"/>
+      <c r="H116" s="19" t="n"/>
+      <c r="I116" s="19" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr"/>
       <c r="B117" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List II</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>46275.41266203704</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="n"/>
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="18" t="n"/>
+      <c r="E118" s="18" t="n"/>
+      <c r="F118" s="18" t="n"/>
+      <c r="G118" s="18" t="n"/>
+      <c r="H118" s="18" t="n"/>
+      <c r="I118" s="18" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="n"/>
+      <c r="B119" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="n"/>
+      <c r="D119" s="21" t="n"/>
+      <c r="E119" s="21" t="n"/>
+      <c r="F119" s="21" t="n"/>
+      <c r="G119" s="21" t="n"/>
+      <c r="H119" s="21" t="n"/>
+      <c r="I119" s="21" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr"/>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C120" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="5" t="n">
+      <c r="E120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="n">
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I117" s="13" t="inlineStr">
+      <c r="I120" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="19" t="n"/>
-      <c r="B118" s="20" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="19" t="n"/>
+      <c r="B121" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C118" s="19" t="n"/>
-      <c r="D118" s="19" t="n"/>
-      <c r="E118" s="19" t="n"/>
-      <c r="F118" s="19" t="n"/>
-      <c r="G118" s="19" t="n"/>
-      <c r="H118" s="19" t="n"/>
-      <c r="I118" s="19" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr"/>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Linked List Cycle II</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>46274.44269675926</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B120" s="18" t="n"/>
-      <c r="C120" s="18" t="n"/>
-      <c r="D120" s="18" t="n"/>
-      <c r="E120" s="18" t="n"/>
-      <c r="F120" s="18" t="n"/>
-      <c r="G120" s="18" t="n"/>
-      <c r="H120" s="18" t="n"/>
-      <c r="I120" s="18" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="21" t="n"/>
-      <c r="B121" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C121" s="21" t="n"/>
-      <c r="D121" s="21" t="n"/>
-      <c r="E121" s="21" t="n"/>
-      <c r="F121" s="21" t="n"/>
-      <c r="G121" s="21" t="n"/>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="21" t="n"/>
+      <c r="C121" s="19" t="n"/>
+      <c r="D121" s="19" t="n"/>
+      <c r="E121" s="19" t="n"/>
+      <c r="F121" s="19" t="n"/>
+      <c r="G121" s="19" t="n"/>
+      <c r="H121" s="19" t="n"/>
+      <c r="I121" s="19" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr"/>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List</t>
+          <t>Linked List Cycle II</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
-        <v>206</v>
+        <v>142</v>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
@@ -8062,7 +8139,7 @@
         </is>
       </c>
       <c r="H122" s="12" t="n">
-        <v>46274.48334490741</v>
+        <v>46274.44269675926</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -8073,7 +8150,7 @@
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B123" s="18" t="n"/>
@@ -8104,121 +8181,121 @@
       <c r="A125" s="5" t="inlineStr"/>
       <c r="B125" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>46274.48334490741</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="n"/>
+      <c r="C126" s="18" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="18" t="n"/>
+      <c r="G126" s="18" t="n"/>
+      <c r="H126" s="18" t="n"/>
+      <c r="I126" s="18" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="n"/>
+      <c r="B127" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="n"/>
+      <c r="D127" s="21" t="n"/>
+      <c r="E127" s="21" t="n"/>
+      <c r="F127" s="21" t="n"/>
+      <c r="G127" s="21" t="n"/>
+      <c r="H127" s="21" t="n"/>
+      <c r="I127" s="21" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr"/>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C128" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="5" t="n">
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="n">
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I125" s="13" t="inlineStr">
+      <c r="I128" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="16" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B126" s="2" t="n"/>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B127" s="18" t="n"/>
-      <c r="C127" s="18" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-      <c r="G127" s="18" t="n"/>
-      <c r="H127" s="18" t="n"/>
-      <c r="I127" s="18" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="21" t="n"/>
-      <c r="B128" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C128" s="21" t="n"/>
-      <c r="D128" s="21" t="n"/>
-      <c r="E128" s="21" t="n"/>
-      <c r="F128" s="21" t="n"/>
-      <c r="G128" s="21" t="n"/>
-      <c r="H128" s="21" t="n"/>
-      <c r="I128" s="21" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr"/>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B130" s="18" t="n"/>
@@ -8249,11 +8326,11 @@
       <c r="A132" s="5" t="inlineStr"/>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
@@ -8261,10 +8338,10 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
@@ -8272,7 +8349,7 @@
         </is>
       </c>
       <c r="H132" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -8283,7 +8360,7 @@
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B133" s="18" t="n"/>
@@ -8299,7 +8376,7 @@
       <c r="A134" s="21" t="n"/>
       <c r="B134" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C134" s="21" t="n"/>
@@ -8314,11 +8391,11 @@
       <c r="A135" s="5" t="inlineStr"/>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C135" s="5" t="n">
-        <v>3918</v>
+        <v>3626</v>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
@@ -8329,7 +8406,7 @@
         <v>1</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
@@ -8337,7 +8414,7 @@
         </is>
       </c>
       <c r="H135" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -8346,174 +8423,174 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="7" t="inlineStr"/>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>Count Commas in Range</t>
-        </is>
-      </c>
-      <c r="C136" s="7" t="n">
-        <v>4245</v>
-      </c>
-      <c r="D136" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E136" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="n">
-        <v>46273.3956712963</v>
-      </c>
-      <c r="I136" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B136" s="18" t="n"/>
+      <c r="C136" s="18" t="n"/>
+      <c r="D136" s="18" t="n"/>
+      <c r="E136" s="18" t="n"/>
+      <c r="F136" s="18" t="n"/>
+      <c r="G136" s="18" t="n"/>
+      <c r="H136" s="18" t="n"/>
+      <c r="I136" s="18" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="19" t="n"/>
-      <c r="B137" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C137" s="19" t="n"/>
-      <c r="D137" s="19" t="n"/>
-      <c r="E137" s="19" t="n"/>
-      <c r="F137" s="19" t="n"/>
-      <c r="G137" s="19" t="n"/>
-      <c r="H137" s="19" t="n"/>
-      <c r="I137" s="19" t="n"/>
+      <c r="A137" s="21" t="n"/>
+      <c r="B137" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="n"/>
+      <c r="D137" s="21" t="n"/>
+      <c r="E137" s="21" t="n"/>
+      <c r="F137" s="21" t="n"/>
+      <c r="G137" s="21" t="n"/>
+      <c r="H137" s="21" t="n"/>
+      <c r="I137" s="21" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr"/>
       <c r="B138" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr"/>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I139" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="19" t="n"/>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C140" s="19" t="n"/>
+      <c r="D140" s="19" t="n"/>
+      <c r="E140" s="19" t="n"/>
+      <c r="F140" s="19" t="n"/>
+      <c r="G140" s="19" t="n"/>
+      <c r="H140" s="19" t="n"/>
+      <c r="I140" s="19" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr"/>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C138" s="5" t="n">
+      <c r="C141" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="5" t="n">
+      <c r="E141" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G138" s="5" t="inlineStr">
+      <c r="G141" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H138" s="12" t="n">
+      <c r="H141" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I138" s="13" t="inlineStr">
+      <c r="I141" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="16" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B139" s="2" t="n"/>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n"/>
-      <c r="E139" s="2" t="n"/>
-      <c r="F139" s="2" t="n"/>
-      <c r="G139" s="2" t="n"/>
-      <c r="H139" s="2" t="n"/>
-      <c r="I139" s="2" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B140" s="18" t="n"/>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="18" t="n"/>
-      <c r="E140" s="18" t="n"/>
-      <c r="F140" s="18" t="n"/>
-      <c r="G140" s="18" t="n"/>
-      <c r="H140" s="18" t="n"/>
-      <c r="I140" s="18" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="21" t="n"/>
-      <c r="B141" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C141" s="21" t="n"/>
-      <c r="D141" s="21" t="n"/>
-      <c r="E141" s="21" t="n"/>
-      <c r="F141" s="21" t="n"/>
-      <c r="G141" s="21" t="n"/>
-      <c r="H141" s="21" t="n"/>
-      <c r="I141" s="21" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr"/>
-      <c r="B142" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H142" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B143" s="18" t="n"/>
@@ -8526,48 +8603,48 @@
       <c r="I143" s="18" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="19" t="n"/>
-      <c r="B144" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="n"/>
-      <c r="D144" s="19" t="n"/>
-      <c r="E144" s="19" t="n"/>
-      <c r="F144" s="19" t="n"/>
-      <c r="G144" s="19" t="n"/>
-      <c r="H144" s="19" t="n"/>
-      <c r="I144" s="19" t="n"/>
+      <c r="A144" s="21" t="n"/>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C144" s="21" t="n"/>
+      <c r="D144" s="21" t="n"/>
+      <c r="E144" s="21" t="n"/>
+      <c r="F144" s="21" t="n"/>
+      <c r="G144" s="21" t="n"/>
+      <c r="H144" s="21" t="n"/>
+      <c r="I144" s="21" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr"/>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C145" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H145" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -8578,7 +8655,7 @@
     <row r="146">
       <c r="A146" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B146" s="18" t="n"/>
@@ -8591,40 +8668,40 @@
       <c r="I146" s="18" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="21" t="n"/>
-      <c r="B147" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C147" s="21" t="n"/>
-      <c r="D147" s="21" t="n"/>
-      <c r="E147" s="21" t="n"/>
-      <c r="F147" s="21" t="n"/>
-      <c r="G147" s="21" t="n"/>
-      <c r="H147" s="21" t="n"/>
-      <c r="I147" s="21" t="n"/>
+      <c r="A147" s="19" t="n"/>
+      <c r="B147" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="n"/>
+      <c r="D147" s="19" t="n"/>
+      <c r="E147" s="19" t="n"/>
+      <c r="F147" s="19" t="n"/>
+      <c r="G147" s="19" t="n"/>
+      <c r="H147" s="19" t="n"/>
+      <c r="I147" s="19" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr"/>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C148" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
@@ -8632,7 +8709,7 @@
         </is>
       </c>
       <c r="H148" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -8643,7 +8720,7 @@
     <row r="149">
       <c r="A149" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B149" s="18" t="n"/>
@@ -8674,11 +8751,11 @@
       <c r="A151" s="5" t="inlineStr"/>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Reverse Degree of a String</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>3811</v>
+        <v>242</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
@@ -8686,10 +8763,10 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
@@ -8697,7 +8774,7 @@
         </is>
       </c>
       <c r="H151" s="12" t="n">
-        <v>46285.42987268518</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -8708,7 +8785,7 @@
     <row r="152">
       <c r="A152" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B152" s="18" t="n"/>
@@ -8739,11 +8816,11 @@
       <c r="A154" s="5" t="inlineStr"/>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Reverse Degree of a String</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
-        <v>125</v>
+        <v>3811</v>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
@@ -8751,18 +8828,18 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H154" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46285.42987268518</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -8773,7 +8850,7 @@
     <row r="155">
       <c r="A155" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B155" s="18" t="n"/>
@@ -8804,121 +8881,121 @@
       <c r="A157" s="5" t="inlineStr"/>
       <c r="B157" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="n"/>
+      <c r="C158" s="18" t="n"/>
+      <c r="D158" s="18" t="n"/>
+      <c r="E158" s="18" t="n"/>
+      <c r="F158" s="18" t="n"/>
+      <c r="G158" s="18" t="n"/>
+      <c r="H158" s="18" t="n"/>
+      <c r="I158" s="18" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="21" t="n"/>
+      <c r="B159" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C159" s="21" t="n"/>
+      <c r="D159" s="21" t="n"/>
+      <c r="E159" s="21" t="n"/>
+      <c r="F159" s="21" t="n"/>
+      <c r="G159" s="21" t="n"/>
+      <c r="H159" s="21" t="n"/>
+      <c r="I159" s="21" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr"/>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C157" s="5" t="n">
+      <c r="C160" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n">
+      <c r="E160" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F157" s="5" t="n">
+      <c r="F160" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G157" s="5" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H157" s="12" t="n">
+      <c r="H160" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I157" s="13" t="inlineStr">
+      <c r="I160" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="16" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n"/>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" s="2" t="n"/>
-      <c r="F158" s="2" t="n"/>
-      <c r="G158" s="2" t="n"/>
-      <c r="H158" s="2" t="n"/>
-      <c r="I158" s="2" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B159" s="18" t="n"/>
-      <c r="C159" s="18" t="n"/>
-      <c r="D159" s="18" t="n"/>
-      <c r="E159" s="18" t="n"/>
-      <c r="F159" s="18" t="n"/>
-      <c r="G159" s="18" t="n"/>
-      <c r="H159" s="18" t="n"/>
-      <c r="I159" s="18" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="21" t="n"/>
-      <c r="B160" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C160" s="21" t="n"/>
-      <c r="D160" s="21" t="n"/>
-      <c r="E160" s="21" t="n"/>
-      <c r="F160" s="21" t="n"/>
-      <c r="G160" s="21" t="n"/>
-      <c r="H160" s="21" t="n"/>
-      <c r="I160" s="21" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr"/>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G161" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H161" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I161" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="2" t="n"/>
+      <c r="H161" s="2" t="n"/>
+      <c r="I161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B162" s="18" t="n"/>
@@ -8934,7 +9011,7 @@
       <c r="A163" s="21" t="n"/>
       <c r="B163" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C163" s="21" t="n"/>
@@ -8949,233 +9026,298 @@
       <c r="A164" s="5" t="inlineStr"/>
       <c r="B164" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B165" s="18" t="n"/>
+      <c r="C165" s="18" t="n"/>
+      <c r="D165" s="18" t="n"/>
+      <c r="E165" s="18" t="n"/>
+      <c r="F165" s="18" t="n"/>
+      <c r="G165" s="18" t="n"/>
+      <c r="H165" s="18" t="n"/>
+      <c r="I165" s="18" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="21" t="n"/>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C166" s="21" t="n"/>
+      <c r="D166" s="21" t="n"/>
+      <c r="E166" s="21" t="n"/>
+      <c r="F166" s="21" t="n"/>
+      <c r="G166" s="21" t="n"/>
+      <c r="H166" s="21" t="n"/>
+      <c r="I166" s="21" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr"/>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C164" s="5" t="n">
+      <c r="C167" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E164" s="5" t="n">
+      <c r="E167" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F164" s="5" t="n">
+      <c r="F167" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G164" s="5" t="inlineStr">
+      <c r="G167" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H164" s="12" t="n">
+      <c r="H167" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I164" s="13" t="inlineStr">
+      <c r="I167" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="7" t="inlineStr"/>
-      <c r="B165" s="6" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr"/>
+      <c r="B168" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C165" s="7" t="n">
+      <c r="C168" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D165" s="7" t="inlineStr">
+      <c r="D168" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E165" s="7" t="n">
+      <c r="E168" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F165" s="7" t="n">
+      <c r="F168" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G165" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H165" s="14" t="n">
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H168" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I165" s="15" t="inlineStr">
+      <c r="I168" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="17" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B166" s="18" t="n"/>
-      <c r="C166" s="18" t="n"/>
-      <c r="D166" s="18" t="n"/>
-      <c r="E166" s="18" t="n"/>
-      <c r="F166" s="18" t="n"/>
-      <c r="G166" s="18" t="n"/>
-      <c r="H166" s="18" t="n"/>
-      <c r="I166" s="18" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="21" t="n"/>
-      <c r="B167" s="22" t="inlineStr">
+      <c r="B169" s="18" t="n"/>
+      <c r="C169" s="18" t="n"/>
+      <c r="D169" s="18" t="n"/>
+      <c r="E169" s="18" t="n"/>
+      <c r="F169" s="18" t="n"/>
+      <c r="G169" s="18" t="n"/>
+      <c r="H169" s="18" t="n"/>
+      <c r="I169" s="18" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="21" t="n"/>
+      <c r="B170" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C167" s="21" t="n"/>
-      <c r="D167" s="21" t="n"/>
-      <c r="E167" s="21" t="n"/>
-      <c r="F167" s="21" t="n"/>
-      <c r="G167" s="21" t="n"/>
-      <c r="H167" s="21" t="n"/>
-      <c r="I167" s="21" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="5" t="inlineStr"/>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="C170" s="21" t="n"/>
+      <c r="D170" s="21" t="n"/>
+      <c r="E170" s="21" t="n"/>
+      <c r="F170" s="21" t="n"/>
+      <c r="G170" s="21" t="n"/>
+      <c r="H170" s="21" t="n"/>
+      <c r="I170" s="21" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr"/>
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C168" s="5" t="n">
+      <c r="C171" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" s="5" t="n">
+      <c r="E171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G168" s="5" t="inlineStr">
+      <c r="G171" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H168" s="12" t="n">
+      <c r="H171" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I168" s="13" t="inlineStr">
+      <c r="I171" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="16" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n"/>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" s="2" t="n"/>
-      <c r="F169" s="2" t="n"/>
-      <c r="G169" s="2" t="n"/>
-      <c r="H169" s="2" t="n"/>
-      <c r="I169" s="2" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="17" t="inlineStr">
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="n"/>
+      <c r="H172" s="2" t="n"/>
+      <c r="I172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B170" s="18" t="n"/>
-      <c r="C170" s="18" t="n"/>
-      <c r="D170" s="18" t="n"/>
-      <c r="E170" s="18" t="n"/>
-      <c r="F170" s="18" t="n"/>
-      <c r="G170" s="18" t="n"/>
-      <c r="H170" s="18" t="n"/>
-      <c r="I170" s="18" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="21" t="n"/>
-      <c r="B171" s="22" t="inlineStr">
+      <c r="B173" s="18" t="n"/>
+      <c r="C173" s="18" t="n"/>
+      <c r="D173" s="18" t="n"/>
+      <c r="E173" s="18" t="n"/>
+      <c r="F173" s="18" t="n"/>
+      <c r="G173" s="18" t="n"/>
+      <c r="H173" s="18" t="n"/>
+      <c r="I173" s="18" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="21" t="n"/>
+      <c r="B174" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C171" s="21" t="n"/>
-      <c r="D171" s="21" t="n"/>
-      <c r="E171" s="21" t="n"/>
-      <c r="F171" s="21" t="n"/>
-      <c r="G171" s="21" t="n"/>
-      <c r="H171" s="21" t="n"/>
-      <c r="I171" s="21" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr"/>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="C174" s="21" t="n"/>
+      <c r="D174" s="21" t="n"/>
+      <c r="E174" s="21" t="n"/>
+      <c r="F174" s="21" t="n"/>
+      <c r="G174" s="21" t="n"/>
+      <c r="H174" s="21" t="n"/>
+      <c r="I174" s="21" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr"/>
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C172" s="5" t="n">
+      <c r="C175" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E172" s="5" t="n">
+      <c r="E175" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F172" s="5" t="n">
+      <c r="F175" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G172" s="5" t="inlineStr">
+      <c r="G175" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H172" s="12" t="n">
+      <c r="H175" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I172" s="13" t="inlineStr">
+      <c r="I175" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="110">
+  <mergeCells count="112">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B144:I144"/>
+    <mergeCell ref="A172:I172"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="A108:I108"/>
+    <mergeCell ref="B159:I159"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="B134:I134"/>
     <mergeCell ref="A101:I101"/>
-    <mergeCell ref="B167:I167"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A62:I62"/>
@@ -9188,6 +9330,7 @@
     <mergeCell ref="B137:I137"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B74:I74"/>
+    <mergeCell ref="A142:I142"/>
     <mergeCell ref="B83:I83"/>
     <mergeCell ref="A169:I169"/>
     <mergeCell ref="B36:I36"/>
@@ -9195,22 +9338,22 @@
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="B113:I113"/>
     <mergeCell ref="B109:I109"/>
-    <mergeCell ref="B141:I141"/>
     <mergeCell ref="B150:I150"/>
+    <mergeCell ref="A136:I136"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A139:I139"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B86:I86"/>
+    <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
     <mergeCell ref="A91:I91"/>
+    <mergeCell ref="A165:I165"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="A115:I115"/>
     <mergeCell ref="A155:I155"/>
-    <mergeCell ref="B128:I128"/>
+    <mergeCell ref="A173:I173"/>
     <mergeCell ref="A143:I143"/>
-    <mergeCell ref="A166:I166"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="A94:I94"/>
@@ -9220,9 +9363,9 @@
     <mergeCell ref="A133:I133"/>
     <mergeCell ref="B156:I156"/>
     <mergeCell ref="B66:I66"/>
-    <mergeCell ref="A120:I120"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
+    <mergeCell ref="B140:I140"/>
     <mergeCell ref="A104:I104"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
@@ -9230,21 +9373,23 @@
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
+    <mergeCell ref="B166:I166"/>
+    <mergeCell ref="B119:I119"/>
     <mergeCell ref="B116:I116"/>
-    <mergeCell ref="A170:I170"/>
     <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B118:I118"/>
+    <mergeCell ref="B174:I174"/>
     <mergeCell ref="A130:I130"/>
+    <mergeCell ref="B127:I127"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="A123:I123"/>
     <mergeCell ref="B95:I95"/>
-    <mergeCell ref="B160:I160"/>
     <mergeCell ref="A146:I146"/>
     <mergeCell ref="B153:I153"/>
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="B121:I121"/>
     <mergeCell ref="A149:I149"/>
-    <mergeCell ref="B121:I121"/>
     <mergeCell ref="A158:I158"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
@@ -9253,15 +9398,14 @@
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A159:I159"/>
     <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B170:I170"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A112:I112"/>
-    <mergeCell ref="B171:I171"/>
     <mergeCell ref="A152:I152"/>
+    <mergeCell ref="A161:I161"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A127:I127"/>
     <mergeCell ref="B99:I99"/>
     <mergeCell ref="B92:I92"/>
     <mergeCell ref="A98:I98"/>
@@ -9315,25 +9459,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9345,7 +9490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9578,24 +9723,77 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="154" customHeight="1">
+    <row r="9" ht="448" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
+          <t>Merge k Sorted Lists</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>/**
+ * Definition for singly-linked list.
+ * public class ListNode {
+ *     int val;
+ *     ListNode next;
+ *     ListNode() {}
+ *     ListNode(int val) { this.val = val; }
+ *     ListNode(int val, ListNode next) { this.val = val; this.next = next; }
+ * }
+ */
+class Solution {
+    public ListNode mergeKLists(ListNode[] lists) {
+    PriorityQueue&lt;Integer&gt; pq = new PriorityQueue&lt;&gt;();
+    for(ListNode ls:lists){
+        ListNode temp = ls;
+        while(temp != null){
+            pq.add(temp.val);
+            temp = temp.next;
+        }
+    }
+    ListNode dummy = new ListNode(0);
+    ListNode current = dummy;
+    while (!pq.isEmpty()) {
+    current.next= new ListNode(pq.poll()); 
+    current = current.next;
+    }
+    current.next = null;
+    ListNode result = dummy.next; 
+    return result; 
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="154" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int removeDuplicates(int[] nums) {
@@ -9611,24 +9809,24 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="364" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+    <row r="11" ht="364" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Search in Rotated Sorted Array</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int search(int[] nums, int target) {
@@ -9659,24 +9857,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="378" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="378" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>First Missing Positive</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstMissingPositive(int[] nums) {
@@ -9707,24 +9905,24 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="196" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13" ht="196" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Maximum Subarray</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int maxSubArray(int[] nums) {
@@ -9743,24 +9941,24 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="238" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14" ht="238" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Merge Intervals</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] merge(int[][] intervals) {
@@ -9782,24 +9980,24 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="532" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15" ht="532" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
@@ -9833,24 +10031,24 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="560" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="560" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Reverse Linked List II</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -9904,24 +10102,24 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="560" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="17" ht="560" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -9960,24 +10158,24 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="406" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="406" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;111 - Minimum Depth of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/minimum-depth-of-binary-tree/"&gt;minimum-depth-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a binary tree, find its minimum depth.&lt;/p&gt;
 &lt;p&gt;The minimum depth is the number of nodes along the shortest path from the root node down to the nearest leaf node.&lt;/p&gt;
@@ -10004,24 +10202,24 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="532" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="532" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -10055,24 +10253,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="532" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="532" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;136 - Single Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/single-number/"&gt;single-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a &lt;strong&gt;non-empty&lt;/strong&gt;&amp;nbsp;array of integers &lt;code&gt;nums&lt;/code&gt;, every element appears &lt;em&gt;twice&lt;/em&gt; except for one. Find that single one.&lt;/p&gt;
 &lt;p&gt;You must&amp;nbsp;implement a solution with a linear runtime complexity and use&amp;nbsp;only constant&amp;nbsp;extra space.&lt;/p&gt;
@@ -10103,24 +10301,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="238" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="238" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -10142,24 +10340,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="560" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="560" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>141</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -10205,24 +10403,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="560" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="560" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle II</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -10275,24 +10473,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="210" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="210" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Find Peak Element</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>162</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int findPeakElement(int[] nums) {
@@ -10312,24 +10510,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="266" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="266" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] twoSum(int[] numbers, int target) {
@@ -10353,24 +10551,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="294" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="294" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -10396,24 +10594,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="392" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="392" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -10446,24 +10644,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="238" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="238" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -10485,24 +10683,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="238" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="238" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -10524,24 +10722,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="322" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="322" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Sliding Window Maximum</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>239</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] maxSlidingWindow(int[] nums, int k) {
@@ -10565,24 +10763,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="392" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="392" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -10615,24 +10813,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="182" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="182" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -10650,24 +10848,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="476" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="476" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Find the Duplicate Number</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int findDuplicate(int[] nums) {
@@ -10705,24 +10903,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="308" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="308" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>303</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -10746,24 +10944,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="420" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="420" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -10795,24 +10993,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="308" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="308" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Find All Duplicates in an Array</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>442</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public List&lt;Integer&gt; findDuplicates(int[] nums) {
@@ -10839,24 +11037,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="322" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="322" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>503</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElements(int[] nums) {
@@ -10881,24 +11079,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="546" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="546" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -10936,24 +11134,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="182" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="182" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -10971,24 +11169,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="546" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="546" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11032,24 +11230,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="196" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="196" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -11068,24 +11266,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="462" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="462" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -11115,24 +11313,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="252" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="252" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>739</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -11152,24 +11350,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="378" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="378" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -11201,24 +11399,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="294" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="294" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11244,24 +11442,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="560" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="560" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -11297,24 +11495,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="294" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="294" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -11337,24 +11535,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="224" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="224" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -11375,24 +11573,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="420" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="420" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -11427,24 +11625,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="378" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="378" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -11476,24 +11674,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="266" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="266" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -11517,24 +11715,24 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="350" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52" ht="350" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -11564,24 +11762,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="238" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53" ht="238" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -11603,24 +11801,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="308" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="308" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -11647,24 +11845,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="280" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="280" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -11687,24 +11885,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="448" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="448" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -11739,24 +11937,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="378" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="378" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -11788,24 +11986,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="266" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="266" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -11829,24 +12027,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="560" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="560" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -11899,24 +12097,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="196" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="196" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>3811</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -11934,24 +12132,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="238" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="238" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -11971,24 +12169,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="252" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="252" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -12011,24 +12209,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="140" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="140" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>4245</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -12042,24 +12240,24 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="294" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="294" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -12085,24 +12283,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="252" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="252" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -12206,10 +12404,10 @@
         <v>23</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -12244,10 +12442,10 @@
         <v>23</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1530,19 +1530,19 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Depth-First Search</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Math, Recursion, Memoization</t>
+          <t>Breadth-First Search, Union-Find, Graph Theory</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>0</v>
@@ -1551,24 +1551,24 @@
         <v>1</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>42.1</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Dynamic Programming — TOTAL</t>
+          <t>Depth-First Search — TOTAL</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr"/>
       <c r="C37" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="9" t="n">
         <v>0</v>
@@ -1582,97 +1582,97 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Math, Recursion, Memoization</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Dynamic Programming — TOTAL</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
+      <c r="C40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H40" s="7" t="n">
         <v>45.9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>43.4</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>46.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>0</v>
@@ -1684,68 +1684,68 @@
         <v>0</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>44.2</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>42.3</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Linked List — TOTAL</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr"/>
-      <c r="C43" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>Math</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Bit Manipulation, Primality Test</t>
-        </is>
-      </c>
       <c r="C44" s="7" t="n">
         <v>1</v>
       </c>
@@ -1759,180 +1759,180 @@
         <v>1</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Linked List — TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Bit Manipulation, Primality Test</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Enumeration</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="5" t="n">
+      <c r="C47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>42.5</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C48" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="n">
+      <c r="D48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G48" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H48" s="7" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr"/>
-      <c r="C47" s="9" t="n">
+      <c r="B49" s="8" t="inlineStr"/>
+      <c r="C49" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="9" t="n">
+      <c r="D49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G47" s="9" t="inlineStr"/>
-      <c r="H47" s="9" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="7" t="n">
+      <c r="C50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr"/>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>47.9</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr"/>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sorting</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>44.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
@@ -1941,17 +1941,17 @@
         <v>1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>44.1</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
@@ -1970,200 +1970,200 @@
         <v>2</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
+          <t>Simulation</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>44.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="n">
+      <c r="C55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H55" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr"/>
-      <c r="C54" s="9" t="n">
+      <c r="B56" s="8" t="inlineStr"/>
+      <c r="C56" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D54" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="9" t="n">
+      <c r="D56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G54" s="9" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="9" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="5" t="n">
+      <c r="C57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="5" t="n">
         <v>47</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr"/>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C58" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7" t="n">
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G58" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="H58" s="7" t="n">
         <v>65.40000000000001</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr"/>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="5" t="n">
+      <c r="C59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Tree — TOTAL</t>
-        </is>
-      </c>
-      <c r="B58" s="8" t="inlineStr"/>
-      <c r="C58" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G58" s="9" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Uncategorized</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>53.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>Uncategorized — TOTAL</t>
+          <t>Tree — TOTAL</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr"/>
       <c r="C60" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D60" s="9" t="n">
         <v>0</v>
@@ -2172,32 +2172,84 @@
         <v>0</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G60" s="9" t="inlineStr"/>
       <c r="H60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Uncategorized — TOTAL</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr"/>
+      <c r="C62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr"/>
+      <c r="H62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr"/>
-      <c r="C61" s="11" t="n">
+      <c r="B63" s="10" t="inlineStr"/>
+      <c r="C63" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="D61" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="E61" s="11" t="n">
+      <c r="D63" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E63" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F61" s="11" t="n">
-        <v>61</v>
-      </c>
-      <c r="G61" s="11" t="inlineStr"/>
-      <c r="H61" s="11" t="inlineStr"/>
+      <c r="F63" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="G63" s="11" t="inlineStr"/>
+      <c r="H63" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2213,7 +2265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5374,11 +5426,61 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>684</v>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Redundant Connection</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Depth-First Search</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Breadth-First Search, Union-Find, Graph Theory</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" s="14" t="n">
+        <v>46287.51434027778</v>
+      </c>
+      <c r="L66" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F65">
+  <conditionalFormatting sqref="F5:F66">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5451,6 +5553,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5462,7 +5565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7810,7 +7913,7 @@
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B107" s="2" t="n"/>
@@ -7825,7 +7928,7 @@
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B108" s="18" t="n"/>
@@ -7838,48 +7941,48 @@
       <c r="I108" s="18" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="21" t="n"/>
-      <c r="B109" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C109" s="21" t="n"/>
-      <c r="D109" s="21" t="n"/>
-      <c r="E109" s="21" t="n"/>
-      <c r="F109" s="21" t="n"/>
-      <c r="G109" s="21" t="n"/>
-      <c r="H109" s="21" t="n"/>
-      <c r="I109" s="21" t="n"/>
+      <c r="A109" s="19" t="n"/>
+      <c r="B109" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C109" s="19" t="n"/>
+      <c r="D109" s="19" t="n"/>
+      <c r="E109" s="19" t="n"/>
+      <c r="F109" s="19" t="n"/>
+      <c r="G109" s="19" t="n"/>
+      <c r="H109" s="19" t="n"/>
+      <c r="I109" s="19" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr"/>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Fibonacci Number</t>
+          <t>Redundant Connection</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>1013</v>
+        <v>684</v>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>42.1</v>
+        <v>44.9</v>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H110" s="12" t="n">
-        <v>46247.78516203703</v>
+        <v>46287.51434027778</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -7890,7 +7993,7 @@
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
+          <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B111" s="2" t="n"/>
@@ -7905,7 +8008,7 @@
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
+          <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B112" s="18" t="n"/>
@@ -7918,384 +8021,384 @@
       <c r="I112" s="18" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="23" t="n"/>
-      <c r="B113" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C113" s="23" t="n"/>
-      <c r="D113" s="23" t="n"/>
-      <c r="E113" s="23" t="n"/>
-      <c r="F113" s="23" t="n"/>
-      <c r="G113" s="23" t="n"/>
-      <c r="H113" s="23" t="n"/>
-      <c r="I113" s="23" t="n"/>
+      <c r="A113" s="21" t="n"/>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="n"/>
+      <c r="D113" s="21" t="n"/>
+      <c r="E113" s="21" t="n"/>
+      <c r="F113" s="21" t="n"/>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="21" t="n"/>
+      <c r="I113" s="21" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr"/>
       <c r="B114" s="4" t="inlineStr">
         <is>
+          <t>Fibonacci Number</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>46247.78516203703</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="23" t="n"/>
+      <c r="B117" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C117" s="23" t="n"/>
+      <c r="D117" s="23" t="n"/>
+      <c r="E117" s="23" t="n"/>
+      <c r="F117" s="23" t="n"/>
+      <c r="G117" s="23" t="n"/>
+      <c r="H117" s="23" t="n"/>
+      <c r="I117" s="23" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr"/>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
           <t>Merge k Sorted Lists</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C118" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E114" s="5" t="n">
+      <c r="E118" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F114" s="5" t="n">
+      <c r="F118" s="5" t="n">
         <v>45.9</v>
       </c>
-      <c r="G114" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H114" s="12" t="n">
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="n">
         <v>46286.43949074074</v>
       </c>
-      <c r="I114" s="13" t="inlineStr">
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="17" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B115" s="18" t="n"/>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="18" t="n"/>
-      <c r="E115" s="18" t="n"/>
-      <c r="F115" s="18" t="n"/>
-      <c r="G115" s="18" t="n"/>
-      <c r="H115" s="18" t="n"/>
-      <c r="I115" s="18" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="19" t="n"/>
-      <c r="B116" s="20" t="inlineStr">
+      <c r="B119" s="18" t="n"/>
+      <c r="C119" s="18" t="n"/>
+      <c r="D119" s="18" t="n"/>
+      <c r="E119" s="18" t="n"/>
+      <c r="F119" s="18" t="n"/>
+      <c r="G119" s="18" t="n"/>
+      <c r="H119" s="18" t="n"/>
+      <c r="I119" s="18" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="19" t="n"/>
+      <c r="B120" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C116" s="19" t="n"/>
-      <c r="D116" s="19" t="n"/>
-      <c r="E116" s="19" t="n"/>
-      <c r="F116" s="19" t="n"/>
-      <c r="G116" s="19" t="n"/>
-      <c r="H116" s="19" t="n"/>
-      <c r="I116" s="19" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr"/>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="C120" s="19" t="n"/>
+      <c r="D120" s="19" t="n"/>
+      <c r="E120" s="19" t="n"/>
+      <c r="F120" s="19" t="n"/>
+      <c r="G120" s="19" t="n"/>
+      <c r="H120" s="19" t="n"/>
+      <c r="I120" s="19" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr"/>
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>Reverse Linked List II</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C121" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="5" t="n">
+      <c r="E121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="5" t="n">
         <v>43.4</v>
       </c>
-      <c r="G117" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="n">
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="n">
         <v>46275.41266203704</v>
       </c>
-      <c r="I117" s="13" t="inlineStr">
+      <c r="I121" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="17" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B118" s="18" t="n"/>
-      <c r="C118" s="18" t="n"/>
-      <c r="D118" s="18" t="n"/>
-      <c r="E118" s="18" t="n"/>
-      <c r="F118" s="18" t="n"/>
-      <c r="G118" s="18" t="n"/>
-      <c r="H118" s="18" t="n"/>
-      <c r="I118" s="18" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="21" t="n"/>
-      <c r="B119" s="22" t="inlineStr">
+      <c r="B122" s="18" t="n"/>
+      <c r="C122" s="18" t="n"/>
+      <c r="D122" s="18" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="18" t="n"/>
+      <c r="G122" s="18" t="n"/>
+      <c r="H122" s="18" t="n"/>
+      <c r="I122" s="18" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="n"/>
+      <c r="B123" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C119" s="21" t="n"/>
-      <c r="D119" s="21" t="n"/>
-      <c r="E119" s="21" t="n"/>
-      <c r="F119" s="21" t="n"/>
-      <c r="G119" s="21" t="n"/>
-      <c r="H119" s="21" t="n"/>
-      <c r="I119" s="21" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr"/>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="C123" s="21" t="n"/>
+      <c r="D123" s="21" t="n"/>
+      <c r="E123" s="21" t="n"/>
+      <c r="F123" s="21" t="n"/>
+      <c r="G123" s="21" t="n"/>
+      <c r="H123" s="21" t="n"/>
+      <c r="I123" s="21" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr"/>
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C120" s="5" t="n">
+      <c r="C124" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D120" s="5" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="5" t="n">
+      <c r="E124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="n">
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I120" s="13" t="inlineStr">
+      <c r="I124" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="19" t="n"/>
-      <c r="B121" s="20" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="19" t="n"/>
+      <c r="B125" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C121" s="19" t="n"/>
-      <c r="D121" s="19" t="n"/>
-      <c r="E121" s="19" t="n"/>
-      <c r="F121" s="19" t="n"/>
-      <c r="G121" s="19" t="n"/>
-      <c r="H121" s="19" t="n"/>
-      <c r="I121" s="19" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr"/>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="C125" s="19" t="n"/>
+      <c r="D125" s="19" t="n"/>
+      <c r="E125" s="19" t="n"/>
+      <c r="F125" s="19" t="n"/>
+      <c r="G125" s="19" t="n"/>
+      <c r="H125" s="19" t="n"/>
+      <c r="I125" s="19" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr"/>
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle II</t>
         </is>
       </c>
-      <c r="C122" s="5" t="n">
+      <c r="C126" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F122" s="5" t="n">
+      <c r="E126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="n">
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="n">
         <v>46274.44269675926</v>
       </c>
-      <c r="I122" s="13" t="inlineStr">
+      <c r="I126" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="17" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B123" s="18" t="n"/>
-      <c r="C123" s="18" t="n"/>
-      <c r="D123" s="18" t="n"/>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
-      <c r="G123" s="18" t="n"/>
-      <c r="H123" s="18" t="n"/>
-      <c r="I123" s="18" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="21" t="n"/>
-      <c r="B124" s="22" t="inlineStr">
+      <c r="B127" s="18" t="n"/>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+      <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="n"/>
+      <c r="B128" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C124" s="21" t="n"/>
-      <c r="D124" s="21" t="n"/>
-      <c r="E124" s="21" t="n"/>
-      <c r="F124" s="21" t="n"/>
-      <c r="G124" s="21" t="n"/>
-      <c r="H124" s="21" t="n"/>
-      <c r="I124" s="21" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr"/>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="C128" s="21" t="n"/>
+      <c r="D128" s="21" t="n"/>
+      <c r="E128" s="21" t="n"/>
+      <c r="F128" s="21" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="21" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr"/>
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C129" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="5" t="n">
+      <c r="E129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="5" t="n">
         <v>44.2</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="n">
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="n">
         <v>46274.48334490741</v>
       </c>
-      <c r="I125" s="13" t="inlineStr">
+      <c r="I129" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B126" s="18" t="n"/>
-      <c r="C126" s="18" t="n"/>
-      <c r="D126" s="18" t="n"/>
-      <c r="E126" s="18" t="n"/>
-      <c r="F126" s="18" t="n"/>
-      <c r="G126" s="18" t="n"/>
-      <c r="H126" s="18" t="n"/>
-      <c r="I126" s="18" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="21" t="n"/>
-      <c r="B127" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C127" s="21" t="n"/>
-      <c r="D127" s="21" t="n"/>
-      <c r="E127" s="21" t="n"/>
-      <c r="F127" s="21" t="n"/>
-      <c r="G127" s="21" t="n"/>
-      <c r="H127" s="21" t="n"/>
-      <c r="I127" s="21" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr"/>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>Middle of the Linked List</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="n">
-        <v>908</v>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>46274.41063657407</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="n"/>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="n"/>
-      <c r="F129" s="2" t="n"/>
-      <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B130" s="18" t="n"/>
@@ -8326,11 +8429,11 @@
       <c r="A132" s="5" t="inlineStr"/>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
+          <t>Middle of the Linked List</t>
         </is>
       </c>
       <c r="C132" s="5" t="n">
-        <v>767</v>
+        <v>908</v>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
@@ -8338,7 +8441,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F132" s="5" t="n">
         <v>42.3</v>
@@ -8349,653 +8452,653 @@
         </is>
       </c>
       <c r="H132" s="12" t="n">
+        <v>46274.41063657407</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="n"/>
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="2" t="n"/>
+      <c r="I133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="n"/>
+      <c r="C134" s="18" t="n"/>
+      <c r="D134" s="18" t="n"/>
+      <c r="E134" s="18" t="n"/>
+      <c r="F134" s="18" t="n"/>
+      <c r="G134" s="18" t="n"/>
+      <c r="H134" s="18" t="n"/>
+      <c r="I134" s="18" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="n"/>
+      <c r="B135" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C135" s="21" t="n"/>
+      <c r="D135" s="21" t="n"/>
+      <c r="E135" s="21" t="n"/>
+      <c r="F135" s="21" t="n"/>
+      <c r="G135" s="21" t="n"/>
+      <c r="H135" s="21" t="n"/>
+      <c r="I135" s="21" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr"/>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Prime Number of Set Bits in Binary Representation</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>767</v>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="n">
         <v>46255.88138888889</v>
       </c>
-      <c r="I132" s="13" t="inlineStr">
+      <c r="I136" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="17" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B133" s="18" t="n"/>
-      <c r="C133" s="18" t="n"/>
-      <c r="D133" s="18" t="n"/>
-      <c r="E133" s="18" t="n"/>
-      <c r="F133" s="18" t="n"/>
-      <c r="G133" s="18" t="n"/>
-      <c r="H133" s="18" t="n"/>
-      <c r="I133" s="18" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="21" t="n"/>
-      <c r="B134" s="22" t="inlineStr">
+      <c r="B137" s="18" t="n"/>
+      <c r="C137" s="18" t="n"/>
+      <c r="D137" s="18" t="n"/>
+      <c r="E137" s="18" t="n"/>
+      <c r="F137" s="18" t="n"/>
+      <c r="G137" s="18" t="n"/>
+      <c r="H137" s="18" t="n"/>
+      <c r="I137" s="18" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="21" t="n"/>
+      <c r="B138" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C134" s="21" t="n"/>
-      <c r="D134" s="21" t="n"/>
-      <c r="E134" s="21" t="n"/>
-      <c r="F134" s="21" t="n"/>
-      <c r="G134" s="21" t="n"/>
-      <c r="H134" s="21" t="n"/>
-      <c r="I134" s="21" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr"/>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="C138" s="21" t="n"/>
+      <c r="D138" s="21" t="n"/>
+      <c r="E138" s="21" t="n"/>
+      <c r="F138" s="21" t="n"/>
+      <c r="G138" s="21" t="n"/>
+      <c r="H138" s="21" t="n"/>
+      <c r="I138" s="21" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr"/>
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C135" s="5" t="n">
+      <c r="C139" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E135" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" s="5" t="n">
+      <c r="E139" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H135" s="12" t="n">
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="n">
         <v>46240.74578703703</v>
       </c>
-      <c r="I135" s="13" t="inlineStr">
+      <c r="I139" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="17" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B136" s="18" t="n"/>
-      <c r="C136" s="18" t="n"/>
-      <c r="D136" s="18" t="n"/>
-      <c r="E136" s="18" t="n"/>
-      <c r="F136" s="18" t="n"/>
-      <c r="G136" s="18" t="n"/>
-      <c r="H136" s="18" t="n"/>
-      <c r="I136" s="18" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="21" t="n"/>
-      <c r="B137" s="22" t="inlineStr">
+      <c r="B140" s="18" t="n"/>
+      <c r="C140" s="18" t="n"/>
+      <c r="D140" s="18" t="n"/>
+      <c r="E140" s="18" t="n"/>
+      <c r="F140" s="18" t="n"/>
+      <c r="G140" s="18" t="n"/>
+      <c r="H140" s="18" t="n"/>
+      <c r="I140" s="18" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="n"/>
+      <c r="B141" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C137" s="21" t="n"/>
-      <c r="D137" s="21" t="n"/>
-      <c r="E137" s="21" t="n"/>
-      <c r="F137" s="21" t="n"/>
-      <c r="G137" s="21" t="n"/>
-      <c r="H137" s="21" t="n"/>
-      <c r="I137" s="21" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr"/>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="C141" s="21" t="n"/>
+      <c r="D141" s="21" t="n"/>
+      <c r="E141" s="21" t="n"/>
+      <c r="F141" s="21" t="n"/>
+      <c r="G141" s="21" t="n"/>
+      <c r="H141" s="21" t="n"/>
+      <c r="I141" s="21" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr"/>
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C138" s="5" t="n">
+      <c r="C142" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D138" s="5" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E138" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="5" t="n">
+      <c r="E142" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G138" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H138" s="12" t="n">
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I138" s="13" t="inlineStr">
+      <c r="I142" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="7" t="inlineStr"/>
-      <c r="B139" s="6" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="7" t="inlineStr"/>
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C139" s="7" t="n">
+      <c r="C143" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D139" s="7" t="inlineStr">
+      <c r="D143" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E139" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="7" t="n">
+      <c r="E143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="7" t="n">
         <v>42.6</v>
       </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H139" s="14" t="n">
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="n">
         <v>46273.3956712963</v>
       </c>
-      <c r="I139" s="15" t="inlineStr">
+      <c r="I143" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="19" t="n"/>
-      <c r="B140" s="20" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="19" t="n"/>
+      <c r="B144" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C140" s="19" t="n"/>
-      <c r="D140" s="19" t="n"/>
-      <c r="E140" s="19" t="n"/>
-      <c r="F140" s="19" t="n"/>
-      <c r="G140" s="19" t="n"/>
-      <c r="H140" s="19" t="n"/>
-      <c r="I140" s="19" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr"/>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H141" s="12" t="n">
-        <v>46241.79645833333</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="n"/>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" s="2" t="n"/>
-      <c r="F142" s="2" t="n"/>
-      <c r="G142" s="2" t="n"/>
-      <c r="H142" s="2" t="n"/>
-      <c r="I142" s="2" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B143" s="18" t="n"/>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="18" t="n"/>
-      <c r="E143" s="18" t="n"/>
-      <c r="F143" s="18" t="n"/>
-      <c r="G143" s="18" t="n"/>
-      <c r="H143" s="18" t="n"/>
-      <c r="I143" s="18" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="21" t="n"/>
-      <c r="B144" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C144" s="21" t="n"/>
-      <c r="D144" s="21" t="n"/>
-      <c r="E144" s="21" t="n"/>
-      <c r="F144" s="21" t="n"/>
-      <c r="G144" s="21" t="n"/>
-      <c r="H144" s="21" t="n"/>
-      <c r="I144" s="21" t="n"/>
+      <c r="C144" s="19" t="n"/>
+      <c r="D144" s="19" t="n"/>
+      <c r="E144" s="19" t="n"/>
+      <c r="F144" s="19" t="n"/>
+      <c r="G144" s="19" t="n"/>
+      <c r="H144" s="19" t="n"/>
+      <c r="I144" s="19" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr"/>
       <c r="B145" s="4" t="inlineStr">
         <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>46241.79645833333</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="n"/>
+      <c r="G146" s="2" t="n"/>
+      <c r="H146" s="2" t="n"/>
+      <c r="I146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="n"/>
+      <c r="C147" s="18" t="n"/>
+      <c r="D147" s="18" t="n"/>
+      <c r="E147" s="18" t="n"/>
+      <c r="F147" s="18" t="n"/>
+      <c r="G147" s="18" t="n"/>
+      <c r="H147" s="18" t="n"/>
+      <c r="I147" s="18" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="21" t="n"/>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C148" s="21" t="n"/>
+      <c r="D148" s="21" t="n"/>
+      <c r="E148" s="21" t="n"/>
+      <c r="F148" s="21" t="n"/>
+      <c r="G148" s="21" t="n"/>
+      <c r="H148" s="21" t="n"/>
+      <c r="I148" s="21" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr"/>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C145" s="5" t="n">
+      <c r="C149" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E145" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" s="5" t="n">
+      <c r="E149" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G145" s="5" t="inlineStr">
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H145" s="12" t="n">
+      <c r="H149" s="12" t="n">
         <v>46241.78204861111</v>
       </c>
-      <c r="I145" s="13" t="inlineStr">
+      <c r="I149" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="17" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B146" s="18" t="n"/>
-      <c r="C146" s="18" t="n"/>
-      <c r="D146" s="18" t="n"/>
-      <c r="E146" s="18" t="n"/>
-      <c r="F146" s="18" t="n"/>
-      <c r="G146" s="18" t="n"/>
-      <c r="H146" s="18" t="n"/>
-      <c r="I146" s="18" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="19" t="n"/>
-      <c r="B147" s="20" t="inlineStr">
+      <c r="B150" s="18" t="n"/>
+      <c r="C150" s="18" t="n"/>
+      <c r="D150" s="18" t="n"/>
+      <c r="E150" s="18" t="n"/>
+      <c r="F150" s="18" t="n"/>
+      <c r="G150" s="18" t="n"/>
+      <c r="H150" s="18" t="n"/>
+      <c r="I150" s="18" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="19" t="n"/>
+      <c r="B151" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C147" s="19" t="n"/>
-      <c r="D147" s="19" t="n"/>
-      <c r="E147" s="19" t="n"/>
-      <c r="F147" s="19" t="n"/>
-      <c r="G147" s="19" t="n"/>
-      <c r="H147" s="19" t="n"/>
-      <c r="I147" s="19" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="inlineStr"/>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="C151" s="19" t="n"/>
+      <c r="D151" s="19" t="n"/>
+      <c r="E151" s="19" t="n"/>
+      <c r="F151" s="19" t="n"/>
+      <c r="G151" s="19" t="n"/>
+      <c r="H151" s="19" t="n"/>
+      <c r="I151" s="19" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr"/>
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
-      <c r="C148" s="5" t="n">
+      <c r="C152" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="5" t="n">
+      <c r="E152" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="F148" s="5" t="n">
+      <c r="F152" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H148" s="12" t="n">
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="n">
         <v>46253.82314814815</v>
       </c>
-      <c r="I148" s="13" t="inlineStr">
+      <c r="I152" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="17" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B149" s="18" t="n"/>
-      <c r="C149" s="18" t="n"/>
-      <c r="D149" s="18" t="n"/>
-      <c r="E149" s="18" t="n"/>
-      <c r="F149" s="18" t="n"/>
-      <c r="G149" s="18" t="n"/>
-      <c r="H149" s="18" t="n"/>
-      <c r="I149" s="18" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="21" t="n"/>
-      <c r="B150" s="22" t="inlineStr">
+      <c r="B153" s="18" t="n"/>
+      <c r="C153" s="18" t="n"/>
+      <c r="D153" s="18" t="n"/>
+      <c r="E153" s="18" t="n"/>
+      <c r="F153" s="18" t="n"/>
+      <c r="G153" s="18" t="n"/>
+      <c r="H153" s="18" t="n"/>
+      <c r="I153" s="18" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="21" t="n"/>
+      <c r="B154" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C150" s="21" t="n"/>
-      <c r="D150" s="21" t="n"/>
-      <c r="E150" s="21" t="n"/>
-      <c r="F150" s="21" t="n"/>
-      <c r="G150" s="21" t="n"/>
-      <c r="H150" s="21" t="n"/>
-      <c r="I150" s="21" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr"/>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="C154" s="21" t="n"/>
+      <c r="D154" s="21" t="n"/>
+      <c r="E154" s="21" t="n"/>
+      <c r="F154" s="21" t="n"/>
+      <c r="G154" s="21" t="n"/>
+      <c r="H154" s="21" t="n"/>
+      <c r="I154" s="21" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr"/>
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C151" s="5" t="n">
+      <c r="C155" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E151" s="5" t="n">
+      <c r="E155" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F151" s="5" t="n">
+      <c r="F155" s="5" t="n">
         <v>44.6</v>
       </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="n">
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="n">
         <v>46243.94849537037</v>
       </c>
-      <c r="I151" s="13" t="inlineStr">
+      <c r="I155" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="17" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B152" s="18" t="n"/>
-      <c r="C152" s="18" t="n"/>
-      <c r="D152" s="18" t="n"/>
-      <c r="E152" s="18" t="n"/>
-      <c r="F152" s="18" t="n"/>
-      <c r="G152" s="18" t="n"/>
-      <c r="H152" s="18" t="n"/>
-      <c r="I152" s="18" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="21" t="n"/>
-      <c r="B153" s="22" t="inlineStr">
+      <c r="B156" s="18" t="n"/>
+      <c r="C156" s="18" t="n"/>
+      <c r="D156" s="18" t="n"/>
+      <c r="E156" s="18" t="n"/>
+      <c r="F156" s="18" t="n"/>
+      <c r="G156" s="18" t="n"/>
+      <c r="H156" s="18" t="n"/>
+      <c r="I156" s="18" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="21" t="n"/>
+      <c r="B157" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C153" s="21" t="n"/>
-      <c r="D153" s="21" t="n"/>
-      <c r="E153" s="21" t="n"/>
-      <c r="F153" s="21" t="n"/>
-      <c r="G153" s="21" t="n"/>
-      <c r="H153" s="21" t="n"/>
-      <c r="I153" s="21" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="5" t="inlineStr"/>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="C157" s="21" t="n"/>
+      <c r="D157" s="21" t="n"/>
+      <c r="E157" s="21" t="n"/>
+      <c r="F157" s="21" t="n"/>
+      <c r="G157" s="21" t="n"/>
+      <c r="H157" s="21" t="n"/>
+      <c r="I157" s="21" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr"/>
+      <c r="B158" s="4" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C154" s="5" t="n">
+      <c r="C158" s="5" t="n">
         <v>3811</v>
       </c>
-      <c r="D154" s="5" t="inlineStr">
+      <c r="D158" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E154" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" s="5" t="n">
+      <c r="E158" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="5" t="n">
         <v>44.1</v>
       </c>
-      <c r="G154" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H154" s="12" t="n">
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H158" s="12" t="n">
         <v>46285.42987268518</v>
       </c>
-      <c r="I154" s="13" t="inlineStr">
+      <c r="I158" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="17" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B155" s="18" t="n"/>
-      <c r="C155" s="18" t="n"/>
-      <c r="D155" s="18" t="n"/>
-      <c r="E155" s="18" t="n"/>
-      <c r="F155" s="18" t="n"/>
-      <c r="G155" s="18" t="n"/>
-      <c r="H155" s="18" t="n"/>
-      <c r="I155" s="18" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="21" t="n"/>
-      <c r="B156" s="22" t="inlineStr">
+      <c r="B159" s="18" t="n"/>
+      <c r="C159" s="18" t="n"/>
+      <c r="D159" s="18" t="n"/>
+      <c r="E159" s="18" t="n"/>
+      <c r="F159" s="18" t="n"/>
+      <c r="G159" s="18" t="n"/>
+      <c r="H159" s="18" t="n"/>
+      <c r="I159" s="18" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="21" t="n"/>
+      <c r="B160" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C156" s="21" t="n"/>
-      <c r="D156" s="21" t="n"/>
-      <c r="E156" s="21" t="n"/>
-      <c r="F156" s="21" t="n"/>
-      <c r="G156" s="21" t="n"/>
-      <c r="H156" s="21" t="n"/>
-      <c r="I156" s="21" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr"/>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="C160" s="21" t="n"/>
+      <c r="D160" s="21" t="n"/>
+      <c r="E160" s="21" t="n"/>
+      <c r="F160" s="21" t="n"/>
+      <c r="G160" s="21" t="n"/>
+      <c r="H160" s="21" t="n"/>
+      <c r="I160" s="21" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr"/>
+      <c r="B161" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C157" s="5" t="n">
+      <c r="C161" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D161" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n">
+      <c r="E161" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F157" s="5" t="n">
+      <c r="F161" s="5" t="n">
         <v>45.3</v>
       </c>
-      <c r="G157" s="5" t="inlineStr">
+      <c r="G161" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H157" s="12" t="n">
+      <c r="H161" s="12" t="n">
         <v>46243.9169675926</v>
       </c>
-      <c r="I157" s="13" t="inlineStr">
+      <c r="I161" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B158" s="18" t="n"/>
-      <c r="C158" s="18" t="n"/>
-      <c r="D158" s="18" t="n"/>
-      <c r="E158" s="18" t="n"/>
-      <c r="F158" s="18" t="n"/>
-      <c r="G158" s="18" t="n"/>
-      <c r="H158" s="18" t="n"/>
-      <c r="I158" s="18" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="21" t="n"/>
-      <c r="B159" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C159" s="21" t="n"/>
-      <c r="D159" s="21" t="n"/>
-      <c r="E159" s="21" t="n"/>
-      <c r="F159" s="21" t="n"/>
-      <c r="G159" s="21" t="n"/>
-      <c r="H159" s="21" t="n"/>
-      <c r="I159" s="21" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="5" t="inlineStr"/>
-      <c r="B160" s="4" t="inlineStr">
-        <is>
-          <t>Valid Palindrome II</t>
-        </is>
-      </c>
-      <c r="C160" s="5" t="n">
-        <v>680</v>
-      </c>
-      <c r="D160" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E160" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F160" s="5" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="G160" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H160" s="12" t="n">
-        <v>46245.98399305555</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="n"/>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" s="2" t="n"/>
-      <c r="F161" s="2" t="n"/>
-      <c r="G161" s="2" t="n"/>
-      <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B162" s="18" t="n"/>
@@ -9026,132 +9129,112 @@
       <c r="A164" s="5" t="inlineStr"/>
       <c r="B164" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome II</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>680</v>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="n">
+        <v>46245.98399305555</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="n"/>
+      <c r="H165" s="2" t="n"/>
+      <c r="I165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B166" s="18" t="n"/>
+      <c r="C166" s="18" t="n"/>
+      <c r="D166" s="18" t="n"/>
+      <c r="E166" s="18" t="n"/>
+      <c r="F166" s="18" t="n"/>
+      <c r="G166" s="18" t="n"/>
+      <c r="H166" s="18" t="n"/>
+      <c r="I166" s="18" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="21" t="n"/>
+      <c r="B167" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C167" s="21" t="n"/>
+      <c r="D167" s="21" t="n"/>
+      <c r="E167" s="21" t="n"/>
+      <c r="F167" s="21" t="n"/>
+      <c r="G167" s="21" t="n"/>
+      <c r="H167" s="21" t="n"/>
+      <c r="I167" s="21" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr"/>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C164" s="5" t="n">
+      <c r="C168" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E164" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="5" t="n">
+      <c r="E168" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G164" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H164" s="12" t="n">
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H168" s="12" t="n">
         <v>46248.99621527778</v>
       </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B165" s="18" t="n"/>
-      <c r="C165" s="18" t="n"/>
-      <c r="D165" s="18" t="n"/>
-      <c r="E165" s="18" t="n"/>
-      <c r="F165" s="18" t="n"/>
-      <c r="G165" s="18" t="n"/>
-      <c r="H165" s="18" t="n"/>
-      <c r="I165" s="18" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="21" t="n"/>
-      <c r="B166" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C166" s="21" t="n"/>
-      <c r="D166" s="21" t="n"/>
-      <c r="E166" s="21" t="n"/>
-      <c r="F166" s="21" t="n"/>
-      <c r="G166" s="21" t="n"/>
-      <c r="H166" s="21" t="n"/>
-      <c r="I166" s="21" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr"/>
-      <c r="B167" s="4" t="inlineStr">
-        <is>
-          <t>Minimum Depth of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C167" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E167" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G167" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H167" s="12" t="n">
-        <v>46246.95925925926</v>
-      </c>
-      <c r="I167" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="inlineStr"/>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>Average of Levels in Binary Tree</t>
-        </is>
-      </c>
-      <c r="C168" s="7" t="n">
-        <v>637</v>
-      </c>
-      <c r="D168" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E168" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" s="7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="G168" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H168" s="14" t="n">
-        <v>46246.98880787037</v>
-      </c>
-      <c r="I168" s="15" t="inlineStr">
+      <c r="I168" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -9160,7 +9243,7 @@
     <row r="169">
       <c r="A169" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B169" s="18" t="n"/>
@@ -9176,7 +9259,7 @@
       <c r="A170" s="21" t="n"/>
       <c r="B170" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 1 problem(s)</t>
+          <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
       <c r="C170" s="21" t="n"/>
@@ -9191,11 +9274,11 @@
       <c r="A171" s="5" t="inlineStr"/>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Binary Tree Inorder Traversal</t>
+          <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
       <c r="C171" s="5" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
@@ -9203,10 +9286,10 @@
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>43.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
@@ -9214,7 +9297,7 @@
         </is>
       </c>
       <c r="H171" s="12" t="n">
-        <v>46246.86910879629</v>
+        <v>46246.95925925926</v>
       </c>
       <c r="I171" s="13" t="inlineStr">
         <is>
@@ -9223,24 +9306,44 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="n"/>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="2" t="n"/>
-      <c r="F172" s="2" t="n"/>
-      <c r="G172" s="2" t="n"/>
-      <c r="H172" s="2" t="n"/>
-      <c r="I172" s="2" t="n"/>
+      <c r="A172" s="7" t="inlineStr"/>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>Average of Levels in Binary Tree</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="n">
+        <v>637</v>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F172" s="7" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H172" s="14" t="n">
+        <v>46246.98880787037</v>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B173" s="18" t="n"/>
@@ -9271,148 +9374,231 @@
       <c r="A175" s="5" t="inlineStr"/>
       <c r="B175" s="4" t="inlineStr">
         <is>
+          <t>Binary Tree Inorder Traversal</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H175" s="12" t="n">
+        <v>46246.86910879629</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="2" t="n"/>
+      <c r="G176" s="2" t="n"/>
+      <c r="H176" s="2" t="n"/>
+      <c r="I176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="n"/>
+      <c r="C177" s="18" t="n"/>
+      <c r="D177" s="18" t="n"/>
+      <c r="E177" s="18" t="n"/>
+      <c r="F177" s="18" t="n"/>
+      <c r="G177" s="18" t="n"/>
+      <c r="H177" s="18" t="n"/>
+      <c r="I177" s="18" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="21" t="n"/>
+      <c r="B178" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C178" s="21" t="n"/>
+      <c r="D178" s="21" t="n"/>
+      <c r="E178" s="21" t="n"/>
+      <c r="F178" s="21" t="n"/>
+      <c r="G178" s="21" t="n"/>
+      <c r="H178" s="21" t="n"/>
+      <c r="I178" s="21" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr"/>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C175" s="5" t="n">
+      <c r="C179" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E175" s="5" t="n">
+      <c r="E179" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F175" s="5" t="n">
+      <c r="F179" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G175" s="5" t="inlineStr">
+      <c r="G179" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H175" s="12" t="n">
+      <c r="H179" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I175" s="13" t="inlineStr">
+      <c r="I179" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="115">
+    <mergeCell ref="B135:I135"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B144:I144"/>
-    <mergeCell ref="A172:I172"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="A108:I108"/>
-    <mergeCell ref="B159:I159"/>
+    <mergeCell ref="B125:I125"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="B134:I134"/>
     <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B167:I167"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="B88:I88"/>
     <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B147:I147"/>
     <mergeCell ref="A111:I111"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="B137:I137"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B74:I74"/>
-    <mergeCell ref="A142:I142"/>
     <mergeCell ref="B83:I83"/>
     <mergeCell ref="A169:I169"/>
+    <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
+    <mergeCell ref="A153:I153"/>
     <mergeCell ref="B113:I113"/>
+    <mergeCell ref="A137:I137"/>
     <mergeCell ref="B109:I109"/>
-    <mergeCell ref="B150:I150"/>
-    <mergeCell ref="A136:I136"/>
+    <mergeCell ref="A177:I177"/>
+    <mergeCell ref="B141:I141"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B86:I86"/>
-    <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A116:I116"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="A165:I165"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="A115:I115"/>
-    <mergeCell ref="A155:I155"/>
+    <mergeCell ref="B178:I178"/>
     <mergeCell ref="A173:I173"/>
-    <mergeCell ref="A143:I143"/>
+    <mergeCell ref="B128:I128"/>
+    <mergeCell ref="A166:I166"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="A94:I94"/>
     <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B154:I154"/>
     <mergeCell ref="B163:I163"/>
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="B138:I138"/>
     <mergeCell ref="A133:I133"/>
-    <mergeCell ref="B156:I156"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="B140:I140"/>
     <mergeCell ref="A104:I104"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
+    <mergeCell ref="B117:I117"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
+    <mergeCell ref="B151:I151"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B166:I166"/>
-    <mergeCell ref="B119:I119"/>
-    <mergeCell ref="B116:I116"/>
+    <mergeCell ref="A147:I147"/>
+    <mergeCell ref="A156:I156"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="B174:I174"/>
     <mergeCell ref="A130:I130"/>
-    <mergeCell ref="B127:I127"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
-    <mergeCell ref="A123:I123"/>
     <mergeCell ref="B95:I95"/>
+    <mergeCell ref="B160:I160"/>
     <mergeCell ref="A146:I146"/>
-    <mergeCell ref="B153:I153"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="B121:I121"/>
-    <mergeCell ref="A149:I149"/>
-    <mergeCell ref="A158:I158"/>
+    <mergeCell ref="A119:I119"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
     <mergeCell ref="B131:I131"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
+    <mergeCell ref="A150:I150"/>
     <mergeCell ref="B60:I60"/>
+    <mergeCell ref="A159:I159"/>
+    <mergeCell ref="A122:I122"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="B170:I170"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="B148:I148"/>
     <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="B157:I157"/>
     <mergeCell ref="A112:I112"/>
-    <mergeCell ref="A152:I152"/>
-    <mergeCell ref="A161:I161"/>
     <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A127:I127"/>
     <mergeCell ref="B99:I99"/>
+    <mergeCell ref="A176:I176"/>
     <mergeCell ref="B92:I92"/>
     <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A107:I107"/>
-    <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="A162:I162"/>
@@ -9458,27 +9644,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId62"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9490,7 +9677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11313,24 +11500,81 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="252" customHeight="1">
+    <row r="43" ht="518" customHeight="1">
       <c r="A43" s="5" t="n">
         <v>39</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>Redundant Connection</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>684</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+ class UniounFind{
+    int[] parent;
+	public UniounFind(int size) {
+		parent = new int[size+1];
+		for(int i=0;i&lt;size;i++) {
+			parent[i] = i;
+		}
+    	}
+	public int find(int i) {
+		if(parent[i] == i) {
+			return i;
+		}
+		return find(parent[i]);
+	}
+    public void unioun(int first,int second) {
+	     parent[first] = second;
+	}
+ }
+    public int[] findRedundantConnection(int[][] edges) {
+    UniounFind uf = new UniounFind(edges.length);
+    int[] result = new int[2];
+       for(int[] n:edges){
+        int parent1 = uf.find(n[0]);
+        int parent2 = uf.find(n[1]);
+        if(parent1 == parent2){
+            result[0] = n[0];
+            result[1] = n[1];
+        }else{
+            uf.unioun(parent1,parent2);
+        }
+       }  
+       return result; 
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="252" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>739</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -11350,24 +11594,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="378" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="378" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -11399,24 +11643,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="294" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="294" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>908</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11442,24 +11686,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="560" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="560" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -11495,24 +11739,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="294" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="294" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -11535,24 +11779,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="224" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="224" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -11573,24 +11817,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="420" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="420" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -11625,24 +11869,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="378" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="378" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -11674,24 +11918,24 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="266" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52" ht="266" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>1570</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -11715,24 +11959,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="350" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53" ht="350" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -11762,24 +12006,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="238" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="238" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -11801,24 +12045,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="308" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="308" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -11845,24 +12089,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="280" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="280" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -11885,24 +12129,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="448" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="448" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -11937,24 +12181,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="378" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="378" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -11986,24 +12230,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="266" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="266" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -12027,24 +12271,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="560" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="560" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -12097,24 +12341,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="196" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="196" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>3811</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -12132,24 +12376,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="238" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="238" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -12169,24 +12413,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="252" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="252" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -12209,24 +12453,24 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="140" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="140" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -12240,24 +12484,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="294" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="294" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -12283,24 +12527,24 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="252" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="252" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -12401,13 +12645,13 @@
         <v>35</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -12439,13 +12683,13 @@
         <v>35</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -885,14 +885,14 @@
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -904,73 +904,73 @@
         <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>54.4</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Prefix Sum</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1544</v>
+        <v>18</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>48.6</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table, Prefix Sum</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -979,24 +979,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -1005,24 +1005,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>57.9</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1031,24 +1031,24 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>46.3</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -1057,24 +1057,24 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1083,17 +1083,17 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -1109,17 +1109,17 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
@@ -1135,24 +1135,24 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -1161,24 +1161,24 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
@@ -1187,24 +1187,24 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -1213,21 +1213,21 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>1</v>
@@ -1236,72 +1236,72 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>65.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>143.4</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>46.7</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -1317,24 +1317,24 @@
         <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Sorting, Quicksort</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -1343,73 +1343,73 @@
         <v>1</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>48.9</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Stack, Monotonic Stack</t>
+          <t>Sorting, Quicksort</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>34.3</v>
+        <v>8</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>67.40000000000001</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Stack, Monotonic Stack</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>3</v>
+        <v>34.3</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>47.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>47.2</v>
@@ -1431,33 +1431,33 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>48.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+          <t>Two Pointers, Binary Search</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -1473,229 +1473,229 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="n">
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H35" s="5" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="D35" s="9" t="n">
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="D36" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E36" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="F36" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Breadth-First Search, Union-Find, Graph Theory</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="7" t="n">
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>44.9</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Depth-First Search — TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr"/>
-      <c r="C39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H41" s="5" t="n">
         <v>45.9</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr"/>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>43.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="7" t="n">
         <v>1</v>
@@ -1704,261 +1704,261 @@
         <v>0</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>46.8</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="7" t="n">
+      <c r="C45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Linked List — TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr"/>
-      <c r="C45" s="9" t="n">
+      <c r="B46" s="8" t="inlineStr"/>
+      <c r="C46" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D45" s="9" t="n">
+      <c r="D46" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="E46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G45" s="9" t="inlineStr"/>
-      <c r="H45" s="9" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="7" t="n">
+      <c r="C47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H47" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
+      <c r="D49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G49" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H49" s="5" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr"/>
-      <c r="C49" s="9" t="n">
+      <c r="B50" s="8" t="inlineStr"/>
+      <c r="C50" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="9" t="n">
+      <c r="D50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G49" s="9" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="7" t="n">
+      <c r="C51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr"/>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>0</v>
@@ -1967,17 +1967,17 @@
         <v>1</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H52" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
@@ -1993,17 +1993,17 @@
         <v>1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
@@ -2019,237 +2019,263 @@
         <v>1</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
+      <c r="C56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H55" s="5" t="n">
+      <c r="H56" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr"/>
-      <c r="C56" s="9" t="n">
+      <c r="B57" s="8" t="inlineStr"/>
+      <c r="C57" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D56" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="9" t="n">
+      <c r="D57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G56" s="9" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="5" t="n">
+      <c r="C58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr"/>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr"/>
       <c r="B59" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="5" t="n">
+      <c r="C60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr"/>
-      <c r="C60" s="9" t="n">
+      <c r="B61" s="8" t="inlineStr"/>
+      <c r="C61" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="9" t="n">
+      <c r="D61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G60" s="9" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="5" t="n">
+      <c r="C62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H61" s="5" t="n">
+      <c r="H62" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr"/>
-      <c r="C62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="9" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr"/>
+      <c r="C63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr"/>
+      <c r="H63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr"/>
-      <c r="C63" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D63" s="11" t="n">
+      <c r="B64" s="10" t="inlineStr"/>
+      <c r="C64" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="D64" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E64" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F63" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="G63" s="11" t="inlineStr"/>
-      <c r="H63" s="11" t="inlineStr"/>
+      <c r="F64" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="G64" s="11" t="inlineStr"/>
+      <c r="H64" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2265,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5476,11 +5502,61 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Best Time to Buy and Sell Stock</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>46287.52454861111</v>
+      </c>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F66">
+  <conditionalFormatting sqref="F5:F67">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5554,6 +5630,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5565,7 +5642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I179"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5608,7 +5685,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   38 solved   (Low: 17 · Medium: 19 · High: 2)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   39 solved   (Low: 18 · Medium: 19 · High: 2)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -6098,7 +6175,7 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Dynamic Programming   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B26" s="18" t="n"/>
@@ -6111,40 +6188,40 @@
       <c r="I26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
+      <c r="A27" s="21" t="n"/>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Best Time to Buy and Sell Stock</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>4003</v>
+        <v>121</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -6152,7 +6229,7 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>46247.80789351852</v>
+        <v>46287.52454861111</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -6163,7 +6240,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table   —   3 solved   (Low: 2 · Medium: 0 · High: 1)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B29" s="18" t="n"/>
@@ -6176,48 +6253,48 @@
       <c r="I29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="n"/>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Two Sum</t>
+          <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1</v>
+        <v>4003</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46251.8174537037</v>
+        <v>46247.80789351852</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -6226,83 +6303,63 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="n">
-        <v>46252.95966435185</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table   —   3 solved   (Low: 2 · Medium: 0 · High: 1)</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="18" t="n"/>
+      <c r="I32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="n"/>
-      <c r="B33" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="23" t="n"/>
-      <c r="G33" s="23" t="n"/>
-      <c r="H33" s="23" t="n"/>
-      <c r="I33" s="23" t="n"/>
+      <c r="A33" s="21" t="n"/>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>First Missing Positive</t>
+          <t>Two Sum</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>71.09999999999999</v>
+        <v>47</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46273.670625</v>
+        <v>46251.8174537037</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -6311,55 +6368,75 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="18" t="n"/>
+      <c r="A35" s="7" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>46252.95966435185</v>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n"/>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="19" t="n"/>
+      <c r="A36" s="23" t="n"/>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="n"/>
+      <c r="G36" s="23" t="n"/>
+      <c r="H36" s="23" t="n"/>
+      <c r="I36" s="23" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Subarray Sum Equals K</t>
+          <t>First Missing Positive</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>560</v>
+        <v>41</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1544</v>
+        <v>1</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>48.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -6367,7 +6444,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46263.40873842593</v>
+        <v>46273.670625</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -6378,7 +6455,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
@@ -6391,40 +6468,40 @@
       <c r="I38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Contains Duplicate II</t>
+          <t>Subarray Sum Equals K</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>219</v>
+        <v>560</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -6432,7 +6509,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46258.98878472222</v>
+        <v>46263.40873842593</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -6443,7 +6520,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -6456,40 +6533,40 @@
       <c r="I41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="n"/>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="19" t="n"/>
-      <c r="I42" s="19" t="n"/>
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="21" t="n"/>
+      <c r="I42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Find All Duplicates in an Array</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>442</v>
+        <v>219</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>57.9</v>
+        <v>104.8</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -6497,7 +6574,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46273.57508101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -6508,7 +6585,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -6521,40 +6598,40 @@
       <c r="I44" s="18" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="n"/>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
+      <c r="A45" s="19" t="n"/>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="19" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Find All Duplicates in an Array</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>1353</v>
+        <v>442</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>46.3</v>
+        <v>57.9</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -6562,7 +6639,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46273.57508101852</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -6573,7 +6650,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -6586,40 +6663,40 @@
       <c r="I47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n"/>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -6627,7 +6704,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -6638,7 +6715,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -6651,48 +6728,48 @@
       <c r="I50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="n"/>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
+      <c r="A51" s="19" t="n"/>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
+      <c r="G51" s="19" t="n"/>
+      <c r="H51" s="19" t="n"/>
+      <c r="I51" s="19" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -6703,7 +6780,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -6734,11 +6811,11 @@
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
@@ -6746,18 +6823,18 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -6768,7 +6845,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -6799,11 +6876,11 @@
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
@@ -6811,10 +6888,10 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -6822,7 +6899,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -6833,7 +6910,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -6846,40 +6923,40 @@
       <c r="I59" s="18" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="19" t="n"/>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-      <c r="G60" s="19" t="n"/>
-      <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
@@ -6887,7 +6964,7 @@
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -6898,7 +6975,7 @@
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -6911,40 +6988,40 @@
       <c r="I62" s="18" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="21" t="n"/>
-      <c r="B63" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="n"/>
-      <c r="D63" s="21" t="n"/>
-      <c r="E63" s="21" t="n"/>
-      <c r="F63" s="21" t="n"/>
-      <c r="G63" s="21" t="n"/>
-      <c r="H63" s="21" t="n"/>
-      <c r="I63" s="21" t="n"/>
+      <c r="A63" s="19" t="n"/>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="n"/>
+      <c r="D63" s="19" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="19" t="n"/>
+      <c r="G63" s="19" t="n"/>
+      <c r="H63" s="19" t="n"/>
+      <c r="I63" s="19" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -6952,7 +7029,7 @@
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -6963,7 +7040,7 @@
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -6976,40 +7053,40 @@
       <c r="I65" s="18" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="19" t="n"/>
-      <c r="B66" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
-      <c r="G66" s="19" t="n"/>
-      <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
+      <c r="A66" s="21" t="n"/>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="21" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -7017,7 +7094,7 @@
         </is>
       </c>
       <c r="H67" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -7028,7 +7105,7 @@
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B68" s="18" t="n"/>
@@ -7041,155 +7118,155 @@
       <c r="I68" s="18" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="21" t="n"/>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
+      <c r="A69" s="19" t="n"/>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="19" t="n"/>
+      <c r="H69" s="19" t="n"/>
+      <c r="I69" s="19" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
+          <t>Matrix Block Sum</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>46262.8983912037</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C73" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="5" t="n">
+      <c r="E73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="n">
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
         <v>46270.61052083333</v>
       </c>
-      <c r="I70" s="13" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="19" t="n"/>
-      <c r="B71" s="20" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="19" t="n"/>
+      <c r="B74" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C71" s="19" t="n"/>
-      <c r="D71" s="19" t="n"/>
-      <c r="E71" s="19" t="n"/>
-      <c r="F71" s="19" t="n"/>
-      <c r="G71" s="19" t="n"/>
-      <c r="H71" s="19" t="n"/>
-      <c r="I71" s="19" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Flight Bookings</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>46262.6837962963</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="18" t="n"/>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="18" t="n"/>
-      <c r="I73" s="18" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="23" t="n"/>
-      <c r="B74" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C74" s="23" t="n"/>
-      <c r="D74" s="23" t="n"/>
-      <c r="E74" s="23" t="n"/>
-      <c r="F74" s="23" t="n"/>
-      <c r="G74" s="23" t="n"/>
-      <c r="H74" s="23" t="n"/>
-      <c r="I74" s="23" t="n"/>
+      <c r="C74" s="19" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="19" t="n"/>
+      <c r="G74" s="19" t="n"/>
+      <c r="H74" s="19" t="n"/>
+      <c r="I74" s="19" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window Maximum</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>239</v>
+        <v>1206</v>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>143.4</v>
+        <v>85</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
@@ -7197,7 +7274,7 @@
         </is>
       </c>
       <c r="H75" s="12" t="n">
-        <v>46276.50631944444</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -7208,7 +7285,7 @@
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B76" s="18" t="n"/>
@@ -7221,40 +7298,40 @@
       <c r="I76" s="18" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="21" t="n"/>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C77" s="21" t="n"/>
-      <c r="D77" s="21" t="n"/>
-      <c r="E77" s="21" t="n"/>
-      <c r="F77" s="21" t="n"/>
-      <c r="G77" s="21" t="n"/>
-      <c r="H77" s="21" t="n"/>
-      <c r="I77" s="21" t="n"/>
+      <c r="A77" s="23" t="n"/>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C77" s="23" t="n"/>
+      <c r="D77" s="23" t="n"/>
+      <c r="E77" s="23" t="n"/>
+      <c r="F77" s="23" t="n"/>
+      <c r="G77" s="23" t="n"/>
+      <c r="H77" s="23" t="n"/>
+      <c r="I77" s="23" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Sliding Window Maximum</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
-        <v>3347</v>
+        <v>239</v>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>46.7</v>
+        <v>143.4</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
@@ -7262,7 +7339,7 @@
         </is>
       </c>
       <c r="H78" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46276.50631944444</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -7273,7 +7350,7 @@
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B79" s="18" t="n"/>
@@ -7304,11 +7381,11 @@
       <c r="A81" s="5" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
@@ -7316,10 +7393,10 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
@@ -7327,7 +7404,7 @@
         </is>
       </c>
       <c r="H81" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -7338,7 +7415,7 @@
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sorting, Quicksort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B82" s="18" t="n"/>
@@ -7351,40 +7428,40 @@
       <c r="I82" s="18" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="19" t="n"/>
-      <c r="B83" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C83" s="19" t="n"/>
-      <c r="D83" s="19" t="n"/>
-      <c r="E83" s="19" t="n"/>
-      <c r="F83" s="19" t="n"/>
-      <c r="G83" s="19" t="n"/>
-      <c r="H83" s="19" t="n"/>
-      <c r="I83" s="19" t="n"/>
+      <c r="A83" s="21" t="n"/>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="n"/>
+      <c r="D83" s="21" t="n"/>
+      <c r="E83" s="21" t="n"/>
+      <c r="F83" s="21" t="n"/>
+      <c r="G83" s="21" t="n"/>
+      <c r="H83" s="21" t="n"/>
+      <c r="I83" s="21" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Merge Intervals</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>56</v>
+        <v>643</v>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>48.9</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
@@ -7392,7 +7469,7 @@
         </is>
       </c>
       <c r="H84" s="12" t="n">
-        <v>46273.68709490741</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -7403,7 +7480,7 @@
     <row r="85">
       <c r="A85" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack   —   3 solved   (Low: 1 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sorting, Quicksort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B85" s="18" t="n"/>
@@ -7416,200 +7493,200 @@
       <c r="I85" s="18" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="21" t="n"/>
-      <c r="B86" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C86" s="21" t="n"/>
-      <c r="D86" s="21" t="n"/>
-      <c r="E86" s="21" t="n"/>
-      <c r="F86" s="21" t="n"/>
-      <c r="G86" s="21" t="n"/>
-      <c r="H86" s="21" t="n"/>
-      <c r="I86" s="21" t="n"/>
+      <c r="A86" s="19" t="n"/>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C86" s="19" t="n"/>
+      <c r="D86" s="19" t="n"/>
+      <c r="E86" s="19" t="n"/>
+      <c r="F86" s="19" t="n"/>
+      <c r="G86" s="19" t="n"/>
+      <c r="H86" s="19" t="n"/>
+      <c r="I86" s="19" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr"/>
       <c r="B87" s="4" t="inlineStr">
         <is>
+          <t>Merge Intervals</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>46273.68709490741</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack   —   3 solved   (Low: 1 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="18" t="n"/>
+      <c r="E88" s="18" t="n"/>
+      <c r="F88" s="18" t="n"/>
+      <c r="G88" s="18" t="n"/>
+      <c r="H88" s="18" t="n"/>
+      <c r="I88" s="18" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="21" t="n"/>
+      <c r="E89" s="21" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="21" t="n"/>
+      <c r="I89" s="21" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr"/>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C90" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E90" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F90" s="5" t="n">
         <v>45.6</v>
       </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H87" s="12" t="n">
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="n">
         <v>46275.51596064815</v>
       </c>
-      <c r="I87" s="13" t="inlineStr">
+      <c r="I90" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="19" t="n"/>
-      <c r="B88" s="20" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="19" t="n"/>
+      <c r="B91" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C88" s="19" t="n"/>
-      <c r="D88" s="19" t="n"/>
-      <c r="E88" s="19" t="n"/>
-      <c r="F88" s="19" t="n"/>
-      <c r="G88" s="19" t="n"/>
-      <c r="H88" s="19" t="n"/>
-      <c r="I88" s="19" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="C91" s="19" t="n"/>
+      <c r="D91" s="19" t="n"/>
+      <c r="E91" s="19" t="n"/>
+      <c r="F91" s="19" t="n"/>
+      <c r="G91" s="19" t="n"/>
+      <c r="H91" s="19" t="n"/>
+      <c r="I91" s="19" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr"/>
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C92" s="5" t="n">
         <v>503</v>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="E92" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F92" s="5" t="n">
         <v>48.5</v>
       </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H89" s="12" t="n">
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="n">
         <v>46275.6128125</v>
       </c>
-      <c r="I89" s="13" t="inlineStr">
+      <c r="I92" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="7" t="inlineStr"/>
-      <c r="B90" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr"/>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C90" s="7" t="n">
+      <c r="C93" s="7" t="n">
         <v>739</v>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="7" t="n">
+      <c r="E93" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F90" s="7" t="n">
+      <c r="F93" s="7" t="n">
         <v>108.1</v>
       </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H90" s="14" t="n">
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H93" s="14" t="n">
         <v>46275.62596064815</v>
       </c>
-      <c r="I90" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B91" s="18" t="n"/>
-      <c r="C91" s="18" t="n"/>
-      <c r="D91" s="18" t="n"/>
-      <c r="E91" s="18" t="n"/>
-      <c r="F91" s="18" t="n"/>
-      <c r="G91" s="18" t="n"/>
-      <c r="H91" s="18" t="n"/>
-      <c r="I91" s="18" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="21" t="n"/>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="n"/>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr"/>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Score Validator</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="n">
-        <v>4281</v>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="n">
-        <v>46247.02123842593</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7618,7 +7695,7 @@
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B94" s="18" t="n"/>
@@ -7634,7 +7711,7 @@
       <c r="A95" s="21" t="n"/>
       <c r="B95" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C95" s="21" t="n"/>
@@ -7649,132 +7726,132 @@
       <c r="A96" s="5" t="inlineStr"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="18" t="n"/>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="n"/>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="21" t="n"/>
+      <c r="E98" s="21" t="n"/>
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C99" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="5" t="n">
+      <c r="E99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="n">
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I96" s="13" t="inlineStr">
+      <c r="I99" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="7" t="inlineStr"/>
-      <c r="B97" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C97" s="7" t="n">
+      <c r="C100" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D100" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E97" s="7" t="n">
+      <c r="E100" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F97" s="7" t="n">
+      <c r="F100" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H97" s="14" t="n">
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B98" s="18" t="n"/>
-      <c r="C98" s="18" t="n"/>
-      <c r="D98" s="18" t="n"/>
-      <c r="E98" s="18" t="n"/>
-      <c r="F98" s="18" t="n"/>
-      <c r="G98" s="18" t="n"/>
-      <c r="H98" s="18" t="n"/>
-      <c r="I98" s="18" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="19" t="n"/>
-      <c r="B99" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C99" s="19" t="n"/>
-      <c r="D99" s="19" t="n"/>
-      <c r="E99" s="19" t="n"/>
-      <c r="F99" s="19" t="n"/>
-      <c r="G99" s="19" t="n"/>
-      <c r="H99" s="19" t="n"/>
-      <c r="I99" s="19" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr"/>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Two Sum II - Input Array Is Sorted</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>46272.93130787037</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
+      <c r="I100" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7783,7 +7860,7 @@
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B101" s="18" t="n"/>
@@ -7814,11 +7891,11 @@
       <c r="A103" s="5" t="inlineStr"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Find the Duplicate Number</t>
+          <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>287</v>
+        <v>167</v>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
@@ -7826,10 +7903,10 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
@@ -7837,7 +7914,7 @@
         </is>
       </c>
       <c r="H103" s="12" t="n">
-        <v>46274.9421875</v>
+        <v>46272.93130787037</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -7848,7 +7925,7 @@
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B104" s="18" t="n"/>
@@ -7879,281 +7956,281 @@
       <c r="A106" s="5" t="inlineStr"/>
       <c r="B106" s="4" t="inlineStr">
         <is>
+          <t>Find the Duplicate Number</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>46274.9421875</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="18" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="18" t="n"/>
+      <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="n"/>
+      <c r="I107" s="18" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="n"/>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C108" s="19" t="n"/>
+      <c r="D108" s="19" t="n"/>
+      <c r="E108" s="19" t="n"/>
+      <c r="F108" s="19" t="n"/>
+      <c r="G108" s="19" t="n"/>
+      <c r="H108" s="19" t="n"/>
+      <c r="I108" s="19" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr"/>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C109" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F106" s="5" t="n">
+      <c r="F109" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H106" s="12" t="n">
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I106" s="13" t="inlineStr">
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="16" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n"/>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="17" t="inlineStr">
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B108" s="18" t="n"/>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-      <c r="G108" s="18" t="n"/>
-      <c r="H108" s="18" t="n"/>
-      <c r="I108" s="18" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="19" t="n"/>
-      <c r="B109" s="20" t="inlineStr">
+      <c r="B111" s="18" t="n"/>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="18" t="n"/>
+      <c r="E111" s="18" t="n"/>
+      <c r="F111" s="18" t="n"/>
+      <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="n"/>
+      <c r="I111" s="18" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="n"/>
+      <c r="B112" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C109" s="19" t="n"/>
-      <c r="D109" s="19" t="n"/>
-      <c r="E109" s="19" t="n"/>
-      <c r="F109" s="19" t="n"/>
-      <c r="G109" s="19" t="n"/>
-      <c r="H109" s="19" t="n"/>
-      <c r="I109" s="19" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr"/>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="C112" s="19" t="n"/>
+      <c r="D112" s="19" t="n"/>
+      <c r="E112" s="19" t="n"/>
+      <c r="F112" s="19" t="n"/>
+      <c r="G112" s="19" t="n"/>
+      <c r="H112" s="19" t="n"/>
+      <c r="I112" s="19" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr"/>
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C110" s="5" t="n">
+      <c r="C113" s="5" t="n">
         <v>684</v>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="5" t="n">
+      <c r="E113" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="5" t="n">
         <v>44.9</v>
       </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H110" s="12" t="n">
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="n">
         <v>46287.51434027778</v>
       </c>
-      <c r="I110" s="13" t="inlineStr">
+      <c r="I113" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="16" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B111" s="2" t="n"/>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n"/>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="17" t="inlineStr">
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="21" t="n"/>
-      <c r="B113" s="22" t="inlineStr">
+      <c r="B115" s="18" t="n"/>
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="n"/>
+      <c r="B116" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C113" s="21" t="n"/>
-      <c r="D113" s="21" t="n"/>
-      <c r="E113" s="21" t="n"/>
-      <c r="F113" s="21" t="n"/>
-      <c r="G113" s="21" t="n"/>
-      <c r="H113" s="21" t="n"/>
-      <c r="I113" s="21" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr"/>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="C116" s="21" t="n"/>
+      <c r="D116" s="21" t="n"/>
+      <c r="E116" s="21" t="n"/>
+      <c r="F116" s="21" t="n"/>
+      <c r="G116" s="21" t="n"/>
+      <c r="H116" s="21" t="n"/>
+      <c r="I116" s="21" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr"/>
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C117" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="5" t="n">
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H117" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I114" s="13" t="inlineStr">
+      <c r="I117" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n"/>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B116" s="18" t="n"/>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="23" t="n"/>
-      <c r="B117" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C117" s="23" t="n"/>
-      <c r="D117" s="23" t="n"/>
-      <c r="E117" s="23" t="n"/>
-      <c r="F117" s="23" t="n"/>
-      <c r="G117" s="23" t="n"/>
-      <c r="H117" s="23" t="n"/>
-      <c r="I117" s="23" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr"/>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Merge k Sorted Lists</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H118" s="12" t="n">
-        <v>46286.43949074074</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B119" s="18" t="n"/>
@@ -8166,40 +8243,40 @@
       <c r="I119" s="18" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="19" t="n"/>
-      <c r="B120" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C120" s="19" t="n"/>
-      <c r="D120" s="19" t="n"/>
-      <c r="E120" s="19" t="n"/>
-      <c r="F120" s="19" t="n"/>
-      <c r="G120" s="19" t="n"/>
-      <c r="H120" s="19" t="n"/>
-      <c r="I120" s="19" t="n"/>
+      <c r="A120" s="23" t="n"/>
+      <c r="B120" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C120" s="23" t="n"/>
+      <c r="D120" s="23" t="n"/>
+      <c r="E120" s="23" t="n"/>
+      <c r="F120" s="23" t="n"/>
+      <c r="G120" s="23" t="n"/>
+      <c r="H120" s="23" t="n"/>
+      <c r="I120" s="23" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr"/>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List II</t>
+          <t>Merge k Sorted Lists</t>
         </is>
       </c>
       <c r="C121" s="5" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>43.4</v>
+        <v>45.9</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
@@ -8207,7 +8284,7 @@
         </is>
       </c>
       <c r="H121" s="12" t="n">
-        <v>46275.41266203704</v>
+        <v>46286.43949074074</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -8218,7 +8295,7 @@
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B122" s="18" t="n"/>
@@ -8231,155 +8308,155 @@
       <c r="I122" s="18" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="21" t="n"/>
-      <c r="B123" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C123" s="21" t="n"/>
-      <c r="D123" s="21" t="n"/>
-      <c r="E123" s="21" t="n"/>
-      <c r="F123" s="21" t="n"/>
-      <c r="G123" s="21" t="n"/>
-      <c r="H123" s="21" t="n"/>
-      <c r="I123" s="21" t="n"/>
+      <c r="A123" s="19" t="n"/>
+      <c r="B123" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C123" s="19" t="n"/>
+      <c r="D123" s="19" t="n"/>
+      <c r="E123" s="19" t="n"/>
+      <c r="F123" s="19" t="n"/>
+      <c r="G123" s="19" t="n"/>
+      <c r="H123" s="19" t="n"/>
+      <c r="I123" s="19" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr"/>
       <c r="B124" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List II</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>46275.41266203704</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B125" s="18" t="n"/>
+      <c r="C125" s="18" t="n"/>
+      <c r="D125" s="18" t="n"/>
+      <c r="E125" s="18" t="n"/>
+      <c r="F125" s="18" t="n"/>
+      <c r="G125" s="18" t="n"/>
+      <c r="H125" s="18" t="n"/>
+      <c r="I125" s="18" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="21" t="n"/>
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C126" s="21" t="n"/>
+      <c r="D126" s="21" t="n"/>
+      <c r="E126" s="21" t="n"/>
+      <c r="F126" s="21" t="n"/>
+      <c r="G126" s="21" t="n"/>
+      <c r="H126" s="21" t="n"/>
+      <c r="I126" s="21" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr"/>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C124" s="5" t="n">
+      <c r="C127" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="5" t="n">
+      <c r="E127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H124" s="12" t="n">
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I124" s="13" t="inlineStr">
+      <c r="I127" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="19" t="n"/>
-      <c r="B125" s="20" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="19" t="n"/>
+      <c r="B128" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C125" s="19" t="n"/>
-      <c r="D125" s="19" t="n"/>
-      <c r="E125" s="19" t="n"/>
-      <c r="F125" s="19" t="n"/>
-      <c r="G125" s="19" t="n"/>
-      <c r="H125" s="19" t="n"/>
-      <c r="I125" s="19" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr"/>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>Linked List Cycle II</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G126" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H126" s="12" t="n">
-        <v>46274.44269675926</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B127" s="18" t="n"/>
-      <c r="C127" s="18" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-      <c r="G127" s="18" t="n"/>
-      <c r="H127" s="18" t="n"/>
-      <c r="I127" s="18" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="21" t="n"/>
-      <c r="B128" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C128" s="21" t="n"/>
-      <c r="D128" s="21" t="n"/>
-      <c r="E128" s="21" t="n"/>
-      <c r="F128" s="21" t="n"/>
-      <c r="G128" s="21" t="n"/>
-      <c r="H128" s="21" t="n"/>
-      <c r="I128" s="21" t="n"/>
+      <c r="C128" s="19" t="n"/>
+      <c r="D128" s="19" t="n"/>
+      <c r="E128" s="19" t="n"/>
+      <c r="F128" s="19" t="n"/>
+      <c r="G128" s="19" t="n"/>
+      <c r="H128" s="19" t="n"/>
+      <c r="I128" s="19" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr"/>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List</t>
+          <t>Linked List Cycle II</t>
         </is>
       </c>
       <c r="C129" s="5" t="n">
-        <v>206</v>
+        <v>142</v>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
@@ -8387,7 +8464,7 @@
         </is>
       </c>
       <c r="H129" s="12" t="n">
-        <v>46274.48334490741</v>
+        <v>46274.44269675926</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -8398,7 +8475,7 @@
     <row r="130">
       <c r="A130" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B130" s="18" t="n"/>
@@ -8429,121 +8506,121 @@
       <c r="A132" s="5" t="inlineStr"/>
       <c r="B132" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>46274.48334490741</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B133" s="18" t="n"/>
+      <c r="C133" s="18" t="n"/>
+      <c r="D133" s="18" t="n"/>
+      <c r="E133" s="18" t="n"/>
+      <c r="F133" s="18" t="n"/>
+      <c r="G133" s="18" t="n"/>
+      <c r="H133" s="18" t="n"/>
+      <c r="I133" s="18" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="21" t="n"/>
+      <c r="B134" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C134" s="21" t="n"/>
+      <c r="D134" s="21" t="n"/>
+      <c r="E134" s="21" t="n"/>
+      <c r="F134" s="21" t="n"/>
+      <c r="G134" s="21" t="n"/>
+      <c r="H134" s="21" t="n"/>
+      <c r="I134" s="21" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr"/>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C132" s="5" t="n">
+      <c r="C135" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="5" t="n">
+      <c r="E135" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H132" s="12" t="n">
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I132" s="13" t="inlineStr">
+      <c r="I135" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="16" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B133" s="2" t="n"/>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n"/>
-      <c r="E133" s="2" t="n"/>
-      <c r="F133" s="2" t="n"/>
-      <c r="G133" s="2" t="n"/>
-      <c r="H133" s="2" t="n"/>
-      <c r="I133" s="2" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B134" s="18" t="n"/>
-      <c r="C134" s="18" t="n"/>
-      <c r="D134" s="18" t="n"/>
-      <c r="E134" s="18" t="n"/>
-      <c r="F134" s="18" t="n"/>
-      <c r="G134" s="18" t="n"/>
-      <c r="H134" s="18" t="n"/>
-      <c r="I134" s="18" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="21" t="n"/>
-      <c r="B135" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C135" s="21" t="n"/>
-      <c r="D135" s="21" t="n"/>
-      <c r="E135" s="21" t="n"/>
-      <c r="F135" s="21" t="n"/>
-      <c r="G135" s="21" t="n"/>
-      <c r="H135" s="21" t="n"/>
-      <c r="I135" s="21" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr"/>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H136" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="2" t="n"/>
+      <c r="H136" s="2" t="n"/>
+      <c r="I136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B137" s="18" t="n"/>
@@ -8574,11 +8651,11 @@
       <c r="A139" s="5" t="inlineStr"/>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
@@ -8586,10 +8663,10 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -8597,7 +8674,7 @@
         </is>
       </c>
       <c r="H139" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -8608,7 +8685,7 @@
     <row r="140">
       <c r="A140" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B140" s="18" t="n"/>
@@ -8624,7 +8701,7 @@
       <c r="A141" s="21" t="n"/>
       <c r="B141" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C141" s="21" t="n"/>
@@ -8639,11 +8716,11 @@
       <c r="A142" s="5" t="inlineStr"/>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C142" s="5" t="n">
-        <v>3918</v>
+        <v>3626</v>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
@@ -8654,7 +8731,7 @@
         <v>1</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
@@ -8662,7 +8739,7 @@
         </is>
       </c>
       <c r="H142" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -8671,174 +8748,174 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="7" t="inlineStr"/>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>Count Commas in Range</t>
-        </is>
-      </c>
-      <c r="C143" s="7" t="n">
-        <v>4245</v>
-      </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H143" s="14" t="n">
-        <v>46273.3956712963</v>
-      </c>
-      <c r="I143" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A143" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="n"/>
+      <c r="C143" s="18" t="n"/>
+      <c r="D143" s="18" t="n"/>
+      <c r="E143" s="18" t="n"/>
+      <c r="F143" s="18" t="n"/>
+      <c r="G143" s="18" t="n"/>
+      <c r="H143" s="18" t="n"/>
+      <c r="I143" s="18" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="19" t="n"/>
-      <c r="B144" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C144" s="19" t="n"/>
-      <c r="D144" s="19" t="n"/>
-      <c r="E144" s="19" t="n"/>
-      <c r="F144" s="19" t="n"/>
-      <c r="G144" s="19" t="n"/>
-      <c r="H144" s="19" t="n"/>
-      <c r="I144" s="19" t="n"/>
+      <c r="A144" s="21" t="n"/>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C144" s="21" t="n"/>
+      <c r="D144" s="21" t="n"/>
+      <c r="E144" s="21" t="n"/>
+      <c r="F144" s="21" t="n"/>
+      <c r="G144" s="21" t="n"/>
+      <c r="H144" s="21" t="n"/>
+      <c r="I144" s="21" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr"/>
       <c r="B145" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="7" t="inlineStr"/>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H146" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I146" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="19" t="n"/>
+      <c r="B147" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C147" s="19" t="n"/>
+      <c r="D147" s="19" t="n"/>
+      <c r="E147" s="19" t="n"/>
+      <c r="F147" s="19" t="n"/>
+      <c r="G147" s="19" t="n"/>
+      <c r="H147" s="19" t="n"/>
+      <c r="I147" s="19" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr"/>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C145" s="5" t="n">
+      <c r="C148" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" s="5" t="n">
+      <c r="E148" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G145" s="5" t="inlineStr">
+      <c r="G148" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H145" s="12" t="n">
+      <c r="H148" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I145" s="13" t="inlineStr">
+      <c r="I148" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="16" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="n"/>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" s="2" t="n"/>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="n"/>
-      <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B147" s="18" t="n"/>
-      <c r="C147" s="18" t="n"/>
-      <c r="D147" s="18" t="n"/>
-      <c r="E147" s="18" t="n"/>
-      <c r="F147" s="18" t="n"/>
-      <c r="G147" s="18" t="n"/>
-      <c r="H147" s="18" t="n"/>
-      <c r="I147" s="18" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="21" t="n"/>
-      <c r="B148" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C148" s="21" t="n"/>
-      <c r="D148" s="21" t="n"/>
-      <c r="E148" s="21" t="n"/>
-      <c r="F148" s="21" t="n"/>
-      <c r="G148" s="21" t="n"/>
-      <c r="H148" s="21" t="n"/>
-      <c r="I148" s="21" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr"/>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="2" t="n"/>
+      <c r="H149" s="2" t="n"/>
+      <c r="I149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B150" s="18" t="n"/>
@@ -8851,48 +8928,48 @@
       <c r="I150" s="18" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="19" t="n"/>
-      <c r="B151" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C151" s="19" t="n"/>
-      <c r="D151" s="19" t="n"/>
-      <c r="E151" s="19" t="n"/>
-      <c r="F151" s="19" t="n"/>
-      <c r="G151" s="19" t="n"/>
-      <c r="H151" s="19" t="n"/>
-      <c r="I151" s="19" t="n"/>
+      <c r="A151" s="21" t="n"/>
+      <c r="B151" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C151" s="21" t="n"/>
+      <c r="D151" s="21" t="n"/>
+      <c r="E151" s="21" t="n"/>
+      <c r="F151" s="21" t="n"/>
+      <c r="G151" s="21" t="n"/>
+      <c r="H151" s="21" t="n"/>
+      <c r="I151" s="21" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr"/>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C152" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H152" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -8903,7 +8980,7 @@
     <row r="153">
       <c r="A153" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B153" s="18" t="n"/>
@@ -8916,40 +8993,40 @@
       <c r="I153" s="18" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="21" t="n"/>
-      <c r="B154" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C154" s="21" t="n"/>
-      <c r="D154" s="21" t="n"/>
-      <c r="E154" s="21" t="n"/>
-      <c r="F154" s="21" t="n"/>
-      <c r="G154" s="21" t="n"/>
-      <c r="H154" s="21" t="n"/>
-      <c r="I154" s="21" t="n"/>
+      <c r="A154" s="19" t="n"/>
+      <c r="B154" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="n"/>
+      <c r="D154" s="19" t="n"/>
+      <c r="E154" s="19" t="n"/>
+      <c r="F154" s="19" t="n"/>
+      <c r="G154" s="19" t="n"/>
+      <c r="H154" s="19" t="n"/>
+      <c r="I154" s="19" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr"/>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C155" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
@@ -8957,7 +9034,7 @@
         </is>
       </c>
       <c r="H155" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I155" s="13" t="inlineStr">
         <is>
@@ -8968,7 +9045,7 @@
     <row r="156">
       <c r="A156" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B156" s="18" t="n"/>
@@ -8999,11 +9076,11 @@
       <c r="A158" s="5" t="inlineStr"/>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Reverse Degree of a String</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C158" s="5" t="n">
-        <v>3811</v>
+        <v>242</v>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
@@ -9011,10 +9088,10 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
@@ -9022,7 +9099,7 @@
         </is>
       </c>
       <c r="H158" s="12" t="n">
-        <v>46285.42987268518</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -9033,7 +9110,7 @@
     <row r="159">
       <c r="A159" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B159" s="18" t="n"/>
@@ -9064,11 +9141,11 @@
       <c r="A161" s="5" t="inlineStr"/>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Reverse Degree of a String</t>
         </is>
       </c>
       <c r="C161" s="5" t="n">
-        <v>125</v>
+        <v>3811</v>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
@@ -9076,18 +9153,18 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H161" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46285.42987268518</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -9098,7 +9175,7 @@
     <row r="162">
       <c r="A162" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B162" s="18" t="n"/>
@@ -9129,121 +9206,121 @@
       <c r="A164" s="5" t="inlineStr"/>
       <c r="B164" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H164" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B165" s="18" t="n"/>
+      <c r="C165" s="18" t="n"/>
+      <c r="D165" s="18" t="n"/>
+      <c r="E165" s="18" t="n"/>
+      <c r="F165" s="18" t="n"/>
+      <c r="G165" s="18" t="n"/>
+      <c r="H165" s="18" t="n"/>
+      <c r="I165" s="18" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="21" t="n"/>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C166" s="21" t="n"/>
+      <c r="D166" s="21" t="n"/>
+      <c r="E166" s="21" t="n"/>
+      <c r="F166" s="21" t="n"/>
+      <c r="G166" s="21" t="n"/>
+      <c r="H166" s="21" t="n"/>
+      <c r="I166" s="21" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr"/>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C164" s="5" t="n">
+      <c r="C167" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D167" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E164" s="5" t="n">
+      <c r="E167" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F164" s="5" t="n">
+      <c r="F167" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G164" s="5" t="inlineStr">
+      <c r="G167" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H164" s="12" t="n">
+      <c r="H167" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I164" s="13" t="inlineStr">
+      <c r="I167" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="16" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B165" s="2" t="n"/>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" s="2" t="n"/>
-      <c r="F165" s="2" t="n"/>
-      <c r="G165" s="2" t="n"/>
-      <c r="H165" s="2" t="n"/>
-      <c r="I165" s="2" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B166" s="18" t="n"/>
-      <c r="C166" s="18" t="n"/>
-      <c r="D166" s="18" t="n"/>
-      <c r="E166" s="18" t="n"/>
-      <c r="F166" s="18" t="n"/>
-      <c r="G166" s="18" t="n"/>
-      <c r="H166" s="18" t="n"/>
-      <c r="I166" s="18" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="21" t="n"/>
-      <c r="B167" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C167" s="21" t="n"/>
-      <c r="D167" s="21" t="n"/>
-      <c r="E167" s="21" t="n"/>
-      <c r="F167" s="21" t="n"/>
-      <c r="G167" s="21" t="n"/>
-      <c r="H167" s="21" t="n"/>
-      <c r="I167" s="21" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="5" t="inlineStr"/>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H168" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="n"/>
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="2" t="n"/>
+      <c r="I168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B169" s="18" t="n"/>
@@ -9259,7 +9336,7 @@
       <c r="A170" s="21" t="n"/>
       <c r="B170" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C170" s="21" t="n"/>
@@ -9274,239 +9351,304 @@
       <c r="A171" s="5" t="inlineStr"/>
       <c r="B171" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="n"/>
+      <c r="C172" s="18" t="n"/>
+      <c r="D172" s="18" t="n"/>
+      <c r="E172" s="18" t="n"/>
+      <c r="F172" s="18" t="n"/>
+      <c r="G172" s="18" t="n"/>
+      <c r="H172" s="18" t="n"/>
+      <c r="I172" s="18" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="21" t="n"/>
+      <c r="B173" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C173" s="21" t="n"/>
+      <c r="D173" s="21" t="n"/>
+      <c r="E173" s="21" t="n"/>
+      <c r="F173" s="21" t="n"/>
+      <c r="G173" s="21" t="n"/>
+      <c r="H173" s="21" t="n"/>
+      <c r="I173" s="21" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr"/>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C171" s="5" t="n">
+      <c r="C174" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E171" s="5" t="n">
+      <c r="E174" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F171" s="5" t="n">
+      <c r="F174" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G171" s="5" t="inlineStr">
+      <c r="G174" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H171" s="12" t="n">
+      <c r="H174" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I171" s="13" t="inlineStr">
+      <c r="I174" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="7" t="inlineStr"/>
-      <c r="B172" s="6" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr"/>
+      <c r="B175" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C172" s="7" t="n">
+      <c r="C175" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D172" s="7" t="inlineStr">
+      <c r="D175" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E172" s="7" t="n">
+      <c r="E175" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F172" s="7" t="n">
+      <c r="F175" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H172" s="14" t="n">
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H175" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I172" s="15" t="inlineStr">
+      <c r="I175" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="17" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B173" s="18" t="n"/>
-      <c r="C173" s="18" t="n"/>
-      <c r="D173" s="18" t="n"/>
-      <c r="E173" s="18" t="n"/>
-      <c r="F173" s="18" t="n"/>
-      <c r="G173" s="18" t="n"/>
-      <c r="H173" s="18" t="n"/>
-      <c r="I173" s="18" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="21" t="n"/>
-      <c r="B174" s="22" t="inlineStr">
+      <c r="B176" s="18" t="n"/>
+      <c r="C176" s="18" t="n"/>
+      <c r="D176" s="18" t="n"/>
+      <c r="E176" s="18" t="n"/>
+      <c r="F176" s="18" t="n"/>
+      <c r="G176" s="18" t="n"/>
+      <c r="H176" s="18" t="n"/>
+      <c r="I176" s="18" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="21" t="n"/>
+      <c r="B177" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C174" s="21" t="n"/>
-      <c r="D174" s="21" t="n"/>
-      <c r="E174" s="21" t="n"/>
-      <c r="F174" s="21" t="n"/>
-      <c r="G174" s="21" t="n"/>
-      <c r="H174" s="21" t="n"/>
-      <c r="I174" s="21" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="5" t="inlineStr"/>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="C177" s="21" t="n"/>
+      <c r="D177" s="21" t="n"/>
+      <c r="E177" s="21" t="n"/>
+      <c r="F177" s="21" t="n"/>
+      <c r="G177" s="21" t="n"/>
+      <c r="H177" s="21" t="n"/>
+      <c r="I177" s="21" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr"/>
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C175" s="5" t="n">
+      <c r="C178" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="5" t="n">
+      <c r="E178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G175" s="5" t="inlineStr">
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H175" s="12" t="n">
+      <c r="H178" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I175" s="13" t="inlineStr">
+      <c r="I178" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="16" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B176" s="2" t="n"/>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n"/>
-      <c r="E176" s="2" t="n"/>
-      <c r="F176" s="2" t="n"/>
-      <c r="G176" s="2" t="n"/>
-      <c r="H176" s="2" t="n"/>
-      <c r="I176" s="2" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="17" t="inlineStr">
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="n"/>
+      <c r="F179" s="2" t="n"/>
+      <c r="G179" s="2" t="n"/>
+      <c r="H179" s="2" t="n"/>
+      <c r="I179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B177" s="18" t="n"/>
-      <c r="C177" s="18" t="n"/>
-      <c r="D177" s="18" t="n"/>
-      <c r="E177" s="18" t="n"/>
-      <c r="F177" s="18" t="n"/>
-      <c r="G177" s="18" t="n"/>
-      <c r="H177" s="18" t="n"/>
-      <c r="I177" s="18" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="21" t="n"/>
-      <c r="B178" s="22" t="inlineStr">
+      <c r="B180" s="18" t="n"/>
+      <c r="C180" s="18" t="n"/>
+      <c r="D180" s="18" t="n"/>
+      <c r="E180" s="18" t="n"/>
+      <c r="F180" s="18" t="n"/>
+      <c r="G180" s="18" t="n"/>
+      <c r="H180" s="18" t="n"/>
+      <c r="I180" s="18" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="21" t="n"/>
+      <c r="B181" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C178" s="21" t="n"/>
-      <c r="D178" s="21" t="n"/>
-      <c r="E178" s="21" t="n"/>
-      <c r="F178" s="21" t="n"/>
-      <c r="G178" s="21" t="n"/>
-      <c r="H178" s="21" t="n"/>
-      <c r="I178" s="21" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="inlineStr"/>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="C181" s="21" t="n"/>
+      <c r="D181" s="21" t="n"/>
+      <c r="E181" s="21" t="n"/>
+      <c r="F181" s="21" t="n"/>
+      <c r="G181" s="21" t="n"/>
+      <c r="H181" s="21" t="n"/>
+      <c r="I181" s="21" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr"/>
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C179" s="5" t="n">
+      <c r="C182" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n">
+      <c r="E182" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F179" s="5" t="n">
+      <c r="F182" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G179" s="5" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H179" s="12" t="n">
+      <c r="H182" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I179" s="13" t="inlineStr">
+      <c r="I182" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="115">
-    <mergeCell ref="B135:I135"/>
+  <mergeCells count="117">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B144:I144"/>
+    <mergeCell ref="A172:I172"/>
     <mergeCell ref="B54:I54"/>
-    <mergeCell ref="A108:I108"/>
-    <mergeCell ref="B125:I125"/>
+    <mergeCell ref="B72:I72"/>
     <mergeCell ref="A56:I56"/>
+    <mergeCell ref="B134:I134"/>
     <mergeCell ref="A101:I101"/>
-    <mergeCell ref="B167:I167"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="B120:I120"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="B181:I181"/>
     <mergeCell ref="A62:I62"/>
-    <mergeCell ref="B88:I88"/>
     <mergeCell ref="A68:I68"/>
+    <mergeCell ref="B147:I147"/>
     <mergeCell ref="A111:I111"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
@@ -9519,34 +9661,35 @@
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="A153:I153"/>
-    <mergeCell ref="B113:I113"/>
+    <mergeCell ref="B173:I173"/>
     <mergeCell ref="A137:I137"/>
-    <mergeCell ref="B109:I109"/>
-    <mergeCell ref="A177:I177"/>
     <mergeCell ref="B141:I141"/>
+    <mergeCell ref="A136:I136"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A179:I179"/>
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="A71:I71"/>
     <mergeCell ref="B86:I86"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A116:I116"/>
-    <mergeCell ref="A91:I91"/>
     <mergeCell ref="A165:I165"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="A180:I180"/>
     <mergeCell ref="A115:I115"/>
-    <mergeCell ref="B178:I178"/>
-    <mergeCell ref="A173:I173"/>
     <mergeCell ref="B128:I128"/>
-    <mergeCell ref="A166:I166"/>
+    <mergeCell ref="A143:I143"/>
+    <mergeCell ref="B177:I177"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="A94:I94"/>
+    <mergeCell ref="A168:I168"/>
     <mergeCell ref="B63:I63"/>
     <mergeCell ref="B154:I154"/>
     <mergeCell ref="B163:I163"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="B138:I138"/>
+    <mergeCell ref="B91:I91"/>
     <mergeCell ref="A133:I133"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="B27:I27"/>
@@ -9554,26 +9697,29 @@
     <mergeCell ref="A104:I104"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="B151:I151"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A147:I147"/>
+    <mergeCell ref="B166:I166"/>
     <mergeCell ref="A156:I156"/>
+    <mergeCell ref="B116:I116"/>
     <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B174:I174"/>
+    <mergeCell ref="B112:I112"/>
     <mergeCell ref="A130:I130"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B95:I95"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="A110:I110"/>
     <mergeCell ref="B160:I160"/>
-    <mergeCell ref="A146:I146"/>
     <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A149:I149"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B71:I71"/>
     <mergeCell ref="B131:I131"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="A47:I47"/>
@@ -9582,26 +9728,24 @@
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="A159:I159"/>
     <mergeCell ref="A122:I122"/>
+    <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="B170:I170"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="B148:I148"/>
+    <mergeCell ref="A125:I125"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A134:I134"/>
     <mergeCell ref="B157:I157"/>
-    <mergeCell ref="A112:I112"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A127:I127"/>
-    <mergeCell ref="B99:I99"/>
     <mergeCell ref="A176:I176"/>
-    <mergeCell ref="B92:I92"/>
-    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="A114:I114"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A73:I73"/>
     <mergeCell ref="A107:I107"/>
     <mergeCell ref="B6:I6"/>
+    <mergeCell ref="A88:I88"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="A162:I162"/>
+    <mergeCell ref="B126:I126"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -9614,8 +9758,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId15"/>
@@ -9628,44 +9772,45 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9677,7 +9822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10389,24 +10534,61 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="532" customHeight="1">
+    <row r="19" ht="210" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>Best Time to Buy and Sell Stock</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int maxProfit(int[] prices) {
+    int min = Integer.MAX_VALUE;
+    int profit = 0;
+    int result = 0;
+    for(int i=0;i&lt;prices.length;i++){
+        min = Math.min(prices[i],min);
+        profit = prices[i] - min;
+        if(result&lt;profit){
+            result = profit;
+        }
+    }
+    return result;   
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="532" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -10440,24 +10622,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="532" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="532" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;136 - Single Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/single-number/"&gt;single-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a &lt;strong&gt;non-empty&lt;/strong&gt;&amp;nbsp;array of integers &lt;code&gt;nums&lt;/code&gt;, every element appears &lt;em&gt;twice&lt;/em&gt; except for one. Find that single one.&lt;/p&gt;
 &lt;p&gt;You must&amp;nbsp;implement a solution with a linear runtime complexity and use&amp;nbsp;only constant&amp;nbsp;extra space.&lt;/p&gt;
@@ -10488,24 +10670,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="238" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="238" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -10527,24 +10709,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="560" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="560" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -10590,24 +10772,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="560" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="560" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Linked List Cycle II</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>142</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -10660,24 +10842,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="210" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="210" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Find Peak Element</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>162</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int findPeakElement(int[] nums) {
@@ -10697,24 +10879,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="266" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="266" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>167</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] twoSum(int[] numbers, int target) {
@@ -10738,24 +10920,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="294" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="294" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -10781,24 +10963,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="392" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="392" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>206</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -10831,24 +11013,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="238" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="238" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -10870,24 +11052,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="238" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="238" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>219</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -10909,24 +11091,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="322" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="322" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Sliding Window Maximum</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>239</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] maxSlidingWindow(int[] nums, int k) {
@@ -10950,24 +11132,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="392" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="392" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -11000,24 +11182,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="182" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="182" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -11035,24 +11217,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="476" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="476" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Find the Duplicate Number</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>287</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int findDuplicate(int[] nums) {
@@ -11090,24 +11272,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="308" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="308" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -11131,24 +11313,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="420" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="420" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>304</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -11180,24 +11362,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="308" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="308" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Find All Duplicates in an Array</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>442</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public List&lt;Integer&gt; findDuplicates(int[] nums) {
@@ -11224,24 +11406,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="322" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="322" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>503</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElements(int[] nums) {
@@ -11266,24 +11448,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="546" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="546" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11321,24 +11503,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="182" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="182" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -11356,24 +11538,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="546" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="546" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11417,24 +11599,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="196" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="196" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -11453,24 +11635,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="462" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="462" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -11500,24 +11682,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="518" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="518" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>class Solution {
  class UniounFind{
@@ -11557,24 +11739,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="252" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="252" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>739</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -11594,24 +11776,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="378" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="378" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -11643,24 +11825,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="294" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="294" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11686,24 +11868,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="560" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="560" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -11739,24 +11921,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="294" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="294" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -11779,24 +11961,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="224" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="224" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -11817,24 +11999,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="420" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="420" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -11869,24 +12051,24 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="378" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52" ht="378" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -11918,24 +12100,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="266" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53" ht="266" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -11959,24 +12141,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="350" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="350" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -12006,24 +12188,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="238" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="238" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -12045,24 +12227,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="308" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="308" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -12089,24 +12271,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="280" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="280" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -12129,24 +12311,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="448" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="448" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -12181,24 +12363,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="378" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="378" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -12230,24 +12412,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="266" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="266" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -12271,24 +12453,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="560" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="560" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -12341,24 +12523,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="196" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="196" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>3811</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -12376,24 +12558,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="238" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="238" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -12413,24 +12595,24 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="252" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="252" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -12453,24 +12635,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="140" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="140" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>4245</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -12484,24 +12666,24 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="294" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="294" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -12527,24 +12709,24 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="252" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="67" ht="252" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C67" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -12642,7 +12824,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>24</v>
@@ -12651,7 +12833,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -12680,7 +12862,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>24</v>
@@ -12689,7 +12871,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1568,19 +1568,19 @@
         <v>0</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>44.9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
@@ -1594,13 +1594,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="9" t="inlineStr"/>
       <c r="H38" s="9" t="inlineStr"/>
@@ -2266,13 +2266,13 @@
         <v>36</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E64" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G64" s="11" t="inlineStr"/>
       <c r="H64" s="11" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5552,11 +5552,61 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>547</v>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Number of Provinces</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Depth-First Search</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Breadth-First Search, Union-Find, Graph Theory</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J68" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" s="14" t="n">
+        <v>46287.65729166667</v>
+      </c>
+      <c r="L68" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F67">
+  <conditionalFormatting sqref="F5:F68">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5631,6 +5681,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5642,7 +5693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8055,7 +8106,7 @@
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
         </is>
       </c>
       <c r="B110" s="2" t="n"/>
@@ -8070,7 +8121,7 @@
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
         </is>
       </c>
       <c r="B111" s="18" t="n"/>
@@ -8086,7 +8137,7 @@
       <c r="A112" s="19" t="n"/>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
+          <t>Medium (Medium) — 2 problem(s)</t>
         </is>
       </c>
       <c r="C112" s="19" t="n"/>
@@ -8101,1527 +8152,1562 @@
       <c r="A113" s="5" t="inlineStr"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
+          <t>Number of Provinces</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>547</v>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>46287.65729166667</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr"/>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C114" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="5" t="n">
+      <c r="E114" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H113" s="12" t="n">
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="n">
         <v>46287.51434027778</v>
       </c>
-      <c r="I113" s="13" t="inlineStr">
+      <c r="I114" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="16" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B114" s="2" t="n"/>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2" t="n"/>
-      <c r="I114" s="2" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="17" t="inlineStr">
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B115" s="18" t="n"/>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="18" t="n"/>
-      <c r="E115" s="18" t="n"/>
-      <c r="F115" s="18" t="n"/>
-      <c r="G115" s="18" t="n"/>
-      <c r="H115" s="18" t="n"/>
-      <c r="I115" s="18" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="21" t="n"/>
-      <c r="B116" s="22" t="inlineStr">
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="n"/>
+      <c r="B117" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C116" s="21" t="n"/>
-      <c r="D116" s="21" t="n"/>
-      <c r="E116" s="21" t="n"/>
-      <c r="F116" s="21" t="n"/>
-      <c r="G116" s="21" t="n"/>
-      <c r="H116" s="21" t="n"/>
-      <c r="I116" s="21" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr"/>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="C117" s="21" t="n"/>
+      <c r="D117" s="21" t="n"/>
+      <c r="E117" s="21" t="n"/>
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr"/>
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C118" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="5" t="n">
+      <c r="E118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H117" s="12" t="n">
+      <c r="H118" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I117" s="13" t="inlineStr">
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="17" t="inlineStr">
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
-      <c r="B119" s="18" t="n"/>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="18" t="n"/>
-      <c r="E119" s="18" t="n"/>
-      <c r="F119" s="18" t="n"/>
-      <c r="G119" s="18" t="n"/>
-      <c r="H119" s="18" t="n"/>
-      <c r="I119" s="18" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="23" t="n"/>
-      <c r="B120" s="24" t="inlineStr">
+      <c r="B120" s="18" t="n"/>
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="18" t="n"/>
+      <c r="E120" s="18" t="n"/>
+      <c r="F120" s="18" t="n"/>
+      <c r="G120" s="18" t="n"/>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="23" t="n"/>
+      <c r="B121" s="24" t="inlineStr">
         <is>
           <t>High (Hard) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C120" s="23" t="n"/>
-      <c r="D120" s="23" t="n"/>
-      <c r="E120" s="23" t="n"/>
-      <c r="F120" s="23" t="n"/>
-      <c r="G120" s="23" t="n"/>
-      <c r="H120" s="23" t="n"/>
-      <c r="I120" s="23" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr"/>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="C121" s="23" t="n"/>
+      <c r="D121" s="23" t="n"/>
+      <c r="E121" s="23" t="n"/>
+      <c r="F121" s="23" t="n"/>
+      <c r="G121" s="23" t="n"/>
+      <c r="H121" s="23" t="n"/>
+      <c r="I121" s="23" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr"/>
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>Merge k Sorted Lists</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C122" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
+      <c r="E122" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F122" s="5" t="n">
         <v>45.9</v>
       </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="n">
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="n">
         <v>46286.43949074074</v>
       </c>
-      <c r="I121" s="13" t="inlineStr">
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="17" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="18" t="n"/>
-      <c r="D122" s="18" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
-      <c r="G122" s="18" t="n"/>
-      <c r="H122" s="18" t="n"/>
-      <c r="I122" s="18" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="19" t="n"/>
-      <c r="B123" s="20" t="inlineStr">
+      <c r="B123" s="18" t="n"/>
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
+      <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="19" t="n"/>
+      <c r="B124" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C123" s="19" t="n"/>
-      <c r="D123" s="19" t="n"/>
-      <c r="E123" s="19" t="n"/>
-      <c r="F123" s="19" t="n"/>
-      <c r="G123" s="19" t="n"/>
-      <c r="H123" s="19" t="n"/>
-      <c r="I123" s="19" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr"/>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="C124" s="19" t="n"/>
+      <c r="D124" s="19" t="n"/>
+      <c r="E124" s="19" t="n"/>
+      <c r="F124" s="19" t="n"/>
+      <c r="G124" s="19" t="n"/>
+      <c r="H124" s="19" t="n"/>
+      <c r="I124" s="19" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr"/>
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>Reverse Linked List II</t>
         </is>
       </c>
-      <c r="C124" s="5" t="n">
+      <c r="C125" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="5" t="n">
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
         <v>43.4</v>
       </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H124" s="12" t="n">
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="n">
         <v>46275.41266203704</v>
       </c>
-      <c r="I124" s="13" t="inlineStr">
+      <c r="I125" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="17" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B125" s="18" t="n"/>
-      <c r="C125" s="18" t="n"/>
-      <c r="D125" s="18" t="n"/>
-      <c r="E125" s="18" t="n"/>
-      <c r="F125" s="18" t="n"/>
-      <c r="G125" s="18" t="n"/>
-      <c r="H125" s="18" t="n"/>
-      <c r="I125" s="18" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="21" t="n"/>
-      <c r="B126" s="22" t="inlineStr">
+      <c r="B126" s="18" t="n"/>
+      <c r="C126" s="18" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="18" t="n"/>
+      <c r="G126" s="18" t="n"/>
+      <c r="H126" s="18" t="n"/>
+      <c r="I126" s="18" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="n"/>
+      <c r="B127" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C126" s="21" t="n"/>
-      <c r="D126" s="21" t="n"/>
-      <c r="E126" s="21" t="n"/>
-      <c r="F126" s="21" t="n"/>
-      <c r="G126" s="21" t="n"/>
-      <c r="H126" s="21" t="n"/>
-      <c r="I126" s="21" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr"/>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="C127" s="21" t="n"/>
+      <c r="D127" s="21" t="n"/>
+      <c r="E127" s="21" t="n"/>
+      <c r="F127" s="21" t="n"/>
+      <c r="G127" s="21" t="n"/>
+      <c r="H127" s="21" t="n"/>
+      <c r="I127" s="21" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr"/>
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C127" s="5" t="n">
+      <c r="C128" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="5" t="n">
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G127" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="n">
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I127" s="13" t="inlineStr">
+      <c r="I128" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="19" t="n"/>
-      <c r="B128" s="20" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="19" t="n"/>
+      <c r="B129" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C128" s="19" t="n"/>
-      <c r="D128" s="19" t="n"/>
-      <c r="E128" s="19" t="n"/>
-      <c r="F128" s="19" t="n"/>
-      <c r="G128" s="19" t="n"/>
-      <c r="H128" s="19" t="n"/>
-      <c r="I128" s="19" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr"/>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="C129" s="19" t="n"/>
+      <c r="D129" s="19" t="n"/>
+      <c r="E129" s="19" t="n"/>
+      <c r="F129" s="19" t="n"/>
+      <c r="G129" s="19" t="n"/>
+      <c r="H129" s="19" t="n"/>
+      <c r="I129" s="19" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr"/>
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle II</t>
         </is>
       </c>
-      <c r="C129" s="5" t="n">
+      <c r="C130" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" s="5" t="n">
+      <c r="E130" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="G129" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="n">
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H130" s="12" t="n">
         <v>46274.44269675926</v>
       </c>
-      <c r="I129" s="13" t="inlineStr">
+      <c r="I130" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="17" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B130" s="18" t="n"/>
-      <c r="C130" s="18" t="n"/>
-      <c r="D130" s="18" t="n"/>
-      <c r="E130" s="18" t="n"/>
-      <c r="F130" s="18" t="n"/>
-      <c r="G130" s="18" t="n"/>
-      <c r="H130" s="18" t="n"/>
-      <c r="I130" s="18" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="21" t="n"/>
-      <c r="B131" s="22" t="inlineStr">
+      <c r="B131" s="18" t="n"/>
+      <c r="C131" s="18" t="n"/>
+      <c r="D131" s="18" t="n"/>
+      <c r="E131" s="18" t="n"/>
+      <c r="F131" s="18" t="n"/>
+      <c r="G131" s="18" t="n"/>
+      <c r="H131" s="18" t="n"/>
+      <c r="I131" s="18" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="21" t="n"/>
+      <c r="B132" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C131" s="21" t="n"/>
-      <c r="D131" s="21" t="n"/>
-      <c r="E131" s="21" t="n"/>
-      <c r="F131" s="21" t="n"/>
-      <c r="G131" s="21" t="n"/>
-      <c r="H131" s="21" t="n"/>
-      <c r="I131" s="21" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr"/>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="C132" s="21" t="n"/>
+      <c r="D132" s="21" t="n"/>
+      <c r="E132" s="21" t="n"/>
+      <c r="F132" s="21" t="n"/>
+      <c r="G132" s="21" t="n"/>
+      <c r="H132" s="21" t="n"/>
+      <c r="I132" s="21" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr"/>
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C132" s="5" t="n">
+      <c r="C133" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E132" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="5" t="n">
+      <c r="E133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="5" t="n">
         <v>44.2</v>
       </c>
-      <c r="G132" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H132" s="12" t="n">
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="n">
         <v>46274.48334490741</v>
       </c>
-      <c r="I132" s="13" t="inlineStr">
+      <c r="I133" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="17" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B133" s="18" t="n"/>
-      <c r="C133" s="18" t="n"/>
-      <c r="D133" s="18" t="n"/>
-      <c r="E133" s="18" t="n"/>
-      <c r="F133" s="18" t="n"/>
-      <c r="G133" s="18" t="n"/>
-      <c r="H133" s="18" t="n"/>
-      <c r="I133" s="18" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="21" t="n"/>
-      <c r="B134" s="22" t="inlineStr">
+      <c r="B134" s="18" t="n"/>
+      <c r="C134" s="18" t="n"/>
+      <c r="D134" s="18" t="n"/>
+      <c r="E134" s="18" t="n"/>
+      <c r="F134" s="18" t="n"/>
+      <c r="G134" s="18" t="n"/>
+      <c r="H134" s="18" t="n"/>
+      <c r="I134" s="18" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="n"/>
+      <c r="B135" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C134" s="21" t="n"/>
-      <c r="D134" s="21" t="n"/>
-      <c r="E134" s="21" t="n"/>
-      <c r="F134" s="21" t="n"/>
-      <c r="G134" s="21" t="n"/>
-      <c r="H134" s="21" t="n"/>
-      <c r="I134" s="21" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr"/>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="C135" s="21" t="n"/>
+      <c r="D135" s="21" t="n"/>
+      <c r="E135" s="21" t="n"/>
+      <c r="F135" s="21" t="n"/>
+      <c r="G135" s="21" t="n"/>
+      <c r="H135" s="21" t="n"/>
+      <c r="I135" s="21" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr"/>
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C135" s="5" t="n">
+      <c r="C136" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D135" s="5" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E135" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" s="5" t="n">
+      <c r="E136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G135" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H135" s="12" t="n">
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I135" s="13" t="inlineStr">
+      <c r="I136" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="16" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B136" s="2" t="n"/>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n"/>
-      <c r="E136" s="2" t="n"/>
-      <c r="F136" s="2" t="n"/>
-      <c r="G136" s="2" t="n"/>
-      <c r="H136" s="2" t="n"/>
-      <c r="I136" s="2" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="17" t="inlineStr">
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="2" t="n"/>
+      <c r="H137" s="2" t="n"/>
+      <c r="I137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B137" s="18" t="n"/>
-      <c r="C137" s="18" t="n"/>
-      <c r="D137" s="18" t="n"/>
-      <c r="E137" s="18" t="n"/>
-      <c r="F137" s="18" t="n"/>
-      <c r="G137" s="18" t="n"/>
-      <c r="H137" s="18" t="n"/>
-      <c r="I137" s="18" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="21" t="n"/>
-      <c r="B138" s="22" t="inlineStr">
+      <c r="B138" s="18" t="n"/>
+      <c r="C138" s="18" t="n"/>
+      <c r="D138" s="18" t="n"/>
+      <c r="E138" s="18" t="n"/>
+      <c r="F138" s="18" t="n"/>
+      <c r="G138" s="18" t="n"/>
+      <c r="H138" s="18" t="n"/>
+      <c r="I138" s="18" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="21" t="n"/>
+      <c r="B139" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C138" s="21" t="n"/>
-      <c r="D138" s="21" t="n"/>
-      <c r="E138" s="21" t="n"/>
-      <c r="F138" s="21" t="n"/>
-      <c r="G138" s="21" t="n"/>
-      <c r="H138" s="21" t="n"/>
-      <c r="I138" s="21" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr"/>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="C139" s="21" t="n"/>
+      <c r="D139" s="21" t="n"/>
+      <c r="E139" s="21" t="n"/>
+      <c r="F139" s="21" t="n"/>
+      <c r="G139" s="21" t="n"/>
+      <c r="H139" s="21" t="n"/>
+      <c r="I139" s="21" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr"/>
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n">
+      <c r="C140" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E139" s="5" t="n">
+      <c r="E140" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F139" s="5" t="n">
+      <c r="F140" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="n">
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="n">
         <v>46255.88138888889</v>
       </c>
-      <c r="I139" s="13" t="inlineStr">
+      <c r="I140" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="17" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B140" s="18" t="n"/>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="18" t="n"/>
-      <c r="E140" s="18" t="n"/>
-      <c r="F140" s="18" t="n"/>
-      <c r="G140" s="18" t="n"/>
-      <c r="H140" s="18" t="n"/>
-      <c r="I140" s="18" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="21" t="n"/>
-      <c r="B141" s="22" t="inlineStr">
+      <c r="B141" s="18" t="n"/>
+      <c r="C141" s="18" t="n"/>
+      <c r="D141" s="18" t="n"/>
+      <c r="E141" s="18" t="n"/>
+      <c r="F141" s="18" t="n"/>
+      <c r="G141" s="18" t="n"/>
+      <c r="H141" s="18" t="n"/>
+      <c r="I141" s="18" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="21" t="n"/>
+      <c r="B142" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C141" s="21" t="n"/>
-      <c r="D141" s="21" t="n"/>
-      <c r="E141" s="21" t="n"/>
-      <c r="F141" s="21" t="n"/>
-      <c r="G141" s="21" t="n"/>
-      <c r="H141" s="21" t="n"/>
-      <c r="I141" s="21" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr"/>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="C142" s="21" t="n"/>
+      <c r="D142" s="21" t="n"/>
+      <c r="E142" s="21" t="n"/>
+      <c r="F142" s="21" t="n"/>
+      <c r="G142" s="21" t="n"/>
+      <c r="H142" s="21" t="n"/>
+      <c r="I142" s="21" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr"/>
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C142" s="5" t="n">
+      <c r="C143" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" s="5" t="n">
+      <c r="E143" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H142" s="12" t="n">
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="n">
         <v>46240.74578703703</v>
       </c>
-      <c r="I142" s="13" t="inlineStr">
+      <c r="I143" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="17" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B143" s="18" t="n"/>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="18" t="n"/>
-      <c r="E143" s="18" t="n"/>
-      <c r="F143" s="18" t="n"/>
-      <c r="G143" s="18" t="n"/>
-      <c r="H143" s="18" t="n"/>
-      <c r="I143" s="18" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="21" t="n"/>
-      <c r="B144" s="22" t="inlineStr">
+      <c r="B144" s="18" t="n"/>
+      <c r="C144" s="18" t="n"/>
+      <c r="D144" s="18" t="n"/>
+      <c r="E144" s="18" t="n"/>
+      <c r="F144" s="18" t="n"/>
+      <c r="G144" s="18" t="n"/>
+      <c r="H144" s="18" t="n"/>
+      <c r="I144" s="18" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="21" t="n"/>
+      <c r="B145" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C144" s="21" t="n"/>
-      <c r="D144" s="21" t="n"/>
-      <c r="E144" s="21" t="n"/>
-      <c r="F144" s="21" t="n"/>
-      <c r="G144" s="21" t="n"/>
-      <c r="H144" s="21" t="n"/>
-      <c r="I144" s="21" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr"/>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="C145" s="21" t="n"/>
+      <c r="D145" s="21" t="n"/>
+      <c r="E145" s="21" t="n"/>
+      <c r="F145" s="21" t="n"/>
+      <c r="G145" s="21" t="n"/>
+      <c r="H145" s="21" t="n"/>
+      <c r="I145" s="21" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="inlineStr"/>
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C145" s="5" t="n">
+      <c r="C146" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E145" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" s="5" t="n">
+      <c r="E146" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G145" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H145" s="12" t="n">
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H146" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I145" s="13" t="inlineStr">
+      <c r="I146" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr"/>
-      <c r="B146" s="6" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="7" t="inlineStr"/>
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C146" s="7" t="n">
+      <c r="C147" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D146" s="7" t="inlineStr">
+      <c r="D147" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E146" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="7" t="n">
+      <c r="E147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="7" t="n">
         <v>42.6</v>
       </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H146" s="14" t="n">
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H147" s="14" t="n">
         <v>46273.3956712963</v>
       </c>
-      <c r="I146" s="15" t="inlineStr">
+      <c r="I147" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="19" t="n"/>
-      <c r="B147" s="20" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="19" t="n"/>
+      <c r="B148" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C147" s="19" t="n"/>
-      <c r="D147" s="19" t="n"/>
-      <c r="E147" s="19" t="n"/>
-      <c r="F147" s="19" t="n"/>
-      <c r="G147" s="19" t="n"/>
-      <c r="H147" s="19" t="n"/>
-      <c r="I147" s="19" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="inlineStr"/>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="C148" s="19" t="n"/>
+      <c r="D148" s="19" t="n"/>
+      <c r="E148" s="19" t="n"/>
+      <c r="F148" s="19" t="n"/>
+      <c r="G148" s="19" t="n"/>
+      <c r="H148" s="19" t="n"/>
+      <c r="I148" s="19" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="inlineStr"/>
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C148" s="5" t="n">
+      <c r="C149" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D148" s="5" t="inlineStr">
+      <c r="D149" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" s="5" t="n">
+      <c r="E149" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G148" s="5" t="inlineStr">
+      <c r="G149" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H148" s="12" t="n">
+      <c r="H149" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I148" s="13" t="inlineStr">
+      <c r="I149" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="16" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B149" s="2" t="n"/>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" s="2" t="n"/>
-      <c r="F149" s="2" t="n"/>
-      <c r="G149" s="2" t="n"/>
-      <c r="H149" s="2" t="n"/>
-      <c r="I149" s="2" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="17" t="inlineStr">
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
+      <c r="G150" s="2" t="n"/>
+      <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B150" s="18" t="n"/>
-      <c r="C150" s="18" t="n"/>
-      <c r="D150" s="18" t="n"/>
-      <c r="E150" s="18" t="n"/>
-      <c r="F150" s="18" t="n"/>
-      <c r="G150" s="18" t="n"/>
-      <c r="H150" s="18" t="n"/>
-      <c r="I150" s="18" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="21" t="n"/>
-      <c r="B151" s="22" t="inlineStr">
+      <c r="B151" s="18" t="n"/>
+      <c r="C151" s="18" t="n"/>
+      <c r="D151" s="18" t="n"/>
+      <c r="E151" s="18" t="n"/>
+      <c r="F151" s="18" t="n"/>
+      <c r="G151" s="18" t="n"/>
+      <c r="H151" s="18" t="n"/>
+      <c r="I151" s="18" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="21" t="n"/>
+      <c r="B152" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C151" s="21" t="n"/>
-      <c r="D151" s="21" t="n"/>
-      <c r="E151" s="21" t="n"/>
-      <c r="F151" s="21" t="n"/>
-      <c r="G151" s="21" t="n"/>
-      <c r="H151" s="21" t="n"/>
-      <c r="I151" s="21" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="5" t="inlineStr"/>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="C152" s="21" t="n"/>
+      <c r="D152" s="21" t="n"/>
+      <c r="E152" s="21" t="n"/>
+      <c r="F152" s="21" t="n"/>
+      <c r="G152" s="21" t="n"/>
+      <c r="H152" s="21" t="n"/>
+      <c r="I152" s="21" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="5" t="inlineStr"/>
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C152" s="5" t="n">
+      <c r="C153" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D153" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F152" s="5" t="n">
+      <c r="E153" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G152" s="5" t="inlineStr">
+      <c r="G153" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H152" s="12" t="n">
+      <c r="H153" s="12" t="n">
         <v>46241.78204861111</v>
       </c>
-      <c r="I152" s="13" t="inlineStr">
+      <c r="I153" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="17" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B153" s="18" t="n"/>
-      <c r="C153" s="18" t="n"/>
-      <c r="D153" s="18" t="n"/>
-      <c r="E153" s="18" t="n"/>
-      <c r="F153" s="18" t="n"/>
-      <c r="G153" s="18" t="n"/>
-      <c r="H153" s="18" t="n"/>
-      <c r="I153" s="18" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="19" t="n"/>
-      <c r="B154" s="20" t="inlineStr">
+      <c r="B154" s="18" t="n"/>
+      <c r="C154" s="18" t="n"/>
+      <c r="D154" s="18" t="n"/>
+      <c r="E154" s="18" t="n"/>
+      <c r="F154" s="18" t="n"/>
+      <c r="G154" s="18" t="n"/>
+      <c r="H154" s="18" t="n"/>
+      <c r="I154" s="18" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="19" t="n"/>
+      <c r="B155" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C154" s="19" t="n"/>
-      <c r="D154" s="19" t="n"/>
-      <c r="E154" s="19" t="n"/>
-      <c r="F154" s="19" t="n"/>
-      <c r="G154" s="19" t="n"/>
-      <c r="H154" s="19" t="n"/>
-      <c r="I154" s="19" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr"/>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="C155" s="19" t="n"/>
+      <c r="D155" s="19" t="n"/>
+      <c r="E155" s="19" t="n"/>
+      <c r="F155" s="19" t="n"/>
+      <c r="G155" s="19" t="n"/>
+      <c r="H155" s="19" t="n"/>
+      <c r="I155" s="19" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="5" t="inlineStr"/>
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
-      <c r="C155" s="5" t="n">
+      <c r="C156" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D156" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="5" t="n">
+      <c r="E156" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="F155" s="5" t="n">
+      <c r="F156" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G155" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H155" s="12" t="n">
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H156" s="12" t="n">
         <v>46253.82314814815</v>
       </c>
-      <c r="I155" s="13" t="inlineStr">
+      <c r="I156" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="17" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B156" s="18" t="n"/>
-      <c r="C156" s="18" t="n"/>
-      <c r="D156" s="18" t="n"/>
-      <c r="E156" s="18" t="n"/>
-      <c r="F156" s="18" t="n"/>
-      <c r="G156" s="18" t="n"/>
-      <c r="H156" s="18" t="n"/>
-      <c r="I156" s="18" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="21" t="n"/>
-      <c r="B157" s="22" t="inlineStr">
+      <c r="B157" s="18" t="n"/>
+      <c r="C157" s="18" t="n"/>
+      <c r="D157" s="18" t="n"/>
+      <c r="E157" s="18" t="n"/>
+      <c r="F157" s="18" t="n"/>
+      <c r="G157" s="18" t="n"/>
+      <c r="H157" s="18" t="n"/>
+      <c r="I157" s="18" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="21" t="n"/>
+      <c r="B158" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C157" s="21" t="n"/>
-      <c r="D157" s="21" t="n"/>
-      <c r="E157" s="21" t="n"/>
-      <c r="F157" s="21" t="n"/>
-      <c r="G157" s="21" t="n"/>
-      <c r="H157" s="21" t="n"/>
-      <c r="I157" s="21" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="5" t="inlineStr"/>
-      <c r="B158" s="4" t="inlineStr">
+      <c r="C158" s="21" t="n"/>
+      <c r="D158" s="21" t="n"/>
+      <c r="E158" s="21" t="n"/>
+      <c r="F158" s="21" t="n"/>
+      <c r="G158" s="21" t="n"/>
+      <c r="H158" s="21" t="n"/>
+      <c r="I158" s="21" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr"/>
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C158" s="5" t="n">
+      <c r="C159" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D158" s="5" t="inlineStr">
+      <c r="D159" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E158" s="5" t="n">
+      <c r="E159" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F158" s="5" t="n">
+      <c r="F159" s="5" t="n">
         <v>44.6</v>
       </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H158" s="12" t="n">
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H159" s="12" t="n">
         <v>46243.94849537037</v>
       </c>
-      <c r="I158" s="13" t="inlineStr">
+      <c r="I159" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="17" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B159" s="18" t="n"/>
-      <c r="C159" s="18" t="n"/>
-      <c r="D159" s="18" t="n"/>
-      <c r="E159" s="18" t="n"/>
-      <c r="F159" s="18" t="n"/>
-      <c r="G159" s="18" t="n"/>
-      <c r="H159" s="18" t="n"/>
-      <c r="I159" s="18" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="21" t="n"/>
-      <c r="B160" s="22" t="inlineStr">
+      <c r="B160" s="18" t="n"/>
+      <c r="C160" s="18" t="n"/>
+      <c r="D160" s="18" t="n"/>
+      <c r="E160" s="18" t="n"/>
+      <c r="F160" s="18" t="n"/>
+      <c r="G160" s="18" t="n"/>
+      <c r="H160" s="18" t="n"/>
+      <c r="I160" s="18" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="21" t="n"/>
+      <c r="B161" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C160" s="21" t="n"/>
-      <c r="D160" s="21" t="n"/>
-      <c r="E160" s="21" t="n"/>
-      <c r="F160" s="21" t="n"/>
-      <c r="G160" s="21" t="n"/>
-      <c r="H160" s="21" t="n"/>
-      <c r="I160" s="21" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr"/>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="C161" s="21" t="n"/>
+      <c r="D161" s="21" t="n"/>
+      <c r="E161" s="21" t="n"/>
+      <c r="F161" s="21" t="n"/>
+      <c r="G161" s="21" t="n"/>
+      <c r="H161" s="21" t="n"/>
+      <c r="I161" s="21" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="inlineStr"/>
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C161" s="5" t="n">
+      <c r="C162" s="5" t="n">
         <v>3811</v>
       </c>
-      <c r="D161" s="5" t="inlineStr">
+      <c r="D162" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E161" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" s="5" t="n">
+      <c r="E162" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="5" t="n">
         <v>44.1</v>
       </c>
-      <c r="G161" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H161" s="12" t="n">
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H162" s="12" t="n">
         <v>46285.42987268518</v>
       </c>
-      <c r="I161" s="13" t="inlineStr">
+      <c r="I162" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="17" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B162" s="18" t="n"/>
-      <c r="C162" s="18" t="n"/>
-      <c r="D162" s="18" t="n"/>
-      <c r="E162" s="18" t="n"/>
-      <c r="F162" s="18" t="n"/>
-      <c r="G162" s="18" t="n"/>
-      <c r="H162" s="18" t="n"/>
-      <c r="I162" s="18" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="21" t="n"/>
-      <c r="B163" s="22" t="inlineStr">
+      <c r="B163" s="18" t="n"/>
+      <c r="C163" s="18" t="n"/>
+      <c r="D163" s="18" t="n"/>
+      <c r="E163" s="18" t="n"/>
+      <c r="F163" s="18" t="n"/>
+      <c r="G163" s="18" t="n"/>
+      <c r="H163" s="18" t="n"/>
+      <c r="I163" s="18" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="21" t="n"/>
+      <c r="B164" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C163" s="21" t="n"/>
-      <c r="D163" s="21" t="n"/>
-      <c r="E163" s="21" t="n"/>
-      <c r="F163" s="21" t="n"/>
-      <c r="G163" s="21" t="n"/>
-      <c r="H163" s="21" t="n"/>
-      <c r="I163" s="21" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="5" t="inlineStr"/>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="C164" s="21" t="n"/>
+      <c r="D164" s="21" t="n"/>
+      <c r="E164" s="21" t="n"/>
+      <c r="F164" s="21" t="n"/>
+      <c r="G164" s="21" t="n"/>
+      <c r="H164" s="21" t="n"/>
+      <c r="I164" s="21" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="inlineStr"/>
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C164" s="5" t="n">
+      <c r="C165" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D164" s="5" t="inlineStr">
+      <c r="D165" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E164" s="5" t="n">
+      <c r="E165" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F164" s="5" t="n">
+      <c r="F165" s="5" t="n">
         <v>45.3</v>
       </c>
-      <c r="G164" s="5" t="inlineStr">
+      <c r="G165" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H164" s="12" t="n">
+      <c r="H165" s="12" t="n">
         <v>46243.9169675926</v>
       </c>
-      <c r="I164" s="13" t="inlineStr">
+      <c r="I165" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="17" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B165" s="18" t="n"/>
-      <c r="C165" s="18" t="n"/>
-      <c r="D165" s="18" t="n"/>
-      <c r="E165" s="18" t="n"/>
-      <c r="F165" s="18" t="n"/>
-      <c r="G165" s="18" t="n"/>
-      <c r="H165" s="18" t="n"/>
-      <c r="I165" s="18" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="21" t="n"/>
-      <c r="B166" s="22" t="inlineStr">
+      <c r="B166" s="18" t="n"/>
+      <c r="C166" s="18" t="n"/>
+      <c r="D166" s="18" t="n"/>
+      <c r="E166" s="18" t="n"/>
+      <c r="F166" s="18" t="n"/>
+      <c r="G166" s="18" t="n"/>
+      <c r="H166" s="18" t="n"/>
+      <c r="I166" s="18" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="21" t="n"/>
+      <c r="B167" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C166" s="21" t="n"/>
-      <c r="D166" s="21" t="n"/>
-      <c r="E166" s="21" t="n"/>
-      <c r="F166" s="21" t="n"/>
-      <c r="G166" s="21" t="n"/>
-      <c r="H166" s="21" t="n"/>
-      <c r="I166" s="21" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr"/>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="C167" s="21" t="n"/>
+      <c r="D167" s="21" t="n"/>
+      <c r="E167" s="21" t="n"/>
+      <c r="F167" s="21" t="n"/>
+      <c r="G167" s="21" t="n"/>
+      <c r="H167" s="21" t="n"/>
+      <c r="I167" s="21" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="inlineStr"/>
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C167" s="5" t="n">
+      <c r="C168" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="D168" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E167" s="5" t="n">
+      <c r="E168" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F167" s="5" t="n">
+      <c r="F168" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G167" s="5" t="inlineStr">
+      <c r="G168" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H167" s="12" t="n">
+      <c r="H168" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I167" s="13" t="inlineStr">
+      <c r="I168" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="16" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B168" s="2" t="n"/>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n"/>
-      <c r="E168" s="2" t="n"/>
-      <c r="F168" s="2" t="n"/>
-      <c r="G168" s="2" t="n"/>
-      <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="17" t="inlineStr">
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="2" t="n"/>
+      <c r="I169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B169" s="18" t="n"/>
-      <c r="C169" s="18" t="n"/>
-      <c r="D169" s="18" t="n"/>
-      <c r="E169" s="18" t="n"/>
-      <c r="F169" s="18" t="n"/>
-      <c r="G169" s="18" t="n"/>
-      <c r="H169" s="18" t="n"/>
-      <c r="I169" s="18" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="21" t="n"/>
-      <c r="B170" s="22" t="inlineStr">
+      <c r="B170" s="18" t="n"/>
+      <c r="C170" s="18" t="n"/>
+      <c r="D170" s="18" t="n"/>
+      <c r="E170" s="18" t="n"/>
+      <c r="F170" s="18" t="n"/>
+      <c r="G170" s="18" t="n"/>
+      <c r="H170" s="18" t="n"/>
+      <c r="I170" s="18" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="21" t="n"/>
+      <c r="B171" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C170" s="21" t="n"/>
-      <c r="D170" s="21" t="n"/>
-      <c r="E170" s="21" t="n"/>
-      <c r="F170" s="21" t="n"/>
-      <c r="G170" s="21" t="n"/>
-      <c r="H170" s="21" t="n"/>
-      <c r="I170" s="21" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr"/>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="C171" s="21" t="n"/>
+      <c r="D171" s="21" t="n"/>
+      <c r="E171" s="21" t="n"/>
+      <c r="F171" s="21" t="n"/>
+      <c r="G171" s="21" t="n"/>
+      <c r="H171" s="21" t="n"/>
+      <c r="I171" s="21" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="inlineStr"/>
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C171" s="5" t="n">
+      <c r="C172" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D172" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="5" t="n">
+      <c r="E172" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="n">
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H172" s="12" t="n">
         <v>46248.99621527778</v>
       </c>
-      <c r="I171" s="13" t="inlineStr">
+      <c r="I172" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="17" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B172" s="18" t="n"/>
-      <c r="C172" s="18" t="n"/>
-      <c r="D172" s="18" t="n"/>
-      <c r="E172" s="18" t="n"/>
-      <c r="F172" s="18" t="n"/>
-      <c r="G172" s="18" t="n"/>
-      <c r="H172" s="18" t="n"/>
-      <c r="I172" s="18" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="21" t="n"/>
-      <c r="B173" s="22" t="inlineStr">
+      <c r="B173" s="18" t="n"/>
+      <c r="C173" s="18" t="n"/>
+      <c r="D173" s="18" t="n"/>
+      <c r="E173" s="18" t="n"/>
+      <c r="F173" s="18" t="n"/>
+      <c r="G173" s="18" t="n"/>
+      <c r="H173" s="18" t="n"/>
+      <c r="I173" s="18" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="21" t="n"/>
+      <c r="B174" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C173" s="21" t="n"/>
-      <c r="D173" s="21" t="n"/>
-      <c r="E173" s="21" t="n"/>
-      <c r="F173" s="21" t="n"/>
-      <c r="G173" s="21" t="n"/>
-      <c r="H173" s="21" t="n"/>
-      <c r="I173" s="21" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr"/>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="C174" s="21" t="n"/>
+      <c r="D174" s="21" t="n"/>
+      <c r="E174" s="21" t="n"/>
+      <c r="F174" s="21" t="n"/>
+      <c r="G174" s="21" t="n"/>
+      <c r="H174" s="21" t="n"/>
+      <c r="I174" s="21" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="inlineStr"/>
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C174" s="5" t="n">
+      <c r="C175" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D174" s="5" t="inlineStr">
+      <c r="D175" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E174" s="5" t="n">
+      <c r="E175" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F174" s="5" t="n">
+      <c r="F175" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G174" s="5" t="inlineStr">
+      <c r="G175" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H174" s="12" t="n">
+      <c r="H175" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I174" s="13" t="inlineStr">
+      <c r="I175" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="7" t="inlineStr"/>
-      <c r="B175" s="6" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr"/>
+      <c r="B176" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C175" s="7" t="n">
+      <c r="C176" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D175" s="7" t="inlineStr">
+      <c r="D176" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E175" s="7" t="n">
+      <c r="E176" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F175" s="7" t="n">
+      <c r="F176" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H175" s="14" t="n">
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H176" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I175" s="15" t="inlineStr">
+      <c r="I176" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="17" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B176" s="18" t="n"/>
-      <c r="C176" s="18" t="n"/>
-      <c r="D176" s="18" t="n"/>
-      <c r="E176" s="18" t="n"/>
-      <c r="F176" s="18" t="n"/>
-      <c r="G176" s="18" t="n"/>
-      <c r="H176" s="18" t="n"/>
-      <c r="I176" s="18" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="21" t="n"/>
-      <c r="B177" s="22" t="inlineStr">
+      <c r="B177" s="18" t="n"/>
+      <c r="C177" s="18" t="n"/>
+      <c r="D177" s="18" t="n"/>
+      <c r="E177" s="18" t="n"/>
+      <c r="F177" s="18" t="n"/>
+      <c r="G177" s="18" t="n"/>
+      <c r="H177" s="18" t="n"/>
+      <c r="I177" s="18" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="21" t="n"/>
+      <c r="B178" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C177" s="21" t="n"/>
-      <c r="D177" s="21" t="n"/>
-      <c r="E177" s="21" t="n"/>
-      <c r="F177" s="21" t="n"/>
-      <c r="G177" s="21" t="n"/>
-      <c r="H177" s="21" t="n"/>
-      <c r="I177" s="21" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr"/>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="C178" s="21" t="n"/>
+      <c r="D178" s="21" t="n"/>
+      <c r="E178" s="21" t="n"/>
+      <c r="F178" s="21" t="n"/>
+      <c r="G178" s="21" t="n"/>
+      <c r="H178" s="21" t="n"/>
+      <c r="I178" s="21" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr"/>
+      <c r="B179" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C178" s="5" t="n">
+      <c r="C179" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E178" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="5" t="n">
+      <c r="E179" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G178" s="5" t="inlineStr">
+      <c r="G179" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H178" s="12" t="n">
+      <c r="H179" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I178" s="13" t="inlineStr">
+      <c r="I179" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="16" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B179" s="2" t="n"/>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n"/>
-      <c r="E179" s="2" t="n"/>
-      <c r="F179" s="2" t="n"/>
-      <c r="G179" s="2" t="n"/>
-      <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="17" t="inlineStr">
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B180" s="18" t="n"/>
-      <c r="C180" s="18" t="n"/>
-      <c r="D180" s="18" t="n"/>
-      <c r="E180" s="18" t="n"/>
-      <c r="F180" s="18" t="n"/>
-      <c r="G180" s="18" t="n"/>
-      <c r="H180" s="18" t="n"/>
-      <c r="I180" s="18" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="21" t="n"/>
-      <c r="B181" s="22" t="inlineStr">
+      <c r="B181" s="18" t="n"/>
+      <c r="C181" s="18" t="n"/>
+      <c r="D181" s="18" t="n"/>
+      <c r="E181" s="18" t="n"/>
+      <c r="F181" s="18" t="n"/>
+      <c r="G181" s="18" t="n"/>
+      <c r="H181" s="18" t="n"/>
+      <c r="I181" s="18" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="21" t="n"/>
+      <c r="B182" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C181" s="21" t="n"/>
-      <c r="D181" s="21" t="n"/>
-      <c r="E181" s="21" t="n"/>
-      <c r="F181" s="21" t="n"/>
-      <c r="G181" s="21" t="n"/>
-      <c r="H181" s="21" t="n"/>
-      <c r="I181" s="21" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="inlineStr"/>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="C182" s="21" t="n"/>
+      <c r="D182" s="21" t="n"/>
+      <c r="E182" s="21" t="n"/>
+      <c r="F182" s="21" t="n"/>
+      <c r="G182" s="21" t="n"/>
+      <c r="H182" s="21" t="n"/>
+      <c r="I182" s="21" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr"/>
+      <c r="B183" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C182" s="5" t="n">
+      <c r="C183" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="D183" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E182" s="5" t="n">
+      <c r="E183" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F182" s="5" t="n">
+      <c r="F183" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G182" s="5" t="inlineStr">
+      <c r="G183" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H182" s="12" t="n">
+      <c r="H183" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I182" s="13" t="inlineStr">
+      <c r="I183" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -9629,123 +9715,123 @@
     </row>
   </sheetData>
   <mergeCells count="117">
+    <mergeCell ref="B135:I135"/>
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B144:I144"/>
-    <mergeCell ref="A172:I172"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="B134:I134"/>
+    <mergeCell ref="A154:I154"/>
+    <mergeCell ref="A163:I163"/>
     <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B167:I167"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B161:I161"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A17:I17"/>
-    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="B145:I145"/>
+    <mergeCell ref="A126:I126"/>
     <mergeCell ref="B98:I98"/>
-    <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
-    <mergeCell ref="B181:I181"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B147:I147"/>
     <mergeCell ref="A111:I111"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B83:I83"/>
+    <mergeCell ref="B139:I139"/>
     <mergeCell ref="A169:I169"/>
-    <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A153:I153"/>
-    <mergeCell ref="B173:I173"/>
     <mergeCell ref="A137:I137"/>
-    <mergeCell ref="B141:I141"/>
-    <mergeCell ref="A136:I136"/>
+    <mergeCell ref="A177:I177"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A179:I179"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="B86:I86"/>
     <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B152:I152"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A165:I165"/>
+    <mergeCell ref="A116:I116"/>
+    <mergeCell ref="A181:I181"/>
+    <mergeCell ref="A131:I131"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="A180:I180"/>
     <mergeCell ref="A115:I115"/>
-    <mergeCell ref="B128:I128"/>
-    <mergeCell ref="A143:I143"/>
-    <mergeCell ref="B177:I177"/>
+    <mergeCell ref="B178:I178"/>
+    <mergeCell ref="A173:I173"/>
+    <mergeCell ref="A157:I157"/>
+    <mergeCell ref="A166:I166"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B164:I164"/>
     <mergeCell ref="A94:I94"/>
-    <mergeCell ref="A168:I168"/>
     <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B154:I154"/>
-    <mergeCell ref="B163:I163"/>
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="B138:I138"/>
     <mergeCell ref="B91:I91"/>
-    <mergeCell ref="A133:I133"/>
     <mergeCell ref="B66:I66"/>
+    <mergeCell ref="A120:I120"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
+    <mergeCell ref="B155:I155"/>
     <mergeCell ref="A104:I104"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A32:I32"/>
+    <mergeCell ref="B117:I117"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="B151:I151"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B132:I132"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B166:I166"/>
-    <mergeCell ref="A156:I156"/>
-    <mergeCell ref="B116:I116"/>
+    <mergeCell ref="A170:I170"/>
     <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B182:I182"/>
+    <mergeCell ref="B174:I174"/>
     <mergeCell ref="B112:I112"/>
-    <mergeCell ref="A130:I130"/>
+    <mergeCell ref="B127:I127"/>
+    <mergeCell ref="B158:I158"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
+    <mergeCell ref="A123:I123"/>
     <mergeCell ref="B95:I95"/>
+    <mergeCell ref="A138:I138"/>
     <mergeCell ref="B89:I89"/>
     <mergeCell ref="A110:I110"/>
-    <mergeCell ref="B160:I160"/>
     <mergeCell ref="A119:I119"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="A149:I149"/>
+    <mergeCell ref="B129:I129"/>
+    <mergeCell ref="B121:I121"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B131:I131"/>
     <mergeCell ref="B18:I18"/>
+    <mergeCell ref="A151:I151"/>
     <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A160:I160"/>
+    <mergeCell ref="A141:I141"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A150:I150"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A159:I159"/>
-    <mergeCell ref="A122:I122"/>
+    <mergeCell ref="A144:I144"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B170:I170"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="B148:I148"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="B157:I157"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="B171:I171"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A176:I176"/>
     <mergeCell ref="B108:I108"/>
-    <mergeCell ref="A114:I114"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A107:I107"/>
+    <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="A88:I88"/>
+    <mergeCell ref="B142:I142"/>
     <mergeCell ref="B80:I80"/>
-    <mergeCell ref="A162:I162"/>
-    <mergeCell ref="B126:I126"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -9788,29 +9874,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId64"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9822,7 +9909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11503,24 +11590,93 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="182" customHeight="1">
+    <row r="40" ht="560" customHeight="1">
       <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>Number of Provinces</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>547</v>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public class Uniounandfind {
+	int[] parent;
+	public Uniounandfind(int size) {
+		parent = new int[size];
+		for(int i=0;i&lt;size;i++) {
+			parent[i] = i;
+		}
+	}
+	public int find(int i) {
+		if(parent[i] == i) {
+			return i;
+		}
+		return find(parent[i]);
+	}
+	public void unioun(int first,int second) {
+	     parent[first] = second;
+	}
+    public  int province() {
+		int count =0;
+		for(int i=0;i&lt;parent.length;i++) {
+			if(parent[i] == i) {
+				count++;
+			}
+		}
+		return count;
+	}
+	public void build(int[][] nums) {
+		for(int i=0;i&lt;nums.length;i++) {
+			for(int j=i+1;j&lt;nums.length;j++) {
+				if(nums[i][j] == 1) {
+					int parent1 =  find(i);
+					int parent2 = find(j);
+					if(parent1 != parent2) {
+						unioun(parent1 , parent2);
+					}
+				}
+			}
+		}
+	}
+    }
+    public int findCircleNum(int[][] isConnected) {
+     Uniounandfind uf = new Uniounandfind(isConnected.length);
+	 uf.build(isConnected);
+     return uf.province();    
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="182" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -11538,24 +11694,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="546" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="546" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11599,24 +11755,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="196" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="196" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -11635,24 +11791,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="462" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="462" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -11682,24 +11838,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="518" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="518" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>684</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>class Solution {
  class UniounFind{
@@ -11739,24 +11895,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="252" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="252" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>739</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -11776,24 +11932,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="378" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="378" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -11825,24 +11981,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="294" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="294" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>908</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11868,24 +12024,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="560" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="560" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -11921,24 +12077,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="294" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="294" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -11961,24 +12117,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="224" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="224" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -11999,24 +12155,24 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="420" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52" ht="420" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -12051,24 +12207,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="378" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53" ht="378" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -12100,24 +12256,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="266" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="266" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>1570</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -12141,24 +12297,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="350" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="350" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -12188,24 +12344,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="238" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="238" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -12227,24 +12383,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="308" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="308" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -12271,24 +12427,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="280" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="280" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -12311,24 +12467,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="448" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="448" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -12363,24 +12519,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="378" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="378" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -12412,24 +12568,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="266" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="266" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -12453,24 +12609,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="560" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="560" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -12523,24 +12679,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="196" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="196" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>3811</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -12558,24 +12714,24 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="238" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="238" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -12595,24 +12751,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="252" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="252" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -12635,24 +12791,24 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="140" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="140" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -12666,24 +12822,24 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="294" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="67" ht="294" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C67" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -12709,24 +12865,24 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="252" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+    <row r="68" ht="252" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C68" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -12827,13 +12983,13 @@
         <v>36</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -12865,13 +13021,13 @@
         <v>36</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2431,7 +2431,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H143" s="12" t="n">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H149" s="12" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H153" s="12" t="n">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H156" s="12" t="n">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H179" s="12" t="n">
@@ -9964,7 +9964,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="560" customHeight="1">
+    <row r="5" ht="196" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -9978,126 +9978,117 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] nums, int target) {
+        int[] arr=new int[2];
+       	 for(int i=0;i&lt;nums.length;i++) { 
+		 for(int j=i+1;j&lt;nums.length;j++) { 
+			 if(nums[i]+nums[j]==target) { 
+				arr[0]=i;
+                arr[1]=j;
+			 }
+		 }
+	 }
+     return arr;
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="504" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
-&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
-&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 1
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
+Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
 &lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="252" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>class Solution {
-    public int lengthOfLongestSubstring(String s) {
-    int left =0;
-    int max = 0;
-    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
-    for(int right =0;right&lt;s.length();right++){
-         char currentChar = s.charAt(right);
-          while(hs.contains(s.charAt(right))){
-            hs.remove(s.charAt(left));
-            left++;
-          }
-          hs.add(s.charAt(right));
-          max = Math.max(max,right-left +1); 
+    public static int rever(int num){
+        int rev =0;
+        while(num != 0){
+            int rem = num%10;
+            if(rev&gt;Integer.MAX_VALUE/10) return 0;
+            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
+            rev=rev*10+rem;
+            num/=10;
+        }
+        return rev;
     }
-    return max;
+    public int reverse(int x) {
+    // int i=0;
+    // if(x&gt;=0)  i=1;
+    // else i = -1;
+    int num = rever(x);
+    return num;
     }
 }</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="462" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 123
-&lt;strong&gt;Output:&lt;/strong&gt; 321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = -123
-&lt;strong&gt;Output:&lt;/strong&gt; -321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 120
-&lt;strong&gt;Output:&lt;/strong&gt; 21
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10390,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="532" customHeight="1">
+    <row r="15" ht="210" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10413,40 +10404,26 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 5
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 4
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 6
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public int lengthOfLastWord(String s) {
+    char[] ch =s.toCharArray();
+    int count=0;
+    int i = s.length()-1;
+    while(s.charAt(i) == ' '){
+        i--;
+    }
+    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
+        count++;
+        i--;
+    }
+    return count;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -10521,7 +10498,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="560" customHeight="1">
+    <row r="17" ht="420" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10535,45 +10512,39 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    public  void inorder(TreeNode root,List list){
+    if(root == null) return;
+    inorder(root.left,list);
+    list.add(root.val);
+    inorder(root.right,list);
+    }
+    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
+    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
+    inorder(root,list);
+    return list;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -11269,7 +11240,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="182" customHeight="1">
+    <row r="33" ht="308" customHeight="1">
       <c r="A33" s="5" t="n">
         <v>29</v>
       </c>
@@ -11283,24 +11254,29 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public void moveZeroes(int[] nums) {
-    int numbers = 0;
-    for(int traverse = 0;traverse&lt;nums.length;traverse++){
-        if(nums[traverse] != 0){
-            int temp = nums[traverse];
-            nums[traverse] = nums[numbers];
-            nums[numbers] = temp;
-            numbers++;
-        }
-    }  
-    }
-}</t>
+          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
+&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
+&lt;strong&gt;Output:&lt;/strong&gt; [0]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
         </is>
       </c>
     </row>
@@ -12091,29 +12067,32 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E50" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
-&lt;strong&gt;Output:&lt;/strong&gt; true
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
-&lt;strong&gt;Output:&lt;/strong&gt; false
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public boolean isBoomerang(int[][] points) {
+    int x1=0,x2=0,x3=0;
+    int y1=0,y2=0,y3=0;
+    for(int i =0;i&lt;points.length;i++){
+        for(int j=0;j&lt;points[i].length-1;j++){
+           if(i==0){
+            x1 = points[i][j];
+            y1 = points[i][j+1];
+           }else if(i == 1){
+             x2 = points[i][j];
+             y2 = points[i][j+1];
+           }else{
+            x3 = points[i][j];
+            y3 = points[i][j+1];
+           }
+        }
+    } 
+    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12547,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="266" customHeight="1">
+    <row r="61" ht="490" customHeight="1">
       <c r="A61" s="5" t="n">
         <v>57</v>
       </c>
@@ -12582,100 +12561,77 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E61" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public static int digits(int num){
-        int multiply =1;
-        while(num!=0){
-            int rem = num%10;
-            multiply *= rem;
-            num /= 10;
-        }
-        return multiply;
-    }
-    public int smallestNumber(int n, int t) {
-    while(true){
-        if(digits(n)%t == 0){
-          return n;
-        } 
-        n++;
-    }
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="560" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
-A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
+          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
+&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="308" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int largestInteger(int[] nums, int k) {
+    int[] arr = new int[51];
+    for(int i = 0;i&lt;nums.length-k+1;i++){
+        boolean[] seen = new boolean[51];
+        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
+            if (!seen[nums[j]]){
+               arr[nums[j]]++;
+               seen[nums[j]] = true;
+            } 
+        }
+    } 
+    int high =-1;
+    for(int i=0;i&lt;arr.length;i++){
+        if(arr[i] == 1){
+           if(high&lt;i) high = i;
+        }
+    } 
+    return high;
+    }
+}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1561,167 +1561,167 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>Breadth-First Search, Union-Find, Graph Theory</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G38" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H38" s="7" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Depth-First Search — TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr"/>
-      <c r="C38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5" t="n">
+      <c r="C40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H42" s="7" t="n">
         <v>45.9</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>43.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>1</v>
@@ -1730,261 +1730,261 @@
         <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>46.8</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="5" t="n">
+      <c r="C46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Linked List — TOTAL</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
-      <c r="C46" s="9" t="n">
+      <c r="B47" s="8" t="inlineStr"/>
+      <c r="C47" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D47" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="E47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="9" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="n">
+      <c r="C48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="H48" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr"/>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5" t="n">
+      <c r="D50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="5" t="n">
+      <c r="G50" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H50" s="7" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr"/>
-      <c r="C50" s="9" t="n">
+      <c r="B51" s="8" t="inlineStr"/>
+      <c r="C51" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="9" t="n">
+      <c r="D51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="5" t="n">
+      <c r="C52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr"/>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H52" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
@@ -1993,17 +1993,17 @@
         <v>1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
@@ -2019,17 +2019,17 @@
         <v>1</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
@@ -2045,237 +2045,263 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="7" t="n">
+      <c r="C57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H56" s="7" t="n">
+      <c r="H57" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr"/>
-      <c r="C57" s="9" t="n">
+      <c r="B58" s="8" t="inlineStr"/>
+      <c r="C58" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D57" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="9" t="n">
+      <c r="D58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G57" s="9" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="7" t="n">
+      <c r="C59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr"/>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr"/>
       <c r="B60" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="7" t="n">
+      <c r="C61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr"/>
-      <c r="C61" s="9" t="n">
+      <c r="B62" s="8" t="inlineStr"/>
+      <c r="C62" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="9" t="n">
+      <c r="D62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G61" s="9" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="G62" s="9" t="inlineStr"/>
+      <c r="H62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="7" t="n">
+      <c r="C63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H62" s="7" t="n">
+      <c r="H63" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr"/>
-      <c r="C63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="9" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr"/>
+      <c r="C64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr"/>
+      <c r="H64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr"/>
-      <c r="C64" s="11" t="n">
+      <c r="B65" s="10" t="inlineStr"/>
+      <c r="C65" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="D64" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E64" s="11" t="n">
+      <c r="D65" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E65" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F64" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="G64" s="11" t="inlineStr"/>
-      <c r="H64" s="11" t="inlineStr"/>
+      <c r="F65" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="G65" s="11" t="inlineStr"/>
+      <c r="H65" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2291,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2431,7 +2457,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2481,7 +2507,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2531,7 +2557,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2781,7 +2807,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2881,7 +2907,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3281,7 +3307,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3331,7 +3357,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3381,7 +3407,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -3981,7 +4007,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -5597,6 +5623,56 @@
         <v>46287.65729166667</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Course Schedule</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Depth-First Search</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>46288.65751157407</v>
+      </c>
+      <c r="L69" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5606,7 +5682,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F68">
+  <conditionalFormatting sqref="F5:F69">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5682,6 +5758,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5693,7 +5770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I183"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6406,7 +6483,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6441,7 +6518,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -6881,7 +6958,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -7896,7 +7973,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -8106,7 +8183,7 @@
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   3 solved   (Low: 0 · Medium: 3 · High: 0)</t>
         </is>
       </c>
       <c r="B110" s="2" t="n"/>
@@ -8121,7 +8198,7 @@
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B111" s="18" t="n"/>
@@ -8137,7 +8214,7 @@
       <c r="A112" s="19" t="n"/>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Medium (Medium) — 2 problem(s)</t>
+          <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C112" s="19" t="n"/>
@@ -8152,236 +8229,236 @@
       <c r="A113" s="5" t="inlineStr"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
+          <t>Course Schedule</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>46288.65751157407</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="n"/>
+      <c r="C114" s="18" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="18" t="n"/>
+      <c r="F114" s="18" t="n"/>
+      <c r="G114" s="18" t="n"/>
+      <c r="H114" s="18" t="n"/>
+      <c r="I114" s="18" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="19" t="n"/>
+      <c r="B115" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C115" s="19" t="n"/>
+      <c r="D115" s="19" t="n"/>
+      <c r="E115" s="19" t="n"/>
+      <c r="F115" s="19" t="n"/>
+      <c r="G115" s="19" t="n"/>
+      <c r="H115" s="19" t="n"/>
+      <c r="I115" s="19" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr"/>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C116" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="5" t="n">
+      <c r="E116" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F113" s="5" t="n">
+      <c r="F116" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H113" s="12" t="n">
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="n">
         <v>46287.65729166667</v>
       </c>
-      <c r="I113" s="13" t="inlineStr">
+      <c r="I116" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr"/>
-      <c r="B114" s="6" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr"/>
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C114" s="7" t="n">
+      <c r="C117" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="7" t="n">
+      <c r="E117" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H114" s="14" t="n">
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="n">
         <v>46287.51434027778</v>
       </c>
-      <c r="I114" s="15" t="inlineStr">
+      <c r="I117" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n"/>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="17" t="inlineStr">
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B116" s="18" t="n"/>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="21" t="n"/>
-      <c r="B117" s="22" t="inlineStr">
+      <c r="B119" s="18" t="n"/>
+      <c r="C119" s="18" t="n"/>
+      <c r="D119" s="18" t="n"/>
+      <c r="E119" s="18" t="n"/>
+      <c r="F119" s="18" t="n"/>
+      <c r="G119" s="18" t="n"/>
+      <c r="H119" s="18" t="n"/>
+      <c r="I119" s="18" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="n"/>
+      <c r="B120" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C117" s="21" t="n"/>
-      <c r="D117" s="21" t="n"/>
-      <c r="E117" s="21" t="n"/>
-      <c r="F117" s="21" t="n"/>
-      <c r="G117" s="21" t="n"/>
-      <c r="H117" s="21" t="n"/>
-      <c r="I117" s="21" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr"/>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="C120" s="21" t="n"/>
+      <c r="D120" s="21" t="n"/>
+      <c r="E120" s="21" t="n"/>
+      <c r="F120" s="21" t="n"/>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="21" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr"/>
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C121" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="5" t="n">
+      <c r="E121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H118" s="12" t="n">
+      <c r="H121" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I118" s="13" t="inlineStr">
+      <c r="I121" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="16" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
         </is>
       </c>
-      <c r="B119" s="2" t="n"/>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="2" t="n"/>
-      <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B120" s="18" t="n"/>
-      <c r="C120" s="18" t="n"/>
-      <c r="D120" s="18" t="n"/>
-      <c r="E120" s="18" t="n"/>
-      <c r="F120" s="18" t="n"/>
-      <c r="G120" s="18" t="n"/>
-      <c r="H120" s="18" t="n"/>
-      <c r="I120" s="18" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="23" t="n"/>
-      <c r="B121" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C121" s="23" t="n"/>
-      <c r="D121" s="23" t="n"/>
-      <c r="E121" s="23" t="n"/>
-      <c r="F121" s="23" t="n"/>
-      <c r="G121" s="23" t="n"/>
-      <c r="H121" s="23" t="n"/>
-      <c r="I121" s="23" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr"/>
-      <c r="B122" s="4" t="inlineStr">
-        <is>
-          <t>Merge k Sorted Lists</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="n">
-        <v>46286.43949074074</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="n"/>
+      <c r="I122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B123" s="18" t="n"/>
@@ -8394,40 +8471,40 @@
       <c r="I123" s="18" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="19" t="n"/>
-      <c r="B124" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C124" s="19" t="n"/>
-      <c r="D124" s="19" t="n"/>
-      <c r="E124" s="19" t="n"/>
-      <c r="F124" s="19" t="n"/>
-      <c r="G124" s="19" t="n"/>
-      <c r="H124" s="19" t="n"/>
-      <c r="I124" s="19" t="n"/>
+      <c r="A124" s="23" t="n"/>
+      <c r="B124" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C124" s="23" t="n"/>
+      <c r="D124" s="23" t="n"/>
+      <c r="E124" s="23" t="n"/>
+      <c r="F124" s="23" t="n"/>
+      <c r="G124" s="23" t="n"/>
+      <c r="H124" s="23" t="n"/>
+      <c r="I124" s="23" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr"/>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List II</t>
+          <t>Merge k Sorted Lists</t>
         </is>
       </c>
       <c r="C125" s="5" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>43.4</v>
+        <v>45.9</v>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
@@ -8435,7 +8512,7 @@
         </is>
       </c>
       <c r="H125" s="12" t="n">
-        <v>46275.41266203704</v>
+        <v>46286.43949074074</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -8446,7 +8523,7 @@
     <row r="126">
       <c r="A126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B126" s="18" t="n"/>
@@ -8459,155 +8536,155 @@
       <c r="I126" s="18" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="21" t="n"/>
-      <c r="B127" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C127" s="21" t="n"/>
-      <c r="D127" s="21" t="n"/>
-      <c r="E127" s="21" t="n"/>
-      <c r="F127" s="21" t="n"/>
-      <c r="G127" s="21" t="n"/>
-      <c r="H127" s="21" t="n"/>
-      <c r="I127" s="21" t="n"/>
+      <c r="A127" s="19" t="n"/>
+      <c r="B127" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="n"/>
+      <c r="D127" s="19" t="n"/>
+      <c r="E127" s="19" t="n"/>
+      <c r="F127" s="19" t="n"/>
+      <c r="G127" s="19" t="n"/>
+      <c r="H127" s="19" t="n"/>
+      <c r="I127" s="19" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr"/>
       <c r="B128" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List II</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>46275.41266203704</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B129" s="18" t="n"/>
+      <c r="C129" s="18" t="n"/>
+      <c r="D129" s="18" t="n"/>
+      <c r="E129" s="18" t="n"/>
+      <c r="F129" s="18" t="n"/>
+      <c r="G129" s="18" t="n"/>
+      <c r="H129" s="18" t="n"/>
+      <c r="I129" s="18" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="21" t="n"/>
+      <c r="B130" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C130" s="21" t="n"/>
+      <c r="D130" s="21" t="n"/>
+      <c r="E130" s="21" t="n"/>
+      <c r="F130" s="21" t="n"/>
+      <c r="G130" s="21" t="n"/>
+      <c r="H130" s="21" t="n"/>
+      <c r="I130" s="21" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr"/>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C128" s="5" t="n">
+      <c r="C131" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D131" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="5" t="n">
+      <c r="E131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="n">
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I128" s="13" t="inlineStr">
+      <c r="I131" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="19" t="n"/>
-      <c r="B129" s="20" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="19" t="n"/>
+      <c r="B132" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C129" s="19" t="n"/>
-      <c r="D129" s="19" t="n"/>
-      <c r="E129" s="19" t="n"/>
-      <c r="F129" s="19" t="n"/>
-      <c r="G129" s="19" t="n"/>
-      <c r="H129" s="19" t="n"/>
-      <c r="I129" s="19" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr"/>
-      <c r="B130" s="4" t="inlineStr">
-        <is>
-          <t>Linked List Cycle II</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G130" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H130" s="12" t="n">
-        <v>46274.44269675926</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B131" s="18" t="n"/>
-      <c r="C131" s="18" t="n"/>
-      <c r="D131" s="18" t="n"/>
-      <c r="E131" s="18" t="n"/>
-      <c r="F131" s="18" t="n"/>
-      <c r="G131" s="18" t="n"/>
-      <c r="H131" s="18" t="n"/>
-      <c r="I131" s="18" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="21" t="n"/>
-      <c r="B132" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C132" s="21" t="n"/>
-      <c r="D132" s="21" t="n"/>
-      <c r="E132" s="21" t="n"/>
-      <c r="F132" s="21" t="n"/>
-      <c r="G132" s="21" t="n"/>
-      <c r="H132" s="21" t="n"/>
-      <c r="I132" s="21" t="n"/>
+      <c r="C132" s="19" t="n"/>
+      <c r="D132" s="19" t="n"/>
+      <c r="E132" s="19" t="n"/>
+      <c r="F132" s="19" t="n"/>
+      <c r="G132" s="19" t="n"/>
+      <c r="H132" s="19" t="n"/>
+      <c r="I132" s="19" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr"/>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List</t>
+          <t>Linked List Cycle II</t>
         </is>
       </c>
       <c r="C133" s="5" t="n">
-        <v>206</v>
+        <v>142</v>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
@@ -8615,7 +8692,7 @@
         </is>
       </c>
       <c r="H133" s="12" t="n">
-        <v>46274.48334490741</v>
+        <v>46274.44269675926</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -8626,7 +8703,7 @@
     <row r="134">
       <c r="A134" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B134" s="18" t="n"/>
@@ -8657,121 +8734,121 @@
       <c r="A136" s="5" t="inlineStr"/>
       <c r="B136" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>46274.48334490741</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B137" s="18" t="n"/>
+      <c r="C137" s="18" t="n"/>
+      <c r="D137" s="18" t="n"/>
+      <c r="E137" s="18" t="n"/>
+      <c r="F137" s="18" t="n"/>
+      <c r="G137" s="18" t="n"/>
+      <c r="H137" s="18" t="n"/>
+      <c r="I137" s="18" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="21" t="n"/>
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C138" s="21" t="n"/>
+      <c r="D138" s="21" t="n"/>
+      <c r="E138" s="21" t="n"/>
+      <c r="F138" s="21" t="n"/>
+      <c r="G138" s="21" t="n"/>
+      <c r="H138" s="21" t="n"/>
+      <c r="I138" s="21" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr"/>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C136" s="5" t="n">
+      <c r="C139" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D136" s="5" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="5" t="n">
+      <c r="E139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H136" s="12" t="n">
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I136" s="13" t="inlineStr">
+      <c r="I139" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="16" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B137" s="2" t="n"/>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" s="2" t="n"/>
-      <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="n"/>
-      <c r="H137" s="2" t="n"/>
-      <c r="I137" s="2" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B138" s="18" t="n"/>
-      <c r="C138" s="18" t="n"/>
-      <c r="D138" s="18" t="n"/>
-      <c r="E138" s="18" t="n"/>
-      <c r="F138" s="18" t="n"/>
-      <c r="G138" s="18" t="n"/>
-      <c r="H138" s="18" t="n"/>
-      <c r="I138" s="18" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="21" t="n"/>
-      <c r="B139" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C139" s="21" t="n"/>
-      <c r="D139" s="21" t="n"/>
-      <c r="E139" s="21" t="n"/>
-      <c r="F139" s="21" t="n"/>
-      <c r="G139" s="21" t="n"/>
-      <c r="H139" s="21" t="n"/>
-      <c r="I139" s="21" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr"/>
-      <c r="B140" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G140" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H140" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="n"/>
+      <c r="I140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B141" s="18" t="n"/>
@@ -8802,11 +8879,11 @@
       <c r="A143" s="5" t="inlineStr"/>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C143" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
@@ -8814,18 +8891,18 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H143" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I143" s="13" t="inlineStr">
         <is>
@@ -8836,7 +8913,7 @@
     <row r="144">
       <c r="A144" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B144" s="18" t="n"/>
@@ -8852,7 +8929,7 @@
       <c r="A145" s="21" t="n"/>
       <c r="B145" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C145" s="21" t="n"/>
@@ -8867,11 +8944,11 @@
       <c r="A146" s="5" t="inlineStr"/>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
-        <v>3918</v>
+        <v>3626</v>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
@@ -8882,7 +8959,7 @@
         <v>1</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
@@ -8890,7 +8967,7 @@
         </is>
       </c>
       <c r="H146" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -8899,174 +8976,174 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="inlineStr"/>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>Count Commas in Range</t>
-        </is>
-      </c>
-      <c r="C147" s="7" t="n">
-        <v>4245</v>
-      </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H147" s="14" t="n">
-        <v>46273.3956712963</v>
-      </c>
-      <c r="I147" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A147" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B147" s="18" t="n"/>
+      <c r="C147" s="18" t="n"/>
+      <c r="D147" s="18" t="n"/>
+      <c r="E147" s="18" t="n"/>
+      <c r="F147" s="18" t="n"/>
+      <c r="G147" s="18" t="n"/>
+      <c r="H147" s="18" t="n"/>
+      <c r="I147" s="18" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="19" t="n"/>
-      <c r="B148" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C148" s="19" t="n"/>
-      <c r="D148" s="19" t="n"/>
-      <c r="E148" s="19" t="n"/>
-      <c r="F148" s="19" t="n"/>
-      <c r="G148" s="19" t="n"/>
-      <c r="H148" s="19" t="n"/>
-      <c r="I148" s="19" t="n"/>
+      <c r="A148" s="21" t="n"/>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C148" s="21" t="n"/>
+      <c r="D148" s="21" t="n"/>
+      <c r="E148" s="21" t="n"/>
+      <c r="F148" s="21" t="n"/>
+      <c r="G148" s="21" t="n"/>
+      <c r="H148" s="21" t="n"/>
+      <c r="I148" s="21" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr"/>
       <c r="B149" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr"/>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H150" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="19" t="n"/>
+      <c r="B151" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C151" s="19" t="n"/>
+      <c r="D151" s="19" t="n"/>
+      <c r="E151" s="19" t="n"/>
+      <c r="F151" s="19" t="n"/>
+      <c r="G151" s="19" t="n"/>
+      <c r="H151" s="19" t="n"/>
+      <c r="I151" s="19" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="5" t="inlineStr"/>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C149" s="5" t="n">
+      <c r="C152" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D152" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" s="5" t="n">
+      <c r="E152" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="n">
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I149" s="13" t="inlineStr">
+      <c r="I152" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="16" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B150" s="2" t="n"/>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n"/>
-      <c r="E150" s="2" t="n"/>
-      <c r="F150" s="2" t="n"/>
-      <c r="G150" s="2" t="n"/>
-      <c r="H150" s="2" t="n"/>
-      <c r="I150" s="2" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B151" s="18" t="n"/>
-      <c r="C151" s="18" t="n"/>
-      <c r="D151" s="18" t="n"/>
-      <c r="E151" s="18" t="n"/>
-      <c r="F151" s="18" t="n"/>
-      <c r="G151" s="18" t="n"/>
-      <c r="H151" s="18" t="n"/>
-      <c r="I151" s="18" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="21" t="n"/>
-      <c r="B152" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C152" s="21" t="n"/>
-      <c r="D152" s="21" t="n"/>
-      <c r="E152" s="21" t="n"/>
-      <c r="F152" s="21" t="n"/>
-      <c r="G152" s="21" t="n"/>
-      <c r="H152" s="21" t="n"/>
-      <c r="I152" s="21" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="5" t="inlineStr"/>
-      <c r="B153" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C153" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E153" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G153" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H153" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="n"/>
+      <c r="G153" s="2" t="n"/>
+      <c r="H153" s="2" t="n"/>
+      <c r="I153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B154" s="18" t="n"/>
@@ -9079,40 +9156,40 @@
       <c r="I154" s="18" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="19" t="n"/>
-      <c r="B155" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C155" s="19" t="n"/>
-      <c r="D155" s="19" t="n"/>
-      <c r="E155" s="19" t="n"/>
-      <c r="F155" s="19" t="n"/>
-      <c r="G155" s="19" t="n"/>
-      <c r="H155" s="19" t="n"/>
-      <c r="I155" s="19" t="n"/>
+      <c r="A155" s="21" t="n"/>
+      <c r="B155" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C155" s="21" t="n"/>
+      <c r="D155" s="21" t="n"/>
+      <c r="E155" s="21" t="n"/>
+      <c r="F155" s="21" t="n"/>
+      <c r="G155" s="21" t="n"/>
+      <c r="H155" s="21" t="n"/>
+      <c r="I155" s="21" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr"/>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C156" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
@@ -9120,7 +9197,7 @@
         </is>
       </c>
       <c r="H156" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -9131,7 +9208,7 @@
     <row r="157">
       <c r="A157" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B157" s="18" t="n"/>
@@ -9144,40 +9221,40 @@
       <c r="I157" s="18" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="21" t="n"/>
-      <c r="B158" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C158" s="21" t="n"/>
-      <c r="D158" s="21" t="n"/>
-      <c r="E158" s="21" t="n"/>
-      <c r="F158" s="21" t="n"/>
-      <c r="G158" s="21" t="n"/>
-      <c r="H158" s="21" t="n"/>
-      <c r="I158" s="21" t="n"/>
+      <c r="A158" s="19" t="n"/>
+      <c r="B158" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="n"/>
+      <c r="D158" s="19" t="n"/>
+      <c r="E158" s="19" t="n"/>
+      <c r="F158" s="19" t="n"/>
+      <c r="G158" s="19" t="n"/>
+      <c r="H158" s="19" t="n"/>
+      <c r="I158" s="19" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr"/>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
@@ -9185,7 +9262,7 @@
         </is>
       </c>
       <c r="H159" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -9196,7 +9273,7 @@
     <row r="160">
       <c r="A160" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B160" s="18" t="n"/>
@@ -9227,11 +9304,11 @@
       <c r="A162" s="5" t="inlineStr"/>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Reverse Degree of a String</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
-        <v>3811</v>
+        <v>242</v>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
@@ -9239,10 +9316,10 @@
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
@@ -9250,7 +9327,7 @@
         </is>
       </c>
       <c r="H162" s="12" t="n">
-        <v>46285.42987268518</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -9261,7 +9338,7 @@
     <row r="163">
       <c r="A163" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B163" s="18" t="n"/>
@@ -9292,11 +9369,11 @@
       <c r="A165" s="5" t="inlineStr"/>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Reverse Degree of a String</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>125</v>
+        <v>3811</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
@@ -9304,18 +9381,18 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H165" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46285.42987268518</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -9326,7 +9403,7 @@
     <row r="166">
       <c r="A166" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B166" s="18" t="n"/>
@@ -9357,121 +9434,121 @@
       <c r="A168" s="5" t="inlineStr"/>
       <c r="B168" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H168" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B169" s="18" t="n"/>
+      <c r="C169" s="18" t="n"/>
+      <c r="D169" s="18" t="n"/>
+      <c r="E169" s="18" t="n"/>
+      <c r="F169" s="18" t="n"/>
+      <c r="G169" s="18" t="n"/>
+      <c r="H169" s="18" t="n"/>
+      <c r="I169" s="18" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="21" t="n"/>
+      <c r="B170" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C170" s="21" t="n"/>
+      <c r="D170" s="21" t="n"/>
+      <c r="E170" s="21" t="n"/>
+      <c r="F170" s="21" t="n"/>
+      <c r="G170" s="21" t="n"/>
+      <c r="H170" s="21" t="n"/>
+      <c r="I170" s="21" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="inlineStr"/>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C168" s="5" t="n">
+      <c r="C171" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D171" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E168" s="5" t="n">
+      <c r="E171" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F168" s="5" t="n">
+      <c r="F171" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G168" s="5" t="inlineStr">
+      <c r="G171" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H168" s="12" t="n">
+      <c r="H171" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I168" s="13" t="inlineStr">
+      <c r="I171" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="16" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n"/>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" s="2" t="n"/>
-      <c r="F169" s="2" t="n"/>
-      <c r="G169" s="2" t="n"/>
-      <c r="H169" s="2" t="n"/>
-      <c r="I169" s="2" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B170" s="18" t="n"/>
-      <c r="C170" s="18" t="n"/>
-      <c r="D170" s="18" t="n"/>
-      <c r="E170" s="18" t="n"/>
-      <c r="F170" s="18" t="n"/>
-      <c r="G170" s="18" t="n"/>
-      <c r="H170" s="18" t="n"/>
-      <c r="I170" s="18" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="21" t="n"/>
-      <c r="B171" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C171" s="21" t="n"/>
-      <c r="D171" s="21" t="n"/>
-      <c r="E171" s="21" t="n"/>
-      <c r="F171" s="21" t="n"/>
-      <c r="G171" s="21" t="n"/>
-      <c r="H171" s="21" t="n"/>
-      <c r="I171" s="21" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr"/>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C172" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D172" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G172" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H172" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="n"/>
+      <c r="H172" s="2" t="n"/>
+      <c r="I172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B173" s="18" t="n"/>
@@ -9487,7 +9564,7 @@
       <c r="A174" s="21" t="n"/>
       <c r="B174" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C174" s="21" t="n"/>
@@ -9502,221 +9579,287 @@
       <c r="A175" s="5" t="inlineStr"/>
       <c r="B175" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H175" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B176" s="18" t="n"/>
+      <c r="C176" s="18" t="n"/>
+      <c r="D176" s="18" t="n"/>
+      <c r="E176" s="18" t="n"/>
+      <c r="F176" s="18" t="n"/>
+      <c r="G176" s="18" t="n"/>
+      <c r="H176" s="18" t="n"/>
+      <c r="I176" s="18" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="21" t="n"/>
+      <c r="B177" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C177" s="21" t="n"/>
+      <c r="D177" s="21" t="n"/>
+      <c r="E177" s="21" t="n"/>
+      <c r="F177" s="21" t="n"/>
+      <c r="G177" s="21" t="n"/>
+      <c r="H177" s="21" t="n"/>
+      <c r="I177" s="21" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr"/>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C175" s="5" t="n">
+      <c r="C178" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D175" s="5" t="inlineStr">
+      <c r="D178" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E175" s="5" t="n">
+      <c r="E178" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F175" s="5" t="n">
+      <c r="F178" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G175" s="5" t="inlineStr">
+      <c r="G178" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H175" s="12" t="n">
+      <c r="H178" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I175" s="13" t="inlineStr">
+      <c r="I178" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="7" t="inlineStr"/>
-      <c r="B176" s="6" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr"/>
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C176" s="7" t="n">
+      <c r="C179" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D176" s="7" t="inlineStr">
+      <c r="D179" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E176" s="7" t="n">
+      <c r="E179" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F176" s="7" t="n">
+      <c r="F179" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H176" s="14" t="n">
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H179" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I176" s="15" t="inlineStr">
+      <c r="I179" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="17" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B177" s="18" t="n"/>
-      <c r="C177" s="18" t="n"/>
-      <c r="D177" s="18" t="n"/>
-      <c r="E177" s="18" t="n"/>
-      <c r="F177" s="18" t="n"/>
-      <c r="G177" s="18" t="n"/>
-      <c r="H177" s="18" t="n"/>
-      <c r="I177" s="18" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="21" t="n"/>
-      <c r="B178" s="22" t="inlineStr">
+      <c r="B180" s="18" t="n"/>
+      <c r="C180" s="18" t="n"/>
+      <c r="D180" s="18" t="n"/>
+      <c r="E180" s="18" t="n"/>
+      <c r="F180" s="18" t="n"/>
+      <c r="G180" s="18" t="n"/>
+      <c r="H180" s="18" t="n"/>
+      <c r="I180" s="18" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="21" t="n"/>
+      <c r="B181" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C178" s="21" t="n"/>
-      <c r="D178" s="21" t="n"/>
-      <c r="E178" s="21" t="n"/>
-      <c r="F178" s="21" t="n"/>
-      <c r="G178" s="21" t="n"/>
-      <c r="H178" s="21" t="n"/>
-      <c r="I178" s="21" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="inlineStr"/>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="C181" s="21" t="n"/>
+      <c r="D181" s="21" t="n"/>
+      <c r="E181" s="21" t="n"/>
+      <c r="F181" s="21" t="n"/>
+      <c r="G181" s="21" t="n"/>
+      <c r="H181" s="21" t="n"/>
+      <c r="I181" s="21" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr"/>
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C179" s="5" t="n">
+      <c r="C182" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" s="5" t="n">
+      <c r="E182" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G179" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H179" s="12" t="n">
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H182" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I179" s="13" t="inlineStr">
+      <c r="I182" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="16" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B180" s="2" t="n"/>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" s="2" t="n"/>
-      <c r="F180" s="2" t="n"/>
-      <c r="G180" s="2" t="n"/>
-      <c r="H180" s="2" t="n"/>
-      <c r="I180" s="2" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="17" t="inlineStr">
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="2" t="n"/>
+      <c r="H183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B181" s="18" t="n"/>
-      <c r="C181" s="18" t="n"/>
-      <c r="D181" s="18" t="n"/>
-      <c r="E181" s="18" t="n"/>
-      <c r="F181" s="18" t="n"/>
-      <c r="G181" s="18" t="n"/>
-      <c r="H181" s="18" t="n"/>
-      <c r="I181" s="18" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="21" t="n"/>
-      <c r="B182" s="22" t="inlineStr">
+      <c r="B184" s="18" t="n"/>
+      <c r="C184" s="18" t="n"/>
+      <c r="D184" s="18" t="n"/>
+      <c r="E184" s="18" t="n"/>
+      <c r="F184" s="18" t="n"/>
+      <c r="G184" s="18" t="n"/>
+      <c r="H184" s="18" t="n"/>
+      <c r="I184" s="18" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="21" t="n"/>
+      <c r="B185" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C182" s="21" t="n"/>
-      <c r="D182" s="21" t="n"/>
-      <c r="E182" s="21" t="n"/>
-      <c r="F182" s="21" t="n"/>
-      <c r="G182" s="21" t="n"/>
-      <c r="H182" s="21" t="n"/>
-      <c r="I182" s="21" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="5" t="inlineStr"/>
-      <c r="B183" s="4" t="inlineStr">
+      <c r="C185" s="21" t="n"/>
+      <c r="D185" s="21" t="n"/>
+      <c r="E185" s="21" t="n"/>
+      <c r="F185" s="21" t="n"/>
+      <c r="G185" s="21" t="n"/>
+      <c r="H185" s="21" t="n"/>
+      <c r="I185" s="21" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr"/>
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C183" s="5" t="n">
+      <c r="C186" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E183" s="5" t="n">
+      <c r="E186" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F183" s="5" t="n">
+      <c r="F186" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G183" s="5" t="inlineStr">
+      <c r="G186" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H183" s="12" t="n">
+      <c r="H186" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I183" s="13" t="inlineStr">
+      <c r="I186" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="119">
     <mergeCell ref="B135:I135"/>
     <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A172:I172"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="A56:I56"/>
@@ -9729,10 +9872,13 @@
     <mergeCell ref="B161:I161"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A17:I17"/>
-    <mergeCell ref="B145:I145"/>
+    <mergeCell ref="B120:I120"/>
     <mergeCell ref="A126:I126"/>
     <mergeCell ref="B98:I98"/>
+    <mergeCell ref="B145:I145"/>
+    <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
+    <mergeCell ref="B181:I181"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A111:I111"/>
@@ -9741,56 +9887,54 @@
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B83:I83"/>
-    <mergeCell ref="B139:I139"/>
     <mergeCell ref="A169:I169"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
+    <mergeCell ref="A153:I153"/>
     <mergeCell ref="A137:I137"/>
-    <mergeCell ref="A177:I177"/>
+    <mergeCell ref="B115:I115"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="B86:I86"/>
+    <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
-    <mergeCell ref="B152:I152"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A116:I116"/>
-    <mergeCell ref="A181:I181"/>
-    <mergeCell ref="A131:I131"/>
+    <mergeCell ref="A184:I184"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="A180:I180"/>
-    <mergeCell ref="A115:I115"/>
-    <mergeCell ref="B178:I178"/>
     <mergeCell ref="A173:I173"/>
     <mergeCell ref="A157:I157"/>
     <mergeCell ref="A166:I166"/>
+    <mergeCell ref="B177:I177"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="B164:I164"/>
     <mergeCell ref="A94:I94"/>
     <mergeCell ref="B63:I63"/>
+    <mergeCell ref="A183:I183"/>
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="B138:I138"/>
     <mergeCell ref="B91:I91"/>
     <mergeCell ref="B66:I66"/>
-    <mergeCell ref="A120:I120"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="B155:I155"/>
     <mergeCell ref="A104:I104"/>
+    <mergeCell ref="B130:I130"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="B117:I117"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
+    <mergeCell ref="B151:I151"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="B132:I132"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A170:I170"/>
+    <mergeCell ref="A147:I147"/>
     <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B182:I182"/>
     <mergeCell ref="B174:I174"/>
     <mergeCell ref="B112:I112"/>
     <mergeCell ref="B127:I127"/>
@@ -9800,31 +9944,31 @@
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="A123:I123"/>
     <mergeCell ref="B95:I95"/>
-    <mergeCell ref="A138:I138"/>
     <mergeCell ref="B89:I89"/>
     <mergeCell ref="A110:I110"/>
     <mergeCell ref="A119:I119"/>
-    <mergeCell ref="B129:I129"/>
-    <mergeCell ref="B121:I121"/>
+    <mergeCell ref="B185:I185"/>
+    <mergeCell ref="A118:I118"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B18:I18"/>
-    <mergeCell ref="A151:I151"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A160:I160"/>
     <mergeCell ref="A141:I141"/>
     <mergeCell ref="B42:I42"/>
-    <mergeCell ref="A150:I150"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="A144:I144"/>
+    <mergeCell ref="A122:I122"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
+    <mergeCell ref="B170:I170"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="B148:I148"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A134:I134"/>
-    <mergeCell ref="B171:I171"/>
     <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A176:I176"/>
     <mergeCell ref="B108:I108"/>
+    <mergeCell ref="A114:I114"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A107:I107"/>
     <mergeCell ref="B124:I124"/>
@@ -9874,30 +10018,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId65"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9909,7 +10054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9964,7 +10109,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="196" customHeight="1">
+    <row r="5" ht="560" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -9978,117 +10123,126 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int[] twoSum(int[] nums, int target) {
-        int[] arr=new int[2];
-       	 for(int i=0;i&lt;nums.length;i++) { 
-		 for(int j=i+1;j&lt;nums.length;j++) { 
-			 if(nums[i]+nums[j]==target) { 
-				arr[0]=i;
-                arr[1]=j;
-			 }
-		 }
-	 }
-     return arr;
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="504" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
+          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
+&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 1
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
-Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="252" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int lengthOfLongestSubstring(String s) {
+    int left =0;
+    int max = 0;
+    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
+    for(int right =0;right&lt;s.length();right++){
+         char currentChar = s.charAt(right);
+          while(hs.contains(s.charAt(right))){
+            hs.remove(s.charAt(left));
+            left++;
+          }
+          hs.add(s.charAt(right));
+          max = Math.max(max,right-left +1); 
+    }
+    return max;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="462" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 123
+&lt;strong&gt;Output:&lt;/strong&gt; 321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = -123
+&lt;strong&gt;Output:&lt;/strong&gt; -321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 120
+&lt;strong&gt;Output:&lt;/strong&gt; 21
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int rever(int num){
-        int rev =0;
-        while(num != 0){
-            int rem = num%10;
-            if(rev&gt;Integer.MAX_VALUE/10) return 0;
-            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
-            rev=rev*10+rem;
-            num/=10;
-        }
-        return rev;
-    }
-    public int reverse(int x) {
-    // int i=0;
-    // if(x&gt;=0)  i=1;
-    // else i = -1;
-    int num = rever(x);
-    return num;
-    }
-}</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10544,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="210" customHeight="1">
+    <row r="15" ht="532" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10404,26 +10558,40 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int lengthOfLastWord(String s) {
-    char[] ch =s.toCharArray();
-    int count=0;
-    int i = s.length()-1;
-    while(s.charAt(i) == ' '){
-        i--;
-    }
-    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
-        count++;
-        i--;
-    }
-    return count;
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 5
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 4
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 6
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10666,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="420" customHeight="1">
+    <row r="17" ht="560" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10512,39 +10680,45 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>/**
- * Definition for a binary tree node.
- * public class TreeNode {
- *     int val;
- *     TreeNode left;
- *     TreeNode right;
- *     TreeNode() {}
- *     TreeNode(int val) { this.val = val; }
- *     TreeNode(int val, TreeNode left, TreeNode right) {
- *         this.val = val;
- *         this.left = left;
- *         this.right = right;
- *     }
- * }
- */
-class Solution {
-    public  void inorder(TreeNode root,List list){
-    if(root == null) return;
-    inorder(root.left,list);
-    list.add(root.val);
-    inorder(root.right,list);
-    }
-    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
-    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
-    inorder(root,list);
-    return list;
-    }
-}</t>
+          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
         </is>
       </c>
     </row>
@@ -11071,24 +11245,91 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="238" customHeight="1">
+    <row r="29" ht="560" customHeight="1">
       <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Course Schedule</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public class TopologicalSortUsingKhansAlgorithm {
+	int[] indegree;
+	boolean[] visited;
+	public TopologicalSortUsingKhansAlgorithm(int vertices) {
+		visited = new boolean[vertices];
+		indegree = new int[vertices];
+	}
+	public boolean topoligicalSort(int[][] edges) {
+        int count =0;
+		Queue&lt;Integer&gt; queue = new LinkedList&lt;&gt;();
+		List&lt;Integer&gt;[] graph = new ArrayList[indegree.length];
+		for(int i=0; i&lt;visited.length; i++) {
+		    graph[i] = new ArrayList&lt;&gt;();
+		}
+		for(int[] edge:edges) {
+			graph[edge[0]].add(edge[1]);
+				indegree[edge[1]]++;
+		}
+		for(int i=0;i&lt;indegree.length;i++) {
+			if(indegree[i] == 0) {
+				queue.add(i);
+			}
+		}
+		while(!queue.isEmpty()) {
+			int current = queue.poll();
+			count++;
+			for(int neighbour:graph[current]) {
+			       indegree[neighbour]--;	
+			       if(indegree[neighbour] == 0) {
+			    	       queue.add(neighbour);
+			       }
+			}
+		}
+		if(count == indegree.length){
+            return true;
+        }
+		return false;
+	}
+    }
+    public boolean canFinish(int numCourses, int[][] prerequisites) {
+    TopologicalSortUsingKhansAlgorithm tsort = new TopologicalSortUsingKhansAlgorithm(numCourses);
+    return tsort.topoligicalSort(prerequisites);    
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="238" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -11110,24 +11351,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="238" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="238" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -11149,24 +11390,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="322" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="322" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Sliding Window Maximum</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>239</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] maxSlidingWindow(int[] nums, int k) {
@@ -11190,24 +11431,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="392" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="392" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -11240,64 +11481,59 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="308" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Move Zeroes</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>283</v>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
-&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
-&lt;strong&gt;Output:&lt;/strong&gt; [0]
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="476" customHeight="1">
+    <row r="34" ht="182" customHeight="1">
       <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>Move Zeroes</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>283</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public void moveZeroes(int[] nums) {
+    int numbers = 0;
+    for(int traverse = 0;traverse&lt;nums.length;traverse++){
+        if(nums[traverse] != 0){
+            int temp = nums[traverse];
+            nums[traverse] = nums[numbers];
+            nums[numbers] = temp;
+            numbers++;
+        }
+    }  
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="476" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>Find the Duplicate Number</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int findDuplicate(int[] nums) {
@@ -11335,24 +11571,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="308" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="308" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>303</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -11376,24 +11612,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="420" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="420" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -11425,24 +11661,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="308" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="308" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Find All Duplicates in an Array</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>442</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public List&lt;Integer&gt; findDuplicates(int[] nums) {
@@ -11469,24 +11705,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="322" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="322" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>503</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElements(int[] nums) {
@@ -11511,24 +11747,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="546" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="546" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11566,24 +11802,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="560" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="560" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public class Uniounandfind {
@@ -11635,24 +11871,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="182" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="182" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -11670,24 +11906,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="546" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="546" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11731,24 +11967,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="196" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="196" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -11767,24 +12003,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="462" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="462" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -11814,24 +12050,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="518" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="518" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>class Solution {
  class UniounFind{
@@ -11871,24 +12107,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="252" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="252" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>739</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -11908,24 +12144,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="378" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="378" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -11957,24 +12193,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="294" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="294" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -12000,24 +12236,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="560" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="560" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -12053,67 +12289,64 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="294" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Valid Boomerang</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>1115</v>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public boolean isBoomerang(int[][] points) {
-    int x1=0,x2=0,x3=0;
-    int y1=0,y2=0,y3=0;
-    for(int i =0;i&lt;points.length;i++){
-        for(int j=0;j&lt;points[i].length-1;j++){
-           if(i==0){
-            x1 = points[i][j];
-            y1 = points[i][j+1];
-           }else if(i == 1){
-             x2 = points[i][j];
-             y2 = points[i][j+1];
-           }else{
-            x3 = points[i][j];
-            y3 = points[i][j+1];
-           }
-        }
-    } 
-    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="224" customHeight="1">
+    <row r="51" ht="294" customHeight="1">
       <c r="A51" s="5" t="n">
         <v>47</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
+          <t>Valid Boomerang</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="224" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -12134,24 +12367,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="420" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53" ht="420" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -12186,24 +12419,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="378" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="378" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -12235,24 +12468,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="266" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="266" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -12276,24 +12509,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="350" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="350" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -12323,24 +12556,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="238" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="238" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -12362,24 +12595,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="308" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="308" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -12406,24 +12639,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="280" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="280" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -12446,24 +12679,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="448" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="448" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -12498,24 +12731,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="378" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="378" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -12547,112 +12780,135 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="490" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="266" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static int digits(int num){
+        int multiply =1;
+        while(num!=0){
+            int rem = num%10;
+            multiply *= rem;
+            num /= 10;
+        }
+        return multiply;
+    }
+    public int smallestNumber(int n, int t) {
+    while(true){
+        if(digits(n)%t == 0){
+          return n;
+        } 
+        n++;
+    }
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="560" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E61" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
+A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
         </is>
       </c>
     </row>
-    <row r="62" ht="308" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public int largestInteger(int[] nums, int k) {
-    int[] arr = new int[51];
-    for(int i = 0;i&lt;nums.length-k+1;i++){
-        boolean[] seen = new boolean[51];
-        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
-            if (!seen[nums[j]]){
-               arr[nums[j]]++;
-               seen[nums[j]] = true;
-            } 
-        }
-    } 
-    int high =-1;
-    for(int i=0;i&lt;arr.length;i++){
-        if(arr[i] == 1){
-           if(high&lt;i) high = i;
-        }
-    } 
-    return high;
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="196" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="196" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>3811</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -12670,24 +12926,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="238" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="238" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -12707,24 +12963,24 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="252" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="252" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -12747,24 +13003,24 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="140" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="67" ht="140" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C67" s="5" t="n">
         <v>4245</v>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -12778,24 +13034,24 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="294" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+    <row r="68" ht="294" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C68" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -12821,24 +13077,24 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="252" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="69" ht="252" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C69" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -12939,13 +13195,13 @@
         <v>36</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -12977,13 +13233,13 @@
         <v>36</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
+          <t>Breadth-First Search, Graph Theory, Topological Sort</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -1577,177 +1577,177 @@
         <v>1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
+          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Breadth-First Search, Union-Find, Graph Theory</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G39" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H39" s="5" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Depth-First Search — TOTAL</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr"/>
-      <c r="C39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="n">
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
+      <c r="C43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H43" s="5" t="n">
         <v>45.9</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr"/>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>43.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="7" t="n">
         <v>1</v>
@@ -1756,261 +1756,261 @@
         <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>46.8</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="7" t="n">
+      <c r="C47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Linked List — TOTAL</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr"/>
-      <c r="C47" s="9" t="n">
+      <c r="B48" s="8" t="inlineStr"/>
+      <c r="C48" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D48" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="9" t="n">
+      <c r="E48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G47" s="9" t="inlineStr"/>
-      <c r="H47" s="9" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="G48" s="9" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="n">
+      <c r="C49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H48" s="7" t="n">
+      <c r="H49" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr"/>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
+      <c r="D51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G51" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H51" s="5" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr"/>
-      <c r="C51" s="9" t="n">
+      <c r="B52" s="8" t="inlineStr"/>
+      <c r="C52" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="9" t="n">
+      <c r="D52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G51" s="9" t="inlineStr"/>
-      <c r="H51" s="9" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr"/>
+      <c r="H52" s="9" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="7" t="n">
+      <c r="C53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr"/>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>0</v>
@@ -2019,17 +2019,17 @@
         <v>1</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H54" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
@@ -2045,17 +2045,17 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
@@ -2071,237 +2071,263 @@
         <v>1</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="5" t="n">
+      <c r="C58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H57" s="5" t="n">
+      <c r="H58" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr"/>
-      <c r="C58" s="9" t="n">
+      <c r="B59" s="8" t="inlineStr"/>
+      <c r="C59" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="9" t="n">
+      <c r="D59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G58" s="9" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="G59" s="9" t="inlineStr"/>
+      <c r="H59" s="9" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="5" t="n">
+      <c r="C60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="5" t="n">
+      <c r="C62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr"/>
-      <c r="C62" s="9" t="n">
+      <c r="B63" s="8" t="inlineStr"/>
+      <c r="C63" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="9" t="n">
+      <c r="D63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G62" s="9" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="G63" s="9" t="inlineStr"/>
+      <c r="H63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="5" t="n">
+      <c r="C64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H63" s="5" t="n">
+      <c r="H64" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr"/>
-      <c r="C64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="9" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr"/>
+      <c r="C65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr"/>
-      <c r="C65" s="11" t="n">
+      <c r="B66" s="10" t="inlineStr"/>
+      <c r="C66" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="D65" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="E65" s="11" t="n">
+      <c r="D66" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="E66" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="F65" s="11" t="n">
-        <v>65</v>
-      </c>
-      <c r="G65" s="11" t="inlineStr"/>
-      <c r="H65" s="11" t="inlineStr"/>
+      <c r="F66" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="G66" s="11" t="inlineStr"/>
+      <c r="H66" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2317,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2457,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2507,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2557,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2807,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2907,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3307,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3357,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3407,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4007,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -5673,6 +5699,56 @@
         <v>46288.65751157407</v>
       </c>
       <c r="L69" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>210</v>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Course Schedule II</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Depth-First Search</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Breadth-First Search, Graph Theory, Topological Sort</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J70" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" s="14" t="n">
+        <v>46288.67247685185</v>
+      </c>
+      <c r="L70" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5682,7 +5758,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F69">
+  <conditionalFormatting sqref="F5:F70">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5759,6 +5835,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5770,7 +5847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I186"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6483,7 +6560,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6518,7 +6595,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -6958,7 +7035,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -7973,7 +8050,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -8183,7 +8260,7 @@
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   3 solved   (Low: 0 · Medium: 3 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   4 solved   (Low: 0 · Medium: 4 · High: 0)</t>
         </is>
       </c>
       <c r="B110" s="2" t="n"/>
@@ -8198,7 +8275,7 @@
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B111" s="18" t="n"/>
@@ -8229,11 +8306,11 @@
       <c r="A113" s="5" t="inlineStr"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Course Schedule</t>
+          <t>Course Schedule II</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
@@ -8241,10 +8318,10 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
@@ -8252,7 +8329,7 @@
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>46288.65751157407</v>
+        <v>46288.67247685185</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -8263,7 +8340,7 @@
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B114" s="18" t="n"/>
@@ -8279,7 +8356,7 @@
       <c r="A115" s="19" t="n"/>
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>Medium (Medium) — 2 problem(s)</t>
+          <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C115" s="19" t="n"/>
@@ -8294,236 +8371,236 @@
       <c r="A116" s="5" t="inlineStr"/>
       <c r="B116" s="4" t="inlineStr">
         <is>
+          <t>Course Schedule</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>46288.65751157407</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B117" s="18" t="n"/>
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="18" t="n"/>
+      <c r="E117" s="18" t="n"/>
+      <c r="F117" s="18" t="n"/>
+      <c r="G117" s="18" t="n"/>
+      <c r="H117" s="18" t="n"/>
+      <c r="I117" s="18" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="19" t="n"/>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C118" s="19" t="n"/>
+      <c r="D118" s="19" t="n"/>
+      <c r="E118" s="19" t="n"/>
+      <c r="F118" s="19" t="n"/>
+      <c r="G118" s="19" t="n"/>
+      <c r="H118" s="19" t="n"/>
+      <c r="I118" s="19" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr"/>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C116" s="5" t="n">
+      <c r="C119" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="5" t="n">
+      <c r="E119" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F116" s="5" t="n">
+      <c r="F119" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H116" s="12" t="n">
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="n">
         <v>46287.65729166667</v>
       </c>
-      <c r="I116" s="13" t="inlineStr">
+      <c r="I119" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr"/>
-      <c r="B117" s="6" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr"/>
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C117" s="7" t="n">
+      <c r="C120" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D120" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E117" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="7" t="n">
+      <c r="E120" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H117" s="14" t="n">
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H120" s="14" t="n">
         <v>46287.51434027778</v>
       </c>
-      <c r="I117" s="15" t="inlineStr">
+      <c r="I120" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="17" t="inlineStr">
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="2" t="n"/>
+      <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B119" s="18" t="n"/>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="18" t="n"/>
-      <c r="E119" s="18" t="n"/>
-      <c r="F119" s="18" t="n"/>
-      <c r="G119" s="18" t="n"/>
-      <c r="H119" s="18" t="n"/>
-      <c r="I119" s="18" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="21" t="n"/>
-      <c r="B120" s="22" t="inlineStr">
+      <c r="B122" s="18" t="n"/>
+      <c r="C122" s="18" t="n"/>
+      <c r="D122" s="18" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="18" t="n"/>
+      <c r="G122" s="18" t="n"/>
+      <c r="H122" s="18" t="n"/>
+      <c r="I122" s="18" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="n"/>
+      <c r="B123" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C120" s="21" t="n"/>
-      <c r="D120" s="21" t="n"/>
-      <c r="E120" s="21" t="n"/>
-      <c r="F120" s="21" t="n"/>
-      <c r="G120" s="21" t="n"/>
-      <c r="H120" s="21" t="n"/>
-      <c r="I120" s="21" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr"/>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="C123" s="21" t="n"/>
+      <c r="D123" s="21" t="n"/>
+      <c r="E123" s="21" t="n"/>
+      <c r="F123" s="21" t="n"/>
+      <c r="G123" s="21" t="n"/>
+      <c r="H123" s="21" t="n"/>
+      <c r="I123" s="21" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr"/>
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C124" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="5" t="n">
+      <c r="E124" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H121" s="12" t="n">
+      <c r="H124" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I121" s="13" t="inlineStr">
+      <c r="I124" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="16" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
         </is>
       </c>
-      <c r="B122" s="2" t="n"/>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="2" t="n"/>
-      <c r="F122" s="2" t="n"/>
-      <c r="G122" s="2" t="n"/>
-      <c r="H122" s="2" t="n"/>
-      <c r="I122" s="2" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B123" s="18" t="n"/>
-      <c r="C123" s="18" t="n"/>
-      <c r="D123" s="18" t="n"/>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
-      <c r="G123" s="18" t="n"/>
-      <c r="H123" s="18" t="n"/>
-      <c r="I123" s="18" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="23" t="n"/>
-      <c r="B124" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C124" s="23" t="n"/>
-      <c r="D124" s="23" t="n"/>
-      <c r="E124" s="23" t="n"/>
-      <c r="F124" s="23" t="n"/>
-      <c r="G124" s="23" t="n"/>
-      <c r="H124" s="23" t="n"/>
-      <c r="I124" s="23" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr"/>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Merge k Sorted Lists</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F125" s="5" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="n">
-        <v>46286.43949074074</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="2" t="n"/>
+      <c r="I125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B126" s="18" t="n"/>
@@ -8536,40 +8613,40 @@
       <c r="I126" s="18" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="19" t="n"/>
-      <c r="B127" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C127" s="19" t="n"/>
-      <c r="D127" s="19" t="n"/>
-      <c r="E127" s="19" t="n"/>
-      <c r="F127" s="19" t="n"/>
-      <c r="G127" s="19" t="n"/>
-      <c r="H127" s="19" t="n"/>
-      <c r="I127" s="19" t="n"/>
+      <c r="A127" s="23" t="n"/>
+      <c r="B127" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C127" s="23" t="n"/>
+      <c r="D127" s="23" t="n"/>
+      <c r="E127" s="23" t="n"/>
+      <c r="F127" s="23" t="n"/>
+      <c r="G127" s="23" t="n"/>
+      <c r="H127" s="23" t="n"/>
+      <c r="I127" s="23" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr"/>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List II</t>
+          <t>Merge k Sorted Lists</t>
         </is>
       </c>
       <c r="C128" s="5" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>43.4</v>
+        <v>45.9</v>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
@@ -8577,7 +8654,7 @@
         </is>
       </c>
       <c r="H128" s="12" t="n">
-        <v>46275.41266203704</v>
+        <v>46286.43949074074</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -8588,7 +8665,7 @@
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B129" s="18" t="n"/>
@@ -8601,155 +8678,155 @@
       <c r="I129" s="18" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="21" t="n"/>
-      <c r="B130" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C130" s="21" t="n"/>
-      <c r="D130" s="21" t="n"/>
-      <c r="E130" s="21" t="n"/>
-      <c r="F130" s="21" t="n"/>
-      <c r="G130" s="21" t="n"/>
-      <c r="H130" s="21" t="n"/>
-      <c r="I130" s="21" t="n"/>
+      <c r="A130" s="19" t="n"/>
+      <c r="B130" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="n"/>
+      <c r="D130" s="19" t="n"/>
+      <c r="E130" s="19" t="n"/>
+      <c r="F130" s="19" t="n"/>
+      <c r="G130" s="19" t="n"/>
+      <c r="H130" s="19" t="n"/>
+      <c r="I130" s="19" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr"/>
       <c r="B131" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List II</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>46275.41266203704</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="n"/>
+      <c r="C132" s="18" t="n"/>
+      <c r="D132" s="18" t="n"/>
+      <c r="E132" s="18" t="n"/>
+      <c r="F132" s="18" t="n"/>
+      <c r="G132" s="18" t="n"/>
+      <c r="H132" s="18" t="n"/>
+      <c r="I132" s="18" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="n"/>
+      <c r="B133" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="n"/>
+      <c r="D133" s="21" t="n"/>
+      <c r="E133" s="21" t="n"/>
+      <c r="F133" s="21" t="n"/>
+      <c r="G133" s="21" t="n"/>
+      <c r="H133" s="21" t="n"/>
+      <c r="I133" s="21" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr"/>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C131" s="5" t="n">
+      <c r="C134" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D131" s="5" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E131" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="5" t="n">
+      <c r="E134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="n">
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I131" s="13" t="inlineStr">
+      <c r="I134" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="19" t="n"/>
-      <c r="B132" s="20" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="19" t="n"/>
+      <c r="B135" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C132" s="19" t="n"/>
-      <c r="D132" s="19" t="n"/>
-      <c r="E132" s="19" t="n"/>
-      <c r="F132" s="19" t="n"/>
-      <c r="G132" s="19" t="n"/>
-      <c r="H132" s="19" t="n"/>
-      <c r="I132" s="19" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr"/>
-      <c r="B133" s="4" t="inlineStr">
-        <is>
-          <t>Linked List Cycle II</t>
-        </is>
-      </c>
-      <c r="C133" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="D133" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H133" s="12" t="n">
-        <v>46274.44269675926</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B134" s="18" t="n"/>
-      <c r="C134" s="18" t="n"/>
-      <c r="D134" s="18" t="n"/>
-      <c r="E134" s="18" t="n"/>
-      <c r="F134" s="18" t="n"/>
-      <c r="G134" s="18" t="n"/>
-      <c r="H134" s="18" t="n"/>
-      <c r="I134" s="18" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="21" t="n"/>
-      <c r="B135" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C135" s="21" t="n"/>
-      <c r="D135" s="21" t="n"/>
-      <c r="E135" s="21" t="n"/>
-      <c r="F135" s="21" t="n"/>
-      <c r="G135" s="21" t="n"/>
-      <c r="H135" s="21" t="n"/>
-      <c r="I135" s="21" t="n"/>
+      <c r="C135" s="19" t="n"/>
+      <c r="D135" s="19" t="n"/>
+      <c r="E135" s="19" t="n"/>
+      <c r="F135" s="19" t="n"/>
+      <c r="G135" s="19" t="n"/>
+      <c r="H135" s="19" t="n"/>
+      <c r="I135" s="19" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr"/>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List</t>
+          <t>Linked List Cycle II</t>
         </is>
       </c>
       <c r="C136" s="5" t="n">
-        <v>206</v>
+        <v>142</v>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>44.2</v>
+        <v>46.8</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -8757,7 +8834,7 @@
         </is>
       </c>
       <c r="H136" s="12" t="n">
-        <v>46274.48334490741</v>
+        <v>46274.44269675926</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -8768,7 +8845,7 @@
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B137" s="18" t="n"/>
@@ -8799,121 +8876,121 @@
       <c r="A139" s="5" t="inlineStr"/>
       <c r="B139" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>46274.48334490741</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="n"/>
+      <c r="C140" s="18" t="n"/>
+      <c r="D140" s="18" t="n"/>
+      <c r="E140" s="18" t="n"/>
+      <c r="F140" s="18" t="n"/>
+      <c r="G140" s="18" t="n"/>
+      <c r="H140" s="18" t="n"/>
+      <c r="I140" s="18" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="n"/>
+      <c r="B141" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="n"/>
+      <c r="D141" s="21" t="n"/>
+      <c r="E141" s="21" t="n"/>
+      <c r="F141" s="21" t="n"/>
+      <c r="G141" s="21" t="n"/>
+      <c r="H141" s="21" t="n"/>
+      <c r="I141" s="21" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr"/>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n">
+      <c r="C142" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="5" t="n">
+      <c r="E142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="n">
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I139" s="13" t="inlineStr">
+      <c r="I142" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="16" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B140" s="2" t="n"/>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" s="2" t="n"/>
-      <c r="F140" s="2" t="n"/>
-      <c r="G140" s="2" t="n"/>
-      <c r="H140" s="2" t="n"/>
-      <c r="I140" s="2" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B141" s="18" t="n"/>
-      <c r="C141" s="18" t="n"/>
-      <c r="D141" s="18" t="n"/>
-      <c r="E141" s="18" t="n"/>
-      <c r="F141" s="18" t="n"/>
-      <c r="G141" s="18" t="n"/>
-      <c r="H141" s="18" t="n"/>
-      <c r="I141" s="18" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="21" t="n"/>
-      <c r="B142" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C142" s="21" t="n"/>
-      <c r="D142" s="21" t="n"/>
-      <c r="E142" s="21" t="n"/>
-      <c r="F142" s="21" t="n"/>
-      <c r="G142" s="21" t="n"/>
-      <c r="H142" s="21" t="n"/>
-      <c r="I142" s="21" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr"/>
-      <c r="B143" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G143" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H143" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="n"/>
+      <c r="G143" s="2" t="n"/>
+      <c r="H143" s="2" t="n"/>
+      <c r="I143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B144" s="18" t="n"/>
@@ -8944,11 +9021,11 @@
       <c r="A146" s="5" t="inlineStr"/>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C146" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
@@ -8956,10 +9033,10 @@
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
@@ -8967,7 +9044,7 @@
         </is>
       </c>
       <c r="H146" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -8978,7 +9055,7 @@
     <row r="147">
       <c r="A147" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B147" s="18" t="n"/>
@@ -8994,7 +9071,7 @@
       <c r="A148" s="21" t="n"/>
       <c r="B148" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C148" s="21" t="n"/>
@@ -9009,11 +9086,11 @@
       <c r="A149" s="5" t="inlineStr"/>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C149" s="5" t="n">
-        <v>3918</v>
+        <v>3626</v>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
@@ -9024,15 +9101,15 @@
         <v>1</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H149" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="I149" s="13" t="inlineStr">
         <is>
@@ -9041,174 +9118,174 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="7" t="inlineStr"/>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>Count Commas in Range</t>
-        </is>
-      </c>
-      <c r="C150" s="7" t="n">
-        <v>4245</v>
-      </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E150" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H150" s="14" t="n">
-        <v>46273.3956712963</v>
-      </c>
-      <c r="I150" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A150" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="n"/>
+      <c r="C150" s="18" t="n"/>
+      <c r="D150" s="18" t="n"/>
+      <c r="E150" s="18" t="n"/>
+      <c r="F150" s="18" t="n"/>
+      <c r="G150" s="18" t="n"/>
+      <c r="H150" s="18" t="n"/>
+      <c r="I150" s="18" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="19" t="n"/>
-      <c r="B151" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C151" s="19" t="n"/>
-      <c r="D151" s="19" t="n"/>
-      <c r="E151" s="19" t="n"/>
-      <c r="F151" s="19" t="n"/>
-      <c r="G151" s="19" t="n"/>
-      <c r="H151" s="19" t="n"/>
-      <c r="I151" s="19" t="n"/>
+      <c r="A151" s="21" t="n"/>
+      <c r="B151" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C151" s="21" t="n"/>
+      <c r="D151" s="21" t="n"/>
+      <c r="E151" s="21" t="n"/>
+      <c r="F151" s="21" t="n"/>
+      <c r="G151" s="21" t="n"/>
+      <c r="H151" s="21" t="n"/>
+      <c r="I151" s="21" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr"/>
       <c r="B152" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H152" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr"/>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H153" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="19" t="n"/>
+      <c r="B154" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C154" s="19" t="n"/>
+      <c r="D154" s="19" t="n"/>
+      <c r="E154" s="19" t="n"/>
+      <c r="F154" s="19" t="n"/>
+      <c r="G154" s="19" t="n"/>
+      <c r="H154" s="19" t="n"/>
+      <c r="I154" s="19" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="5" t="inlineStr"/>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C152" s="5" t="n">
+      <c r="C155" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E152" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" s="5" t="n">
+      <c r="E155" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H152" s="12" t="n">
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I152" s="13" t="inlineStr">
+      <c r="I155" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="16" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B153" s="2" t="n"/>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" s="2" t="n"/>
-      <c r="F153" s="2" t="n"/>
-      <c r="G153" s="2" t="n"/>
-      <c r="H153" s="2" t="n"/>
-      <c r="I153" s="2" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B154" s="18" t="n"/>
-      <c r="C154" s="18" t="n"/>
-      <c r="D154" s="18" t="n"/>
-      <c r="E154" s="18" t="n"/>
-      <c r="F154" s="18" t="n"/>
-      <c r="G154" s="18" t="n"/>
-      <c r="H154" s="18" t="n"/>
-      <c r="I154" s="18" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="21" t="n"/>
-      <c r="B155" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C155" s="21" t="n"/>
-      <c r="D155" s="21" t="n"/>
-      <c r="E155" s="21" t="n"/>
-      <c r="F155" s="21" t="n"/>
-      <c r="G155" s="21" t="n"/>
-      <c r="H155" s="21" t="n"/>
-      <c r="I155" s="21" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="5" t="inlineStr"/>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C156" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F156" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G156" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H156" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I156" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="n"/>
+      <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B157" s="18" t="n"/>
@@ -9221,40 +9298,40 @@
       <c r="I157" s="18" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="19" t="n"/>
-      <c r="B158" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C158" s="19" t="n"/>
-      <c r="D158" s="19" t="n"/>
-      <c r="E158" s="19" t="n"/>
-      <c r="F158" s="19" t="n"/>
-      <c r="G158" s="19" t="n"/>
-      <c r="H158" s="19" t="n"/>
-      <c r="I158" s="19" t="n"/>
+      <c r="A158" s="21" t="n"/>
+      <c r="B158" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C158" s="21" t="n"/>
+      <c r="D158" s="21" t="n"/>
+      <c r="E158" s="21" t="n"/>
+      <c r="F158" s="21" t="n"/>
+      <c r="G158" s="21" t="n"/>
+      <c r="H158" s="21" t="n"/>
+      <c r="I158" s="21" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr"/>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C159" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
@@ -9262,7 +9339,7 @@
         </is>
       </c>
       <c r="H159" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -9273,7 +9350,7 @@
     <row r="160">
       <c r="A160" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B160" s="18" t="n"/>
@@ -9286,48 +9363,48 @@
       <c r="I160" s="18" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="21" t="n"/>
-      <c r="B161" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C161" s="21" t="n"/>
-      <c r="D161" s="21" t="n"/>
-      <c r="E161" s="21" t="n"/>
-      <c r="F161" s="21" t="n"/>
-      <c r="G161" s="21" t="n"/>
-      <c r="H161" s="21" t="n"/>
-      <c r="I161" s="21" t="n"/>
+      <c r="A161" s="19" t="n"/>
+      <c r="B161" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C161" s="19" t="n"/>
+      <c r="D161" s="19" t="n"/>
+      <c r="E161" s="19" t="n"/>
+      <c r="F161" s="19" t="n"/>
+      <c r="G161" s="19" t="n"/>
+      <c r="H161" s="19" t="n"/>
+      <c r="I161" s="19" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr"/>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C162" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H162" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -9338,7 +9415,7 @@
     <row r="163">
       <c r="A163" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B163" s="18" t="n"/>
@@ -9369,11 +9446,11 @@
       <c r="A165" s="5" t="inlineStr"/>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Reverse Degree of a String</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C165" s="5" t="n">
-        <v>3811</v>
+        <v>242</v>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
@@ -9381,10 +9458,10 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
@@ -9392,7 +9469,7 @@
         </is>
       </c>
       <c r="H165" s="12" t="n">
-        <v>46285.42987268518</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I165" s="13" t="inlineStr">
         <is>
@@ -9403,7 +9480,7 @@
     <row r="166">
       <c r="A166" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B166" s="18" t="n"/>
@@ -9434,11 +9511,11 @@
       <c r="A168" s="5" t="inlineStr"/>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Reverse Degree of a String</t>
         </is>
       </c>
       <c r="C168" s="5" t="n">
-        <v>125</v>
+        <v>3811</v>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
@@ -9446,18 +9523,18 @@
         </is>
       </c>
       <c r="E168" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H168" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46285.42987268518</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -9468,7 +9545,7 @@
     <row r="169">
       <c r="A169" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B169" s="18" t="n"/>
@@ -9499,121 +9576,121 @@
       <c r="A171" s="5" t="inlineStr"/>
       <c r="B171" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H171" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B172" s="18" t="n"/>
+      <c r="C172" s="18" t="n"/>
+      <c r="D172" s="18" t="n"/>
+      <c r="E172" s="18" t="n"/>
+      <c r="F172" s="18" t="n"/>
+      <c r="G172" s="18" t="n"/>
+      <c r="H172" s="18" t="n"/>
+      <c r="I172" s="18" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="21" t="n"/>
+      <c r="B173" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C173" s="21" t="n"/>
+      <c r="D173" s="21" t="n"/>
+      <c r="E173" s="21" t="n"/>
+      <c r="F173" s="21" t="n"/>
+      <c r="G173" s="21" t="n"/>
+      <c r="H173" s="21" t="n"/>
+      <c r="I173" s="21" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="inlineStr"/>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C171" s="5" t="n">
+      <c r="C174" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D174" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E171" s="5" t="n">
+      <c r="E174" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F171" s="5" t="n">
+      <c r="F174" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G171" s="5" t="inlineStr">
+      <c r="G174" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H171" s="12" t="n">
+      <c r="H174" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I171" s="13" t="inlineStr">
+      <c r="I174" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="16" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B172" s="2" t="n"/>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n"/>
-      <c r="E172" s="2" t="n"/>
-      <c r="F172" s="2" t="n"/>
-      <c r="G172" s="2" t="n"/>
-      <c r="H172" s="2" t="n"/>
-      <c r="I172" s="2" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B173" s="18" t="n"/>
-      <c r="C173" s="18" t="n"/>
-      <c r="D173" s="18" t="n"/>
-      <c r="E173" s="18" t="n"/>
-      <c r="F173" s="18" t="n"/>
-      <c r="G173" s="18" t="n"/>
-      <c r="H173" s="18" t="n"/>
-      <c r="I173" s="18" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="21" t="n"/>
-      <c r="B174" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C174" s="21" t="n"/>
-      <c r="D174" s="21" t="n"/>
-      <c r="E174" s="21" t="n"/>
-      <c r="F174" s="21" t="n"/>
-      <c r="G174" s="21" t="n"/>
-      <c r="H174" s="21" t="n"/>
-      <c r="I174" s="21" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="5" t="inlineStr"/>
-      <c r="B175" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C175" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D175" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G175" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H175" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I175" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="2" t="n"/>
+      <c r="G175" s="2" t="n"/>
+      <c r="H175" s="2" t="n"/>
+      <c r="I175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B176" s="18" t="n"/>
@@ -9629,7 +9706,7 @@
       <c r="A177" s="21" t="n"/>
       <c r="B177" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C177" s="21" t="n"/>
@@ -9644,226 +9721,290 @@
       <c r="A178" s="5" t="inlineStr"/>
       <c r="B178" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E178" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H178" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B179" s="18" t="n"/>
+      <c r="C179" s="18" t="n"/>
+      <c r="D179" s="18" t="n"/>
+      <c r="E179" s="18" t="n"/>
+      <c r="F179" s="18" t="n"/>
+      <c r="G179" s="18" t="n"/>
+      <c r="H179" s="18" t="n"/>
+      <c r="I179" s="18" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="21" t="n"/>
+      <c r="B180" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C180" s="21" t="n"/>
+      <c r="D180" s="21" t="n"/>
+      <c r="E180" s="21" t="n"/>
+      <c r="F180" s="21" t="n"/>
+      <c r="G180" s="21" t="n"/>
+      <c r="H180" s="21" t="n"/>
+      <c r="I180" s="21" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr"/>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C178" s="5" t="n">
+      <c r="C181" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D181" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E178" s="5" t="n">
+      <c r="E181" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F178" s="5" t="n">
+      <c r="F181" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G178" s="5" t="inlineStr">
+      <c r="G181" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H178" s="12" t="n">
+      <c r="H181" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I178" s="13" t="inlineStr">
+      <c r="I181" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="7" t="inlineStr"/>
-      <c r="B179" s="6" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr"/>
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C179" s="7" t="n">
+      <c r="C182" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D179" s="7" t="inlineStr">
+      <c r="D182" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E179" s="7" t="n">
+      <c r="E182" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F179" s="7" t="n">
+      <c r="F182" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G179" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H179" s="14" t="n">
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H182" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I179" s="15" t="inlineStr">
+      <c r="I182" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="17" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B180" s="18" t="n"/>
-      <c r="C180" s="18" t="n"/>
-      <c r="D180" s="18" t="n"/>
-      <c r="E180" s="18" t="n"/>
-      <c r="F180" s="18" t="n"/>
-      <c r="G180" s="18" t="n"/>
-      <c r="H180" s="18" t="n"/>
-      <c r="I180" s="18" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="21" t="n"/>
-      <c r="B181" s="22" t="inlineStr">
+      <c r="B183" s="18" t="n"/>
+      <c r="C183" s="18" t="n"/>
+      <c r="D183" s="18" t="n"/>
+      <c r="E183" s="18" t="n"/>
+      <c r="F183" s="18" t="n"/>
+      <c r="G183" s="18" t="n"/>
+      <c r="H183" s="18" t="n"/>
+      <c r="I183" s="18" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="21" t="n"/>
+      <c r="B184" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C181" s="21" t="n"/>
-      <c r="D181" s="21" t="n"/>
-      <c r="E181" s="21" t="n"/>
-      <c r="F181" s="21" t="n"/>
-      <c r="G181" s="21" t="n"/>
-      <c r="H181" s="21" t="n"/>
-      <c r="I181" s="21" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="inlineStr"/>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="C184" s="21" t="n"/>
+      <c r="D184" s="21" t="n"/>
+      <c r="E184" s="21" t="n"/>
+      <c r="F184" s="21" t="n"/>
+      <c r="G184" s="21" t="n"/>
+      <c r="H184" s="21" t="n"/>
+      <c r="I184" s="21" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr"/>
+      <c r="B185" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C182" s="5" t="n">
+      <c r="C185" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D182" s="5" t="inlineStr">
+      <c r="D185" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E182" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" s="5" t="n">
+      <c r="E185" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G182" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H182" s="12" t="n">
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H185" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I182" s="13" t="inlineStr">
+      <c r="I185" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="16" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B183" s="2" t="n"/>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n"/>
-      <c r="E183" s="2" t="n"/>
-      <c r="F183" s="2" t="n"/>
-      <c r="G183" s="2" t="n"/>
-      <c r="H183" s="2" t="n"/>
-      <c r="I183" s="2" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="17" t="inlineStr">
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="2" t="n"/>
+      <c r="G186" s="2" t="n"/>
+      <c r="H186" s="2" t="n"/>
+      <c r="I186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B184" s="18" t="n"/>
-      <c r="C184" s="18" t="n"/>
-      <c r="D184" s="18" t="n"/>
-      <c r="E184" s="18" t="n"/>
-      <c r="F184" s="18" t="n"/>
-      <c r="G184" s="18" t="n"/>
-      <c r="H184" s="18" t="n"/>
-      <c r="I184" s="18" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="21" t="n"/>
-      <c r="B185" s="22" t="inlineStr">
+      <c r="B187" s="18" t="n"/>
+      <c r="C187" s="18" t="n"/>
+      <c r="D187" s="18" t="n"/>
+      <c r="E187" s="18" t="n"/>
+      <c r="F187" s="18" t="n"/>
+      <c r="G187" s="18" t="n"/>
+      <c r="H187" s="18" t="n"/>
+      <c r="I187" s="18" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="21" t="n"/>
+      <c r="B188" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C185" s="21" t="n"/>
-      <c r="D185" s="21" t="n"/>
-      <c r="E185" s="21" t="n"/>
-      <c r="F185" s="21" t="n"/>
-      <c r="G185" s="21" t="n"/>
-      <c r="H185" s="21" t="n"/>
-      <c r="I185" s="21" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="inlineStr"/>
-      <c r="B186" s="4" t="inlineStr">
+      <c r="C188" s="21" t="n"/>
+      <c r="D188" s="21" t="n"/>
+      <c r="E188" s="21" t="n"/>
+      <c r="F188" s="21" t="n"/>
+      <c r="G188" s="21" t="n"/>
+      <c r="H188" s="21" t="n"/>
+      <c r="I188" s="21" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr"/>
+      <c r="B189" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C186" s="5" t="n">
+      <c r="C189" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E186" s="5" t="n">
+      <c r="E189" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F186" s="5" t="n">
+      <c r="F189" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G186" s="5" t="inlineStr">
+      <c r="G189" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H186" s="12" t="n">
+      <c r="H189" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I186" s="13" t="inlineStr">
+      <c r="I189" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="119">
+  <mergeCells count="121">
     <mergeCell ref="B135:I135"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A172:I172"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A154:I154"/>
     <mergeCell ref="A163:I163"/>
     <mergeCell ref="A101:I101"/>
     <mergeCell ref="B167:I167"/>
@@ -9872,15 +10013,14 @@
     <mergeCell ref="B161:I161"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A17:I17"/>
-    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="B145:I145"/>
     <mergeCell ref="A126:I126"/>
     <mergeCell ref="B98:I98"/>
-    <mergeCell ref="B145:I145"/>
     <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
-    <mergeCell ref="B181:I181"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A117:I117"/>
     <mergeCell ref="A111:I111"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
@@ -9888,24 +10028,25 @@
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B83:I83"/>
     <mergeCell ref="A169:I169"/>
+    <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A153:I153"/>
+    <mergeCell ref="B173:I173"/>
     <mergeCell ref="A137:I137"/>
+    <mergeCell ref="B141:I141"/>
     <mergeCell ref="B115:I115"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A179:I179"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="B86:I86"/>
     <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A184:I184"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="A180:I180"/>
-    <mergeCell ref="A173:I173"/>
+    <mergeCell ref="A143:I143"/>
     <mergeCell ref="A157:I157"/>
     <mergeCell ref="A166:I166"/>
     <mergeCell ref="B177:I177"/>
@@ -9914,6 +10055,7 @@
     <mergeCell ref="B164:I164"/>
     <mergeCell ref="A94:I94"/>
     <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B154:I154"/>
     <mergeCell ref="A183:I183"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="B138:I138"/>
@@ -9921,8 +10063,9 @@
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="B155:I155"/>
+    <mergeCell ref="B180:I180"/>
     <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A175:I175"/>
     <mergeCell ref="B130:I130"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
@@ -9931,30 +10074,29 @@
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="B151:I151"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="B132:I132"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A147:I147"/>
+    <mergeCell ref="A156:I156"/>
     <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B174:I174"/>
     <mergeCell ref="B112:I112"/>
+    <mergeCell ref="B118:I118"/>
     <mergeCell ref="B127:I127"/>
     <mergeCell ref="B158:I158"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
-    <mergeCell ref="A123:I123"/>
     <mergeCell ref="B95:I95"/>
     <mergeCell ref="B89:I89"/>
+    <mergeCell ref="A132:I132"/>
     <mergeCell ref="A110:I110"/>
-    <mergeCell ref="A119:I119"/>
-    <mergeCell ref="B185:I185"/>
-    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A187:I187"/>
     <mergeCell ref="A50:I50"/>
+    <mergeCell ref="B184:I184"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A160:I160"/>
-    <mergeCell ref="A141:I141"/>
     <mergeCell ref="B42:I42"/>
+    <mergeCell ref="A150:I150"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="A144:I144"/>
     <mergeCell ref="A122:I122"/>
@@ -9962,20 +10104,22 @@
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="B170:I170"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A125:I125"/>
     <mergeCell ref="B148:I148"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A121:I121"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A176:I176"/>
     <mergeCell ref="B108:I108"/>
     <mergeCell ref="A114:I114"/>
+    <mergeCell ref="A186:I186"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A107:I107"/>
-    <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
+    <mergeCell ref="B133:I133"/>
     <mergeCell ref="A88:I88"/>
-    <mergeCell ref="B142:I142"/>
     <mergeCell ref="B80:I80"/>
+    <mergeCell ref="B188:I188"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -10019,30 +10163,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId66"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10054,7 +10199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10109,7 +10254,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="560" customHeight="1">
+    <row r="5" ht="196" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10123,126 +10268,117 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] nums, int target) {
+        int[] arr=new int[2];
+       	 for(int i=0;i&lt;nums.length;i++) { 
+		 for(int j=i+1;j&lt;nums.length;j++) { 
+			 if(nums[i]+nums[j]==target) { 
+				arr[0]=i;
+                arr[1]=j;
+			 }
+		 }
+	 }
+     return arr;
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="504" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
-&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
-&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 1
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
+Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
 &lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="252" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>class Solution {
-    public int lengthOfLongestSubstring(String s) {
-    int left =0;
-    int max = 0;
-    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
-    for(int right =0;right&lt;s.length();right++){
-         char currentChar = s.charAt(right);
-          while(hs.contains(s.charAt(right))){
-            hs.remove(s.charAt(left));
-            left++;
-          }
-          hs.add(s.charAt(right));
-          max = Math.max(max,right-left +1); 
+    public static int rever(int num){
+        int rev =0;
+        while(num != 0){
+            int rem = num%10;
+            if(rev&gt;Integer.MAX_VALUE/10) return 0;
+            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
+            rev=rev*10+rem;
+            num/=10;
+        }
+        return rev;
     }
-    return max;
+    public int reverse(int x) {
+    // int i=0;
+    // if(x&gt;=0)  i=1;
+    // else i = -1;
+    int num = rever(x);
+    return num;
     }
 }</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="462" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 123
-&lt;strong&gt;Output:&lt;/strong&gt; 321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = -123
-&lt;strong&gt;Output:&lt;/strong&gt; -321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 120
-&lt;strong&gt;Output:&lt;/strong&gt; 21
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10680,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="532" customHeight="1">
+    <row r="15" ht="210" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10558,40 +10694,26 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 5
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 4
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 6
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public int lengthOfLastWord(String s) {
+    char[] ch =s.toCharArray();
+    int count=0;
+    int i = s.length()-1;
+    while(s.charAt(i) == ' '){
+        i--;
+    }
+    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
+        count++;
+        i--;
+    }
+    return count;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10788,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="560" customHeight="1">
+    <row r="17" ht="420" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10680,45 +10802,39 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    public  void inorder(TreeNode root,List list){
+    if(root == null) return;
+    inorder(root.left,list);
+    list.add(root.val);
+    inorder(root.right,list);
+    }
+    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
+    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
+    inorder(root,list);
+    return list;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -11351,24 +11467,95 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="238" customHeight="1">
+    <row r="31" ht="560" customHeight="1">
       <c r="A31" s="5" t="n">
         <v>27</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
+          <t>Course Schedule II</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {public class TopologicalSortUsingKhansAlgorithm {
+	int[] indegree;
+	boolean[] visited;
+	public TopologicalSortUsingKhansAlgorithm(int vertices) {
+		visited = new boolean[vertices];
+		indegree = new int[vertices];
+	}
+	public int[] topoligicalSort(int[][] edges) {
+        int count =0;
+		Queue&lt;Integer&gt; queue = new LinkedList&lt;&gt;();
+		ArrayList&lt;Integer&gt; result = new ArrayList&lt;&gt;();
+		List&lt;Integer&gt;[] graph = new ArrayList[indegree.length];
+		for(int i=0; i&lt;visited.length; i++) {
+		    graph[i] = new ArrayList&lt;&gt;();
+		}
+		for(int[] edge:edges) {
+			graph[edge[0]].add(edge[1]);
+				indegree[edge[1]]++;
+		}
+		for(int i=0;i&lt;indegree.length;i++) {
+			if(indegree[i] == 0) {
+				queue.add(i);
+			}
+		}
+		while(!queue.isEmpty()) {
+			int current = queue.poll();
+			result.add(current);
+            count++;
+			for(int neighbour:graph[current]) {
+			       indegree[neighbour]--;	
+			       if(indegree[neighbour] == 0) {
+			    	       queue.add(neighbour);
+			       }
+			}
+		}
+		int[] arr = new int[result.size()];
+        int j = result.size()-1;
+        for (int i = 0; i &lt; result.size(); i++) {
+        arr[j] = result.get(i);
+        j--;
+        }
+		return arr=(count == indegree.length)?arr:new int[0];
+	}
+}
+    public int[] findOrder(int numCourses, int[][] prerequisites) {
+     TopologicalSortUsingKhansAlgorithm tsort = new  TopologicalSortUsingKhansAlgorithm(numCourses);
+    return tsort.topoligicalSort(prerequisites);  
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="238" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>219</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -11390,24 +11577,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="322" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="322" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Sliding Window Maximum</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>239</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] maxSlidingWindow(int[] nums, int k) {
@@ -11431,24 +11618,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="392" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="392" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -11481,59 +11668,64 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="182" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Move Zeroes</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>283</v>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public void moveZeroes(int[] nums) {
-    int numbers = 0;
-    for(int traverse = 0;traverse&lt;nums.length;traverse++){
-        if(nums[traverse] != 0){
-            int temp = nums[traverse];
-            nums[traverse] = nums[numbers];
-            nums[numbers] = temp;
-            numbers++;
-        }
-    }  
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="476" customHeight="1">
+    <row r="35" ht="308" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>Move Zeroes</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
+&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
+&lt;strong&gt;Output:&lt;/strong&gt; [0]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="476" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
           <t>Find the Duplicate Number</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>287</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int findDuplicate(int[] nums) {
@@ -11571,24 +11763,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="308" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="308" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -11612,24 +11804,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="420" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="420" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>304</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -11661,24 +11853,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="308" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="308" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Find All Duplicates in an Array</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>442</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public List&lt;Integer&gt; findDuplicates(int[] nums) {
@@ -11705,24 +11897,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="322" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="322" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>503</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElements(int[] nums) {
@@ -11747,24 +11939,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="546" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="546" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11802,24 +11994,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="560" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="560" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>547</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public class Uniounandfind {
@@ -11871,24 +12063,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="182" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="182" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -11906,24 +12098,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="546" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="546" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -11967,24 +12159,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="196" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="196" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -12003,24 +12195,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="462" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="462" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -12050,24 +12242,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="518" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="518" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>684</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>class Solution {
  class UniounFind{
@@ -12107,24 +12299,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="252" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="252" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>739</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -12144,24 +12336,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="378" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="378" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -12193,24 +12385,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="294" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="294" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>908</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -12236,24 +12428,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="560" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="560" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -12289,64 +12481,67 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="294" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Valid Boomerang</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>1115</v>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
-&lt;strong&gt;Output:&lt;/strong&gt; true
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
-&lt;strong&gt;Output:&lt;/strong&gt; false
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="224" customHeight="1">
+    <row r="52" ht="294" customHeight="1">
       <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>Valid Boomerang</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public boolean isBoomerang(int[][] points) {
+    int x1=0,x2=0,x3=0;
+    int y1=0,y2=0,y3=0;
+    for(int i =0;i&lt;points.length;i++){
+        for(int j=0;j&lt;points[i].length-1;j++){
+           if(i==0){
+            x1 = points[i][j];
+            y1 = points[i][j+1];
+           }else if(i == 1){
+             x2 = points[i][j];
+             y2 = points[i][j+1];
+           }else{
+            x3 = points[i][j];
+            y3 = points[i][j+1];
+           }
+        }
+    } 
+    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="224" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -12367,24 +12562,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="420" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="420" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -12419,24 +12614,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="378" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="378" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -12468,24 +12663,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="266" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="266" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>1570</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -12509,24 +12704,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="350" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="350" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -12556,24 +12751,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="238" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="238" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -12595,24 +12790,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="308" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="308" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -12639,24 +12834,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="280" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="280" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -12679,24 +12874,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="448" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="448" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -12731,24 +12926,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="378" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="378" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -12780,58 +12975,17 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="266" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>Smallest Divisible Digit Product I</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>3626</v>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int digits(int num){
-        int multiply =1;
-        while(num!=0){
-            int rem = num%10;
-            multiply *= rem;
-            num /= 10;
-        }
-        return multiply;
-    }
-    public int smallestNumber(int n, int t) {
-    while(true){
-        if(digits(n)%t == 0){
-          return n;
-        } 
-        n++;
-    }
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="560" customHeight="1">
+    <row r="63" ht="490" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>59</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Find the Largest Almost Missing Integer</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C63" s="5" t="n">
-        <v>3705</v>
+        <v>3626</v>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
@@ -12840,75 +12994,93 @@
       </c>
       <c r="E63" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
-A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
+          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
+&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
         </is>
       </c>
     </row>
-    <row r="64" ht="196" customHeight="1">
+    <row r="64" ht="308" customHeight="1">
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int largestInteger(int[] nums, int k) {
+    int[] arr = new int[51];
+    for(int i = 0;i&lt;nums.length-k+1;i++){
+        boolean[] seen = new boolean[51];
+        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
+            if (!seen[nums[j]]){
+               arr[nums[j]]++;
+               seen[nums[j]] = true;
+            } 
+        }
+    } 
+    int high =-1;
+    for(int i=0;i&lt;arr.length;i++){
+        if(arr[i] == 1){
+           if(high&lt;i) high = i;
+        }
+    } 
+    return high;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="196" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>3811</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -12926,24 +13098,24 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="238" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="238" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -12963,24 +13135,24 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="252" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="67" ht="252" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C67" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -13003,24 +13175,24 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="140" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+    <row r="68" ht="140" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C68" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -13034,24 +13206,24 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="294" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="69" ht="294" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C69" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -13077,24 +13249,24 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="252" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+    <row r="70" ht="252" customHeight="1">
+      <c r="A70" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C70" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -13195,13 +13367,13 @@
         <v>36</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -13233,13 +13405,13 @@
         <v>36</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H149" s="12" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H155" s="12" t="n">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H159" s="12" t="n">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H162" s="12" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H185" s="12" t="n">
@@ -10254,7 +10254,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="196" customHeight="1">
+    <row r="5" ht="560" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10268,117 +10268,126 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int[] twoSum(int[] nums, int target) {
-        int[] arr=new int[2];
-       	 for(int i=0;i&lt;nums.length;i++) { 
-		 for(int j=i+1;j&lt;nums.length;j++) { 
-			 if(nums[i]+nums[j]==target) { 
-				arr[0]=i;
-                arr[1]=j;
-			 }
-		 }
-	 }
-     return arr;
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="504" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
+          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
+&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 1
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
-Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="252" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int lengthOfLongestSubstring(String s) {
+    int left =0;
+    int max = 0;
+    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
+    for(int right =0;right&lt;s.length();right++){
+         char currentChar = s.charAt(right);
+          while(hs.contains(s.charAt(right))){
+            hs.remove(s.charAt(left));
+            left++;
+          }
+          hs.add(s.charAt(right));
+          max = Math.max(max,right-left +1); 
+    }
+    return max;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="462" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 123
+&lt;strong&gt;Output:&lt;/strong&gt; 321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = -123
+&lt;strong&gt;Output:&lt;/strong&gt; -321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 120
+&lt;strong&gt;Output:&lt;/strong&gt; 21
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int rever(int num){
-        int rev =0;
-        while(num != 0){
-            int rem = num%10;
-            if(rev&gt;Integer.MAX_VALUE/10) return 0;
-            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
-            rev=rev*10+rem;
-            num/=10;
-        }
-        return rev;
-    }
-    public int reverse(int x) {
-    // int i=0;
-    // if(x&gt;=0)  i=1;
-    // else i = -1;
-    int num = rever(x);
-    return num;
-    }
-}</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10689,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="210" customHeight="1">
+    <row r="15" ht="532" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10694,26 +10703,40 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int lengthOfLastWord(String s) {
-    char[] ch =s.toCharArray();
-    int count=0;
-    int i = s.length()-1;
-    while(s.charAt(i) == ' '){
-        i--;
-    }
-    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
-        count++;
-        i--;
-    }
-    return count;
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 5
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 4
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 6
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10811,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="420" customHeight="1">
+    <row r="17" ht="560" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10802,39 +10825,45 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>/**
- * Definition for a binary tree node.
- * public class TreeNode {
- *     int val;
- *     TreeNode left;
- *     TreeNode right;
- *     TreeNode() {}
- *     TreeNode(int val) { this.val = val; }
- *     TreeNode(int val, TreeNode left, TreeNode right) {
- *         this.val = val;
- *         this.left = left;
- *         this.right = right;
- *     }
- * }
- */
-class Solution {
-    public  void inorder(TreeNode root,List list){
-    if(root == null) return;
-    inorder(root.left,list);
-    list.add(root.val);
-    inorder(root.right,list);
-    }
-    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
-    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
-    inorder(root,list);
-    return list;
-    }
-}</t>
+          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11697,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="308" customHeight="1">
+    <row r="35" ht="182" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
@@ -11682,29 +11711,24 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
-&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
-&lt;strong&gt;Output:&lt;/strong&gt; [0]
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
+          <t>class Solution {
+    public void moveZeroes(int[] nums) {
+    int numbers = 0;
+    for(int traverse = 0;traverse&lt;nums.length;traverse++){
+        if(nums[traverse] != 0){
+            int temp = nums[traverse];
+            nums[traverse] = nums[numbers];
+            nums[numbers] = temp;
+            numbers++;
+        }
+    }  
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12495,32 +12519,29 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t>class Solution {
-    public boolean isBoomerang(int[][] points) {
-    int x1=0,x2=0,x3=0;
-    int y1=0,y2=0,y3=0;
-    for(int i =0;i&lt;points.length;i++){
-        for(int j=0;j&lt;points[i].length-1;j++){
-           if(i==0){
-            x1 = points[i][j];
-            y1 = points[i][j+1];
-           }else if(i == 1){
-             x2 = points[i][j];
-             y2 = points[i][j+1];
-           }else{
-            x3 = points[i][j];
-            y3 = points[i][j+1];
-           }
-        }
-    } 
-    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -12975,7 +12996,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="490" customHeight="1">
+    <row r="63" ht="266" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>59</v>
       </c>
@@ -12989,77 +13010,100 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static int digits(int num){
+        int multiply =1;
+        while(num!=0){
+            int rem = num%10;
+            multiply *= rem;
+            num /= 10;
+        }
+        return multiply;
+    }
+    public int smallestNumber(int n, int t) {
+    while(true){
+        if(digits(n)%t == 0){
+          return n;
+        } 
+        n++;
+    }
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="560" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E63" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
+A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="308" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public int largestInteger(int[] nums, int k) {
-    int[] arr = new int[51];
-    for(int i = 0;i&lt;nums.length-k+1;i++){
-        boolean[] seen = new boolean[51];
-        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
-            if (!seen[nums[j]]){
-               arr[nums[j]]++;
-               seen[nums[j]] = true;
-            } 
-        }
-    } 
-    int high =-1;
-    for(int i=0;i&lt;arr.length;i++){
-        if(arr[i] == 1){
-           if(high&lt;i) high = i;
-        }
-    } 
-    return high;
-    }
-}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -4993,7 +4993,7 @@
         <v>46.9</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>46274.42709490741</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H149" s="12" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H155" s="12" t="n">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H159" s="12" t="n">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H162" s="12" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H185" s="12" t="n">
@@ -10254,7 +10254,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="560" customHeight="1">
+    <row r="5" ht="196" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10268,126 +10268,117 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] nums, int target) {
+        int[] arr=new int[2];
+       	 for(int i=0;i&lt;nums.length;i++) { 
+		 for(int j=i+1;j&lt;nums.length;j++) { 
+			 if(nums[i]+nums[j]==target) { 
+				arr[0]=i;
+                arr[1]=j;
+			 }
+		 }
+	 }
+     return arr;
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="504" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
-&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
-&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 1
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
+Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
 &lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="252" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>class Solution {
-    public int lengthOfLongestSubstring(String s) {
-    int left =0;
-    int max = 0;
-    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
-    for(int right =0;right&lt;s.length();right++){
-         char currentChar = s.charAt(right);
-          while(hs.contains(s.charAt(right))){
-            hs.remove(s.charAt(left));
-            left++;
-          }
-          hs.add(s.charAt(right));
-          max = Math.max(max,right-left +1); 
+    public static int rever(int num){
+        int rev =0;
+        while(num != 0){
+            int rem = num%10;
+            if(rev&gt;Integer.MAX_VALUE/10) return 0;
+            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
+            rev=rev*10+rem;
+            num/=10;
+        }
+        return rev;
     }
-    return max;
+    public int reverse(int x) {
+    // int i=0;
+    // if(x&gt;=0)  i=1;
+    // else i = -1;
+    int num = rever(x);
+    return num;
     }
 }</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="462" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 123
-&lt;strong&gt;Output:&lt;/strong&gt; 321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = -123
-&lt;strong&gt;Output:&lt;/strong&gt; -321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 120
-&lt;strong&gt;Output:&lt;/strong&gt; 21
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10680,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="532" customHeight="1">
+    <row r="15" ht="210" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10703,40 +10694,26 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 5
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 4
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 6
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public int lengthOfLastWord(String s) {
+    char[] ch =s.toCharArray();
+    int count=0;
+    int i = s.length()-1;
+    while(s.charAt(i) == ' '){
+        i--;
+    }
+    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
+        count++;
+        i--;
+    }
+    return count;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -10811,7 +10788,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="560" customHeight="1">
+    <row r="17" ht="420" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10825,45 +10802,39 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    public  void inorder(TreeNode root,List list){
+    if(root == null) return;
+    inorder(root.left,list);
+    list.add(root.val);
+    inorder(root.right,list);
+    }
+    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
+    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
+    inorder(root,list);
+    return list;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -11118,32 +11089,42 @@
  */
 public class Solution {
     public boolean hasCycle(ListNode head) {
-        if(head == null){
-        return false;
-    }
-    ListNode slowPointer = head;
-    ListNode fastPointer = head;
-    while(fastPointer != null &amp;&amp; fastPointer.next!= null){
-		 slowPointer = slowPointer.next;
-		 fastPointer = fastPointer.next.next;
-             if(slowPointer == fastPointer) {
-			 return true;
-		 }
-	  }
-	  return false;
-    // if(head == null){
+    //     if(head == null){
     //     return false;
     // }
-    // HashSet&lt;ListNode&gt; hs = new HashSet&lt;&gt;();
-    // ListNode temp = head;
-    // while(temp.next != null){
-    //     if(hs.contains(temp)){
-    //         return true;
-    //     }
-    //     hs.add(temp);
-    //     temp = temp.next;
-    // }
-    // return false;  
+    // ListNode slowPointer = head;
+    // ListNode fastPointer = head;
+    // while(fastPointer != null &amp;&amp; fastPointer.next!= null){
+	// 	 slowPointer = slowPointer.next;
+	// 	 fastPointer = fastPointer.next.next;
+    //          if(slowPointer == fastPointer) {
+	// 		 return true;
+	// 	 }
+	//   }
+	//   return false;
+    // // if(head == null){
+    // //     return false;
+    // // }
+    // // HashSet&lt;ListNode&gt; hs = new HashSet&lt;&gt;();
+    // // ListNode temp = head;
+    // // while(temp.next != null){
+    // //     if(hs.contains(temp)){
+    // //         return true;
+    // //     }
+    // //     hs.add(temp);
+    // //     temp = temp.next;
+    // // }
+    // // return false;  
+    ListNode slow = head;
+    ListNode fast = head;
+    while(fast != null &amp;&amp; fast.next != null){
+        slow = slow.next;
+        fast = fast.next.next;
+        if(fast == slow){
+            return true;
+        }
+    }
+    return false;
     }
 }</t>
         </is>
@@ -11697,7 +11678,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="182" customHeight="1">
+    <row r="35" ht="308" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
@@ -11711,24 +11692,29 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public void moveZeroes(int[] nums) {
-    int numbers = 0;
-    for(int traverse = 0;traverse&lt;nums.length;traverse++){
-        if(nums[traverse] != 0){
-            int temp = nums[traverse];
-            nums[traverse] = nums[numbers];
-            nums[numbers] = temp;
-            numbers++;
-        }
-    }  
-    }
-}</t>
+          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
+&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
+&lt;strong&gt;Output:&lt;/strong&gt; [0]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
         </is>
       </c>
     </row>
@@ -12519,29 +12505,32 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
-&lt;strong&gt;Output:&lt;/strong&gt; true
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
-&lt;strong&gt;Output:&lt;/strong&gt; false
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public boolean isBoomerang(int[][] points) {
+    int x1=0,x2=0,x3=0;
+    int y1=0,y2=0,y3=0;
+    for(int i =0;i&lt;points.length;i++){
+        for(int j=0;j&lt;points[i].length-1;j++){
+           if(i==0){
+            x1 = points[i][j];
+            y1 = points[i][j+1];
+           }else if(i == 1){
+             x2 = points[i][j];
+             y2 = points[i][j+1];
+           }else{
+            x3 = points[i][j];
+            y3 = points[i][j+1];
+           }
+        }
+    } 
+    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12996,7 +12985,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="266" customHeight="1">
+    <row r="63" ht="490" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>59</v>
       </c>
@@ -13010,100 +12999,77 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E63" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public static int digits(int num){
-        int multiply =1;
-        while(num!=0){
-            int rem = num%10;
-            multiply *= rem;
-            num /= 10;
-        }
-        return multiply;
-    }
-    public int smallestNumber(int n, int t) {
-    while(true){
-        if(digits(n)%t == 0){
-          return n;
-        } 
-        n++;
-    }
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="560" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
-A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
+          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
+&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="308" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int largestInteger(int[] nums, int k) {
+    int[] arr = new int[51];
+    for(int i = 0;i&lt;nums.length-k+1;i++){
+        boolean[] seen = new boolean[51];
+        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
+            if (!seen[nums[j]]){
+               arr[nums[j]]++;
+               seen[nums[j]] = true;
+            } 
+        }
+    } 
+    int high =-1;
+    for(int i=0;i&lt;arr.length;i++){
+        if(arr[i] == 1){
+           if(high&lt;i) high = i;
+        }
+    } 
+    return high;
+    }
+}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H149" s="12" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H155" s="12" t="n">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H159" s="12" t="n">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H162" s="12" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H185" s="12" t="n">
@@ -10254,7 +10254,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="196" customHeight="1">
+    <row r="5" ht="560" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10268,117 +10268,126 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int[] twoSum(int[] nums, int target) {
-        int[] arr=new int[2];
-       	 for(int i=0;i&lt;nums.length;i++) { 
-		 for(int j=i+1;j&lt;nums.length;j++) { 
-			 if(nums[i]+nums[j]==target) { 
-				arr[0]=i;
-                arr[1]=j;
-			 }
-		 }
-	 }
-     return arr;
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="504" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
+          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
+&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 1
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
-Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="252" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int lengthOfLongestSubstring(String s) {
+    int left =0;
+    int max = 0;
+    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
+    for(int right =0;right&lt;s.length();right++){
+         char currentChar = s.charAt(right);
+          while(hs.contains(s.charAt(right))){
+            hs.remove(s.charAt(left));
+            left++;
+          }
+          hs.add(s.charAt(right));
+          max = Math.max(max,right-left +1); 
+    }
+    return max;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="462" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 123
+&lt;strong&gt;Output:&lt;/strong&gt; 321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = -123
+&lt;strong&gt;Output:&lt;/strong&gt; -321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 120
+&lt;strong&gt;Output:&lt;/strong&gt; 21
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int rever(int num){
-        int rev =0;
-        while(num != 0){
-            int rem = num%10;
-            if(rev&gt;Integer.MAX_VALUE/10) return 0;
-            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
-            rev=rev*10+rem;
-            num/=10;
-        }
-        return rev;
-    }
-    public int reverse(int x) {
-    // int i=0;
-    // if(x&gt;=0)  i=1;
-    // else i = -1;
-    int num = rever(x);
-    return num;
-    }
-}</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10689,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="210" customHeight="1">
+    <row r="15" ht="532" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10694,26 +10703,40 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int lengthOfLastWord(String s) {
-    char[] ch =s.toCharArray();
-    int count=0;
-    int i = s.length()-1;
-    while(s.charAt(i) == ' '){
-        i--;
-    }
-    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
-        count++;
-        i--;
-    }
-    return count;
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 5
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 4
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 6
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10811,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="420" customHeight="1">
+    <row r="17" ht="560" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10802,39 +10825,45 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>/**
- * Definition for a binary tree node.
- * public class TreeNode {
- *     int val;
- *     TreeNode left;
- *     TreeNode right;
- *     TreeNode() {}
- *     TreeNode(int val) { this.val = val; }
- *     TreeNode(int val, TreeNode left, TreeNode right) {
- *         this.val = val;
- *         this.left = left;
- *         this.right = right;
- *     }
- * }
- */
-class Solution {
-    public  void inorder(TreeNode root,List list){
-    if(root == null) return;
-    inorder(root.left,list);
-    list.add(root.val);
-    inorder(root.right,list);
-    }
-    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
-    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
-    inorder(root,list);
-    return list;
-    }
-}</t>
+          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11707,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="308" customHeight="1">
+    <row r="35" ht="182" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
@@ -11692,29 +11721,24 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
-&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
-&lt;strong&gt;Output:&lt;/strong&gt; [0]
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
+          <t>class Solution {
+    public void moveZeroes(int[] nums) {
+    int numbers = 0;
+    for(int traverse = 0;traverse&lt;nums.length;traverse++){
+        if(nums[traverse] != 0){
+            int temp = nums[traverse];
+            nums[traverse] = nums[numbers];
+            nums[numbers] = temp;
+            numbers++;
+        }
+    }  
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12505,32 +12529,29 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t>class Solution {
-    public boolean isBoomerang(int[][] points) {
-    int x1=0,x2=0,x3=0;
-    int y1=0,y2=0,y3=0;
-    for(int i =0;i&lt;points.length;i++){
-        for(int j=0;j&lt;points[i].length-1;j++){
-           if(i==0){
-            x1 = points[i][j];
-            y1 = points[i][j+1];
-           }else if(i == 1){
-             x2 = points[i][j];
-             y2 = points[i][j+1];
-           }else{
-            x3 = points[i][j];
-            y3 = points[i][j+1];
-           }
-        }
-    } 
-    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -12985,7 +13006,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="490" customHeight="1">
+    <row r="63" ht="266" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>59</v>
       </c>
@@ -12999,77 +13020,100 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static int digits(int num){
+        int multiply =1;
+        while(num!=0){
+            int rem = num%10;
+            multiply *= rem;
+            num /= 10;
+        }
+        return multiply;
+    }
+    public int smallestNumber(int n, int t) {
+    while(true){
+        if(digits(n)%t == 0){
+          return n;
+        } 
+        n++;
+    }
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="560" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E63" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
+A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="308" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public int largestInteger(int[] nums, int k) {
-    int[] arr = new int[51];
-    for(int i = 0;i&lt;nums.length-k+1;i++){
-        boolean[] seen = new boolean[51];
-        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
-            if (!seen[nums[j]]){
-               arr[nums[j]]++;
-               seen[nums[j]] = true;
-            } 
-        }
-    } 
-    int high =-1;
-    for(int i=0;i&lt;arr.length;i++){
-        if(arr[i] == 1){
-           if(high&lt;i) high = i;
-        }
-    } 
-    return high;
-    }
-}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1785,7 +1785,7 @@
         <v>2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>46.8</v>
@@ -5037,13 +5037,13 @@
         </is>
       </c>
       <c r="H56" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="7" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="J56" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" s="14" t="n">
         <v>46274.44269675926</v>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
@@ -11191,26 +11191,26 @@
  */
 public class Solution {
     public ListNode detectCycle(ListNode head) {
-   ListNode slowPointer = head;
-   ListNode fastPointer = head;
-   boolean found = false;
-   while(fastPointer != null &amp;&amp; fastPointer.next != null){
-      if(!found){
-        slowPointer = slowPointer.next;
-        fastPointer = fastPointer.next.next;
-       }else{
-        slowPointer = slowPointer.next;
-        fastPointer = fastPointer.next;
-       }
-    if(slowPointer == fastPointer &amp;&amp; !found){
-            slowPointer = head;
-                found = true;  
-    }
-    if(slowPointer == fastPointer &amp;&amp; found){
-              return slowPointer;
-    }
-   }
-    return null;
+//    ListNode slowPointer = head;
+//    ListNode fastPointer = head;
+//    boolean found = false;
+//    while(fastPointer != null &amp;&amp; fastPointer.next != null){
+//       if(!found){
+//         slowPointer = slowPointer.next;
+//         fastPointer = fastPointer.next.next;
+//        }else{
+//         slowPointer = slowPointer.next;
+//         fastPointer = fastPointer.next;
+//        }
+//     if(slowPointer == fastPointer &amp;&amp; !found){
+//             slowPointer = head;
+//                 found = true;  
+//     }
+//     if(slowPointer == fastPointer &amp;&amp; found){
+//               return slowPointer;
+//     }
+//    }
+//     return null;
     // if(head == null){
     //     return head;
     // }
@@ -11223,7 +11223,22 @@
     //     hs.add(temp);
     //     temp = temp.next;
     // }
-    // return null;     
+    // return null;  
+    ListNode slow = head;
+    ListNode fast = head;
+    while(fast != null &amp;&amp; fast.next != null){
+        slow = slow.next;
+        fast = fast.next.next;
+        if(slow == fast){
+            fast = head;
+            while(fast != slow){
+                slow = slow.next;
+                fast = fast.next;
+            }
+            return fast;
+        }
+    }  
+    return null; 
     }
 }</t>
         </is>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="47">
@@ -5090,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>46274.48334490741</v>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="392" customHeight="1">
+    <row r="28" ht="560" customHeight="1">
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
@@ -11396,20 +11396,32 @@
  */
 class Solution {
     public ListNode reverseList(ListNode head) {
+    // if(head == null){
+    //     return head;
+    // }
+    // ListNode current = head;
+    // ListNode prev = null;
+    // ListNode Next = head.next;
+    // while(current!= null){
+    //     Next = current.next;
+    //     current.next = prev;
+    //     prev = current;
+    //     current = Next;
+    // }  
+    // head = prev;
+    // return head; 
     if(head == null){
         return head;
     }
-    ListNode current = head;
     ListNode prev = null;
-    ListNode Next = head.next;
-    while(current!= null){
-        Next = current.next;
-        current.next = prev;
-        prev = current;
-        current = Next;
-    }  
-    head = prev;
-    return head; 
+    ListNode curr = head;
+    while(curr != null){
+        ListNode Next = curr.next;
+        curr.next = prev;
+        prev = curr;
+        curr = Next;
+    }
+     return prev;
     }
 }</t>
         </is>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="7" t="n">
-        <v>43.4</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="45">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>43.4</v>
+        <v>42.9</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>46275.41266203704</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -8711,7 +8711,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>43.4</v>
+        <v>42.9</v>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H149" s="12" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H155" s="12" t="n">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H159" s="12" t="n">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H162" s="12" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H185" s="12" t="n">
@@ -10254,7 +10254,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="560" customHeight="1">
+    <row r="5" ht="196" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10268,126 +10268,117 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] nums, int target) {
+        int[] arr=new int[2];
+       	 for(int i=0;i&lt;nums.length;i++) { 
+		 for(int j=i+1;j&lt;nums.length;j++) { 
+			 if(nums[i]+nums[j]==target) { 
+				arr[0]=i;
+                arr[1]=j;
+			 }
+		 }
+	 }
+     return arr;
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="504" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
-&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
-&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 1
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
+Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
 &lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="252" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>class Solution {
-    public int lengthOfLongestSubstring(String s) {
-    int left =0;
-    int max = 0;
-    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
-    for(int right =0;right&lt;s.length();right++){
-         char currentChar = s.charAt(right);
-          while(hs.contains(s.charAt(right))){
-            hs.remove(s.charAt(left));
-            left++;
-          }
-          hs.add(s.charAt(right));
-          max = Math.max(max,right-left +1); 
+    public static int rever(int num){
+        int rev =0;
+        while(num != 0){
+            int rem = num%10;
+            if(rev&gt;Integer.MAX_VALUE/10) return 0;
+            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
+            rev=rev*10+rem;
+            num/=10;
+        }
+        return rev;
     }
-    return max;
+    public int reverse(int x) {
+    // int i=0;
+    // if(x&gt;=0)  i=1;
+    // else i = -1;
+    int num = rever(x);
+    return num;
     }
 }</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="462" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 123
-&lt;strong&gt;Output:&lt;/strong&gt; 321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = -123
-&lt;strong&gt;Output:&lt;/strong&gt; -321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 120
-&lt;strong&gt;Output:&lt;/strong&gt; 21
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
         </is>
       </c>
     </row>
@@ -10689,7 +10680,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="532" customHeight="1">
+    <row r="15" ht="210" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10703,40 +10694,26 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 5
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 4
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 6
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public int lengthOfLastWord(String s) {
+    char[] ch =s.toCharArray();
+    int count=0;
+    int i = s.length()-1;
+    while(s.charAt(i) == ' '){
+        i--;
+    }
+    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
+        count++;
+        i--;
+    }
+    return count;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -10771,47 +10748,61 @@
  */
 class Solution {
     public ListNode reverseBetween(ListNode head, int left, int right) {
-    ListNode current = null;
-    ListNode prev = null;
-    ListNode Next =null;
-    ListNode beforeLeft = null;
-    ListNode before = null;
-    ListNode temp = head;
-    ListNode leftNode = current;
-    int pos = 1;
-    while(temp != null){
-        if(pos == left){
-            current = temp;
-            Next = temp.next;
-            leftNode  = current;
-            beforeLeft = before;
-            prev = before;
-        }
-        before = temp;
-        temp = temp.next;
-        pos++;
-    }
-    int count = right - left +1;
-    while(count&gt;0){
-        Next = current.next;
-        current.next = prev;
-        prev = current;
-        current = Next;
-        count--;
-    }
-    if(beforeLeft == null){
-        head = prev;
-    }else{
-        beforeLeft.next = prev;
-    }
-    leftNode.next = current; 
-    return head;
+    // ListNode current = null;
+    // ListNode prev = null;
+    // ListNode Next =null;
+    // ListNode beforeLeft = null;
+    // ListNode before = null;
+    // ListNode temp = head;
+    // ListNode leftNode = current;
+    // int pos = 1;
+    // while(temp != null){
+    //     if(pos == left){
+    //         current = temp;
+    //         Next = temp.next;
+    //         leftNode  = current;
+    //         beforeLeft = before;
+    //         prev = before;
+    //     }
+    //     before = temp;
+    //     temp = temp.next;
+    //     pos++;
+    // }
+    // int count = right - left +1;
+    // while(count&gt;0){
+    //     Next = current.next;
+    //     current.next = prev;
+    //     prev = current;
+    //     current = Next;
+    //     count--;
+    // }
+    // if(beforeLeft == null){
+    //     head = prev;
+    // }else{
+    //     beforeLeft.next = prev;
+    // }
+    // leftNode.next = current; 
+    // return head;
+   ListNode temp = new ListNode(0);
+   temp.next = head;
+   ListNode prev = temp;
+   for(int i=1;i&lt;left;i++){
+    prev = prev.next;
+   }
+   ListNode curr = prev.next;
+   for(int i=0;i&lt;right - left;i++){
+    ListNode Next = curr.next;
+    curr.next = Next.next;
+    Next.next = prev.next;
+    prev.next = Next;
+   }
+   return temp.next;
     }
 }</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="560" customHeight="1">
+    <row r="17" ht="420" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10825,45 +10816,39 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    public  void inorder(TreeNode root,List list){
+    if(root == null) return;
+    inorder(root.left,list);
+    list.add(root.val);
+    inorder(root.right,list);
+    }
+    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
+    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
+    inorder(root,list);
+    return list;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11719,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="182" customHeight="1">
+    <row r="35" ht="308" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
@@ -11748,24 +11733,29 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public void moveZeroes(int[] nums) {
-    int numbers = 0;
-    for(int traverse = 0;traverse&lt;nums.length;traverse++){
-        if(nums[traverse] != 0){
-            int temp = nums[traverse];
-            nums[traverse] = nums[numbers];
-            nums[numbers] = temp;
-            numbers++;
-        }
-    }  
-    }
-}</t>
+          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
+&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
+&lt;strong&gt;Output:&lt;/strong&gt; [0]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
         </is>
       </c>
     </row>
@@ -12556,29 +12546,32 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
-&lt;strong&gt;Output:&lt;/strong&gt; true
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
-&lt;strong&gt;Output:&lt;/strong&gt; false
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public boolean isBoomerang(int[][] points) {
+    int x1=0,x2=0,x3=0;
+    int y1=0,y2=0,y3=0;
+    for(int i =0;i&lt;points.length;i++){
+        for(int j=0;j&lt;points[i].length-1;j++){
+           if(i==0){
+            x1 = points[i][j];
+            y1 = points[i][j+1];
+           }else if(i == 1){
+             x2 = points[i][j];
+             y2 = points[i][j+1];
+           }else{
+            x3 = points[i][j];
+            y3 = points[i][j+1];
+           }
+        }
+    } 
+    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -13033,7 +13026,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="266" customHeight="1">
+    <row r="63" ht="490" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>59</v>
       </c>
@@ -13047,100 +13040,77 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E63" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public static int digits(int num){
-        int multiply =1;
-        while(num!=0){
-            int rem = num%10;
-            multiply *= rem;
-            num /= 10;
-        }
-        return multiply;
-    }
-    public int smallestNumber(int n, int t) {
-    while(true){
-        if(digits(n)%t == 0){
-          return n;
-        } 
-        n++;
-    }
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="560" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
-A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
+          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
+&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="308" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int largestInteger(int[] nums, int k) {
+    int[] arr = new int[51];
+    for(int i = 0;i&lt;nums.length-k+1;i++){
+        boolean[] seen = new boolean[51];
+        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
+            if (!seen[nums[j]]){
+               arr[nums[j]]++;
+               seen[nums[j]] = true;
+            } 
+        }
+    } 
+    int high =-1;
+    for(int i=0;i&lt;arr.length;i++){
+        if(arr[i] == 1){
+           if(high&lt;i) high = i;
+        }
+    } 
+    return high;
+    }
+}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H149" s="12" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H155" s="12" t="n">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H159" s="12" t="n">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H162" s="12" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H185" s="12" t="n">
@@ -10254,7 +10254,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="196" customHeight="1">
+    <row r="5" ht="560" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10268,117 +10268,126 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int[] twoSum(int[] nums, int target) {
-        int[] arr=new int[2];
-       	 for(int i=0;i&lt;nums.length;i++) { 
-		 for(int j=i+1;j&lt;nums.length;j++) { 
-			 if(nums[i]+nums[j]==target) { 
-				arr[0]=i;
-                arr[1]=j;
-			 }
-		 }
-	 }
-     return arr;
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="504" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
+          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
+&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 1
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
-Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="252" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int lengthOfLongestSubstring(String s) {
+    int left =0;
+    int max = 0;
+    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
+    for(int right =0;right&lt;s.length();right++){
+         char currentChar = s.charAt(right);
+          while(hs.contains(s.charAt(right))){
+            hs.remove(s.charAt(left));
+            left++;
+          }
+          hs.add(s.charAt(right));
+          max = Math.max(max,right-left +1); 
+    }
+    return max;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="462" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 123
+&lt;strong&gt;Output:&lt;/strong&gt; 321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = -123
+&lt;strong&gt;Output:&lt;/strong&gt; -321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 120
+&lt;strong&gt;Output:&lt;/strong&gt; 21
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int rever(int num){
-        int rev =0;
-        while(num != 0){
-            int rem = num%10;
-            if(rev&gt;Integer.MAX_VALUE/10) return 0;
-            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
-            rev=rev*10+rem;
-            num/=10;
-        }
-        return rev;
-    }
-    public int reverse(int x) {
-    // int i=0;
-    // if(x&gt;=0)  i=1;
-    // else i = -1;
-    int num = rever(x);
-    return num;
-    }
-}</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10689,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="210" customHeight="1">
+    <row r="15" ht="532" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -10694,26 +10703,40 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int lengthOfLastWord(String s) {
-    char[] ch =s.toCharArray();
-    int count=0;
-    int i = s.length()-1;
-    while(s.charAt(i) == ' '){
-        i--;
-    }
-    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
-        count++;
-        i--;
-    }
-    return count;
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 5
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 4
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 6
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10825,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="420" customHeight="1">
+    <row r="17" ht="560" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>13</v>
       </c>
@@ -10816,39 +10839,45 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>/**
- * Definition for a binary tree node.
- * public class TreeNode {
- *     int val;
- *     TreeNode left;
- *     TreeNode right;
- *     TreeNode() {}
- *     TreeNode(int val) { this.val = val; }
- *     TreeNode(int val, TreeNode left, TreeNode right) {
- *         this.val = val;
- *         this.left = left;
- *         this.right = right;
- *     }
- * }
- */
-class Solution {
-    public  void inorder(TreeNode root,List list){
-    if(root == null) return;
-    inorder(root.left,list);
-    list.add(root.val);
-    inorder(root.right,list);
-    }
-    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
-    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
-    inorder(root,list);
-    return list;
-    }
-}</t>
+          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11748,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="308" customHeight="1">
+    <row r="35" ht="182" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
@@ -11733,29 +11762,24 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
-&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
-&lt;strong&gt;Output:&lt;/strong&gt; [0]
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
+          <t>class Solution {
+    public void moveZeroes(int[] nums) {
+    int numbers = 0;
+    for(int traverse = 0;traverse&lt;nums.length;traverse++){
+        if(nums[traverse] != 0){
+            int temp = nums[traverse];
+            nums[traverse] = nums[numbers];
+            nums[numbers] = temp;
+            numbers++;
+        }
+    }  
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12546,32 +12570,29 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t>class Solution {
-    public boolean isBoomerang(int[][] points) {
-    int x1=0,x2=0,x3=0;
-    int y1=0,y2=0,y3=0;
-    for(int i =0;i&lt;points.length;i++){
-        for(int j=0;j&lt;points[i].length-1;j++){
-           if(i==0){
-            x1 = points[i][j];
-            y1 = points[i][j+1];
-           }else if(i == 1){
-             x2 = points[i][j];
-             y2 = points[i][j+1];
-           }else{
-            x3 = points[i][j];
-            y3 = points[i][j+1];
-           }
-        }
-    } 
-    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13047,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="490" customHeight="1">
+    <row r="63" ht="266" customHeight="1">
       <c r="A63" s="5" t="n">
         <v>59</v>
       </c>
@@ -13040,77 +13061,100 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static int digits(int num){
+        int multiply =1;
+        while(num!=0){
+            int rem = num%10;
+            multiply *= rem;
+            num /= 10;
+        }
+        return multiply;
+    }
+    public int smallestNumber(int n, int t) {
+    while(true){
+        if(digits(n)%t == 0){
+          return n;
+        } 
+        n++;
+    }
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="560" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E63" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
+A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="308" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public int largestInteger(int[] nums, int k) {
-    int[] arr = new int[51];
-    for(int i = 0;i&lt;nums.length-k+1;i++){
-        boolean[] seen = new boolean[51];
-        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
-            if (!seen[nums[j]]){
-               arr[nums[j]]++;
-               seen[nums[j]] = true;
-            } 
-        }
-    } 
-    int high =-1;
-    for(int i=0;i&lt;arr.length;i++){
-        if(arr[i] == 1){
-           if(high&lt;i) high = i;
-        }
-    } 
-    return high;
-    }
-}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1805,16 +1805,16 @@
         <v>0</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>44.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="47">
@@ -1857,10 +1857,10 @@
         <v>2</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G48" s="9" t="inlineStr"/>
       <c r="H48" s="9" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         <v>27</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G66" s="11" t="inlineStr"/>
       <c r="H66" s="11" t="inlineStr"/>
@@ -2343,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -5749,6 +5749,56 @@
         <v>46288.67247685185</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Nodes in k-Group</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Linked List</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" s="12" t="n">
+        <v>46288.89429398148</v>
+      </c>
+      <c r="L71" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5758,7 +5808,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F70">
+  <conditionalFormatting sqref="F5:F71">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5836,6 +5886,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5847,7 +5898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I189"/>
+  <dimension ref="A1:I191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6560,7 +6611,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6595,7 +6646,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7035,7 +7086,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -8050,7 +8101,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -8585,7 +8636,7 @@
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: LINKED LIST   —   6 solved   (Low: 3 · Medium: 2 · High: 1)</t>
+          <t xml:space="preserve">  TOPIC: LINKED LIST   —   7 solved   (Low: 3 · Medium: 2 · High: 2)</t>
         </is>
       </c>
       <c r="B125" s="2" t="n"/>
@@ -8845,7 +8896,7 @@
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Recursion   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Recursion   —   2 solved   (Low: 1 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B137" s="18" t="n"/>
@@ -8908,1180 +8959,1225 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="17" t="inlineStr">
+      <c r="A140" s="23" t="n"/>
+      <c r="B140" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C140" s="23" t="n"/>
+      <c r="D140" s="23" t="n"/>
+      <c r="E140" s="23" t="n"/>
+      <c r="F140" s="23" t="n"/>
+      <c r="G140" s="23" t="n"/>
+      <c r="H140" s="23" t="n"/>
+      <c r="I140" s="23" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr"/>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Nodes in k-Group</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H141" s="12" t="n">
+        <v>46288.89429398148</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B140" s="18" t="n"/>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="18" t="n"/>
-      <c r="E140" s="18" t="n"/>
-      <c r="F140" s="18" t="n"/>
-      <c r="G140" s="18" t="n"/>
-      <c r="H140" s="18" t="n"/>
-      <c r="I140" s="18" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="21" t="n"/>
-      <c r="B141" s="22" t="inlineStr">
+      <c r="B142" s="18" t="n"/>
+      <c r="C142" s="18" t="n"/>
+      <c r="D142" s="18" t="n"/>
+      <c r="E142" s="18" t="n"/>
+      <c r="F142" s="18" t="n"/>
+      <c r="G142" s="18" t="n"/>
+      <c r="H142" s="18" t="n"/>
+      <c r="I142" s="18" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="n"/>
+      <c r="B143" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C141" s="21" t="n"/>
-      <c r="D141" s="21" t="n"/>
-      <c r="E141" s="21" t="n"/>
-      <c r="F141" s="21" t="n"/>
-      <c r="G141" s="21" t="n"/>
-      <c r="H141" s="21" t="n"/>
-      <c r="I141" s="21" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="inlineStr"/>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="C143" s="21" t="n"/>
+      <c r="D143" s="21" t="n"/>
+      <c r="E143" s="21" t="n"/>
+      <c r="F143" s="21" t="n"/>
+      <c r="G143" s="21" t="n"/>
+      <c r="H143" s="21" t="n"/>
+      <c r="I143" s="21" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr"/>
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C142" s="5" t="n">
+      <c r="C144" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="5" t="n">
+      <c r="E144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H142" s="12" t="n">
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I142" s="13" t="inlineStr">
+      <c r="I144" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="16" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B143" s="2" t="n"/>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" s="2" t="n"/>
-      <c r="F143" s="2" t="n"/>
-      <c r="G143" s="2" t="n"/>
-      <c r="H143" s="2" t="n"/>
-      <c r="I143" s="2" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="17" t="inlineStr">
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="n"/>
+      <c r="G145" s="2" t="n"/>
+      <c r="H145" s="2" t="n"/>
+      <c r="I145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B144" s="18" t="n"/>
-      <c r="C144" s="18" t="n"/>
-      <c r="D144" s="18" t="n"/>
-      <c r="E144" s="18" t="n"/>
-      <c r="F144" s="18" t="n"/>
-      <c r="G144" s="18" t="n"/>
-      <c r="H144" s="18" t="n"/>
-      <c r="I144" s="18" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="21" t="n"/>
-      <c r="B145" s="22" t="inlineStr">
+      <c r="B146" s="18" t="n"/>
+      <c r="C146" s="18" t="n"/>
+      <c r="D146" s="18" t="n"/>
+      <c r="E146" s="18" t="n"/>
+      <c r="F146" s="18" t="n"/>
+      <c r="G146" s="18" t="n"/>
+      <c r="H146" s="18" t="n"/>
+      <c r="I146" s="18" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="21" t="n"/>
+      <c r="B147" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C145" s="21" t="n"/>
-      <c r="D145" s="21" t="n"/>
-      <c r="E145" s="21" t="n"/>
-      <c r="F145" s="21" t="n"/>
-      <c r="G145" s="21" t="n"/>
-      <c r="H145" s="21" t="n"/>
-      <c r="I145" s="21" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr"/>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="C147" s="21" t="n"/>
+      <c r="D147" s="21" t="n"/>
+      <c r="E147" s="21" t="n"/>
+      <c r="F147" s="21" t="n"/>
+      <c r="G147" s="21" t="n"/>
+      <c r="H147" s="21" t="n"/>
+      <c r="I147" s="21" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr"/>
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C146" s="5" t="n">
+      <c r="C148" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D148" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E146" s="5" t="n">
+      <c r="E148" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F146" s="5" t="n">
+      <c r="F148" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G146" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H146" s="12" t="n">
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H148" s="12" t="n">
         <v>46255.88138888889</v>
       </c>
-      <c r="I146" s="13" t="inlineStr">
+      <c r="I148" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="17" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B147" s="18" t="n"/>
-      <c r="C147" s="18" t="n"/>
-      <c r="D147" s="18" t="n"/>
-      <c r="E147" s="18" t="n"/>
-      <c r="F147" s="18" t="n"/>
-      <c r="G147" s="18" t="n"/>
-      <c r="H147" s="18" t="n"/>
-      <c r="I147" s="18" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="21" t="n"/>
-      <c r="B148" s="22" t="inlineStr">
+      <c r="B149" s="18" t="n"/>
+      <c r="C149" s="18" t="n"/>
+      <c r="D149" s="18" t="n"/>
+      <c r="E149" s="18" t="n"/>
+      <c r="F149" s="18" t="n"/>
+      <c r="G149" s="18" t="n"/>
+      <c r="H149" s="18" t="n"/>
+      <c r="I149" s="18" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="21" t="n"/>
+      <c r="B150" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C148" s="21" t="n"/>
-      <c r="D148" s="21" t="n"/>
-      <c r="E148" s="21" t="n"/>
-      <c r="F148" s="21" t="n"/>
-      <c r="G148" s="21" t="n"/>
-      <c r="H148" s="21" t="n"/>
-      <c r="I148" s="21" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="inlineStr"/>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="C150" s="21" t="n"/>
+      <c r="D150" s="21" t="n"/>
+      <c r="E150" s="21" t="n"/>
+      <c r="F150" s="21" t="n"/>
+      <c r="G150" s="21" t="n"/>
+      <c r="H150" s="21" t="n"/>
+      <c r="I150" s="21" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="5" t="inlineStr"/>
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C149" s="5" t="n">
+      <c r="C151" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D149" s="5" t="inlineStr">
+      <c r="D151" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E149" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" s="5" t="n">
+      <c r="E151" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="G149" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="n">
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="n">
         <v>46240.74578703703</v>
       </c>
-      <c r="I149" s="13" t="inlineStr">
+      <c r="I151" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="17" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B150" s="18" t="n"/>
-      <c r="C150" s="18" t="n"/>
-      <c r="D150" s="18" t="n"/>
-      <c r="E150" s="18" t="n"/>
-      <c r="F150" s="18" t="n"/>
-      <c r="G150" s="18" t="n"/>
-      <c r="H150" s="18" t="n"/>
-      <c r="I150" s="18" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="21" t="n"/>
-      <c r="B151" s="22" t="inlineStr">
+      <c r="B152" s="18" t="n"/>
+      <c r="C152" s="18" t="n"/>
+      <c r="D152" s="18" t="n"/>
+      <c r="E152" s="18" t="n"/>
+      <c r="F152" s="18" t="n"/>
+      <c r="G152" s="18" t="n"/>
+      <c r="H152" s="18" t="n"/>
+      <c r="I152" s="18" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="21" t="n"/>
+      <c r="B153" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C151" s="21" t="n"/>
-      <c r="D151" s="21" t="n"/>
-      <c r="E151" s="21" t="n"/>
-      <c r="F151" s="21" t="n"/>
-      <c r="G151" s="21" t="n"/>
-      <c r="H151" s="21" t="n"/>
-      <c r="I151" s="21" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="5" t="inlineStr"/>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="C153" s="21" t="n"/>
+      <c r="D153" s="21" t="n"/>
+      <c r="E153" s="21" t="n"/>
+      <c r="F153" s="21" t="n"/>
+      <c r="G153" s="21" t="n"/>
+      <c r="H153" s="21" t="n"/>
+      <c r="I153" s="21" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="5" t="inlineStr"/>
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C152" s="5" t="n">
+      <c r="C154" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D152" s="5" t="inlineStr">
+      <c r="D154" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E152" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" s="5" t="n">
+      <c r="E154" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G152" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H152" s="12" t="n">
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H154" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I152" s="13" t="inlineStr">
+      <c r="I154" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="7" t="inlineStr"/>
-      <c r="B153" s="6" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr"/>
+      <c r="B155" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C153" s="7" t="n">
+      <c r="C155" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D153" s="7" t="inlineStr">
+      <c r="D155" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E153" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F153" s="7" t="n">
+      <c r="E155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F155" s="7" t="n">
         <v>42.6</v>
       </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H153" s="14" t="n">
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H155" s="14" t="n">
         <v>46273.3956712963</v>
       </c>
-      <c r="I153" s="15" t="inlineStr">
+      <c r="I155" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="19" t="n"/>
-      <c r="B154" s="20" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="19" t="n"/>
+      <c r="B156" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C154" s="19" t="n"/>
-      <c r="D154" s="19" t="n"/>
-      <c r="E154" s="19" t="n"/>
-      <c r="F154" s="19" t="n"/>
-      <c r="G154" s="19" t="n"/>
-      <c r="H154" s="19" t="n"/>
-      <c r="I154" s="19" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr"/>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="C156" s="19" t="n"/>
+      <c r="D156" s="19" t="n"/>
+      <c r="E156" s="19" t="n"/>
+      <c r="F156" s="19" t="n"/>
+      <c r="G156" s="19" t="n"/>
+      <c r="H156" s="19" t="n"/>
+      <c r="I156" s="19" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="5" t="inlineStr"/>
+      <c r="B157" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C155" s="5" t="n">
+      <c r="C157" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D155" s="5" t="inlineStr">
+      <c r="D157" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F155" s="5" t="n">
+      <c r="E157" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G155" s="5" t="inlineStr">
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="n">
+        <v>46241.79645833333</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="n"/>
+      <c r="I158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B159" s="18" t="n"/>
+      <c r="C159" s="18" t="n"/>
+      <c r="D159" s="18" t="n"/>
+      <c r="E159" s="18" t="n"/>
+      <c r="F159" s="18" t="n"/>
+      <c r="G159" s="18" t="n"/>
+      <c r="H159" s="18" t="n"/>
+      <c r="I159" s="18" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="21" t="n"/>
+      <c r="B160" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C160" s="21" t="n"/>
+      <c r="D160" s="21" t="n"/>
+      <c r="E160" s="21" t="n"/>
+      <c r="F160" s="21" t="n"/>
+      <c r="G160" s="21" t="n"/>
+      <c r="H160" s="21" t="n"/>
+      <c r="I160" s="21" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="inlineStr"/>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Length of Last Word</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="n">
+        <v>46241.78204861111</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B162" s="18" t="n"/>
+      <c r="C162" s="18" t="n"/>
+      <c r="D162" s="18" t="n"/>
+      <c r="E162" s="18" t="n"/>
+      <c r="F162" s="18" t="n"/>
+      <c r="G162" s="18" t="n"/>
+      <c r="H162" s="18" t="n"/>
+      <c r="I162" s="18" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="19" t="n"/>
+      <c r="B163" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C163" s="19" t="n"/>
+      <c r="D163" s="19" t="n"/>
+      <c r="E163" s="19" t="n"/>
+      <c r="F163" s="19" t="n"/>
+      <c r="G163" s="19" t="n"/>
+      <c r="H163" s="19" t="n"/>
+      <c r="I163" s="19" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr"/>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="F164" s="5" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H155" s="12" t="n">
-        <v>46241.79645833333</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
+      <c r="H164" s="12" t="n">
+        <v>46253.82314814815</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="n"/>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" s="2" t="n"/>
-      <c r="F156" s="2" t="n"/>
-      <c r="G156" s="2" t="n"/>
-      <c r="H156" s="2" t="n"/>
-      <c r="I156" s="2" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="17" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B165" s="18" t="n"/>
+      <c r="C165" s="18" t="n"/>
+      <c r="D165" s="18" t="n"/>
+      <c r="E165" s="18" t="n"/>
+      <c r="F165" s="18" t="n"/>
+      <c r="G165" s="18" t="n"/>
+      <c r="H165" s="18" t="n"/>
+      <c r="I165" s="18" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="21" t="n"/>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C166" s="21" t="n"/>
+      <c r="D166" s="21" t="n"/>
+      <c r="E166" s="21" t="n"/>
+      <c r="F166" s="21" t="n"/>
+      <c r="G166" s="21" t="n"/>
+      <c r="H166" s="21" t="n"/>
+      <c r="I166" s="21" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="inlineStr"/>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Valid Anagram</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H167" s="12" t="n">
+        <v>46243.94849537037</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B168" s="18" t="n"/>
+      <c r="C168" s="18" t="n"/>
+      <c r="D168" s="18" t="n"/>
+      <c r="E168" s="18" t="n"/>
+      <c r="F168" s="18" t="n"/>
+      <c r="G168" s="18" t="n"/>
+      <c r="H168" s="18" t="n"/>
+      <c r="I168" s="18" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="21" t="n"/>
+      <c r="B169" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C169" s="21" t="n"/>
+      <c r="D169" s="21" t="n"/>
+      <c r="E169" s="21" t="n"/>
+      <c r="F169" s="21" t="n"/>
+      <c r="G169" s="21" t="n"/>
+      <c r="H169" s="21" t="n"/>
+      <c r="I169" s="21" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="inlineStr"/>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Degree of a String</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="n">
+        <v>3811</v>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H170" s="12" t="n">
+        <v>46285.42987268518</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B171" s="18" t="n"/>
+      <c r="C171" s="18" t="n"/>
+      <c r="D171" s="18" t="n"/>
+      <c r="E171" s="18" t="n"/>
+      <c r="F171" s="18" t="n"/>
+      <c r="G171" s="18" t="n"/>
+      <c r="H171" s="18" t="n"/>
+      <c r="I171" s="18" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="21" t="n"/>
+      <c r="B172" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C172" s="21" t="n"/>
+      <c r="D172" s="21" t="n"/>
+      <c r="E172" s="21" t="n"/>
+      <c r="F172" s="21" t="n"/>
+      <c r="G172" s="21" t="n"/>
+      <c r="H172" s="21" t="n"/>
+      <c r="I172" s="21" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="inlineStr"/>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H173" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B174" s="18" t="n"/>
+      <c r="C174" s="18" t="n"/>
+      <c r="D174" s="18" t="n"/>
+      <c r="E174" s="18" t="n"/>
+      <c r="F174" s="18" t="n"/>
+      <c r="G174" s="18" t="n"/>
+      <c r="H174" s="18" t="n"/>
+      <c r="I174" s="18" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="21" t="n"/>
+      <c r="B175" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C175" s="21" t="n"/>
+      <c r="D175" s="21" t="n"/>
+      <c r="E175" s="21" t="n"/>
+      <c r="F175" s="21" t="n"/>
+      <c r="G175" s="21" t="n"/>
+      <c r="H175" s="21" t="n"/>
+      <c r="I175" s="21" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr"/>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Valid Palindrome II</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="n">
+        <v>680</v>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H176" s="12" t="n">
+        <v>46245.98399305555</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="2" t="n"/>
+      <c r="G177" s="2" t="n"/>
+      <c r="H177" s="2" t="n"/>
+      <c r="I177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B178" s="18" t="n"/>
+      <c r="C178" s="18" t="n"/>
+      <c r="D178" s="18" t="n"/>
+      <c r="E178" s="18" t="n"/>
+      <c r="F178" s="18" t="n"/>
+      <c r="G178" s="18" t="n"/>
+      <c r="H178" s="18" t="n"/>
+      <c r="I178" s="18" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="21" t="n"/>
+      <c r="B179" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C179" s="21" t="n"/>
+      <c r="D179" s="21" t="n"/>
+      <c r="E179" s="21" t="n"/>
+      <c r="F179" s="21" t="n"/>
+      <c r="G179" s="21" t="n"/>
+      <c r="H179" s="21" t="n"/>
+      <c r="I179" s="21" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr"/>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H180" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B181" s="18" t="n"/>
+      <c r="C181" s="18" t="n"/>
+      <c r="D181" s="18" t="n"/>
+      <c r="E181" s="18" t="n"/>
+      <c r="F181" s="18" t="n"/>
+      <c r="G181" s="18" t="n"/>
+      <c r="H181" s="18" t="n"/>
+      <c r="I181" s="18" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="21" t="n"/>
+      <c r="B182" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C182" s="21" t="n"/>
+      <c r="D182" s="21" t="n"/>
+      <c r="E182" s="21" t="n"/>
+      <c r="F182" s="21" t="n"/>
+      <c r="G182" s="21" t="n"/>
+      <c r="H182" s="21" t="n"/>
+      <c r="I182" s="21" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr"/>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Minimum Depth of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="n">
+        <v>46246.95925925926</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr"/>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>Average of Levels in Binary Tree</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="n">
+        <v>637</v>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F184" s="7" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H184" s="14" t="n">
+        <v>46246.98880787037</v>
+      </c>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B185" s="18" t="n"/>
+      <c r="C185" s="18" t="n"/>
+      <c r="D185" s="18" t="n"/>
+      <c r="E185" s="18" t="n"/>
+      <c r="F185" s="18" t="n"/>
+      <c r="G185" s="18" t="n"/>
+      <c r="H185" s="18" t="n"/>
+      <c r="I185" s="18" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="21" t="n"/>
+      <c r="B186" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C186" s="21" t="n"/>
+      <c r="D186" s="21" t="n"/>
+      <c r="E186" s="21" t="n"/>
+      <c r="F186" s="21" t="n"/>
+      <c r="G186" s="21" t="n"/>
+      <c r="H186" s="21" t="n"/>
+      <c r="I186" s="21" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr"/>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Binary Tree Inorder Traversal</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H187" s="12" t="n">
+        <v>46246.86910879629</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="n"/>
+      <c r="G188" s="2" t="n"/>
+      <c r="H188" s="2" t="n"/>
+      <c r="I188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B157" s="18" t="n"/>
-      <c r="C157" s="18" t="n"/>
-      <c r="D157" s="18" t="n"/>
-      <c r="E157" s="18" t="n"/>
-      <c r="F157" s="18" t="n"/>
-      <c r="G157" s="18" t="n"/>
-      <c r="H157" s="18" t="n"/>
-      <c r="I157" s="18" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="21" t="n"/>
-      <c r="B158" s="22" t="inlineStr">
+      <c r="B189" s="18" t="n"/>
+      <c r="C189" s="18" t="n"/>
+      <c r="D189" s="18" t="n"/>
+      <c r="E189" s="18" t="n"/>
+      <c r="F189" s="18" t="n"/>
+      <c r="G189" s="18" t="n"/>
+      <c r="H189" s="18" t="n"/>
+      <c r="I189" s="18" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="21" t="n"/>
+      <c r="B190" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C158" s="21" t="n"/>
-      <c r="D158" s="21" t="n"/>
-      <c r="E158" s="21" t="n"/>
-      <c r="F158" s="21" t="n"/>
-      <c r="G158" s="21" t="n"/>
-      <c r="H158" s="21" t="n"/>
-      <c r="I158" s="21" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr"/>
-      <c r="B159" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C159" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="C190" s="21" t="n"/>
+      <c r="D190" s="21" t="n"/>
+      <c r="E190" s="21" t="n"/>
+      <c r="F190" s="21" t="n"/>
+      <c r="G190" s="21" t="n"/>
+      <c r="H190" s="21" t="n"/>
+      <c r="I190" s="21" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr"/>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Generate Fibonacci Sequence</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E159" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F159" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G159" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H159" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
+      <c r="E191" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F191" s="5" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="H191" s="12" t="n">
+        <v>46247.79274305556</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B160" s="18" t="n"/>
-      <c r="C160" s="18" t="n"/>
-      <c r="D160" s="18" t="n"/>
-      <c r="E160" s="18" t="n"/>
-      <c r="F160" s="18" t="n"/>
-      <c r="G160" s="18" t="n"/>
-      <c r="H160" s="18" t="n"/>
-      <c r="I160" s="18" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="19" t="n"/>
-      <c r="B161" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C161" s="19" t="n"/>
-      <c r="D161" s="19" t="n"/>
-      <c r="E161" s="19" t="n"/>
-      <c r="F161" s="19" t="n"/>
-      <c r="G161" s="19" t="n"/>
-      <c r="H161" s="19" t="n"/>
-      <c r="I161" s="19" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr"/>
-      <c r="B162" s="4" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C162" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D162" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="F162" s="5" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="G162" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H162" s="12" t="n">
-        <v>46253.82314814815</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B163" s="18" t="n"/>
-      <c r="C163" s="18" t="n"/>
-      <c r="D163" s="18" t="n"/>
-      <c r="E163" s="18" t="n"/>
-      <c r="F163" s="18" t="n"/>
-      <c r="G163" s="18" t="n"/>
-      <c r="H163" s="18" t="n"/>
-      <c r="I163" s="18" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="21" t="n"/>
-      <c r="B164" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C164" s="21" t="n"/>
-      <c r="D164" s="21" t="n"/>
-      <c r="E164" s="21" t="n"/>
-      <c r="F164" s="21" t="n"/>
-      <c r="G164" s="21" t="n"/>
-      <c r="H164" s="21" t="n"/>
-      <c r="I164" s="21" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr"/>
-      <c r="B165" s="4" t="inlineStr">
-        <is>
-          <t>Valid Anagram</t>
-        </is>
-      </c>
-      <c r="C165" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="D165" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E165" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" s="5" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="G165" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H165" s="12" t="n">
-        <v>46243.94849537037</v>
-      </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B166" s="18" t="n"/>
-      <c r="C166" s="18" t="n"/>
-      <c r="D166" s="18" t="n"/>
-      <c r="E166" s="18" t="n"/>
-      <c r="F166" s="18" t="n"/>
-      <c r="G166" s="18" t="n"/>
-      <c r="H166" s="18" t="n"/>
-      <c r="I166" s="18" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="21" t="n"/>
-      <c r="B167" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C167" s="21" t="n"/>
-      <c r="D167" s="21" t="n"/>
-      <c r="E167" s="21" t="n"/>
-      <c r="F167" s="21" t="n"/>
-      <c r="G167" s="21" t="n"/>
-      <c r="H167" s="21" t="n"/>
-      <c r="I167" s="21" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="5" t="inlineStr"/>
-      <c r="B168" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Degree of a String</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="n">
-        <v>3811</v>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H168" s="12" t="n">
-        <v>46285.42987268518</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B169" s="18" t="n"/>
-      <c r="C169" s="18" t="n"/>
-      <c r="D169" s="18" t="n"/>
-      <c r="E169" s="18" t="n"/>
-      <c r="F169" s="18" t="n"/>
-      <c r="G169" s="18" t="n"/>
-      <c r="H169" s="18" t="n"/>
-      <c r="I169" s="18" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="21" t="n"/>
-      <c r="B170" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C170" s="21" t="n"/>
-      <c r="D170" s="21" t="n"/>
-      <c r="E170" s="21" t="n"/>
-      <c r="F170" s="21" t="n"/>
-      <c r="G170" s="21" t="n"/>
-      <c r="H170" s="21" t="n"/>
-      <c r="I170" s="21" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="5" t="inlineStr"/>
-      <c r="B171" s="4" t="inlineStr">
-        <is>
-          <t>Valid Palindrome</t>
-        </is>
-      </c>
-      <c r="C171" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E171" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F171" s="5" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="G171" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H171" s="12" t="n">
-        <v>46243.9169675926</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B172" s="18" t="n"/>
-      <c r="C172" s="18" t="n"/>
-      <c r="D172" s="18" t="n"/>
-      <c r="E172" s="18" t="n"/>
-      <c r="F172" s="18" t="n"/>
-      <c r="G172" s="18" t="n"/>
-      <c r="H172" s="18" t="n"/>
-      <c r="I172" s="18" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="21" t="n"/>
-      <c r="B173" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C173" s="21" t="n"/>
-      <c r="D173" s="21" t="n"/>
-      <c r="E173" s="21" t="n"/>
-      <c r="F173" s="21" t="n"/>
-      <c r="G173" s="21" t="n"/>
-      <c r="H173" s="21" t="n"/>
-      <c r="I173" s="21" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr"/>
-      <c r="B174" s="4" t="inlineStr">
-        <is>
-          <t>Valid Palindrome II</t>
-        </is>
-      </c>
-      <c r="C174" s="5" t="n">
-        <v>680</v>
-      </c>
-      <c r="D174" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F174" s="5" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="G174" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H174" s="12" t="n">
-        <v>46245.98399305555</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="n"/>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" s="2" t="n"/>
-      <c r="F175" s="2" t="n"/>
-      <c r="G175" s="2" t="n"/>
-      <c r="H175" s="2" t="n"/>
-      <c r="I175" s="2" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B176" s="18" t="n"/>
-      <c r="C176" s="18" t="n"/>
-      <c r="D176" s="18" t="n"/>
-      <c r="E176" s="18" t="n"/>
-      <c r="F176" s="18" t="n"/>
-      <c r="G176" s="18" t="n"/>
-      <c r="H176" s="18" t="n"/>
-      <c r="I176" s="18" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="21" t="n"/>
-      <c r="B177" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C177" s="21" t="n"/>
-      <c r="D177" s="21" t="n"/>
-      <c r="E177" s="21" t="n"/>
-      <c r="F177" s="21" t="n"/>
-      <c r="G177" s="21" t="n"/>
-      <c r="H177" s="21" t="n"/>
-      <c r="I177" s="21" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr"/>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C178" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D178" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G178" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H178" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B179" s="18" t="n"/>
-      <c r="C179" s="18" t="n"/>
-      <c r="D179" s="18" t="n"/>
-      <c r="E179" s="18" t="n"/>
-      <c r="F179" s="18" t="n"/>
-      <c r="G179" s="18" t="n"/>
-      <c r="H179" s="18" t="n"/>
-      <c r="I179" s="18" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="21" t="n"/>
-      <c r="B180" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C180" s="21" t="n"/>
-      <c r="D180" s="21" t="n"/>
-      <c r="E180" s="21" t="n"/>
-      <c r="F180" s="21" t="n"/>
-      <c r="G180" s="21" t="n"/>
-      <c r="H180" s="21" t="n"/>
-      <c r="I180" s="21" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="5" t="inlineStr"/>
-      <c r="B181" s="4" t="inlineStr">
-        <is>
-          <t>Minimum Depth of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C181" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="D181" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G181" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H181" s="12" t="n">
-        <v>46246.95925925926</v>
-      </c>
-      <c r="I181" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="7" t="inlineStr"/>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>Average of Levels in Binary Tree</t>
-        </is>
-      </c>
-      <c r="C182" s="7" t="n">
-        <v>637</v>
-      </c>
-      <c r="D182" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E182" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F182" s="7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H182" s="14" t="n">
-        <v>46246.98880787037</v>
-      </c>
-      <c r="I182" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B183" s="18" t="n"/>
-      <c r="C183" s="18" t="n"/>
-      <c r="D183" s="18" t="n"/>
-      <c r="E183" s="18" t="n"/>
-      <c r="F183" s="18" t="n"/>
-      <c r="G183" s="18" t="n"/>
-      <c r="H183" s="18" t="n"/>
-      <c r="I183" s="18" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="21" t="n"/>
-      <c r="B184" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C184" s="21" t="n"/>
-      <c r="D184" s="21" t="n"/>
-      <c r="E184" s="21" t="n"/>
-      <c r="F184" s="21" t="n"/>
-      <c r="G184" s="21" t="n"/>
-      <c r="H184" s="21" t="n"/>
-      <c r="I184" s="21" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="5" t="inlineStr"/>
-      <c r="B185" s="4" t="inlineStr">
-        <is>
-          <t>Binary Tree Inorder Traversal</t>
-        </is>
-      </c>
-      <c r="C185" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E185" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G185" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H185" s="12" t="n">
-        <v>46246.86910879629</v>
-      </c>
-      <c r="I185" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B186" s="2" t="n"/>
-      <c r="C186" s="2" t="n"/>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" s="2" t="n"/>
-      <c r="F186" s="2" t="n"/>
-      <c r="G186" s="2" t="n"/>
-      <c r="H186" s="2" t="n"/>
-      <c r="I186" s="2" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B187" s="18" t="n"/>
-      <c r="C187" s="18" t="n"/>
-      <c r="D187" s="18" t="n"/>
-      <c r="E187" s="18" t="n"/>
-      <c r="F187" s="18" t="n"/>
-      <c r="G187" s="18" t="n"/>
-      <c r="H187" s="18" t="n"/>
-      <c r="I187" s="18" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="21" t="n"/>
-      <c r="B188" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C188" s="21" t="n"/>
-      <c r="D188" s="21" t="n"/>
-      <c r="E188" s="21" t="n"/>
-      <c r="F188" s="21" t="n"/>
-      <c r="G188" s="21" t="n"/>
-      <c r="H188" s="21" t="n"/>
-      <c r="I188" s="21" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="5" t="inlineStr"/>
-      <c r="B189" s="4" t="inlineStr">
-        <is>
-          <t>Generate Fibonacci Sequence</t>
-        </is>
-      </c>
-      <c r="C189" s="5" t="n">
-        <v>2775</v>
-      </c>
-      <c r="D189" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E189" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="F189" s="5" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="G189" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="H189" s="12" t="n">
-        <v>46247.79274305556</v>
-      </c>
-      <c r="I189" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="122">
     <mergeCell ref="B135:I135"/>
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A172:I172"/>
     <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B190:I190"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A163:I163"/>
     <mergeCell ref="A101:I101"/>
-    <mergeCell ref="B167:I167"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B161:I161"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="A17:I17"/>
-    <mergeCell ref="B145:I145"/>
+    <mergeCell ref="A188:I188"/>
     <mergeCell ref="A126:I126"/>
     <mergeCell ref="B98:I98"/>
-    <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A62:I62"/>
+    <mergeCell ref="B175:I175"/>
     <mergeCell ref="A68:I68"/>
+    <mergeCell ref="B147:I147"/>
     <mergeCell ref="A117:I117"/>
     <mergeCell ref="A111:I111"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B74:I74"/>
+    <mergeCell ref="A142:I142"/>
     <mergeCell ref="B83:I83"/>
-    <mergeCell ref="A169:I169"/>
     <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B173:I173"/>
     <mergeCell ref="A137:I137"/>
-    <mergeCell ref="B141:I141"/>
+    <mergeCell ref="A177:I177"/>
     <mergeCell ref="B115:I115"/>
+    <mergeCell ref="B150:I150"/>
     <mergeCell ref="B102:I102"/>
+    <mergeCell ref="A145:I145"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A179:I179"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="B86:I86"/>
     <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A181:I181"/>
+    <mergeCell ref="A171:I171"/>
+    <mergeCell ref="A165:I165"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="A143:I143"/>
-    <mergeCell ref="A157:I157"/>
-    <mergeCell ref="A166:I166"/>
-    <mergeCell ref="B177:I177"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B164:I164"/>
     <mergeCell ref="A94:I94"/>
+    <mergeCell ref="A168:I168"/>
     <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B154:I154"/>
-    <mergeCell ref="A183:I183"/>
+    <mergeCell ref="B163:I163"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="B138:I138"/>
     <mergeCell ref="B91:I91"/>
+    <mergeCell ref="B156:I156"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="B180:I180"/>
+    <mergeCell ref="B140:I140"/>
     <mergeCell ref="A104:I104"/>
-    <mergeCell ref="A175:I175"/>
     <mergeCell ref="B130:I130"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A185:I185"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="B151:I151"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A147:I147"/>
-    <mergeCell ref="A156:I156"/>
+    <mergeCell ref="B166:I166"/>
     <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B182:I182"/>
     <mergeCell ref="B112:I112"/>
     <mergeCell ref="B118:I118"/>
     <mergeCell ref="B127:I127"/>
-    <mergeCell ref="B158:I158"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
@@ -10089,37 +10185,43 @@
     <mergeCell ref="B89:I89"/>
     <mergeCell ref="A132:I132"/>
     <mergeCell ref="A110:I110"/>
-    <mergeCell ref="A187:I187"/>
+    <mergeCell ref="A146:I146"/>
+    <mergeCell ref="B160:I160"/>
+    <mergeCell ref="B169:I169"/>
+    <mergeCell ref="B153:I153"/>
+    <mergeCell ref="A174:I174"/>
+    <mergeCell ref="A149:I149"/>
+    <mergeCell ref="A189:I189"/>
+    <mergeCell ref="A158:I158"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B184:I184"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A160:I160"/>
     <mergeCell ref="B42:I42"/>
-    <mergeCell ref="A150:I150"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A144:I144"/>
+    <mergeCell ref="A159:I159"/>
     <mergeCell ref="A122:I122"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="B170:I170"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A125:I125"/>
-    <mergeCell ref="B148:I148"/>
+    <mergeCell ref="B179:I179"/>
     <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A152:I152"/>
     <mergeCell ref="A121:I121"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A176:I176"/>
+    <mergeCell ref="B172:I172"/>
     <mergeCell ref="B108:I108"/>
     <mergeCell ref="A114:I114"/>
-    <mergeCell ref="A186:I186"/>
+    <mergeCell ref="B186:I186"/>
+    <mergeCell ref="B143:I143"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A107:I107"/>
+    <mergeCell ref="A178:I178"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B133:I133"/>
     <mergeCell ref="A88:I88"/>
     <mergeCell ref="B80:I80"/>
-    <mergeCell ref="B188:I188"/>
+    <mergeCell ref="A162:I162"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -10171,23 +10273,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId67"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10199,7 +10302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10254,7 +10357,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="560" customHeight="1">
+    <row r="5" ht="196" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10268,126 +10371,117 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] nums, int target) {
+        int[] arr=new int[2];
+       	 for(int i=0;i&lt;nums.length;i++) { 
+		 for(int j=i+1;j&lt;nums.length;j++) { 
+			 if(nums[i]+nums[j]==target) { 
+				arr[0]=i;
+                arr[1]=j;
+			 }
+		 }
+	 }
+     return arr;
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="504" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
-&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
-&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 1
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
+Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
 &lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="252" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>class Solution {
-    public int lengthOfLongestSubstring(String s) {
-    int left =0;
-    int max = 0;
-    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
-    for(int right =0;right&lt;s.length();right++){
-         char currentChar = s.charAt(right);
-          while(hs.contains(s.charAt(right))){
-            hs.remove(s.charAt(left));
-            left++;
-          }
-          hs.add(s.charAt(right));
-          max = Math.max(max,right-left +1); 
+    public static int rever(int num){
+        int rev =0;
+        while(num != 0){
+            int rem = num%10;
+            if(rev&gt;Integer.MAX_VALUE/10) return 0;
+            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
+            rev=rev*10+rem;
+            num/=10;
+        }
+        return rev;
     }
-    return max;
+    public int reverse(int x) {
+    // int i=0;
+    // if(x&gt;=0)  i=1;
+    // else i = -1;
+    int num = rever(x);
+    return num;
     }
 }</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="462" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 123
-&lt;strong&gt;Output:&lt;/strong&gt; 321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = -123
-&lt;strong&gt;Output:&lt;/strong&gt; -321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 120
-&lt;strong&gt;Output:&lt;/strong&gt; 21
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
         </is>
       </c>
     </row>
@@ -10485,24 +10579,77 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="154" customHeight="1">
+    <row r="10" ht="448" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>Reverse Nodes in k-Group</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>/**
+ * Definition for singly-linked list.
+ * public class ListNode {
+ *     int val;
+ *     ListNode next;
+ *     ListNode() {}
+ *     ListNode(int val) { this.val = val; }
+ *     ListNode(int val, ListNode next) { this.val = val; this.next = next; }
+ * }
+ */
+class Solution {
+    public ListNode reverseKGroup(ListNode head, int k) {
+     ListNode node = head;
+     int count = 0;
+     while(node != null &amp;&amp; count&lt;k){
+          node = node.next;
+          count++;
+     }   
+     if(count&lt;k) return head;
+     ListNode prev = reverseKGroup(node,k);
+     ListNode curr = head;
+     while(count&gt;0){
+        ListNode Next = curr.next;
+        curr.next = prev;
+        prev = curr;
+        curr = Next;
+        count--;
+     }
+     return prev;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="154" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int removeDuplicates(int[] nums) {
@@ -10518,24 +10665,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="364" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="364" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Search in Rotated Sorted Array</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int search(int[] nums, int target) {
@@ -10566,24 +10713,24 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="378" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13" ht="378" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>First Missing Positive</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstMissingPositive(int[] nums) {
@@ -10614,24 +10761,24 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="196" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14" ht="196" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Maximum Subarray</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int maxSubArray(int[] nums) {
@@ -10650,24 +10797,24 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="238" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15" ht="238" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Merge Intervals</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] merge(int[][] intervals) {
@@ -10689,75 +10836,61 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="532" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 5
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 4
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 6
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="560" customHeight="1">
+    <row r="16" ht="210" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>Length of Last Word</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int lengthOfLastWord(String s) {
+    char[] ch =s.toCharArray();
+    int count=0;
+    int i = s.length()-1;
+    while(s.charAt(i) == ' '){
+        i--;
+    }
+    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
+        count++;
+        i--;
+    }
+    return count;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="560" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>Reverse Linked List II</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -10825,80 +10958,74 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="560" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Binary Tree Inorder Traversal</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="406" customHeight="1">
+    <row r="18" ht="420" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>Binary Tree Inorder Traversal</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>94</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    public  void inorder(TreeNode root,List list){
+    if(root == null) return;
+    inorder(root.left,list);
+    list.add(root.val);
+    inorder(root.right,list);
+    }
+    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
+    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
+    inorder(root,list);
+    return list;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="406" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;111 - Minimum Depth of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/minimum-depth-of-binary-tree/"&gt;minimum-depth-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a binary tree, find its minimum depth.&lt;/p&gt;
 &lt;p&gt;The minimum depth is the number of nodes along the shortest path from the root node down to the nearest leaf node.&lt;/p&gt;
@@ -10925,24 +11052,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="210" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="210" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Best Time to Buy and Sell Stock</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int maxProfit(int[] prices) {
@@ -10962,24 +11089,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="532" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="532" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -11013,24 +11140,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="532" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="532" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;136 - Single Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/single-number/"&gt;single-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a &lt;strong&gt;non-empty&lt;/strong&gt;&amp;nbsp;array of integers &lt;code&gt;nums&lt;/code&gt;, every element appears &lt;em&gt;twice&lt;/em&gt; except for one. Find that single one.&lt;/p&gt;
 &lt;p&gt;You must&amp;nbsp;implement a solution with a linear runtime complexity and use&amp;nbsp;only constant&amp;nbsp;extra space.&lt;/p&gt;
@@ -11061,24 +11188,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="238" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="238" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -11100,24 +11227,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="560" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="560" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>141</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11173,24 +11300,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="560" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="560" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle II</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11258,24 +11385,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="210" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="210" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Find Peak Element</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>162</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int findPeakElement(int[] nums) {
@@ -11295,24 +11422,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="266" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="266" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] twoSum(int[] numbers, int target) {
@@ -11336,24 +11463,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="294" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="294" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -11379,24 +11506,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="560" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="560" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11441,24 +11568,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="560" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="560" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Course Schedule</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>207</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public class TopologicalSortUsingKhansAlgorithm {
@@ -11508,24 +11635,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="238" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="238" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -11547,24 +11674,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="560" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="560" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Course Schedule II</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>210</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>class Solution {public class TopologicalSortUsingKhansAlgorithm {
 	int[] indegree;
@@ -11618,24 +11745,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="238" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="238" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -11657,24 +11784,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="322" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="322" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Sliding Window Maximum</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>239</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] maxSlidingWindow(int[] nums, int k) {
@@ -11698,24 +11825,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="392" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="392" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -11748,59 +11875,64 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="182" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Move Zeroes</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>283</v>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public void moveZeroes(int[] nums) {
-    int numbers = 0;
-    for(int traverse = 0;traverse&lt;nums.length;traverse++){
-        if(nums[traverse] != 0){
-            int temp = nums[traverse];
-            nums[traverse] = nums[numbers];
-            nums[numbers] = temp;
-            numbers++;
-        }
-    }  
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="476" customHeight="1">
+    <row r="36" ht="308" customHeight="1">
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>Move Zeroes</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>283</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
+&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
+&lt;strong&gt;Output:&lt;/strong&gt; [0]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="476" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>Find the Duplicate Number</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int findDuplicate(int[] nums) {
@@ -11838,24 +11970,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="308" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="308" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>303</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -11879,24 +12011,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="420" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="420" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -11928,24 +12060,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="308" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="308" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Find All Duplicates in an Array</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>442</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public List&lt;Integer&gt; findDuplicates(int[] nums) {
@@ -11972,24 +12104,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="322" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="322" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>503</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElements(int[] nums) {
@@ -12014,24 +12146,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="546" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="546" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -12069,24 +12201,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="560" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="560" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public class Uniounandfind {
@@ -12138,24 +12270,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="182" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="182" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -12173,24 +12305,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="546" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="546" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -12234,24 +12366,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="196" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="196" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -12270,24 +12402,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="462" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="462" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -12317,24 +12449,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="518" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="518" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>class Solution {
  class UniounFind{
@@ -12374,24 +12506,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="252" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="252" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>739</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -12411,24 +12543,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="378" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="378" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -12460,24 +12592,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="294" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="294" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -12503,24 +12635,24 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="560" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52" ht="560" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -12556,64 +12688,67 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="294" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Valid Boomerang</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>1115</v>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
-&lt;strong&gt;Output:&lt;/strong&gt; true
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
-&lt;strong&gt;Output:&lt;/strong&gt; false
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="224" customHeight="1">
+    <row r="53" ht="294" customHeight="1">
       <c r="A53" s="5" t="n">
         <v>49</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
+          <t>Valid Boomerang</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public boolean isBoomerang(int[][] points) {
+    int x1=0,x2=0,x3=0;
+    int y1=0,y2=0,y3=0;
+    for(int i =0;i&lt;points.length;i++){
+        for(int j=0;j&lt;points[i].length-1;j++){
+           if(i==0){
+            x1 = points[i][j];
+            y1 = points[i][j+1];
+           }else if(i == 1){
+             x2 = points[i][j];
+             y2 = points[i][j+1];
+           }else{
+            x3 = points[i][j];
+            y3 = points[i][j+1];
+           }
+        }
+    } 
+    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="224" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -12634,24 +12769,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="420" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="420" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -12686,24 +12821,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="378" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="378" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -12735,24 +12870,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="266" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="266" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -12776,24 +12911,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="350" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="350" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -12823,24 +12958,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="238" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="238" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -12862,24 +12997,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="308" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="308" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -12906,24 +13041,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="280" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="280" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -12946,24 +13081,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="448" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="448" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -12998,24 +13133,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="378" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="378" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -13047,58 +13182,17 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="266" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Smallest Divisible Digit Product I</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>3626</v>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int digits(int num){
-        int multiply =1;
-        while(num!=0){
-            int rem = num%10;
-            multiply *= rem;
-            num /= 10;
-        }
-        return multiply;
-    }
-    public int smallestNumber(int n, int t) {
-    while(true){
-        if(digits(n)%t == 0){
-          return n;
-        } 
-        n++;
-    }
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="560" customHeight="1">
+    <row r="64" ht="490" customHeight="1">
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Find the Largest Almost Missing Integer</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>3705</v>
+        <v>3626</v>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
@@ -13107,75 +13201,93 @@
       </c>
       <c r="E64" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
-A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
+          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
+&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
         </is>
       </c>
     </row>
-    <row r="65" ht="196" customHeight="1">
+    <row r="65" ht="308" customHeight="1">
       <c r="A65" s="5" t="n">
         <v>61</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int largestInteger(int[] nums, int k) {
+    int[] arr = new int[51];
+    for(int i = 0;i&lt;nums.length-k+1;i++){
+        boolean[] seen = new boolean[51];
+        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
+            if (!seen[nums[j]]){
+               arr[nums[j]]++;
+               seen[nums[j]] = true;
+            } 
+        }
+    } 
+    int high =-1;
+    for(int i=0;i&lt;arr.length;i++){
+        if(arr[i] == 1){
+           if(high&lt;i) high = i;
+        }
+    } 
+    return high;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="196" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>3811</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -13193,24 +13305,24 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="238" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="67" ht="238" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C67" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -13230,24 +13342,24 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="252" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+    <row r="68" ht="252" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C68" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -13270,24 +13382,24 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="140" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="69" ht="140" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C69" s="5" t="n">
         <v>4245</v>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -13301,24 +13413,24 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="294" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+    <row r="70" ht="294" customHeight="1">
+      <c r="A70" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C70" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -13344,24 +13456,24 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="252" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
+    <row r="71" ht="252" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C70" s="7" t="n">
+      <c r="C71" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E71" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -13465,10 +13577,10 @@
         <v>27</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -13503,10 +13615,10 @@
         <v>27</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H100" s="14" t="n">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H151" s="12" t="n">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H157" s="12" t="n">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H161" s="12" t="n">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H164" s="12" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H187" s="12" t="n">
@@ -10357,7 +10357,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="196" customHeight="1">
+    <row r="5" ht="560" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10371,117 +10371,126 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int[] twoSum(int[] nums, int target) {
-        int[] arr=new int[2];
-       	 for(int i=0;i&lt;nums.length;i++) { 
-		 for(int j=i+1;j&lt;nums.length;j++) { 
-			 if(nums[i]+nums[j]==target) { 
-				arr[0]=i;
-                arr[1]=j;
-			 }
-		 }
-	 }
-     return arr;
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="504" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
+          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
+&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 1
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
-Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="252" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int lengthOfLongestSubstring(String s) {
+    int left =0;
+    int max = 0;
+    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
+    for(int right =0;right&lt;s.length();right++){
+         char currentChar = s.charAt(right);
+          while(hs.contains(s.charAt(right))){
+            hs.remove(s.charAt(left));
+            left++;
+          }
+          hs.add(s.charAt(right));
+          max = Math.max(max,right-left +1); 
+    }
+    return max;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="462" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 123
+&lt;strong&gt;Output:&lt;/strong&gt; 321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = -123
+&lt;strong&gt;Output:&lt;/strong&gt; -321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 120
+&lt;strong&gt;Output:&lt;/strong&gt; 21
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int rever(int num){
-        int rev =0;
-        while(num != 0){
-            int rem = num%10;
-            if(rev&gt;Integer.MAX_VALUE/10) return 0;
-            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
-            rev=rev*10+rem;
-            num/=10;
-        }
-        return rev;
-    }
-    public int reverse(int x) {
-    // int i=0;
-    // if(x&gt;=0)  i=1;
-    // else i = -1;
-    int num = rever(x);
-    return num;
-    }
-}</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10845,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="210" customHeight="1">
+    <row r="16" ht="532" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
@@ -10850,26 +10859,40 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int lengthOfLastWord(String s) {
-    char[] ch =s.toCharArray();
-    int count=0;
-    int i = s.length()-1;
-    while(s.charAt(i) == ' '){
-        i--;
-    }
-    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
-        count++;
-        i--;
-    }
-    return count;
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 5
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 4
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 6
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10981,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="420" customHeight="1">
+    <row r="18" ht="560" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
@@ -10972,39 +10995,45 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E18" s="26" t="inlineStr">
         <is>
-          <t>/**
- * Definition for a binary tree node.
- * public class TreeNode {
- *     int val;
- *     TreeNode left;
- *     TreeNode right;
- *     TreeNode() {}
- *     TreeNode(int val) { this.val = val; }
- *     TreeNode(int val, TreeNode left, TreeNode right) {
- *         this.val = val;
- *         this.left = left;
- *         this.right = right;
- *     }
- * }
- */
-class Solution {
-    public  void inorder(TreeNode root,List list){
-    if(root == null) return;
-    inorder(root.left,list);
-    list.add(root.val);
-    inorder(root.right,list);
-    }
-    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
-    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
-    inorder(root,list);
-    return list;
-    }
-}</t>
+          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11904,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="308" customHeight="1">
+    <row r="36" ht="182" customHeight="1">
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
@@ -11889,29 +11918,24 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E36" s="26" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
-&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
-&lt;strong&gt;Output:&lt;/strong&gt; [0]
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
+          <t>class Solution {
+    public void moveZeroes(int[] nums) {
+    int numbers = 0;
+    for(int traverse = 0;traverse&lt;nums.length;traverse++){
+        if(nums[traverse] != 0){
+            int temp = nums[traverse];
+            nums[traverse] = nums[numbers];
+            nums[numbers] = temp;
+            numbers++;
+        }
+    }  
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12702,32 +12726,29 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E53" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public boolean isBoomerang(int[][] points) {
-    int x1=0,x2=0,x3=0;
-    int y1=0,y2=0,y3=0;
-    for(int i =0;i&lt;points.length;i++){
-        for(int j=0;j&lt;points[i].length-1;j++){
-           if(i==0){
-            x1 = points[i][j];
-            y1 = points[i][j+1];
-           }else if(i == 1){
-             x2 = points[i][j];
-             y2 = points[i][j+1];
-           }else{
-            x3 = points[i][j];
-            y3 = points[i][j+1];
-           }
-        }
-    } 
-    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13203,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="490" customHeight="1">
+    <row r="64" ht="266" customHeight="1">
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
@@ -13196,77 +13217,100 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static int digits(int num){
+        int multiply =1;
+        while(num!=0){
+            int rem = num%10;
+            multiply *= rem;
+            num /= 10;
+        }
+        return multiply;
+    }
+    public int smallestNumber(int n, int t) {
+    while(true){
+        if(digits(n)%t == 0){
+          return n;
+        } 
+        n++;
+    }
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="560" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E64" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
+      <c r="E65" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
+A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="308" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E65" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public int largestInteger(int[] nums, int k) {
-    int[] arr = new int[51];
-    for(int i = 0;i&lt;nums.length-k+1;i++){
-        boolean[] seen = new boolean[51];
-        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
-            if (!seen[nums[j]]){
-               arr[nums[j]]++;
-               seen[nums[j]] = true;
-            } 
-        }
-    } 
-    int high =-1;
-    for(int i=0;i&lt;arr.length;i++){
-        if(arr[i] == 1){
-           if(high&lt;i) high = i;
-        }
-    } 
-    return high;
-    }
-}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1041,7 +1041,7 @@
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Stack, Monotonic Stack</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1057,24 +1057,24 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>46.3</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1083,24 +1083,24 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -1109,17 +1109,17 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
@@ -1135,17 +1135,17 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -1161,24 +1161,24 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
@@ -1187,24 +1187,24 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -1213,24 +1213,24 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
@@ -1239,21 +1239,21 @@
         <v>1</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>1</v>
@@ -1262,72 +1262,72 @@
         <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>65.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>143.4</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>46.7</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
@@ -1343,24 +1343,24 @@
         <v>1</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Sorting, Quicksort</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>0</v>
@@ -1369,73 +1369,73 @@
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>48.9</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Stack, Monotonic Stack</t>
+          <t>Sorting, Quicksort</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>34.3</v>
+        <v>8</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>67.40000000000001</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Stack, Monotonic Stack</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>3</v>
+        <v>34.3</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>47.2</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>0</v>
@@ -1444,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H32" s="7" t="n">
         <v>47.2</v>
@@ -1457,33 +1457,33 @@
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>48.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+          <t>Two Pointers, Binary Search</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -1499,281 +1499,281 @@
         <v>1</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="C36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H36" s="7" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="D36" s="9" t="n">
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="D37" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="F37" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Breadth-First Search, Graph Theory, Topological Sort</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H38" s="7" t="n">
         <v>46.9</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>47.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>Breadth-First Search, Union-Find, Graph Theory</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="5" t="n">
+      <c r="C40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="G40" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H40" s="7" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Depth-First Search — TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="9" t="n">
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="E41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr"/>
-      <c r="C42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="n">
+      <c r="C44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H44" s="7" t="n">
         <v>45.9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr"/>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>42.9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="5" t="n">
         <v>1</v>
@@ -1782,30 +1782,30 @@
         <v>0</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>46.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
         <v>2</v>
@@ -1814,229 +1814,229 @@
         <v>0</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>45.3</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="5" t="n">
+      <c r="C48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Linked List — TOTAL</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr"/>
-      <c r="C48" s="9" t="n">
+      <c r="B49" s="8" t="inlineStr"/>
+      <c r="C49" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D48" s="9" t="n">
+      <c r="D49" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E49" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F48" s="9" t="n">
+      <c r="F49" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G48" s="9" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="n">
+      <c r="C50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H50" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr"/>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr"/>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
+      <c r="D52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="G52" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H52" s="7" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr"/>
-      <c r="C52" s="9" t="n">
+      <c r="B53" s="8" t="inlineStr"/>
+      <c r="C53" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D52" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="9" t="n">
+      <c r="D53" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G52" s="9" t="inlineStr"/>
-      <c r="H52" s="9" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr"/>
+      <c r="H53" s="9" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="5" t="n">
+      <c r="C54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr"/>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0</v>
@@ -2045,17 +2045,17 @@
         <v>1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
@@ -2071,17 +2071,17 @@
         <v>1</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
@@ -2097,237 +2097,263 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="7" t="n">
+      <c r="C59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="7" t="n">
+      <c r="H59" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr"/>
-      <c r="C59" s="9" t="n">
+      <c r="B60" s="8" t="inlineStr"/>
+      <c r="C60" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="9" t="n">
+      <c r="D60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G59" s="9" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="9" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="7" t="n">
+      <c r="C61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr"/>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr"/>
       <c r="B62" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="7" t="n">
+      <c r="C63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr"/>
-      <c r="C63" s="9" t="n">
+      <c r="B64" s="8" t="inlineStr"/>
+      <c r="C64" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="9" t="n">
+      <c r="D64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G63" s="9" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr"/>
+      <c r="H64" s="9" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="7" t="n">
+      <c r="C65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H64" s="7" t="n">
+      <c r="H65" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr"/>
-      <c r="C65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="9" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr"/>
+      <c r="C66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr"/>
-      <c r="C66" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="D66" s="11" t="n">
+      <c r="B67" s="10" t="inlineStr"/>
+      <c r="C67" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="D67" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="E66" s="11" t="n">
+      <c r="E67" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="11" t="n">
-        <v>67</v>
-      </c>
-      <c r="G66" s="11" t="inlineStr"/>
-      <c r="H66" s="11" t="inlineStr"/>
+      <c r="F67" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G67" s="11" t="inlineStr"/>
+      <c r="H67" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2343,7 +2369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5804,11 +5830,61 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>496</v>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Next Greater Element I</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Hash Table, Stack, Monotonic Stack</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J72" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" s="14" t="n">
+        <v>46288.95560185185</v>
+      </c>
+      <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F71">
+  <conditionalFormatting sqref="F5:F72">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5887,6 +5963,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5898,7 +5975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:I194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5941,7 +6018,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   39 solved   (Low: 18 · Medium: 19 · High: 2)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   40 solved   (Low: 19 · Medium: 19 · High: 2)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -6906,7 +6983,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Stack, Monotonic Stack   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -6937,11 +7014,11 @@
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Next Greater Element I</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1353</v>
+        <v>496</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
@@ -6949,10 +7026,10 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>46.3</v>
+        <v>44.5</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -6960,7 +7037,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46288.95560185185</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -6971,7 +7048,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -6984,40 +7061,40 @@
       <c r="I50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="n"/>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="19" t="n"/>
-      <c r="F51" s="19" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="19" t="n"/>
-      <c r="I51" s="19" t="n"/>
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -7025,7 +7102,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -7036,7 +7113,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -7049,48 +7126,48 @@
       <c r="I53" s="18" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="n"/>
-      <c r="B54" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
+      <c r="A54" s="19" t="n"/>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="19" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -7101,7 +7178,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -7132,11 +7209,11 @@
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
@@ -7144,18 +7221,18 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -7166,7 +7243,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -7197,11 +7274,11 @@
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
@@ -7209,10 +7286,10 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
@@ -7220,7 +7297,7 @@
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -7231,7 +7308,7 @@
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -7244,40 +7321,40 @@
       <c r="I62" s="18" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="19" t="n"/>
-      <c r="B63" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n"/>
-      <c r="F63" s="19" t="n"/>
-      <c r="G63" s="19" t="n"/>
-      <c r="H63" s="19" t="n"/>
-      <c r="I63" s="19" t="n"/>
+      <c r="A63" s="21" t="n"/>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="21" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -7285,7 +7362,7 @@
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -7296,7 +7373,7 @@
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -7309,40 +7386,40 @@
       <c r="I65" s="18" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="21" t="n"/>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="21" t="n"/>
-      <c r="I66" s="21" t="n"/>
+      <c r="A66" s="19" t="n"/>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C66" s="19" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="19" t="n"/>
+      <c r="G66" s="19" t="n"/>
+      <c r="H66" s="19" t="n"/>
+      <c r="I66" s="19" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -7350,7 +7427,7 @@
         </is>
       </c>
       <c r="H67" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -7361,7 +7438,7 @@
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B68" s="18" t="n"/>
@@ -7374,40 +7451,40 @@
       <c r="I68" s="18" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="19" t="n"/>
-      <c r="B69" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C69" s="19" t="n"/>
-      <c r="D69" s="19" t="n"/>
-      <c r="E69" s="19" t="n"/>
-      <c r="F69" s="19" t="n"/>
-      <c r="G69" s="19" t="n"/>
-      <c r="H69" s="19" t="n"/>
-      <c r="I69" s="19" t="n"/>
+      <c r="A69" s="21" t="n"/>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="21" t="n"/>
+      <c r="E69" s="21" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="21" t="n"/>
+      <c r="I69" s="21" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -7415,7 +7492,7 @@
         </is>
       </c>
       <c r="H70" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -7426,7 +7503,7 @@
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B71" s="18" t="n"/>
@@ -7439,155 +7516,155 @@
       <c r="I71" s="18" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="21" t="n"/>
-      <c r="B72" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="21" t="n"/>
-      <c r="I72" s="21" t="n"/>
+      <c r="A72" s="19" t="n"/>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C72" s="19" t="n"/>
+      <c r="D72" s="19" t="n"/>
+      <c r="E72" s="19" t="n"/>
+      <c r="F72" s="19" t="n"/>
+      <c r="G72" s="19" t="n"/>
+      <c r="H72" s="19" t="n"/>
+      <c r="I72" s="19" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
+          <t>Matrix Block Sum</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>46262.8983912037</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="n"/>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="n"/>
+      <c r="D75" s="21" t="n"/>
+      <c r="E75" s="21" t="n"/>
+      <c r="F75" s="21" t="n"/>
+      <c r="G75" s="21" t="n"/>
+      <c r="H75" s="21" t="n"/>
+      <c r="I75" s="21" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr"/>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C76" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="5" t="n">
+      <c r="E76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="n">
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>46270.61052083333</v>
       </c>
-      <c r="I73" s="13" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="19" t="n"/>
-      <c r="B74" s="20" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="19" t="n"/>
+      <c r="B77" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C74" s="19" t="n"/>
-      <c r="D74" s="19" t="n"/>
-      <c r="E74" s="19" t="n"/>
-      <c r="F74" s="19" t="n"/>
-      <c r="G74" s="19" t="n"/>
-      <c r="H74" s="19" t="n"/>
-      <c r="I74" s="19" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr"/>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Flight Bookings</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="n">
-        <v>46262.6837962963</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B76" s="18" t="n"/>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
-      <c r="H76" s="18" t="n"/>
-      <c r="I76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="23" t="n"/>
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C77" s="23" t="n"/>
-      <c r="D77" s="23" t="n"/>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="23" t="n"/>
-      <c r="G77" s="23" t="n"/>
-      <c r="H77" s="23" t="n"/>
-      <c r="I77" s="23" t="n"/>
+      <c r="C77" s="19" t="n"/>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="19" t="n"/>
+      <c r="G77" s="19" t="n"/>
+      <c r="H77" s="19" t="n"/>
+      <c r="I77" s="19" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window Maximum</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
-        <v>239</v>
+        <v>1206</v>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>143.4</v>
+        <v>85</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
@@ -7595,7 +7672,7 @@
         </is>
       </c>
       <c r="H78" s="12" t="n">
-        <v>46276.50631944444</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -7606,7 +7683,7 @@
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B79" s="18" t="n"/>
@@ -7619,40 +7696,40 @@
       <c r="I79" s="18" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="21" t="n"/>
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C80" s="21" t="n"/>
-      <c r="D80" s="21" t="n"/>
-      <c r="E80" s="21" t="n"/>
-      <c r="F80" s="21" t="n"/>
-      <c r="G80" s="21" t="n"/>
-      <c r="H80" s="21" t="n"/>
-      <c r="I80" s="21" t="n"/>
+      <c r="A80" s="23" t="n"/>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C80" s="23" t="n"/>
+      <c r="D80" s="23" t="n"/>
+      <c r="E80" s="23" t="n"/>
+      <c r="F80" s="23" t="n"/>
+      <c r="G80" s="23" t="n"/>
+      <c r="H80" s="23" t="n"/>
+      <c r="I80" s="23" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Sliding Window Maximum</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>3347</v>
+        <v>239</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>46.7</v>
+        <v>143.4</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
@@ -7660,7 +7737,7 @@
         </is>
       </c>
       <c r="H81" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46276.50631944444</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -7671,7 +7748,7 @@
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B82" s="18" t="n"/>
@@ -7702,11 +7779,11 @@
       <c r="A84" s="5" t="inlineStr"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
@@ -7714,10 +7791,10 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
@@ -7725,7 +7802,7 @@
         </is>
       </c>
       <c r="H84" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -7736,7 +7813,7 @@
     <row r="85">
       <c r="A85" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sorting, Quicksort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B85" s="18" t="n"/>
@@ -7749,40 +7826,40 @@
       <c r="I85" s="18" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="19" t="n"/>
-      <c r="B86" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C86" s="19" t="n"/>
-      <c r="D86" s="19" t="n"/>
-      <c r="E86" s="19" t="n"/>
-      <c r="F86" s="19" t="n"/>
-      <c r="G86" s="19" t="n"/>
-      <c r="H86" s="19" t="n"/>
-      <c r="I86" s="19" t="n"/>
+      <c r="A86" s="21" t="n"/>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="n"/>
+      <c r="D86" s="21" t="n"/>
+      <c r="E86" s="21" t="n"/>
+      <c r="F86" s="21" t="n"/>
+      <c r="G86" s="21" t="n"/>
+      <c r="H86" s="21" t="n"/>
+      <c r="I86" s="21" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr"/>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Merge Intervals</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>56</v>
+        <v>643</v>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>48.9</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
@@ -7790,7 +7867,7 @@
         </is>
       </c>
       <c r="H87" s="12" t="n">
-        <v>46273.68709490741</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -7801,7 +7878,7 @@
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack   —   3 solved   (Low: 1 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sorting, Quicksort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B88" s="18" t="n"/>
@@ -7814,200 +7891,200 @@
       <c r="I88" s="18" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="21" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
+      <c r="A89" s="19" t="n"/>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C89" s="19" t="n"/>
+      <c r="D89" s="19" t="n"/>
+      <c r="E89" s="19" t="n"/>
+      <c r="F89" s="19" t="n"/>
+      <c r="G89" s="19" t="n"/>
+      <c r="H89" s="19" t="n"/>
+      <c r="I89" s="19" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
+          <t>Merge Intervals</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>46273.68709490741</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack   —   3 solved   (Low: 1 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="n"/>
+      <c r="C91" s="18" t="n"/>
+      <c r="D91" s="18" t="n"/>
+      <c r="E91" s="18" t="n"/>
+      <c r="F91" s="18" t="n"/>
+      <c r="G91" s="18" t="n"/>
+      <c r="H91" s="18" t="n"/>
+      <c r="I91" s="18" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="n"/>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C92" s="21" t="n"/>
+      <c r="D92" s="21" t="n"/>
+      <c r="E92" s="21" t="n"/>
+      <c r="F92" s="21" t="n"/>
+      <c r="G92" s="21" t="n"/>
+      <c r="H92" s="21" t="n"/>
+      <c r="I92" s="21" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr"/>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C93" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n">
+      <c r="E93" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F90" s="5" t="n">
+      <c r="F93" s="5" t="n">
         <v>45.6</v>
       </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H90" s="12" t="n">
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="n">
         <v>46275.51596064815</v>
       </c>
-      <c r="I90" s="13" t="inlineStr">
+      <c r="I93" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="19" t="n"/>
-      <c r="B91" s="20" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="19" t="n"/>
+      <c r="B94" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C91" s="19" t="n"/>
-      <c r="D91" s="19" t="n"/>
-      <c r="E91" s="19" t="n"/>
-      <c r="F91" s="19" t="n"/>
-      <c r="G91" s="19" t="n"/>
-      <c r="H91" s="19" t="n"/>
-      <c r="I91" s="19" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr"/>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="C94" s="19" t="n"/>
+      <c r="D94" s="19" t="n"/>
+      <c r="E94" s="19" t="n"/>
+      <c r="F94" s="19" t="n"/>
+      <c r="G94" s="19" t="n"/>
+      <c r="H94" s="19" t="n"/>
+      <c r="I94" s="19" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C95" s="5" t="n">
         <v>503</v>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="E95" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F95" s="5" t="n">
         <v>48.5</v>
       </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="n">
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="n">
         <v>46275.6128125</v>
       </c>
-      <c r="I92" s="13" t="inlineStr">
+      <c r="I95" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr"/>
-      <c r="B93" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C93" s="7" t="n">
+      <c r="C96" s="7" t="n">
         <v>739</v>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n">
+      <c r="E96" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F93" s="7" t="n">
+      <c r="F96" s="7" t="n">
         <v>108.1</v>
       </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H93" s="14" t="n">
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H96" s="14" t="n">
         <v>46275.62596064815</v>
       </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B94" s="18" t="n"/>
-      <c r="C94" s="18" t="n"/>
-      <c r="D94" s="18" t="n"/>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="18" t="n"/>
-      <c r="G94" s="18" t="n"/>
-      <c r="H94" s="18" t="n"/>
-      <c r="I94" s="18" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="21" t="n"/>
-      <c r="B95" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="n"/>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr"/>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Score Validator</t>
-        </is>
-      </c>
-      <c r="C96" s="5" t="n">
-        <v>4281</v>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>46247.02123842593</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8016,7 +8093,7 @@
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B97" s="18" t="n"/>
@@ -8032,7 +8109,7 @@
       <c r="A98" s="21" t="n"/>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C98" s="21" t="n"/>
@@ -8047,132 +8124,132 @@
       <c r="A99" s="5" t="inlineStr"/>
       <c r="B99" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="18" t="n"/>
+      <c r="D100" s="18" t="n"/>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+      <c r="G100" s="18" t="n"/>
+      <c r="H100" s="18" t="n"/>
+      <c r="I100" s="18" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="n"/>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="n"/>
+      <c r="D101" s="21" t="n"/>
+      <c r="E101" s="21" t="n"/>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr"/>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C102" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="5" t="n">
+      <c r="E102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="n">
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I99" s="13" t="inlineStr">
+      <c r="I102" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr"/>
-      <c r="B100" s="6" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr"/>
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C100" s="7" t="n">
+      <c r="C103" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E100" s="7" t="n">
+      <c r="E103" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F100" s="7" t="n">
+      <c r="F103" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H100" s="14" t="n">
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H103" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="19" t="n"/>
-      <c r="B102" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C102" s="19" t="n"/>
-      <c r="D102" s="19" t="n"/>
-      <c r="E102" s="19" t="n"/>
-      <c r="F102" s="19" t="n"/>
-      <c r="G102" s="19" t="n"/>
-      <c r="H102" s="19" t="n"/>
-      <c r="I102" s="19" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr"/>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Two Sum II - Input Array Is Sorted</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>46272.93130787037</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="I103" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8181,7 +8258,7 @@
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B104" s="18" t="n"/>
@@ -8212,11 +8289,11 @@
       <c r="A106" s="5" t="inlineStr"/>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Find the Duplicate Number</t>
+          <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
       <c r="C106" s="5" t="n">
-        <v>287</v>
+        <v>167</v>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
@@ -8224,10 +8301,10 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
@@ -8235,7 +8312,7 @@
         </is>
       </c>
       <c r="H106" s="12" t="n">
-        <v>46274.9421875</v>
+        <v>46272.93130787037</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -8246,7 +8323,7 @@
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B107" s="18" t="n"/>
@@ -8277,121 +8354,121 @@
       <c r="A109" s="5" t="inlineStr"/>
       <c r="B109" s="4" t="inlineStr">
         <is>
+          <t>Find the Duplicate Number</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>46274.9421875</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="18" t="n"/>
+      <c r="E110" s="18" t="n"/>
+      <c r="F110" s="18" t="n"/>
+      <c r="G110" s="18" t="n"/>
+      <c r="H110" s="18" t="n"/>
+      <c r="I110" s="18" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="19" t="n"/>
+      <c r="B111" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C111" s="19" t="n"/>
+      <c r="D111" s="19" t="n"/>
+      <c r="E111" s="19" t="n"/>
+      <c r="F111" s="19" t="n"/>
+      <c r="G111" s="19" t="n"/>
+      <c r="H111" s="19" t="n"/>
+      <c r="I111" s="19" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr"/>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C112" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E112" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F112" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="n">
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I109" s="13" t="inlineStr">
+      <c r="I112" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="16" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   4 solved   (Low: 0 · Medium: 4 · High: 0)</t>
         </is>
       </c>
-      <c r="B110" s="2" t="n"/>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B111" s="18" t="n"/>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="18" t="n"/>
-      <c r="E111" s="18" t="n"/>
-      <c r="F111" s="18" t="n"/>
-      <c r="G111" s="18" t="n"/>
-      <c r="H111" s="18" t="n"/>
-      <c r="I111" s="18" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="19" t="n"/>
-      <c r="B112" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C112" s="19" t="n"/>
-      <c r="D112" s="19" t="n"/>
-      <c r="E112" s="19" t="n"/>
-      <c r="F112" s="19" t="n"/>
-      <c r="G112" s="19" t="n"/>
-      <c r="H112" s="19" t="n"/>
-      <c r="I112" s="19" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr"/>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Course Schedule II</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>46288.67247685185</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B114" s="18" t="n"/>
@@ -8422,11 +8499,11 @@
       <c r="A116" s="5" t="inlineStr"/>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Course Schedule</t>
+          <t>Course Schedule II</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
@@ -8434,10 +8511,10 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
@@ -8445,7 +8522,7 @@
         </is>
       </c>
       <c r="H116" s="12" t="n">
-        <v>46288.65751157407</v>
+        <v>46288.67247685185</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -8456,7 +8533,7 @@
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B117" s="18" t="n"/>
@@ -8472,7 +8549,7 @@
       <c r="A118" s="19" t="n"/>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Medium (Medium) — 2 problem(s)</t>
+          <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C118" s="19" t="n"/>
@@ -8487,236 +8564,236 @@
       <c r="A119" s="5" t="inlineStr"/>
       <c r="B119" s="4" t="inlineStr">
         <is>
+          <t>Course Schedule</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>46288.65751157407</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="n"/>
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="18" t="n"/>
+      <c r="E120" s="18" t="n"/>
+      <c r="F120" s="18" t="n"/>
+      <c r="G120" s="18" t="n"/>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="19" t="n"/>
+      <c r="B121" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C121" s="19" t="n"/>
+      <c r="D121" s="19" t="n"/>
+      <c r="E121" s="19" t="n"/>
+      <c r="F121" s="19" t="n"/>
+      <c r="G121" s="19" t="n"/>
+      <c r="H121" s="19" t="n"/>
+      <c r="I121" s="19" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr"/>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C119" s="5" t="n">
+      <c r="C122" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E119" s="5" t="n">
+      <c r="E122" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F119" s="5" t="n">
+      <c r="F122" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H119" s="12" t="n">
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="n">
         <v>46287.65729166667</v>
       </c>
-      <c r="I119" s="13" t="inlineStr">
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="7" t="inlineStr"/>
-      <c r="B120" s="6" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr"/>
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C120" s="7" t="n">
+      <c r="C123" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D120" s="7" t="inlineStr">
+      <c r="D123" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E120" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="7" t="n">
+      <c r="E123" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H120" s="14" t="n">
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H123" s="14" t="n">
         <v>46287.51434027778</v>
       </c>
-      <c r="I120" s="15" t="inlineStr">
+      <c r="I123" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="16" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B121" s="2" t="n"/>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="2" t="n"/>
-      <c r="F121" s="2" t="n"/>
-      <c r="G121" s="2" t="n"/>
-      <c r="H121" s="2" t="n"/>
-      <c r="I121" s="2" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="17" t="inlineStr">
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="18" t="n"/>
-      <c r="D122" s="18" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
-      <c r="G122" s="18" t="n"/>
-      <c r="H122" s="18" t="n"/>
-      <c r="I122" s="18" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="21" t="n"/>
-      <c r="B123" s="22" t="inlineStr">
+      <c r="B125" s="18" t="n"/>
+      <c r="C125" s="18" t="n"/>
+      <c r="D125" s="18" t="n"/>
+      <c r="E125" s="18" t="n"/>
+      <c r="F125" s="18" t="n"/>
+      <c r="G125" s="18" t="n"/>
+      <c r="H125" s="18" t="n"/>
+      <c r="I125" s="18" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="21" t="n"/>
+      <c r="B126" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C123" s="21" t="n"/>
-      <c r="D123" s="21" t="n"/>
-      <c r="E123" s="21" t="n"/>
-      <c r="F123" s="21" t="n"/>
-      <c r="G123" s="21" t="n"/>
-      <c r="H123" s="21" t="n"/>
-      <c r="I123" s="21" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr"/>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="C126" s="21" t="n"/>
+      <c r="D126" s="21" t="n"/>
+      <c r="E126" s="21" t="n"/>
+      <c r="F126" s="21" t="n"/>
+      <c r="G126" s="21" t="n"/>
+      <c r="H126" s="21" t="n"/>
+      <c r="I126" s="21" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr"/>
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C124" s="5" t="n">
+      <c r="C127" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D127" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E124" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="5" t="n">
+      <c r="E127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G127" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H124" s="12" t="n">
+      <c r="H127" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I124" s="13" t="inlineStr">
+      <c r="I127" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="16" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: LINKED LIST   —   7 solved   (Low: 3 · Medium: 2 · High: 2)</t>
         </is>
       </c>
-      <c r="B125" s="2" t="n"/>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n"/>
-      <c r="E125" s="2" t="n"/>
-      <c r="F125" s="2" t="n"/>
-      <c r="G125" s="2" t="n"/>
-      <c r="H125" s="2" t="n"/>
-      <c r="I125" s="2" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B126" s="18" t="n"/>
-      <c r="C126" s="18" t="n"/>
-      <c r="D126" s="18" t="n"/>
-      <c r="E126" s="18" t="n"/>
-      <c r="F126" s="18" t="n"/>
-      <c r="G126" s="18" t="n"/>
-      <c r="H126" s="18" t="n"/>
-      <c r="I126" s="18" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="23" t="n"/>
-      <c r="B127" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C127" s="23" t="n"/>
-      <c r="D127" s="23" t="n"/>
-      <c r="E127" s="23" t="n"/>
-      <c r="F127" s="23" t="n"/>
-      <c r="G127" s="23" t="n"/>
-      <c r="H127" s="23" t="n"/>
-      <c r="I127" s="23" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr"/>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>Merge k Sorted Lists</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H128" s="12" t="n">
-        <v>46286.43949074074</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="n"/>
+      <c r="I128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B129" s="18" t="n"/>
@@ -8729,40 +8806,40 @@
       <c r="I129" s="18" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="19" t="n"/>
-      <c r="B130" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C130" s="19" t="n"/>
-      <c r="D130" s="19" t="n"/>
-      <c r="E130" s="19" t="n"/>
-      <c r="F130" s="19" t="n"/>
-      <c r="G130" s="19" t="n"/>
-      <c r="H130" s="19" t="n"/>
-      <c r="I130" s="19" t="n"/>
+      <c r="A130" s="23" t="n"/>
+      <c r="B130" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C130" s="23" t="n"/>
+      <c r="D130" s="23" t="n"/>
+      <c r="E130" s="23" t="n"/>
+      <c r="F130" s="23" t="n"/>
+      <c r="G130" s="23" t="n"/>
+      <c r="H130" s="23" t="n"/>
+      <c r="I130" s="23" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr"/>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List II</t>
+          <t>Merge k Sorted Lists</t>
         </is>
       </c>
       <c r="C131" s="5" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>42.9</v>
+        <v>45.9</v>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
@@ -8770,7 +8847,7 @@
         </is>
       </c>
       <c r="H131" s="12" t="n">
-        <v>46275.41266203704</v>
+        <v>46286.43949074074</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -8781,7 +8858,7 @@
     <row r="132">
       <c r="A132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B132" s="18" t="n"/>
@@ -8794,369 +8871,369 @@
       <c r="I132" s="18" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="21" t="n"/>
-      <c r="B133" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C133" s="21" t="n"/>
-      <c r="D133" s="21" t="n"/>
-      <c r="E133" s="21" t="n"/>
-      <c r="F133" s="21" t="n"/>
-      <c r="G133" s="21" t="n"/>
-      <c r="H133" s="21" t="n"/>
-      <c r="I133" s="21" t="n"/>
+      <c r="A133" s="19" t="n"/>
+      <c r="B133" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C133" s="19" t="n"/>
+      <c r="D133" s="19" t="n"/>
+      <c r="E133" s="19" t="n"/>
+      <c r="F133" s="19" t="n"/>
+      <c r="G133" s="19" t="n"/>
+      <c r="H133" s="19" t="n"/>
+      <c r="I133" s="19" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr"/>
       <c r="B134" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List II</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>46275.41266203704</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B135" s="18" t="n"/>
+      <c r="C135" s="18" t="n"/>
+      <c r="D135" s="18" t="n"/>
+      <c r="E135" s="18" t="n"/>
+      <c r="F135" s="18" t="n"/>
+      <c r="G135" s="18" t="n"/>
+      <c r="H135" s="18" t="n"/>
+      <c r="I135" s="18" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="21" t="n"/>
+      <c r="B136" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C136" s="21" t="n"/>
+      <c r="D136" s="21" t="n"/>
+      <c r="E136" s="21" t="n"/>
+      <c r="F136" s="21" t="n"/>
+      <c r="G136" s="21" t="n"/>
+      <c r="H136" s="21" t="n"/>
+      <c r="I136" s="21" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr"/>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C134" s="5" t="n">
+      <c r="C137" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="5" t="n">
+      <c r="E137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H134" s="12" t="n">
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I134" s="13" t="inlineStr">
+      <c r="I137" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="19" t="n"/>
-      <c r="B135" s="20" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="19" t="n"/>
+      <c r="B138" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C135" s="19" t="n"/>
-      <c r="D135" s="19" t="n"/>
-      <c r="E135" s="19" t="n"/>
-      <c r="F135" s="19" t="n"/>
-      <c r="G135" s="19" t="n"/>
-      <c r="H135" s="19" t="n"/>
-      <c r="I135" s="19" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr"/>
-      <c r="B136" s="4" t="inlineStr">
-        <is>
-          <t>Linked List Cycle II</t>
-        </is>
-      </c>
-      <c r="C136" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="D136" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E136" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" s="5" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="G136" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H136" s="12" t="n">
-        <v>46274.44269675926</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Recursion   —   2 solved   (Low: 1 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B137" s="18" t="n"/>
-      <c r="C137" s="18" t="n"/>
-      <c r="D137" s="18" t="n"/>
-      <c r="E137" s="18" t="n"/>
-      <c r="F137" s="18" t="n"/>
-      <c r="G137" s="18" t="n"/>
-      <c r="H137" s="18" t="n"/>
-      <c r="I137" s="18" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="21" t="n"/>
-      <c r="B138" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C138" s="21" t="n"/>
-      <c r="D138" s="21" t="n"/>
-      <c r="E138" s="21" t="n"/>
-      <c r="F138" s="21" t="n"/>
-      <c r="G138" s="21" t="n"/>
-      <c r="H138" s="21" t="n"/>
-      <c r="I138" s="21" t="n"/>
+      <c r="C138" s="19" t="n"/>
+      <c r="D138" s="19" t="n"/>
+      <c r="E138" s="19" t="n"/>
+      <c r="F138" s="19" t="n"/>
+      <c r="G138" s="19" t="n"/>
+      <c r="H138" s="19" t="n"/>
+      <c r="I138" s="19" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr"/>
       <c r="B139" s="4" t="inlineStr">
         <is>
+          <t>Linked List Cycle II</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>46274.44269675926</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Recursion   —   2 solved   (Low: 1 · Medium: 0 · High: 1)</t>
+        </is>
+      </c>
+      <c r="B140" s="18" t="n"/>
+      <c r="C140" s="18" t="n"/>
+      <c r="D140" s="18" t="n"/>
+      <c r="E140" s="18" t="n"/>
+      <c r="F140" s="18" t="n"/>
+      <c r="G140" s="18" t="n"/>
+      <c r="H140" s="18" t="n"/>
+      <c r="I140" s="18" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="n"/>
+      <c r="B141" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="n"/>
+      <c r="D141" s="21" t="n"/>
+      <c r="E141" s="21" t="n"/>
+      <c r="F141" s="21" t="n"/>
+      <c r="G141" s="21" t="n"/>
+      <c r="H141" s="21" t="n"/>
+      <c r="I141" s="21" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr"/>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n">
+      <c r="C142" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="5" t="n">
+      <c r="E142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="5" t="n">
         <v>44.1</v>
       </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="n">
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="n">
         <v>46274.48334490741</v>
       </c>
-      <c r="I139" s="13" t="inlineStr">
+      <c r="I142" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="23" t="n"/>
-      <c r="B140" s="24" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="23" t="n"/>
+      <c r="B143" s="24" t="inlineStr">
         <is>
           <t>High (Hard) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C140" s="23" t="n"/>
-      <c r="D140" s="23" t="n"/>
-      <c r="E140" s="23" t="n"/>
-      <c r="F140" s="23" t="n"/>
-      <c r="G140" s="23" t="n"/>
-      <c r="H140" s="23" t="n"/>
-      <c r="I140" s="23" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr"/>
-      <c r="B141" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Nodes in k-Group</t>
-        </is>
-      </c>
-      <c r="C141" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D141" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="G141" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H141" s="12" t="n">
-        <v>46288.89429398148</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B142" s="18" t="n"/>
-      <c r="C142" s="18" t="n"/>
-      <c r="D142" s="18" t="n"/>
-      <c r="E142" s="18" t="n"/>
-      <c r="F142" s="18" t="n"/>
-      <c r="G142" s="18" t="n"/>
-      <c r="H142" s="18" t="n"/>
-      <c r="I142" s="18" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="21" t="n"/>
-      <c r="B143" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C143" s="21" t="n"/>
-      <c r="D143" s="21" t="n"/>
-      <c r="E143" s="21" t="n"/>
-      <c r="F143" s="21" t="n"/>
-      <c r="G143" s="21" t="n"/>
-      <c r="H143" s="21" t="n"/>
-      <c r="I143" s="21" t="n"/>
+      <c r="C143" s="23" t="n"/>
+      <c r="D143" s="23" t="n"/>
+      <c r="E143" s="23" t="n"/>
+      <c r="F143" s="23" t="n"/>
+      <c r="G143" s="23" t="n"/>
+      <c r="H143" s="23" t="n"/>
+      <c r="I143" s="23" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr"/>
       <c r="B144" s="4" t="inlineStr">
         <is>
+          <t>Reverse Nodes in k-Group</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H144" s="12" t="n">
+        <v>46288.89429398148</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B145" s="18" t="n"/>
+      <c r="C145" s="18" t="n"/>
+      <c r="D145" s="18" t="n"/>
+      <c r="E145" s="18" t="n"/>
+      <c r="F145" s="18" t="n"/>
+      <c r="G145" s="18" t="n"/>
+      <c r="H145" s="18" t="n"/>
+      <c r="I145" s="18" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="21" t="n"/>
+      <c r="B146" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C146" s="21" t="n"/>
+      <c r="D146" s="21" t="n"/>
+      <c r="E146" s="21" t="n"/>
+      <c r="F146" s="21" t="n"/>
+      <c r="G146" s="21" t="n"/>
+      <c r="H146" s="21" t="n"/>
+      <c r="I146" s="21" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="inlineStr"/>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C144" s="5" t="n">
+      <c r="C147" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D144" s="5" t="inlineStr">
+      <c r="D147" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="5" t="n">
+      <c r="E147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H144" s="12" t="n">
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I144" s="13" t="inlineStr">
+      <c r="I147" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="16" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B145" s="2" t="n"/>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="n"/>
-      <c r="G145" s="2" t="n"/>
-      <c r="H145" s="2" t="n"/>
-      <c r="I145" s="2" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B146" s="18" t="n"/>
-      <c r="C146" s="18" t="n"/>
-      <c r="D146" s="18" t="n"/>
-      <c r="E146" s="18" t="n"/>
-      <c r="F146" s="18" t="n"/>
-      <c r="G146" s="18" t="n"/>
-      <c r="H146" s="18" t="n"/>
-      <c r="I146" s="18" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="21" t="n"/>
-      <c r="B147" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C147" s="21" t="n"/>
-      <c r="D147" s="21" t="n"/>
-      <c r="E147" s="21" t="n"/>
-      <c r="F147" s="21" t="n"/>
-      <c r="G147" s="21" t="n"/>
-      <c r="H147" s="21" t="n"/>
-      <c r="I147" s="21" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="inlineStr"/>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C148" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F148" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G148" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H148" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n"/>
+      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B149" s="18" t="n"/>
@@ -9187,11 +9264,11 @@
       <c r="A151" s="5" t="inlineStr"/>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C151" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
@@ -9199,10 +9276,10 @@
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
@@ -9210,7 +9287,7 @@
         </is>
       </c>
       <c r="H151" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -9221,7 +9298,7 @@
     <row r="152">
       <c r="A152" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B152" s="18" t="n"/>
@@ -9237,7 +9314,7 @@
       <c r="A153" s="21" t="n"/>
       <c r="B153" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C153" s="21" t="n"/>
@@ -9252,11 +9329,11 @@
       <c r="A154" s="5" t="inlineStr"/>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
-        <v>3918</v>
+        <v>3626</v>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
@@ -9267,7 +9344,7 @@
         <v>1</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
@@ -9275,7 +9352,7 @@
         </is>
       </c>
       <c r="H154" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -9284,174 +9361,174 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="7" t="inlineStr"/>
-      <c r="B155" s="6" t="inlineStr">
-        <is>
-          <t>Count Commas in Range</t>
-        </is>
-      </c>
-      <c r="C155" s="7" t="n">
-        <v>4245</v>
-      </c>
-      <c r="D155" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H155" s="14" t="n">
-        <v>46273.3956712963</v>
-      </c>
-      <c r="I155" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A155" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B155" s="18" t="n"/>
+      <c r="C155" s="18" t="n"/>
+      <c r="D155" s="18" t="n"/>
+      <c r="E155" s="18" t="n"/>
+      <c r="F155" s="18" t="n"/>
+      <c r="G155" s="18" t="n"/>
+      <c r="H155" s="18" t="n"/>
+      <c r="I155" s="18" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="19" t="n"/>
-      <c r="B156" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="n"/>
-      <c r="D156" s="19" t="n"/>
-      <c r="E156" s="19" t="n"/>
-      <c r="F156" s="19" t="n"/>
-      <c r="G156" s="19" t="n"/>
-      <c r="H156" s="19" t="n"/>
-      <c r="I156" s="19" t="n"/>
+      <c r="A156" s="21" t="n"/>
+      <c r="B156" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C156" s="21" t="n"/>
+      <c r="D156" s="21" t="n"/>
+      <c r="E156" s="21" t="n"/>
+      <c r="F156" s="21" t="n"/>
+      <c r="G156" s="21" t="n"/>
+      <c r="H156" s="21" t="n"/>
+      <c r="I156" s="21" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr"/>
       <c r="B157" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr"/>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H158" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I158" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="19" t="n"/>
+      <c r="B159" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C159" s="19" t="n"/>
+      <c r="D159" s="19" t="n"/>
+      <c r="E159" s="19" t="n"/>
+      <c r="F159" s="19" t="n"/>
+      <c r="G159" s="19" t="n"/>
+      <c r="H159" s="19" t="n"/>
+      <c r="I159" s="19" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="inlineStr"/>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C157" s="5" t="n">
+      <c r="C160" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D160" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E157" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" s="5" t="n">
+      <c r="E160" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G157" s="5" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H157" s="12" t="n">
+      <c r="H160" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I157" s="13" t="inlineStr">
+      <c r="I160" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="16" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n"/>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" s="2" t="n"/>
-      <c r="F158" s="2" t="n"/>
-      <c r="G158" s="2" t="n"/>
-      <c r="H158" s="2" t="n"/>
-      <c r="I158" s="2" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B159" s="18" t="n"/>
-      <c r="C159" s="18" t="n"/>
-      <c r="D159" s="18" t="n"/>
-      <c r="E159" s="18" t="n"/>
-      <c r="F159" s="18" t="n"/>
-      <c r="G159" s="18" t="n"/>
-      <c r="H159" s="18" t="n"/>
-      <c r="I159" s="18" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="21" t="n"/>
-      <c r="B160" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C160" s="21" t="n"/>
-      <c r="D160" s="21" t="n"/>
-      <c r="E160" s="21" t="n"/>
-      <c r="F160" s="21" t="n"/>
-      <c r="G160" s="21" t="n"/>
-      <c r="H160" s="21" t="n"/>
-      <c r="I160" s="21" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr"/>
-      <c r="B161" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C161" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D161" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E161" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F161" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G161" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H161" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I161" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="2" t="n"/>
+      <c r="H161" s="2" t="n"/>
+      <c r="I161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B162" s="18" t="n"/>
@@ -9464,48 +9541,48 @@
       <c r="I162" s="18" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="19" t="n"/>
-      <c r="B163" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C163" s="19" t="n"/>
-      <c r="D163" s="19" t="n"/>
-      <c r="E163" s="19" t="n"/>
-      <c r="F163" s="19" t="n"/>
-      <c r="G163" s="19" t="n"/>
-      <c r="H163" s="19" t="n"/>
-      <c r="I163" s="19" t="n"/>
+      <c r="A163" s="21" t="n"/>
+      <c r="B163" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C163" s="21" t="n"/>
+      <c r="D163" s="21" t="n"/>
+      <c r="E163" s="21" t="n"/>
+      <c r="F163" s="21" t="n"/>
+      <c r="G163" s="21" t="n"/>
+      <c r="H163" s="21" t="n"/>
+      <c r="I163" s="21" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr"/>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C164" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H164" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -9516,7 +9593,7 @@
     <row r="165">
       <c r="A165" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B165" s="18" t="n"/>
@@ -9529,40 +9606,40 @@
       <c r="I165" s="18" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="21" t="n"/>
-      <c r="B166" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C166" s="21" t="n"/>
-      <c r="D166" s="21" t="n"/>
-      <c r="E166" s="21" t="n"/>
-      <c r="F166" s="21" t="n"/>
-      <c r="G166" s="21" t="n"/>
-      <c r="H166" s="21" t="n"/>
-      <c r="I166" s="21" t="n"/>
+      <c r="A166" s="19" t="n"/>
+      <c r="B166" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C166" s="19" t="n"/>
+      <c r="D166" s="19" t="n"/>
+      <c r="E166" s="19" t="n"/>
+      <c r="F166" s="19" t="n"/>
+      <c r="G166" s="19" t="n"/>
+      <c r="H166" s="19" t="n"/>
+      <c r="I166" s="19" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr"/>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
@@ -9570,7 +9647,7 @@
         </is>
       </c>
       <c r="H167" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -9581,7 +9658,7 @@
     <row r="168">
       <c r="A168" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B168" s="18" t="n"/>
@@ -9612,11 +9689,11 @@
       <c r="A170" s="5" t="inlineStr"/>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Reverse Degree of a String</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
-        <v>3811</v>
+        <v>242</v>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
@@ -9624,10 +9701,10 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
@@ -9635,7 +9712,7 @@
         </is>
       </c>
       <c r="H170" s="12" t="n">
-        <v>46285.42987268518</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I170" s="13" t="inlineStr">
         <is>
@@ -9646,7 +9723,7 @@
     <row r="171">
       <c r="A171" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B171" s="18" t="n"/>
@@ -9677,11 +9754,11 @@
       <c r="A173" s="5" t="inlineStr"/>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Reverse Degree of a String</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>125</v>
+        <v>3811</v>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
@@ -9689,18 +9766,18 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H173" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46285.42987268518</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -9711,7 +9788,7 @@
     <row r="174">
       <c r="A174" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B174" s="18" t="n"/>
@@ -9742,121 +9819,121 @@
       <c r="A176" s="5" t="inlineStr"/>
       <c r="B176" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H176" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B177" s="18" t="n"/>
+      <c r="C177" s="18" t="n"/>
+      <c r="D177" s="18" t="n"/>
+      <c r="E177" s="18" t="n"/>
+      <c r="F177" s="18" t="n"/>
+      <c r="G177" s="18" t="n"/>
+      <c r="H177" s="18" t="n"/>
+      <c r="I177" s="18" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="21" t="n"/>
+      <c r="B178" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C178" s="21" t="n"/>
+      <c r="D178" s="21" t="n"/>
+      <c r="E178" s="21" t="n"/>
+      <c r="F178" s="21" t="n"/>
+      <c r="G178" s="21" t="n"/>
+      <c r="H178" s="21" t="n"/>
+      <c r="I178" s="21" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="inlineStr"/>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C176" s="5" t="n">
+      <c r="C179" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D176" s="5" t="inlineStr">
+      <c r="D179" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E176" s="5" t="n">
+      <c r="E179" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F176" s="5" t="n">
+      <c r="F179" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G176" s="5" t="inlineStr">
+      <c r="G179" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H176" s="12" t="n">
+      <c r="H179" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I176" s="13" t="inlineStr">
+      <c r="I179" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="16" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B177" s="2" t="n"/>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" s="2" t="n"/>
-      <c r="F177" s="2" t="n"/>
-      <c r="G177" s="2" t="n"/>
-      <c r="H177" s="2" t="n"/>
-      <c r="I177" s="2" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B178" s="18" t="n"/>
-      <c r="C178" s="18" t="n"/>
-      <c r="D178" s="18" t="n"/>
-      <c r="E178" s="18" t="n"/>
-      <c r="F178" s="18" t="n"/>
-      <c r="G178" s="18" t="n"/>
-      <c r="H178" s="18" t="n"/>
-      <c r="I178" s="18" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="21" t="n"/>
-      <c r="B179" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C179" s="21" t="n"/>
-      <c r="D179" s="21" t="n"/>
-      <c r="E179" s="21" t="n"/>
-      <c r="F179" s="21" t="n"/>
-      <c r="G179" s="21" t="n"/>
-      <c r="H179" s="21" t="n"/>
-      <c r="I179" s="21" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="inlineStr"/>
-      <c r="B180" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C180" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E180" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G180" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H180" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I180" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="2" t="n"/>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="n"/>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="n"/>
+      <c r="I180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B181" s="18" t="n"/>
@@ -9872,7 +9949,7 @@
       <c r="A182" s="21" t="n"/>
       <c r="B182" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C182" s="21" t="n"/>
@@ -9887,255 +9964,321 @@
       <c r="A183" s="5" t="inlineStr"/>
       <c r="B183" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B184" s="18" t="n"/>
+      <c r="C184" s="18" t="n"/>
+      <c r="D184" s="18" t="n"/>
+      <c r="E184" s="18" t="n"/>
+      <c r="F184" s="18" t="n"/>
+      <c r="G184" s="18" t="n"/>
+      <c r="H184" s="18" t="n"/>
+      <c r="I184" s="18" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="21" t="n"/>
+      <c r="B185" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C185" s="21" t="n"/>
+      <c r="D185" s="21" t="n"/>
+      <c r="E185" s="21" t="n"/>
+      <c r="F185" s="21" t="n"/>
+      <c r="G185" s="21" t="n"/>
+      <c r="H185" s="21" t="n"/>
+      <c r="I185" s="21" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr"/>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C183" s="5" t="n">
+      <c r="C186" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E183" s="5" t="n">
+      <c r="E186" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F183" s="5" t="n">
+      <c r="F186" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G183" s="5" t="inlineStr">
+      <c r="G186" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H183" s="12" t="n">
+      <c r="H186" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I183" s="13" t="inlineStr">
+      <c r="I186" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="7" t="inlineStr"/>
-      <c r="B184" s="6" t="inlineStr">
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr"/>
+      <c r="B187" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C184" s="7" t="n">
+      <c r="C187" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D184" s="7" t="inlineStr">
+      <c r="D187" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E184" s="7" t="n">
+      <c r="E187" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F184" s="7" t="n">
+      <c r="F187" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G184" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H184" s="14" t="n">
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H187" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I184" s="15" t="inlineStr">
+      <c r="I187" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="17" t="inlineStr">
+    <row r="188">
+      <c r="A188" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B185" s="18" t="n"/>
-      <c r="C185" s="18" t="n"/>
-      <c r="D185" s="18" t="n"/>
-      <c r="E185" s="18" t="n"/>
-      <c r="F185" s="18" t="n"/>
-      <c r="G185" s="18" t="n"/>
-      <c r="H185" s="18" t="n"/>
-      <c r="I185" s="18" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="21" t="n"/>
-      <c r="B186" s="22" t="inlineStr">
+      <c r="B188" s="18" t="n"/>
+      <c r="C188" s="18" t="n"/>
+      <c r="D188" s="18" t="n"/>
+      <c r="E188" s="18" t="n"/>
+      <c r="F188" s="18" t="n"/>
+      <c r="G188" s="18" t="n"/>
+      <c r="H188" s="18" t="n"/>
+      <c r="I188" s="18" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="21" t="n"/>
+      <c r="B189" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C186" s="21" t="n"/>
-      <c r="D186" s="21" t="n"/>
-      <c r="E186" s="21" t="n"/>
-      <c r="F186" s="21" t="n"/>
-      <c r="G186" s="21" t="n"/>
-      <c r="H186" s="21" t="n"/>
-      <c r="I186" s="21" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="5" t="inlineStr"/>
-      <c r="B187" s="4" t="inlineStr">
+      <c r="C189" s="21" t="n"/>
+      <c r="D189" s="21" t="n"/>
+      <c r="E189" s="21" t="n"/>
+      <c r="F189" s="21" t="n"/>
+      <c r="G189" s="21" t="n"/>
+      <c r="H189" s="21" t="n"/>
+      <c r="I189" s="21" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="5" t="inlineStr"/>
+      <c r="B190" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C187" s="5" t="n">
+      <c r="C190" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="D190" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E187" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F187" s="5" t="n">
+      <c r="E190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G187" s="5" t="inlineStr">
+      <c r="G190" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H187" s="12" t="n">
+      <c r="H190" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I187" s="13" t="inlineStr">
+      <c r="I190" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="16" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B188" s="2" t="n"/>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n"/>
-      <c r="E188" s="2" t="n"/>
-      <c r="F188" s="2" t="n"/>
-      <c r="G188" s="2" t="n"/>
-      <c r="H188" s="2" t="n"/>
-      <c r="I188" s="2" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="17" t="inlineStr">
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="2" t="n"/>
+      <c r="G191" s="2" t="n"/>
+      <c r="H191" s="2" t="n"/>
+      <c r="I191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B189" s="18" t="n"/>
-      <c r="C189" s="18" t="n"/>
-      <c r="D189" s="18" t="n"/>
-      <c r="E189" s="18" t="n"/>
-      <c r="F189" s="18" t="n"/>
-      <c r="G189" s="18" t="n"/>
-      <c r="H189" s="18" t="n"/>
-      <c r="I189" s="18" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="21" t="n"/>
-      <c r="B190" s="22" t="inlineStr">
+      <c r="B192" s="18" t="n"/>
+      <c r="C192" s="18" t="n"/>
+      <c r="D192" s="18" t="n"/>
+      <c r="E192" s="18" t="n"/>
+      <c r="F192" s="18" t="n"/>
+      <c r="G192" s="18" t="n"/>
+      <c r="H192" s="18" t="n"/>
+      <c r="I192" s="18" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="21" t="n"/>
+      <c r="B193" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C190" s="21" t="n"/>
-      <c r="D190" s="21" t="n"/>
-      <c r="E190" s="21" t="n"/>
-      <c r="F190" s="21" t="n"/>
-      <c r="G190" s="21" t="n"/>
-      <c r="H190" s="21" t="n"/>
-      <c r="I190" s="21" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="5" t="inlineStr"/>
-      <c r="B191" s="4" t="inlineStr">
+      <c r="C193" s="21" t="n"/>
+      <c r="D193" s="21" t="n"/>
+      <c r="E193" s="21" t="n"/>
+      <c r="F193" s="21" t="n"/>
+      <c r="G193" s="21" t="n"/>
+      <c r="H193" s="21" t="n"/>
+      <c r="I193" s="21" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr"/>
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C191" s="5" t="n">
+      <c r="C194" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D191" s="5" t="inlineStr">
+      <c r="D194" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E191" s="5" t="n">
+      <c r="E194" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F191" s="5" t="n">
+      <c r="F194" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G191" s="5" t="inlineStr">
+      <c r="G194" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H191" s="12" t="n">
+      <c r="H194" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I191" s="13" t="inlineStr">
+      <c r="I194" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="122">
-    <mergeCell ref="B135:I135"/>
+  <mergeCells count="124">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B190:I190"/>
     <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B159:I159"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A101:I101"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A85:I85"/>
+    <mergeCell ref="B111:I111"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A188:I188"/>
-    <mergeCell ref="A126:I126"/>
     <mergeCell ref="B98:I98"/>
+    <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A135:I135"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="B175:I175"/>
     <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B147:I147"/>
     <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A111:I111"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
+    <mergeCell ref="B146:I146"/>
     <mergeCell ref="A59:I59"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="A142:I142"/>
     <mergeCell ref="B83:I83"/>
-    <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
+    <mergeCell ref="B189:I189"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A137:I137"/>
+    <mergeCell ref="A128:I128"/>
+    <mergeCell ref="B75:I75"/>
     <mergeCell ref="A177:I177"/>
+    <mergeCell ref="B141:I141"/>
     <mergeCell ref="B115:I115"/>
     <mergeCell ref="B150:I150"/>
-    <mergeCell ref="B102:I102"/>
+    <mergeCell ref="B193:I193"/>
+    <mergeCell ref="A192:I192"/>
+    <mergeCell ref="A74:I74"/>
     <mergeCell ref="A145:I145"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="B21:I21"/>
@@ -10143,85 +10286,86 @@
     <mergeCell ref="B86:I86"/>
     <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
-    <mergeCell ref="A76:I76"/>
     <mergeCell ref="A181:I181"/>
+    <mergeCell ref="B136:I136"/>
+    <mergeCell ref="A91:I91"/>
+    <mergeCell ref="A184:I184"/>
+    <mergeCell ref="A100:I100"/>
     <mergeCell ref="A171:I171"/>
     <mergeCell ref="A165:I165"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="A180:I180"/>
+    <mergeCell ref="A155:I155"/>
+    <mergeCell ref="B178:I178"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
-    <mergeCell ref="A94:I94"/>
     <mergeCell ref="A168:I168"/>
     <mergeCell ref="B63:I63"/>
     <mergeCell ref="B163:I163"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="B138:I138"/>
-    <mergeCell ref="B91:I91"/>
     <mergeCell ref="B156:I156"/>
     <mergeCell ref="B66:I66"/>
+    <mergeCell ref="A120:I120"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="B140:I140"/>
     <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A113:I113"/>
     <mergeCell ref="B130:I130"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="A185:I185"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B101:I101"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="B166:I166"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="B182:I182"/>
-    <mergeCell ref="B112:I112"/>
     <mergeCell ref="B118:I118"/>
-    <mergeCell ref="B127:I127"/>
+    <mergeCell ref="A148:I148"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B95:I95"/>
     <mergeCell ref="B89:I89"/>
     <mergeCell ref="A132:I132"/>
     <mergeCell ref="A110:I110"/>
-    <mergeCell ref="A146:I146"/>
-    <mergeCell ref="B160:I160"/>
     <mergeCell ref="B169:I169"/>
+    <mergeCell ref="A124:I124"/>
     <mergeCell ref="B153:I153"/>
     <mergeCell ref="A174:I174"/>
+    <mergeCell ref="B185:I185"/>
     <mergeCell ref="A149:I149"/>
-    <mergeCell ref="A189:I189"/>
-    <mergeCell ref="A158:I158"/>
+    <mergeCell ref="B121:I121"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B18:I18"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A159:I159"/>
-    <mergeCell ref="A122:I122"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A125:I125"/>
-    <mergeCell ref="B179:I179"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A152:I152"/>
-    <mergeCell ref="A121:I121"/>
+    <mergeCell ref="A161:I161"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="B172:I172"/>
     <mergeCell ref="B108:I108"/>
     <mergeCell ref="A114:I114"/>
-    <mergeCell ref="B186:I186"/>
     <mergeCell ref="B143:I143"/>
+    <mergeCell ref="B92:I92"/>
+    <mergeCell ref="A191:I191"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A107:I107"/>
-    <mergeCell ref="A178:I178"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B133:I133"/>
     <mergeCell ref="A88:I88"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="A162:I162"/>
+    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="B126:I126"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -10249,48 +10393,49 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I184" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10302,7 +10447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12128,24 +12273,68 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="322" customHeight="1">
+    <row r="41" ht="308" customHeight="1">
       <c r="A41" s="5" t="n">
         <v>37</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>Next Greater Element I</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>496</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] nextGreaterElement(int[] nums1, int[] nums2) {
+    int[] result  = new int[nums2.length];
+    Arrays.fill(result,-1);
+    Deque&lt;Integer&gt; stack = new ArrayDeque&lt;&gt;();
+    for(int i=0;i&lt;nums2.length;i++){
+        while(!stack.isEmpty() &amp;&amp; nums2[stack.peek()]&lt;nums2[i]){
+            result[stack.pop()] = nums2[i];
+        }
+        stack.push(i);
+    }
+    int[] result2 = new int[nums1.length];
+    for(int i=0;i&lt;nums1.length;i++){
+        for(int j=0;j&lt;nums2.length;j++){
+            if(nums1[i] == nums2[j]){
+              result2[i] = result[j];
+            }
+        }
+    }
+    return result2;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="322" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>503</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElements(int[] nums) {
@@ -12170,24 +12359,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="546" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="546" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -12225,24 +12414,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="560" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="560" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>547</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public class Uniounandfind {
@@ -12294,24 +12483,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="182" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="182" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -12329,24 +12518,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="546" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="546" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -12390,24 +12579,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="196" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="196" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -12426,24 +12615,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="462" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="462" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -12473,24 +12662,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="518" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="518" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>684</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>class Solution {
  class UniounFind{
@@ -12530,24 +12719,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="252" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="252" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>739</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -12567,24 +12756,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="378" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="378" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -12616,24 +12805,24 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="294" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52" ht="294" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>908</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -12659,24 +12848,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="560" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53" ht="560" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -12712,24 +12901,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="294" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="294" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -12752,24 +12941,24 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="224" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
+    <row r="55" ht="224" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C55" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -12790,24 +12979,24 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="420" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
+    <row r="56" ht="420" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -12842,24 +13031,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="378" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="378" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -12891,24 +13080,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="266" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="266" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>1570</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -12932,24 +13121,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="350" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="350" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -12979,24 +13168,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="238" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="238" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -13018,24 +13207,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="308" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="308" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -13062,24 +13251,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="280" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="280" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -13102,24 +13291,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="448" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="448" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -13154,24 +13343,24 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="378" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="378" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -13203,24 +13392,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="266" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="266" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -13244,24 +13433,24 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="560" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="560" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E65" s="25" t="inlineStr">
+      <c r="E66" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -13314,24 +13503,24 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="196" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
+    <row r="67" ht="196" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C67" s="5" t="n">
         <v>3811</v>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -13349,24 +13538,24 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="238" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+    <row r="68" ht="238" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C68" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -13386,24 +13575,24 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="252" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="69" ht="252" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C69" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -13426,24 +13615,24 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="140" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+    <row r="70" ht="140" customHeight="1">
+      <c r="A70" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C70" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -13457,24 +13646,24 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="294" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
+    <row r="71" ht="294" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C70" s="7" t="n">
+      <c r="C71" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E71" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -13500,24 +13689,24 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="252" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
+    <row r="72" ht="252" customHeight="1">
+      <c r="A72" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C72" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E71" s="25" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E72" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -13615,7 +13804,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>27</v>
@@ -13624,7 +13813,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -13653,7 +13842,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>27</v>
@@ -13662,7 +13851,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H58" s="12" t="n">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H103" s="14" t="n">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H154" s="12" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H160" s="12" t="n">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H164" s="12" t="n">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H167" s="12" t="n">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H190" s="12" t="n">
@@ -10502,7 +10502,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="560" customHeight="1">
+    <row r="5" ht="196" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10516,126 +10516,117 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] nums, int target) {
+        int[] arr=new int[2];
+       	 for(int i=0;i&lt;nums.length;i++) { 
+		 for(int j=i+1;j&lt;nums.length;j++) { 
+			 if(nums[i]+nums[j]==target) { 
+				arr[0]=i;
+                arr[1]=j;
+			 }
+		 }
+	 }
+     return arr;
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="504" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
-&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
-&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 1
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
+Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
 &lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="252" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>class Solution {
-    public int lengthOfLongestSubstring(String s) {
-    int left =0;
-    int max = 0;
-    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
-    for(int right =0;right&lt;s.length();right++){
-         char currentChar = s.charAt(right);
-          while(hs.contains(s.charAt(right))){
-            hs.remove(s.charAt(left));
-            left++;
-          }
-          hs.add(s.charAt(right));
-          max = Math.max(max,right-left +1); 
+    public static int rever(int num){
+        int rev =0;
+        while(num != 0){
+            int rem = num%10;
+            if(rev&gt;Integer.MAX_VALUE/10) return 0;
+            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
+            rev=rev*10+rem;
+            num/=10;
+        }
+        return rev;
     }
-    return max;
+    public int reverse(int x) {
+    // int i=0;
+    // if(x&gt;=0)  i=1;
+    // else i = -1;
+    int num = rever(x);
+    return num;
     }
 }</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="462" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 123
-&lt;strong&gt;Output:&lt;/strong&gt; 321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = -123
-&lt;strong&gt;Output:&lt;/strong&gt; -321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 120
-&lt;strong&gt;Output:&lt;/strong&gt; 21
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10981,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="532" customHeight="1">
+    <row r="16" ht="210" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
@@ -11004,40 +10995,26 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 5
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 4
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 6
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public int lengthOfLastWord(String s) {
+    char[] ch =s.toCharArray();
+    int count=0;
+    int i = s.length()-1;
+    while(s.charAt(i) == ' '){
+        i--;
+    }
+    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
+        count++;
+        i--;
+    }
+    return count;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -11126,7 +11103,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="560" customHeight="1">
+    <row r="18" ht="420" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
@@ -11140,45 +11117,39 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E18" s="26" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    public  void inorder(TreeNode root,List list){
+    if(root == null) return;
+    inorder(root.left,list);
+    list.add(root.val);
+    inorder(root.right,list);
+    }
+    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
+    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
+    inorder(root,list);
+    return list;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12020,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="182" customHeight="1">
+    <row r="36" ht="308" customHeight="1">
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
@@ -12063,24 +12034,29 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E36" s="26" t="inlineStr">
         <is>
-          <t>class Solution {
-    public void moveZeroes(int[] nums) {
-    int numbers = 0;
-    for(int traverse = 0;traverse&lt;nums.length;traverse++){
-        if(nums[traverse] != 0){
-            int temp = nums[traverse];
-            nums[traverse] = nums[numbers];
-            nums[numbers] = temp;
-            numbers++;
-        }
-    }  
-    }
-}</t>
+          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
+&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
+&lt;strong&gt;Output:&lt;/strong&gt; [0]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
         </is>
       </c>
     </row>
@@ -12915,29 +12891,32 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E54" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
-&lt;strong&gt;Output:&lt;/strong&gt; true
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
-&lt;strong&gt;Output:&lt;/strong&gt; false
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public boolean isBoomerang(int[][] points) {
+    int x1=0,x2=0,x3=0;
+    int y1=0,y2=0,y3=0;
+    for(int i =0;i&lt;points.length;i++){
+        for(int j=0;j&lt;points[i].length-1;j++){
+           if(i==0){
+            x1 = points[i][j];
+            y1 = points[i][j+1];
+           }else if(i == 1){
+             x2 = points[i][j];
+             y2 = points[i][j+1];
+           }else{
+            x3 = points[i][j];
+            y3 = points[i][j+1];
+           }
+        }
+    } 
+    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13371,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="266" customHeight="1">
+    <row r="65" ht="490" customHeight="1">
       <c r="A65" s="5" t="n">
         <v>61</v>
       </c>
@@ -13406,100 +13385,77 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E65" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public static int digits(int num){
-        int multiply =1;
-        while(num!=0){
-            int rem = num%10;
-            multiply *= rem;
-            num /= 10;
-        }
-        return multiply;
-    }
-    public int smallestNumber(int n, int t) {
-    while(true){
-        if(digits(n)%t == 0){
-          return n;
-        } 
-        n++;
-    }
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="560" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
-A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
+          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
+&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="308" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int largestInteger(int[] nums, int k) {
+    int[] arr = new int[51];
+    for(int i = 0;i&lt;nums.length-k+1;i++){
+        boolean[] seen = new boolean[51];
+        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
+            if (!seen[nums[j]]){
+               arr[nums[j]]++;
+               seen[nums[j]] = true;
+            } 
+        }
+    } 
+    int high =-1;
+    for(int i=0;i&lt;arr.length;i++){
+        if(arr[i] == 1){
+           if(high&lt;i) high = i;
+        }
+    } 
+    return high;
+    }
+}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1431,37 +1431,37 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Stack, Monotonic Stack, Range Minimum/Maximum Query</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>47.2</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>47.2</v>
@@ -1483,33 +1483,33 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>48.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+          <t>Two Pointers, Binary Search</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -1525,281 +1525,281 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H37" s="5" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="9" t="n">
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D38" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="E38" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Breadth-First Search, Graph Theory, Topological Sort</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H39" s="5" t="n">
         <v>46.9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>47.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
           <t>Breadth-First Search, Union-Find, Graph Theory</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7" t="n">
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G41" s="5" t="n">
         <v>2.5</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H41" s="5" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Depth-First Search — TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="9" t="n">
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9" t="n">
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="n">
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr"/>
-      <c r="C43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr"/>
+      <c r="C44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="9" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7" t="n">
+      <c r="C45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H45" s="5" t="n">
         <v>45.9</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>42.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="7" t="n">
         <v>1</v>
@@ -1808,30 +1808,30 @@
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>46.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>2</v>
@@ -1840,229 +1840,229 @@
         <v>0</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>45.3</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="7" t="n">
+      <c r="C49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Linked List — TOTAL</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr"/>
-      <c r="C49" s="9" t="n">
+      <c r="B50" s="8" t="inlineStr"/>
+      <c r="C50" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D49" s="9" t="n">
+      <c r="D50" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="9" t="n">
+      <c r="E50" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F50" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G49" s="9" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="7" t="n">
+      <c r="C51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H50" s="7" t="n">
+      <c r="H51" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr"/>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
+      <c r="D53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G53" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="H52" s="7" t="n">
+      <c r="H53" s="5" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr"/>
-      <c r="C53" s="9" t="n">
+      <c r="B54" s="8" t="inlineStr"/>
+      <c r="C54" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="9" t="n">
+      <c r="D54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G53" s="9" t="inlineStr"/>
-      <c r="H53" s="9" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr"/>
+      <c r="H54" s="9" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="7" t="n">
+      <c r="C55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr"/>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>0</v>
@@ -2071,17 +2071,17 @@
         <v>1</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
@@ -2097,17 +2097,17 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
@@ -2123,237 +2123,263 @@
         <v>1</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr"/>
       <c r="B59" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="5" t="n">
+      <c r="C60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H60" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr"/>
-      <c r="C60" s="9" t="n">
+      <c r="B61" s="8" t="inlineStr"/>
+      <c r="C61" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D60" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="9" t="n">
+      <c r="D61" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G60" s="9" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr"/>
+      <c r="H61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="5" t="n">
+      <c r="C62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr"/>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr"/>
       <c r="B63" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="5" t="n">
+      <c r="C64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr"/>
-      <c r="C64" s="9" t="n">
+      <c r="B65" s="8" t="inlineStr"/>
+      <c r="C65" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="9" t="n">
+      <c r="D65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G64" s="9" t="inlineStr"/>
-      <c r="H64" s="9" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr"/>
+      <c r="H65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5" t="n">
+      <c r="C66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H65" s="5" t="n">
+      <c r="H66" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr"/>
-      <c r="C66" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="9" t="inlineStr"/>
-      <c r="H66" s="9" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr"/>
+      <c r="C67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr"/>
+      <c r="H67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr"/>
-      <c r="C67" s="11" t="n">
+      <c r="B68" s="10" t="inlineStr"/>
+      <c r="C68" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D68" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="E67" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F67" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="G67" s="11" t="inlineStr"/>
-      <c r="H67" s="11" t="inlineStr"/>
+      <c r="E68" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="G68" s="11" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2369,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2509,7 +2535,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2559,7 +2585,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2609,7 +2635,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2859,7 +2885,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2959,7 +2985,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3359,7 +3385,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3409,7 +3435,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3459,7 +3485,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4059,7 +4085,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -5875,6 +5901,56 @@
         <v>46288.95560185185</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Largest Rectangle in Histogram</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Stack, Monotonic Stack, Range Minimum/Maximum Query</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>46288.97087962963</v>
+      </c>
+      <c r="L73" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5884,7 +5960,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F72">
+  <conditionalFormatting sqref="F5:F73">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -5964,6 +6040,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5975,7 +6052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I194"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6018,7 +6095,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   40 solved   (Low: 19 · Medium: 19 · High: 2)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   41 solved   (Low: 19 · Medium: 19 · High: 3)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -6688,7 +6765,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6723,7 +6800,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7228,7 +7305,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H58" s="12" t="n">
@@ -8093,7 +8170,7 @@
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B97" s="18" t="n"/>
@@ -8106,40 +8183,40 @@
       <c r="I97" s="18" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="21" t="n"/>
-      <c r="B98" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C98" s="21" t="n"/>
-      <c r="D98" s="21" t="n"/>
-      <c r="E98" s="21" t="n"/>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
+      <c r="A98" s="23" t="n"/>
+      <c r="B98" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C98" s="23" t="n"/>
+      <c r="D98" s="23" t="n"/>
+      <c r="E98" s="23" t="n"/>
+      <c r="F98" s="23" t="n"/>
+      <c r="G98" s="23" t="n"/>
+      <c r="H98" s="23" t="n"/>
+      <c r="I98" s="23" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr"/>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Largest Rectangle in Histogram</t>
         </is>
       </c>
       <c r="C99" s="5" t="n">
-        <v>4281</v>
+        <v>84</v>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>47.2</v>
+        <v>76.5</v>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
@@ -8147,7 +8224,7 @@
         </is>
       </c>
       <c r="H99" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46288.97087962963</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -8158,7 +8235,7 @@
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B100" s="18" t="n"/>
@@ -8174,7 +8251,7 @@
       <c r="A101" s="21" t="n"/>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C101" s="21" t="n"/>
@@ -8189,132 +8266,132 @@
       <c r="A102" s="5" t="inlineStr"/>
       <c r="B102" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="n"/>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="n"/>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C104" s="21" t="n"/>
+      <c r="D104" s="21" t="n"/>
+      <c r="E104" s="21" t="n"/>
+      <c r="F104" s="21" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="21" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr"/>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C105" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E102" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="5" t="n">
+      <c r="E105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H102" s="12" t="n">
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I102" s="13" t="inlineStr">
+      <c r="I105" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr"/>
-      <c r="B103" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr"/>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C103" s="7" t="n">
+      <c r="C106" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D103" s="7" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E103" s="7" t="n">
+      <c r="E106" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F103" s="7" t="n">
+      <c r="F106" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H103" s="14" t="n">
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H106" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I103" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B104" s="18" t="n"/>
-      <c r="C104" s="18" t="n"/>
-      <c r="D104" s="18" t="n"/>
-      <c r="E104" s="18" t="n"/>
-      <c r="F104" s="18" t="n"/>
-      <c r="G104" s="18" t="n"/>
-      <c r="H104" s="18" t="n"/>
-      <c r="I104" s="18" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="19" t="n"/>
-      <c r="B105" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C105" s="19" t="n"/>
-      <c r="D105" s="19" t="n"/>
-      <c r="E105" s="19" t="n"/>
-      <c r="F105" s="19" t="n"/>
-      <c r="G105" s="19" t="n"/>
-      <c r="H105" s="19" t="n"/>
-      <c r="I105" s="19" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Two Sum II - Input Array Is Sorted</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>46272.93130787037</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
+      <c r="I106" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8323,7 +8400,7 @@
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B107" s="18" t="n"/>
@@ -8354,11 +8431,11 @@
       <c r="A109" s="5" t="inlineStr"/>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Find the Duplicate Number</t>
+          <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
       <c r="C109" s="5" t="n">
-        <v>287</v>
+        <v>167</v>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
@@ -8366,10 +8443,10 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
@@ -8377,7 +8454,7 @@
         </is>
       </c>
       <c r="H109" s="12" t="n">
-        <v>46274.9421875</v>
+        <v>46272.93130787037</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -8388,7 +8465,7 @@
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B110" s="18" t="n"/>
@@ -8419,121 +8496,121 @@
       <c r="A112" s="5" t="inlineStr"/>
       <c r="B112" s="4" t="inlineStr">
         <is>
+          <t>Find the Duplicate Number</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>46274.9421875</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B113" s="18" t="n"/>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="19" t="n"/>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C114" s="19" t="n"/>
+      <c r="D114" s="19" t="n"/>
+      <c r="E114" s="19" t="n"/>
+      <c r="F114" s="19" t="n"/>
+      <c r="G114" s="19" t="n"/>
+      <c r="H114" s="19" t="n"/>
+      <c r="I114" s="19" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr"/>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C115" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E112" s="5" t="n">
+      <c r="E115" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F112" s="5" t="n">
+      <c r="F115" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H112" s="12" t="n">
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I112" s="13" t="inlineStr">
+      <c r="I115" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="16" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   4 solved   (Low: 0 · Medium: 4 · High: 0)</t>
         </is>
       </c>
-      <c r="B113" s="2" t="n"/>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n"/>
-      <c r="E113" s="2" t="n"/>
-      <c r="F113" s="2" t="n"/>
-      <c r="G113" s="2" t="n"/>
-      <c r="H113" s="2" t="n"/>
-      <c r="I113" s="2" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B114" s="18" t="n"/>
-      <c r="C114" s="18" t="n"/>
-      <c r="D114" s="18" t="n"/>
-      <c r="E114" s="18" t="n"/>
-      <c r="F114" s="18" t="n"/>
-      <c r="G114" s="18" t="n"/>
-      <c r="H114" s="18" t="n"/>
-      <c r="I114" s="18" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="19" t="n"/>
-      <c r="B115" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C115" s="19" t="n"/>
-      <c r="D115" s="19" t="n"/>
-      <c r="E115" s="19" t="n"/>
-      <c r="F115" s="19" t="n"/>
-      <c r="G115" s="19" t="n"/>
-      <c r="H115" s="19" t="n"/>
-      <c r="I115" s="19" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr"/>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Course Schedule II</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>46288.67247685185</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="n"/>
+      <c r="I116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B117" s="18" t="n"/>
@@ -8564,11 +8641,11 @@
       <c r="A119" s="5" t="inlineStr"/>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Course Schedule</t>
+          <t>Course Schedule II</t>
         </is>
       </c>
       <c r="C119" s="5" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
@@ -8576,10 +8653,10 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
@@ -8587,7 +8664,7 @@
         </is>
       </c>
       <c r="H119" s="12" t="n">
-        <v>46288.65751157407</v>
+        <v>46288.67247685185</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -8598,7 +8675,7 @@
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B120" s="18" t="n"/>
@@ -8614,7 +8691,7 @@
       <c r="A121" s="19" t="n"/>
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>Medium (Medium) — 2 problem(s)</t>
+          <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C121" s="19" t="n"/>
@@ -8629,236 +8706,236 @@
       <c r="A122" s="5" t="inlineStr"/>
       <c r="B122" s="4" t="inlineStr">
         <is>
+          <t>Course Schedule</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>46288.65751157407</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B123" s="18" t="n"/>
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
+      <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="19" t="n"/>
+      <c r="B124" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="n"/>
+      <c r="D124" s="19" t="n"/>
+      <c r="E124" s="19" t="n"/>
+      <c r="F124" s="19" t="n"/>
+      <c r="G124" s="19" t="n"/>
+      <c r="H124" s="19" t="n"/>
+      <c r="I124" s="19" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr"/>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C122" s="5" t="n">
+      <c r="C125" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="5" t="n">
+      <c r="E125" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F122" s="5" t="n">
+      <c r="F125" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="n">
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="n">
         <v>46287.65729166667</v>
       </c>
-      <c r="I122" s="13" t="inlineStr">
+      <c r="I125" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="7" t="inlineStr"/>
-      <c r="B123" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr"/>
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C123" s="7" t="n">
+      <c r="C126" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D123" s="7" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E123" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F123" s="7" t="n">
+      <c r="E126" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H123" s="14" t="n">
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="n">
         <v>46287.51434027778</v>
       </c>
-      <c r="I123" s="15" t="inlineStr">
+      <c r="I126" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="16" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B124" s="2" t="n"/>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n"/>
-      <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="n"/>
-      <c r="G124" s="2" t="n"/>
-      <c r="H124" s="2" t="n"/>
-      <c r="I124" s="2" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="17" t="inlineStr">
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="2" t="n"/>
+      <c r="I127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B125" s="18" t="n"/>
-      <c r="C125" s="18" t="n"/>
-      <c r="D125" s="18" t="n"/>
-      <c r="E125" s="18" t="n"/>
-      <c r="F125" s="18" t="n"/>
-      <c r="G125" s="18" t="n"/>
-      <c r="H125" s="18" t="n"/>
-      <c r="I125" s="18" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="21" t="n"/>
-      <c r="B126" s="22" t="inlineStr">
+      <c r="B128" s="18" t="n"/>
+      <c r="C128" s="18" t="n"/>
+      <c r="D128" s="18" t="n"/>
+      <c r="E128" s="18" t="n"/>
+      <c r="F128" s="18" t="n"/>
+      <c r="G128" s="18" t="n"/>
+      <c r="H128" s="18" t="n"/>
+      <c r="I128" s="18" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="n"/>
+      <c r="B129" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C126" s="21" t="n"/>
-      <c r="D126" s="21" t="n"/>
-      <c r="E126" s="21" t="n"/>
-      <c r="F126" s="21" t="n"/>
-      <c r="G126" s="21" t="n"/>
-      <c r="H126" s="21" t="n"/>
-      <c r="I126" s="21" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr"/>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="C129" s="21" t="n"/>
+      <c r="D129" s="21" t="n"/>
+      <c r="E129" s="21" t="n"/>
+      <c r="F129" s="21" t="n"/>
+      <c r="G129" s="21" t="n"/>
+      <c r="H129" s="21" t="n"/>
+      <c r="I129" s="21" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr"/>
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C127" s="5" t="n">
+      <c r="C130" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E127" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="5" t="n">
+      <c r="E130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H127" s="12" t="n">
+      <c r="H130" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I127" s="13" t="inlineStr">
+      <c r="I130" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: LINKED LIST   —   7 solved   (Low: 3 · Medium: 2 · High: 2)</t>
         </is>
       </c>
-      <c r="B128" s="2" t="n"/>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="n"/>
-      <c r="F128" s="2" t="n"/>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="n"/>
-      <c r="I128" s="2" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B129" s="18" t="n"/>
-      <c r="C129" s="18" t="n"/>
-      <c r="D129" s="18" t="n"/>
-      <c r="E129" s="18" t="n"/>
-      <c r="F129" s="18" t="n"/>
-      <c r="G129" s="18" t="n"/>
-      <c r="H129" s="18" t="n"/>
-      <c r="I129" s="18" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="23" t="n"/>
-      <c r="B130" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C130" s="23" t="n"/>
-      <c r="D130" s="23" t="n"/>
-      <c r="E130" s="23" t="n"/>
-      <c r="F130" s="23" t="n"/>
-      <c r="G130" s="23" t="n"/>
-      <c r="H130" s="23" t="n"/>
-      <c r="I130" s="23" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="5" t="inlineStr"/>
-      <c r="B131" s="4" t="inlineStr">
-        <is>
-          <t>Merge k Sorted Lists</t>
-        </is>
-      </c>
-      <c r="C131" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G131" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>46286.43949074074</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B132" s="18" t="n"/>
@@ -8871,40 +8948,40 @@
       <c r="I132" s="18" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="19" t="n"/>
-      <c r="B133" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C133" s="19" t="n"/>
-      <c r="D133" s="19" t="n"/>
-      <c r="E133" s="19" t="n"/>
-      <c r="F133" s="19" t="n"/>
-      <c r="G133" s="19" t="n"/>
-      <c r="H133" s="19" t="n"/>
-      <c r="I133" s="19" t="n"/>
+      <c r="A133" s="23" t="n"/>
+      <c r="B133" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C133" s="23" t="n"/>
+      <c r="D133" s="23" t="n"/>
+      <c r="E133" s="23" t="n"/>
+      <c r="F133" s="23" t="n"/>
+      <c r="G133" s="23" t="n"/>
+      <c r="H133" s="23" t="n"/>
+      <c r="I133" s="23" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr"/>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Reverse Linked List II</t>
+          <t>Merge k Sorted Lists</t>
         </is>
       </c>
       <c r="C134" s="5" t="n">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>42.9</v>
+        <v>45.9</v>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
@@ -8912,7 +8989,7 @@
         </is>
       </c>
       <c r="H134" s="12" t="n">
-        <v>46275.41266203704</v>
+        <v>46286.43949074074</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -8923,7 +9000,7 @@
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B135" s="18" t="n"/>
@@ -8936,369 +9013,369 @@
       <c r="I135" s="18" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="21" t="n"/>
-      <c r="B136" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C136" s="21" t="n"/>
-      <c r="D136" s="21" t="n"/>
-      <c r="E136" s="21" t="n"/>
-      <c r="F136" s="21" t="n"/>
-      <c r="G136" s="21" t="n"/>
-      <c r="H136" s="21" t="n"/>
-      <c r="I136" s="21" t="n"/>
+      <c r="A136" s="19" t="n"/>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C136" s="19" t="n"/>
+      <c r="D136" s="19" t="n"/>
+      <c r="E136" s="19" t="n"/>
+      <c r="F136" s="19" t="n"/>
+      <c r="G136" s="19" t="n"/>
+      <c r="H136" s="19" t="n"/>
+      <c r="I136" s="19" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr"/>
       <c r="B137" s="4" t="inlineStr">
         <is>
+          <t>Reverse Linked List II</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="n">
+        <v>46275.41266203704</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="n"/>
+      <c r="C138" s="18" t="n"/>
+      <c r="D138" s="18" t="n"/>
+      <c r="E138" s="18" t="n"/>
+      <c r="F138" s="18" t="n"/>
+      <c r="G138" s="18" t="n"/>
+      <c r="H138" s="18" t="n"/>
+      <c r="I138" s="18" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="21" t="n"/>
+      <c r="B139" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C139" s="21" t="n"/>
+      <c r="D139" s="21" t="n"/>
+      <c r="E139" s="21" t="n"/>
+      <c r="F139" s="21" t="n"/>
+      <c r="G139" s="21" t="n"/>
+      <c r="H139" s="21" t="n"/>
+      <c r="I139" s="21" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr"/>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C137" s="5" t="n">
+      <c r="C140" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D137" s="5" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E137" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" s="5" t="n">
+      <c r="E140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="5" t="n">
         <v>46.9</v>
       </c>
-      <c r="G137" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H137" s="12" t="n">
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H140" s="12" t="n">
         <v>46274.42709490741</v>
       </c>
-      <c r="I137" s="13" t="inlineStr">
+      <c r="I140" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="19" t="n"/>
-      <c r="B138" s="20" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="19" t="n"/>
+      <c r="B141" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C138" s="19" t="n"/>
-      <c r="D138" s="19" t="n"/>
-      <c r="E138" s="19" t="n"/>
-      <c r="F138" s="19" t="n"/>
-      <c r="G138" s="19" t="n"/>
-      <c r="H138" s="19" t="n"/>
-      <c r="I138" s="19" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr"/>
-      <c r="B139" s="4" t="inlineStr">
-        <is>
-          <t>Linked List Cycle II</t>
-        </is>
-      </c>
-      <c r="C139" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="D139" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="n">
-        <v>46274.44269675926</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Recursion   —   2 solved   (Low: 1 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B140" s="18" t="n"/>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="18" t="n"/>
-      <c r="E140" s="18" t="n"/>
-      <c r="F140" s="18" t="n"/>
-      <c r="G140" s="18" t="n"/>
-      <c r="H140" s="18" t="n"/>
-      <c r="I140" s="18" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="21" t="n"/>
-      <c r="B141" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C141" s="21" t="n"/>
-      <c r="D141" s="21" t="n"/>
-      <c r="E141" s="21" t="n"/>
-      <c r="F141" s="21" t="n"/>
-      <c r="G141" s="21" t="n"/>
-      <c r="H141" s="21" t="n"/>
-      <c r="I141" s="21" t="n"/>
+      <c r="C141" s="19" t="n"/>
+      <c r="D141" s="19" t="n"/>
+      <c r="E141" s="19" t="n"/>
+      <c r="F141" s="19" t="n"/>
+      <c r="G141" s="19" t="n"/>
+      <c r="H141" s="19" t="n"/>
+      <c r="I141" s="19" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr"/>
       <c r="B142" s="4" t="inlineStr">
         <is>
+          <t>Linked List Cycle II</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H142" s="12" t="n">
+        <v>46274.44269675926</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Recursion   —   2 solved   (Low: 1 · Medium: 0 · High: 1)</t>
+        </is>
+      </c>
+      <c r="B143" s="18" t="n"/>
+      <c r="C143" s="18" t="n"/>
+      <c r="D143" s="18" t="n"/>
+      <c r="E143" s="18" t="n"/>
+      <c r="F143" s="18" t="n"/>
+      <c r="G143" s="18" t="n"/>
+      <c r="H143" s="18" t="n"/>
+      <c r="I143" s="18" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="21" t="n"/>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C144" s="21" t="n"/>
+      <c r="D144" s="21" t="n"/>
+      <c r="E144" s="21" t="n"/>
+      <c r="F144" s="21" t="n"/>
+      <c r="G144" s="21" t="n"/>
+      <c r="H144" s="21" t="n"/>
+      <c r="I144" s="21" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr"/>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C142" s="5" t="n">
+      <c r="C145" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="D142" s="5" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E142" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" s="5" t="n">
+      <c r="E145" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" s="5" t="n">
         <v>44.1</v>
       </c>
-      <c r="G142" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H142" s="12" t="n">
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="n">
         <v>46274.48334490741</v>
       </c>
-      <c r="I142" s="13" t="inlineStr">
+      <c r="I145" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="23" t="n"/>
-      <c r="B143" s="24" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="23" t="n"/>
+      <c r="B146" s="24" t="inlineStr">
         <is>
           <t>High (Hard) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C143" s="23" t="n"/>
-      <c r="D143" s="23" t="n"/>
-      <c r="E143" s="23" t="n"/>
-      <c r="F143" s="23" t="n"/>
-      <c r="G143" s="23" t="n"/>
-      <c r="H143" s="23" t="n"/>
-      <c r="I143" s="23" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr"/>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Nodes in k-Group</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="G144" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H144" s="12" t="n">
-        <v>46288.89429398148</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B145" s="18" t="n"/>
-      <c r="C145" s="18" t="n"/>
-      <c r="D145" s="18" t="n"/>
-      <c r="E145" s="18" t="n"/>
-      <c r="F145" s="18" t="n"/>
-      <c r="G145" s="18" t="n"/>
-      <c r="H145" s="18" t="n"/>
-      <c r="I145" s="18" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="21" t="n"/>
-      <c r="B146" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C146" s="21" t="n"/>
-      <c r="D146" s="21" t="n"/>
-      <c r="E146" s="21" t="n"/>
-      <c r="F146" s="21" t="n"/>
-      <c r="G146" s="21" t="n"/>
-      <c r="H146" s="21" t="n"/>
-      <c r="I146" s="21" t="n"/>
+      <c r="C146" s="23" t="n"/>
+      <c r="D146" s="23" t="n"/>
+      <c r="E146" s="23" t="n"/>
+      <c r="F146" s="23" t="n"/>
+      <c r="G146" s="23" t="n"/>
+      <c r="H146" s="23" t="n"/>
+      <c r="I146" s="23" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr"/>
       <c r="B147" s="4" t="inlineStr">
         <is>
+          <t>Reverse Nodes in k-Group</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="n">
+        <v>46288.89429398148</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B148" s="18" t="n"/>
+      <c r="C148" s="18" t="n"/>
+      <c r="D148" s="18" t="n"/>
+      <c r="E148" s="18" t="n"/>
+      <c r="F148" s="18" t="n"/>
+      <c r="G148" s="18" t="n"/>
+      <c r="H148" s="18" t="n"/>
+      <c r="I148" s="18" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="21" t="n"/>
+      <c r="B149" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C149" s="21" t="n"/>
+      <c r="D149" s="21" t="n"/>
+      <c r="E149" s="21" t="n"/>
+      <c r="F149" s="21" t="n"/>
+      <c r="G149" s="21" t="n"/>
+      <c r="H149" s="21" t="n"/>
+      <c r="I149" s="21" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="inlineStr"/>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C147" s="5" t="n">
+      <c r="C150" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D147" s="5" t="inlineStr">
+      <c r="D150" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E147" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F147" s="5" t="n">
+      <c r="E150" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G147" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H147" s="12" t="n">
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H150" s="12" t="n">
         <v>46274.41063657407</v>
       </c>
-      <c r="I147" s="13" t="inlineStr">
+      <c r="I150" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="16" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B148" s="2" t="n"/>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="n"/>
-      <c r="G148" s="2" t="n"/>
-      <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B149" s="18" t="n"/>
-      <c r="C149" s="18" t="n"/>
-      <c r="D149" s="18" t="n"/>
-      <c r="E149" s="18" t="n"/>
-      <c r="F149" s="18" t="n"/>
-      <c r="G149" s="18" t="n"/>
-      <c r="H149" s="18" t="n"/>
-      <c r="I149" s="18" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="21" t="n"/>
-      <c r="B150" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C150" s="21" t="n"/>
-      <c r="D150" s="21" t="n"/>
-      <c r="E150" s="21" t="n"/>
-      <c r="F150" s="21" t="n"/>
-      <c r="G150" s="21" t="n"/>
-      <c r="H150" s="21" t="n"/>
-      <c r="I150" s="21" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="5" t="inlineStr"/>
-      <c r="B151" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C151" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H151" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+      <c r="F151" s="2" t="n"/>
+      <c r="G151" s="2" t="n"/>
+      <c r="H151" s="2" t="n"/>
+      <c r="I151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B152" s="18" t="n"/>
@@ -9329,11 +9406,11 @@
       <c r="A154" s="5" t="inlineStr"/>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C154" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
@@ -9341,18 +9418,18 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H154" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -9363,7 +9440,7 @@
     <row r="155">
       <c r="A155" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B155" s="18" t="n"/>
@@ -9379,7 +9456,7 @@
       <c r="A156" s="21" t="n"/>
       <c r="B156" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C156" s="21" t="n"/>
@@ -9394,11 +9471,11 @@
       <c r="A157" s="5" t="inlineStr"/>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C157" s="5" t="n">
-        <v>3918</v>
+        <v>3626</v>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
@@ -9409,7 +9486,7 @@
         <v>1</v>
       </c>
       <c r="F157" s="5" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
@@ -9417,7 +9494,7 @@
         </is>
       </c>
       <c r="H157" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -9426,174 +9503,174 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="7" t="inlineStr"/>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>Count Commas in Range</t>
-        </is>
-      </c>
-      <c r="C158" s="7" t="n">
-        <v>4245</v>
-      </c>
-      <c r="D158" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E158" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H158" s="14" t="n">
-        <v>46273.3956712963</v>
-      </c>
-      <c r="I158" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="n"/>
+      <c r="C158" s="18" t="n"/>
+      <c r="D158" s="18" t="n"/>
+      <c r="E158" s="18" t="n"/>
+      <c r="F158" s="18" t="n"/>
+      <c r="G158" s="18" t="n"/>
+      <c r="H158" s="18" t="n"/>
+      <c r="I158" s="18" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="19" t="n"/>
-      <c r="B159" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C159" s="19" t="n"/>
-      <c r="D159" s="19" t="n"/>
-      <c r="E159" s="19" t="n"/>
-      <c r="F159" s="19" t="n"/>
-      <c r="G159" s="19" t="n"/>
-      <c r="H159" s="19" t="n"/>
-      <c r="I159" s="19" t="n"/>
+      <c r="A159" s="21" t="n"/>
+      <c r="B159" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C159" s="21" t="n"/>
+      <c r="D159" s="21" t="n"/>
+      <c r="E159" s="21" t="n"/>
+      <c r="F159" s="21" t="n"/>
+      <c r="G159" s="21" t="n"/>
+      <c r="H159" s="21" t="n"/>
+      <c r="I159" s="21" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr"/>
       <c r="B160" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H160" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr"/>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H161" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I161" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="19" t="n"/>
+      <c r="B162" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C162" s="19" t="n"/>
+      <c r="D162" s="19" t="n"/>
+      <c r="E162" s="19" t="n"/>
+      <c r="F162" s="19" t="n"/>
+      <c r="G162" s="19" t="n"/>
+      <c r="H162" s="19" t="n"/>
+      <c r="I162" s="19" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr"/>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C160" s="5" t="n">
+      <c r="C163" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D163" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" s="5" t="n">
+      <c r="E163" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G160" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H160" s="12" t="n">
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I160" s="13" t="inlineStr">
+      <c r="I163" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="16" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   6 solved   (Low: 5 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B161" s="2" t="n"/>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n"/>
-      <c r="E161" s="2" t="n"/>
-      <c r="F161" s="2" t="n"/>
-      <c r="G161" s="2" t="n"/>
-      <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B162" s="18" t="n"/>
-      <c r="C162" s="18" t="n"/>
-      <c r="D162" s="18" t="n"/>
-      <c r="E162" s="18" t="n"/>
-      <c r="F162" s="18" t="n"/>
-      <c r="G162" s="18" t="n"/>
-      <c r="H162" s="18" t="n"/>
-      <c r="I162" s="18" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="21" t="n"/>
-      <c r="B163" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C163" s="21" t="n"/>
-      <c r="D163" s="21" t="n"/>
-      <c r="E163" s="21" t="n"/>
-      <c r="F163" s="21" t="n"/>
-      <c r="G163" s="21" t="n"/>
-      <c r="H163" s="21" t="n"/>
-      <c r="I163" s="21" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="5" t="inlineStr"/>
-      <c r="B164" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C164" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D164" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E164" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F164" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G164" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H164" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="n"/>
+      <c r="G164" s="2" t="n"/>
+      <c r="H164" s="2" t="n"/>
+      <c r="I164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B165" s="18" t="n"/>
@@ -9606,40 +9683,40 @@
       <c r="I165" s="18" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="19" t="n"/>
-      <c r="B166" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C166" s="19" t="n"/>
-      <c r="D166" s="19" t="n"/>
-      <c r="E166" s="19" t="n"/>
-      <c r="F166" s="19" t="n"/>
-      <c r="G166" s="19" t="n"/>
-      <c r="H166" s="19" t="n"/>
-      <c r="I166" s="19" t="n"/>
+      <c r="A166" s="21" t="n"/>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C166" s="21" t="n"/>
+      <c r="D166" s="21" t="n"/>
+      <c r="E166" s="21" t="n"/>
+      <c r="F166" s="21" t="n"/>
+      <c r="G166" s="21" t="n"/>
+      <c r="H166" s="21" t="n"/>
+      <c r="I166" s="21" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr"/>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C167" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
@@ -9647,7 +9724,7 @@
         </is>
       </c>
       <c r="H167" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -9658,7 +9735,7 @@
     <row r="168">
       <c r="A168" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B168" s="18" t="n"/>
@@ -9671,40 +9748,40 @@
       <c r="I168" s="18" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="21" t="n"/>
-      <c r="B169" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C169" s="21" t="n"/>
-      <c r="D169" s="21" t="n"/>
-      <c r="E169" s="21" t="n"/>
-      <c r="F169" s="21" t="n"/>
-      <c r="G169" s="21" t="n"/>
-      <c r="H169" s="21" t="n"/>
-      <c r="I169" s="21" t="n"/>
+      <c r="A169" s="19" t="n"/>
+      <c r="B169" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C169" s="19" t="n"/>
+      <c r="D169" s="19" t="n"/>
+      <c r="E169" s="19" t="n"/>
+      <c r="F169" s="19" t="n"/>
+      <c r="G169" s="19" t="n"/>
+      <c r="H169" s="19" t="n"/>
+      <c r="I169" s="19" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr"/>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C170" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
@@ -9712,7 +9789,7 @@
         </is>
       </c>
       <c r="H170" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I170" s="13" t="inlineStr">
         <is>
@@ -9723,7 +9800,7 @@
     <row r="171">
       <c r="A171" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B171" s="18" t="n"/>
@@ -9754,11 +9831,11 @@
       <c r="A173" s="5" t="inlineStr"/>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Reverse Degree of a String</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C173" s="5" t="n">
-        <v>3811</v>
+        <v>242</v>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
@@ -9766,10 +9843,10 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
@@ -9777,7 +9854,7 @@
         </is>
       </c>
       <c r="H173" s="12" t="n">
-        <v>46285.42987268518</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -9788,7 +9865,7 @@
     <row r="174">
       <c r="A174" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B174" s="18" t="n"/>
@@ -9819,11 +9896,11 @@
       <c r="A176" s="5" t="inlineStr"/>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Reverse Degree of a String</t>
         </is>
       </c>
       <c r="C176" s="5" t="n">
-        <v>125</v>
+        <v>3811</v>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
@@ -9831,18 +9908,18 @@
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H176" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46285.42987268518</v>
       </c>
       <c r="I176" s="13" t="inlineStr">
         <is>
@@ -9853,7 +9930,7 @@
     <row r="177">
       <c r="A177" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B177" s="18" t="n"/>
@@ -9884,121 +9961,121 @@
       <c r="A179" s="5" t="inlineStr"/>
       <c r="B179" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E179" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H179" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B180" s="18" t="n"/>
+      <c r="C180" s="18" t="n"/>
+      <c r="D180" s="18" t="n"/>
+      <c r="E180" s="18" t="n"/>
+      <c r="F180" s="18" t="n"/>
+      <c r="G180" s="18" t="n"/>
+      <c r="H180" s="18" t="n"/>
+      <c r="I180" s="18" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="21" t="n"/>
+      <c r="B181" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C181" s="21" t="n"/>
+      <c r="D181" s="21" t="n"/>
+      <c r="E181" s="21" t="n"/>
+      <c r="F181" s="21" t="n"/>
+      <c r="G181" s="21" t="n"/>
+      <c r="H181" s="21" t="n"/>
+      <c r="I181" s="21" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr"/>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C179" s="5" t="n">
+      <c r="C182" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D179" s="5" t="inlineStr">
+      <c r="D182" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n">
+      <c r="E182" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F179" s="5" t="n">
+      <c r="F182" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G179" s="5" t="inlineStr">
+      <c r="G182" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H179" s="12" t="n">
+      <c r="H182" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I179" s="13" t="inlineStr">
+      <c r="I182" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="16" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B180" s="2" t="n"/>
-      <c r="C180" s="2" t="n"/>
-      <c r="D180" s="2" t="n"/>
-      <c r="E180" s="2" t="n"/>
-      <c r="F180" s="2" t="n"/>
-      <c r="G180" s="2" t="n"/>
-      <c r="H180" s="2" t="n"/>
-      <c r="I180" s="2" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B181" s="18" t="n"/>
-      <c r="C181" s="18" t="n"/>
-      <c r="D181" s="18" t="n"/>
-      <c r="E181" s="18" t="n"/>
-      <c r="F181" s="18" t="n"/>
-      <c r="G181" s="18" t="n"/>
-      <c r="H181" s="18" t="n"/>
-      <c r="I181" s="18" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="21" t="n"/>
-      <c r="B182" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C182" s="21" t="n"/>
-      <c r="D182" s="21" t="n"/>
-      <c r="E182" s="21" t="n"/>
-      <c r="F182" s="21" t="n"/>
-      <c r="G182" s="21" t="n"/>
-      <c r="H182" s="21" t="n"/>
-      <c r="I182" s="21" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="5" t="inlineStr"/>
-      <c r="B183" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C183" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E183" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G183" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H183" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I183" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="2" t="n"/>
+      <c r="G183" s="2" t="n"/>
+      <c r="H183" s="2" t="n"/>
+      <c r="I183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B184" s="18" t="n"/>
@@ -10014,7 +10091,7 @@
       <c r="A185" s="21" t="n"/>
       <c r="B185" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C185" s="21" t="n"/>
@@ -10029,267 +10106,331 @@
       <c r="A186" s="5" t="inlineStr"/>
       <c r="B186" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H186" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B187" s="18" t="n"/>
+      <c r="C187" s="18" t="n"/>
+      <c r="D187" s="18" t="n"/>
+      <c r="E187" s="18" t="n"/>
+      <c r="F187" s="18" t="n"/>
+      <c r="G187" s="18" t="n"/>
+      <c r="H187" s="18" t="n"/>
+      <c r="I187" s="18" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="21" t="n"/>
+      <c r="B188" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C188" s="21" t="n"/>
+      <c r="D188" s="21" t="n"/>
+      <c r="E188" s="21" t="n"/>
+      <c r="F188" s="21" t="n"/>
+      <c r="G188" s="21" t="n"/>
+      <c r="H188" s="21" t="n"/>
+      <c r="I188" s="21" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr"/>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C186" s="5" t="n">
+      <c r="C189" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E186" s="5" t="n">
+      <c r="E189" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F186" s="5" t="n">
+      <c r="F189" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G186" s="5" t="inlineStr">
+      <c r="G189" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H186" s="12" t="n">
+      <c r="H189" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I186" s="13" t="inlineStr">
+      <c r="I189" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr"/>
-      <c r="B187" s="6" t="inlineStr">
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr"/>
+      <c r="B190" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C187" s="7" t="n">
+      <c r="C190" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D187" s="7" t="inlineStr">
+      <c r="D190" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E187" s="7" t="n">
+      <c r="E190" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F187" s="7" t="n">
+      <c r="F190" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H187" s="14" t="n">
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H190" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I187" s="15" t="inlineStr">
+      <c r="I190" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="17" t="inlineStr">
+    <row r="191">
+      <c r="A191" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B188" s="18" t="n"/>
-      <c r="C188" s="18" t="n"/>
-      <c r="D188" s="18" t="n"/>
-      <c r="E188" s="18" t="n"/>
-      <c r="F188" s="18" t="n"/>
-      <c r="G188" s="18" t="n"/>
-      <c r="H188" s="18" t="n"/>
-      <c r="I188" s="18" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="21" t="n"/>
-      <c r="B189" s="22" t="inlineStr">
+      <c r="B191" s="18" t="n"/>
+      <c r="C191" s="18" t="n"/>
+      <c r="D191" s="18" t="n"/>
+      <c r="E191" s="18" t="n"/>
+      <c r="F191" s="18" t="n"/>
+      <c r="G191" s="18" t="n"/>
+      <c r="H191" s="18" t="n"/>
+      <c r="I191" s="18" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="21" t="n"/>
+      <c r="B192" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C189" s="21" t="n"/>
-      <c r="D189" s="21" t="n"/>
-      <c r="E189" s="21" t="n"/>
-      <c r="F189" s="21" t="n"/>
-      <c r="G189" s="21" t="n"/>
-      <c r="H189" s="21" t="n"/>
-      <c r="I189" s="21" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="5" t="inlineStr"/>
-      <c r="B190" s="4" t="inlineStr">
+      <c r="C192" s="21" t="n"/>
+      <c r="D192" s="21" t="n"/>
+      <c r="E192" s="21" t="n"/>
+      <c r="F192" s="21" t="n"/>
+      <c r="G192" s="21" t="n"/>
+      <c r="H192" s="21" t="n"/>
+      <c r="I192" s="21" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="inlineStr"/>
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C190" s="5" t="n">
+      <c r="C193" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="D193" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E190" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" s="5" t="n">
+      <c r="E193" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G190" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H190" s="12" t="n">
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H193" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I190" s="13" t="inlineStr">
+      <c r="I193" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="16" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B191" s="2" t="n"/>
-      <c r="C191" s="2" t="n"/>
-      <c r="D191" s="2" t="n"/>
-      <c r="E191" s="2" t="n"/>
-      <c r="F191" s="2" t="n"/>
-      <c r="G191" s="2" t="n"/>
-      <c r="H191" s="2" t="n"/>
-      <c r="I191" s="2" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="17" t="inlineStr">
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="n"/>
+      <c r="G194" s="2" t="n"/>
+      <c r="H194" s="2" t="n"/>
+      <c r="I194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B192" s="18" t="n"/>
-      <c r="C192" s="18" t="n"/>
-      <c r="D192" s="18" t="n"/>
-      <c r="E192" s="18" t="n"/>
-      <c r="F192" s="18" t="n"/>
-      <c r="G192" s="18" t="n"/>
-      <c r="H192" s="18" t="n"/>
-      <c r="I192" s="18" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="21" t="n"/>
-      <c r="B193" s="22" t="inlineStr">
+      <c r="B195" s="18" t="n"/>
+      <c r="C195" s="18" t="n"/>
+      <c r="D195" s="18" t="n"/>
+      <c r="E195" s="18" t="n"/>
+      <c r="F195" s="18" t="n"/>
+      <c r="G195" s="18" t="n"/>
+      <c r="H195" s="18" t="n"/>
+      <c r="I195" s="18" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="21" t="n"/>
+      <c r="B196" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C193" s="21" t="n"/>
-      <c r="D193" s="21" t="n"/>
-      <c r="E193" s="21" t="n"/>
-      <c r="F193" s="21" t="n"/>
-      <c r="G193" s="21" t="n"/>
-      <c r="H193" s="21" t="n"/>
-      <c r="I193" s="21" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="5" t="inlineStr"/>
-      <c r="B194" s="4" t="inlineStr">
+      <c r="C196" s="21" t="n"/>
+      <c r="D196" s="21" t="n"/>
+      <c r="E196" s="21" t="n"/>
+      <c r="F196" s="21" t="n"/>
+      <c r="G196" s="21" t="n"/>
+      <c r="H196" s="21" t="n"/>
+      <c r="I196" s="21" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr"/>
+      <c r="B197" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C194" s="5" t="n">
+      <c r="C197" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D194" s="5" t="inlineStr">
+      <c r="D197" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E194" s="5" t="n">
+      <c r="E197" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F194" s="5" t="n">
+      <c r="F197" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G194" s="5" t="inlineStr">
+      <c r="G197" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H194" s="12" t="n">
+      <c r="H197" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I194" s="13" t="inlineStr">
+      <c r="I197" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="124">
+  <mergeCells count="126">
     <mergeCell ref="A41:I41"/>
+    <mergeCell ref="B144:I144"/>
+    <mergeCell ref="A164:I164"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="B159:I159"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="B105:I105"/>
+    <mergeCell ref="A195:I195"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A85:I85"/>
     <mergeCell ref="B111:I111"/>
     <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A188:I188"/>
     <mergeCell ref="B98:I98"/>
-    <mergeCell ref="A140:I140"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A135:I135"/>
+    <mergeCell ref="B181:I181"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="B175:I175"/>
     <mergeCell ref="A68:I68"/>
+    <mergeCell ref="B162:I162"/>
     <mergeCell ref="A117:I117"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="B146:I146"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B83:I83"/>
+    <mergeCell ref="B139:I139"/>
+    <mergeCell ref="A103:I103"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
-    <mergeCell ref="B189:I189"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="A128:I128"/>
     <mergeCell ref="B75:I75"/>
     <mergeCell ref="A177:I177"/>
     <mergeCell ref="B141:I141"/>
-    <mergeCell ref="B115:I115"/>
-    <mergeCell ref="B150:I150"/>
-    <mergeCell ref="B193:I193"/>
-    <mergeCell ref="A192:I192"/>
     <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A145:I145"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="B86:I86"/>
-    <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
-    <mergeCell ref="A181:I181"/>
+    <mergeCell ref="A194:I194"/>
+    <mergeCell ref="A116:I116"/>
     <mergeCell ref="B136:I136"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="A184:I184"/>
+    <mergeCell ref="A131:I131"/>
     <mergeCell ref="A100:I100"/>
     <mergeCell ref="A171:I171"/>
     <mergeCell ref="A165:I165"/>
@@ -10297,21 +10438,22 @@
     <mergeCell ref="A180:I180"/>
     <mergeCell ref="A155:I155"/>
     <mergeCell ref="B178:I178"/>
+    <mergeCell ref="A143:I143"/>
+    <mergeCell ref="B192:I192"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B114:I114"/>
     <mergeCell ref="A168:I168"/>
     <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B163:I163"/>
+    <mergeCell ref="A183:I183"/>
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="B138:I138"/>
     <mergeCell ref="B156:I156"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="A120:I120"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="B149:I149"/>
     <mergeCell ref="A113:I113"/>
-    <mergeCell ref="B130:I130"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A32:I32"/>
@@ -10322,50 +10464,52 @@
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="B166:I166"/>
     <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B182:I182"/>
+    <mergeCell ref="B196:I196"/>
     <mergeCell ref="B118:I118"/>
     <mergeCell ref="A148:I148"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="B24:I24"/>
+    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A138:I138"/>
     <mergeCell ref="B89:I89"/>
+    <mergeCell ref="B104:I104"/>
+    <mergeCell ref="A110:I110"/>
     <mergeCell ref="A132:I132"/>
-    <mergeCell ref="A110:I110"/>
     <mergeCell ref="B169:I169"/>
-    <mergeCell ref="A124:I124"/>
+    <mergeCell ref="A187:I187"/>
     <mergeCell ref="B153:I153"/>
     <mergeCell ref="A174:I174"/>
+    <mergeCell ref="B129:I129"/>
     <mergeCell ref="B185:I185"/>
-    <mergeCell ref="A149:I149"/>
     <mergeCell ref="B121:I121"/>
+    <mergeCell ref="A158:I158"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B18:I18"/>
+    <mergeCell ref="A151:I151"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A125:I125"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A152:I152"/>
-    <mergeCell ref="A161:I161"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="B172:I172"/>
+    <mergeCell ref="A127:I127"/>
     <mergeCell ref="B108:I108"/>
-    <mergeCell ref="A114:I114"/>
-    <mergeCell ref="B143:I143"/>
     <mergeCell ref="B92:I92"/>
     <mergeCell ref="A191:I191"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A107:I107"/>
+    <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B133:I133"/>
     <mergeCell ref="A88:I88"/>
     <mergeCell ref="B80:I80"/>
-    <mergeCell ref="A162:I162"/>
     <mergeCell ref="B94:I94"/>
-    <mergeCell ref="B126:I126"/>
+    <mergeCell ref="B188:I188"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -10404,38 +10548,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I186" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I187" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I189" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I190" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I194" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I193" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I197" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10447,7 +10592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10502,7 +10647,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="196" customHeight="1">
+    <row r="5" ht="560" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10516,117 +10661,126 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int[] twoSum(int[] nums, int target) {
-        int[] arr=new int[2];
-       	 for(int i=0;i&lt;nums.length;i++) { 
-		 for(int j=i+1;j&lt;nums.length;j++) { 
-			 if(nums[i]+nums[j]==target) { 
-				arr[0]=i;
-                arr[1]=j;
-			 }
-		 }
-	 }
-     return arr;
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="504" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
+          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
+&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 1
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
-Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="252" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int lengthOfLongestSubstring(String s) {
+    int left =0;
+    int max = 0;
+    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
+    for(int right =0;right&lt;s.length();right++){
+         char currentChar = s.charAt(right);
+          while(hs.contains(s.charAt(right))){
+            hs.remove(s.charAt(left));
+            left++;
+          }
+          hs.add(s.charAt(right));
+          max = Math.max(max,right-left +1); 
+    }
+    return max;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="462" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 123
+&lt;strong&gt;Output:&lt;/strong&gt; 321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = -123
+&lt;strong&gt;Output:&lt;/strong&gt; -321
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; x = 120
+&lt;strong&gt;Output:&lt;/strong&gt; 21
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="280" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public static int rever(int num){
-        int rev =0;
-        while(num != 0){
-            int rem = num%10;
-            if(rev&gt;Integer.MAX_VALUE/10) return 0;
-            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
-            rev=rev*10+rem;
-            num/=10;
-        }
-        return rev;
-    }
-    public int reverse(int x) {
-    // int i=0;
-    // if(x&gt;=0)  i=1;
-    // else i = -1;
-    int num = rever(x);
-    return num;
-    }
-}</t>
         </is>
       </c>
     </row>
@@ -10981,7 +11135,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="210" customHeight="1">
+    <row r="16" ht="532" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
@@ -10995,47 +11149,99 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
+          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 5
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 4
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 6
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="224" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Largest Rectangle in Histogram</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
           <t>class Solution {
-    public int lengthOfLastWord(String s) {
-    char[] ch =s.toCharArray();
-    int count=0;
-    int i = s.length()-1;
-    while(s.charAt(i) == ' '){
-        i--;
-    }
-    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
-        count++;
-        i--;
-    }
-    return count;
+    public int largestRectangleArea(int[] heights) {
+    Deque&lt;Integer&gt; stack = new ArrayDeque&lt;&gt;();
+    int maxArea = 0;
+    for(int i=0;i&lt;=heights.length;i++){
+        int h = (i == heights.length)?0:heights[i];
+        while(!stack.isEmpty() &amp;&amp; heights[stack.peek()] &gt;=h ){
+           int height = heights[stack.poll()];
+           int width = (stack.isEmpty()) ? i: i - stack.peek() -1;
+           maxArea = Math.max(maxArea , width*height);
+        }
+        stack.push(i);
+    }  
+    return maxArea;
     }
 }</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="560" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="560" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Reverse Linked List II</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11103,74 +11309,80 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="420" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Binary Tree Inorder Traversal</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="inlineStr">
-        <is>
-          <t>/**
- * Definition for a binary tree node.
- * public class TreeNode {
- *     int val;
- *     TreeNode left;
- *     TreeNode right;
- *     TreeNode() {}
- *     TreeNode(int val) { this.val = val; }
- *     TreeNode(int val, TreeNode left, TreeNode right) {
- *         this.val = val;
- *         this.left = left;
- *         this.right = right;
- *     }
- * }
- */
-class Solution {
-    public  void inorder(TreeNode root,List list){
-    if(root == null) return;
-    inorder(root.left,list);
-    list.add(root.val);
-    inorder(root.right,list);
-    }
-    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
-    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
-    inorder(root,list);
-    return list;
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="406" customHeight="1">
+    <row r="19" ht="560" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>Binary Tree Inorder Traversal</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="406" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E19" s="25" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;111 - Minimum Depth of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/minimum-depth-of-binary-tree/"&gt;minimum-depth-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a binary tree, find its minimum depth.&lt;/p&gt;
 &lt;p&gt;The minimum depth is the number of nodes along the shortest path from the root node down to the nearest leaf node.&lt;/p&gt;
@@ -11197,24 +11409,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="210" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="210" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Best Time to Buy and Sell Stock</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int maxProfit(int[] prices) {
@@ -11234,24 +11446,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="532" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="532" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -11285,24 +11497,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="532" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="532" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;136 - Single Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/single-number/"&gt;single-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a &lt;strong&gt;non-empty&lt;/strong&gt;&amp;nbsp;array of integers &lt;code&gt;nums&lt;/code&gt;, every element appears &lt;em&gt;twice&lt;/em&gt; except for one. Find that single one.&lt;/p&gt;
 &lt;p&gt;You must&amp;nbsp;implement a solution with a linear runtime complexity and use&amp;nbsp;only constant&amp;nbsp;extra space.&lt;/p&gt;
@@ -11333,24 +11545,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="238" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="238" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -11372,24 +11584,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="560" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="560" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Linked List Cycle</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11445,24 +11657,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="560" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="560" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Linked List Cycle II</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>142</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11530,24 +11742,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="210" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="210" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Find Peak Element</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>162</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int findPeakElement(int[] nums) {
@@ -11567,24 +11779,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="266" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="266" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>167</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] twoSum(int[] numbers, int target) {
@@ -11608,24 +11820,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="294" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="294" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -11651,24 +11863,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="560" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="560" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Reverse Linked List</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>206</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="25" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -11713,24 +11925,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="560" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="560" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Course Schedule</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>207</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public class TopologicalSortUsingKhansAlgorithm {
@@ -11780,24 +11992,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="238" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="238" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="25" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -11819,24 +12031,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="560" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="560" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Course Schedule II</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
         <is>
           <t>class Solution {public class TopologicalSortUsingKhansAlgorithm {
 	int[] indegree;
@@ -11890,24 +12102,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="238" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="238" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>219</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -11929,24 +12141,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="322" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="322" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Sliding Window Maximum</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>239</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] maxSlidingWindow(int[] nums, int k) {
@@ -11970,24 +12182,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="392" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="392" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="25" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -12020,64 +12232,59 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="308" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Move Zeroes</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>283</v>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
-&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
-&lt;strong&gt;Output:&lt;/strong&gt; [0]
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="476" customHeight="1">
+    <row r="37" ht="182" customHeight="1">
       <c r="A37" s="5" t="n">
         <v>33</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Move Zeroes</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public void moveZeroes(int[] nums) {
+    int numbers = 0;
+    for(int traverse = 0;traverse&lt;nums.length;traverse++){
+        if(nums[traverse] != 0){
+            int temp = nums[traverse];
+            nums[traverse] = nums[numbers];
+            nums[numbers] = temp;
+            numbers++;
+        }
+    }  
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="476" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>Find the Duplicate Number</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>287</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int findDuplicate(int[] nums) {
@@ -12115,24 +12322,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="308" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="308" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -12156,24 +12363,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="420" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="420" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>304</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="25" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -12205,24 +12412,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="308" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="308" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Find All Duplicates in an Array</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>442</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public List&lt;Integer&gt; findDuplicates(int[] nums) {
@@ -12249,24 +12456,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="308" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="308" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Next Greater Element I</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>496</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElement(int[] nums1, int[] nums2) {
@@ -12293,24 +12500,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="322" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="322" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>503</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] nextGreaterElements(int[] nums) {
@@ -12335,24 +12542,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="546" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="546" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -12390,24 +12597,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="560" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="560" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public class Uniounandfind {
@@ -12459,24 +12666,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="182" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="182" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="25" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -12494,24 +12701,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="546" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="546" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -12555,24 +12762,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="196" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="196" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="25" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -12591,24 +12798,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="462" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="462" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -12638,24 +12845,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="518" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="518" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
         <is>
           <t>class Solution {
  class UniounFind{
@@ -12695,24 +12902,24 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="252" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
+    <row r="51" ht="252" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C51" s="5" t="n">
         <v>739</v>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] dailyTemperatures(int[] temperatures) {
@@ -12732,24 +12939,24 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="378" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52" ht="378" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C52" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -12781,24 +12988,24 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="294" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
+    <row r="53" ht="294" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Middle of the Linked List</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C53" s="5" t="n">
         <v>908</v>
       </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E52" s="26" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>/**
  * Definition for singly-linked list.
@@ -12824,24 +13031,24 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="560" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
+    <row r="54" ht="560" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E53" s="25" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -12877,67 +13084,64 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="294" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Valid Boomerang</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>1115</v>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E54" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public boolean isBoomerang(int[][] points) {
-    int x1=0,x2=0,x3=0;
-    int y1=0,y2=0,y3=0;
-    for(int i =0;i&lt;points.length;i++){
-        for(int j=0;j&lt;points[i].length-1;j++){
-           if(i==0){
-            x1 = points[i][j];
-            y1 = points[i][j+1];
-           }else if(i == 1){
-             x2 = points[i][j];
-             y2 = points[i][j+1];
-           }else{
-            x3 = points[i][j];
-            y3 = points[i][j+1];
-           }
-        }
-    } 
-    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="224" customHeight="1">
+    <row r="55" ht="294" customHeight="1">
       <c r="A55" s="5" t="n">
         <v>51</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>Valid Boomerang</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="224" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E55" s="25" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -12958,24 +13162,24 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="420" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="57" ht="420" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C57" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -13010,24 +13214,24 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="378" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
+    <row r="58" ht="378" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C58" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E57" s="25" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -13059,24 +13263,24 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="266" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
+    <row r="59" ht="266" customHeight="1">
+      <c r="A59" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C59" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E58" s="26" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] finalPrices(int[] prices) {
@@ -13100,24 +13304,24 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="350" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="350" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C60" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E59" s="25" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -13147,24 +13351,24 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="238" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
+    <row r="61" ht="238" customHeight="1">
+      <c r="A61" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C61" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E60" s="26" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -13186,24 +13390,24 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="308" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" ht="308" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E61" s="25" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -13230,24 +13434,24 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="280" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>58</v>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="63" ht="280" customHeight="1">
+      <c r="A63" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C63" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E62" s="26" t="inlineStr">
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -13270,24 +13474,24 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="448" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="64" ht="448" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E63" s="25" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -13322,24 +13526,24 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="378" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
+    <row r="65" ht="378" customHeight="1">
+      <c r="A65" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C65" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E64" s="26" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -13371,112 +13575,135 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="490" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="266" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C66" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static int digits(int num){
+        int multiply =1;
+        while(num!=0){
+            int rem = num%10;
+            multiply *= rem;
+            num /= 10;
+        }
+        return multiply;
+    }
+    public int smallestNumber(int n, int t) {
+    while(true){
+        if(digits(n)%t == 0){
+          return n;
+        } 
+        n++;
+    }
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="560" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E65" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
+      <c r="E67" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
+A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
         </is>
       </c>
     </row>
-    <row r="66" ht="308" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E66" s="26" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public int largestInteger(int[] nums, int k) {
-    int[] arr = new int[51];
-    for(int i = 0;i&lt;nums.length-k+1;i++){
-        boolean[] seen = new boolean[51];
-        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
-            if (!seen[nums[j]]){
-               arr[nums[j]]++;
-               seen[nums[j]] = true;
-            } 
-        }
-    } 
-    int high =-1;
-    for(int i=0;i&lt;arr.length;i++){
-        if(arr[i] == 1){
-           if(high&lt;i) high = i;
-        }
-    } 
-    return high;
-    }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="196" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
+    <row r="68" ht="196" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Reverse Degree of a String</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C68" s="7" t="n">
         <v>3811</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int reverseDegree(String s) {
@@ -13494,24 +13721,24 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="238" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="69" ht="238" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C69" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E68" s="26" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E69" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -13531,24 +13758,24 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="252" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
+    <row r="70" ht="252" customHeight="1">
+      <c r="A70" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C70" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E69" s="25" t="inlineStr">
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -13571,24 +13798,24 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="140" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
+    <row r="71" ht="140" customHeight="1">
+      <c r="A71" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C70" s="7" t="n">
+      <c r="C71" s="5" t="n">
         <v>4245</v>
       </c>
-      <c r="D70" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E71" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -13602,24 +13829,24 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="294" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
+    <row r="72" ht="294" customHeight="1">
+      <c r="A72" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C72" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E71" s="25" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E72" s="26" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -13645,24 +13872,24 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="252" customHeight="1">
-      <c r="A72" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
+    <row r="73" ht="252" customHeight="1">
+      <c r="A73" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C72" s="7" t="n">
+      <c r="C73" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E72" s="26" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E73" s="25" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {
@@ -13766,10 +13993,10 @@
         <v>27</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -13804,10 +14031,10 @@
         <v>27</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -2535,7 +2535,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -5445,7 +5445,7 @@
         <v>143.4</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>46276.50631944444</v>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H34" s="12" t="n">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H35" s="14" t="n">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H58" s="12" t="n">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H106" s="14" t="n">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H157" s="12" t="n">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H163" s="12" t="n">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H167" s="12" t="n">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H170" s="12" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H193" s="12" t="n">
@@ -10647,7 +10647,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="560" customHeight="1">
+    <row r="5" ht="196" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -10661,126 +10661,117 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] nums, int target) {
+        int[] arr=new int[2];
+       	 for(int i=0;i&lt;nums.length;i++) { 
+		 for(int j=i+1;j&lt;nums.length;j++) { 
+			 if(nums[i]+nums[j]==target) { 
+				arr[0]=i;
+                arr[1]=j;
+			 }
+		 }
+	 }
+     return arr;
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="504" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
-        <is>
-          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
-&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3 - Longest Substring Without Repeating Characters&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-substring-without-repeating-characters/"&gt;longest-substring-without-repeating-characters&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, find the length of the &lt;strong&gt;longest&lt;/strong&gt; &lt;span data-keyword="substring-nonempty"&gt;&lt;strong&gt;substring&lt;/strong&gt;&lt;/span&gt; without duplicate characters.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
-&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abcabcbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;abc&amp;quot;, with the length of 3. Note that &lt;code&gt;&amp;quot;bca&amp;quot;&lt;/code&gt; and &lt;code&gt;&amp;quot;cab&amp;quot;&lt;/code&gt; are also correct answers.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;bbbbb&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 1
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;b&amp;quot;, with the length of 1.
 &lt;/pre&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
 &lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
-&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;pwwkew&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 3
+&lt;strong&gt;Explanation:&lt;/strong&gt; The answer is &amp;quot;wke&amp;quot;, with the length of 3.
+Notice that the answer must be a substring, &amp;quot;pwke&amp;quot; is a subsequence and not a substring.
 &lt;/pre&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of English letters, digits, symbols and spaces.&lt;/li&gt;
 &lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="252" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="280" customHeight="1">
+      <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reverse Integer</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>class Solution {
-    public int lengthOfLongestSubstring(String s) {
-    int left =0;
-    int max = 0;
-    HashSet&lt;Character&gt; hs = new HashSet&lt;&gt;();
-    for(int right =0;right&lt;s.length();right++){
-         char currentChar = s.charAt(right);
-          while(hs.contains(s.charAt(right))){
-            hs.remove(s.charAt(left));
-            left++;
-          }
-          hs.add(s.charAt(right));
-          max = Math.max(max,right-left +1); 
+    public static int rever(int num){
+        int rev =0;
+        while(num != 0){
+            int rem = num%10;
+            if(rev&gt;Integer.MAX_VALUE/10) return 0;
+            if (rev &lt; Integer.MIN_VALUE / 10) return 0;
+            rev=rev*10+rem;
+            num/=10;
+        }
+        return rev;
     }
-    return max;
+    public int reverse(int x) {
+    // int i=0;
+    // if(x&gt;=0)  i=1;
+    // else i = -1;
+    int num = rever(x);
+    return num;
     }
 }</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="462" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Reverse Integer</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E7" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;7 - Reverse Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/reverse-integer/"&gt;reverse-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a signed 32-bit integer &lt;code&gt;x&lt;/code&gt;, return &lt;code&gt;x&lt;/code&gt;&lt;em&gt; with its digits reversed&lt;/em&gt;. If reversing &lt;code&gt;x&lt;/code&gt; causes the value to go outside the signed 32-bit integer range &lt;code&gt;[-2&lt;sup&gt;31&lt;/sup&gt;, 2&lt;sup&gt;31&lt;/sup&gt; - 1]&lt;/code&gt;, then return &lt;code&gt;0&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Assume the environment does not allow you to store 64-bit integers (signed or unsigned).&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 123
-&lt;strong&gt;Output:&lt;/strong&gt; 321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = -123
-&lt;strong&gt;Output:&lt;/strong&gt; -321
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; x = 120
-&lt;strong&gt;Output:&lt;/strong&gt; 21
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= x &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11126,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="532" customHeight="1">
+    <row r="16" ht="210" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
@@ -11149,40 +11140,26 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 5
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 4
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
-&lt;strong&gt;Output:&lt;/strong&gt; 6
-&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public int lengthOfLastWord(String s) {
+    char[] ch =s.toCharArray();
+    int count=0;
+    int i = s.length()-1;
+    while(s.charAt(i) == ' '){
+        i--;
+    }
+    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
+        count++;
+        i--;
+    }
+    return count;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -11309,7 +11286,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="560" customHeight="1">
+    <row r="19" ht="420" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>15</v>
       </c>
@@ -11323,45 +11300,39 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
         <is>
-          <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,null,2,3]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1,3,2]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/screenshot-2024-08-29-202743.png" style="width: 200px; height: 264px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1,2,3,4,5,null,8,null,null,6,7,9]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[4,2,6,5,7,1,3,9,8]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;&lt;img alt="" src="https://assets.leetcode.com/uploads/2024/08/29/tree_2.png" style="width: 350px; height: 286px;" /&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = []&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 4:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;root = [1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;[1]&lt;/span&gt;&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[0, 100]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;strong&gt;Follow up:&lt;/strong&gt; Recursive solution is trivial, could you do it iteratively?</t>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    public  void inorder(TreeNode root,List list){
+    if(root == null) return;
+    inorder(root.left,list);
+    list.add(root.val);
+    inorder(root.right,list);
+    }
+    public List&lt;Integer&gt; inorderTraversal(TreeNode root) {
+    List&lt;Integer&gt; list = new ArrayList&lt;&gt;();
+    inorder(root,list);
+    return list;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -12141,7 +12112,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="322" customHeight="1">
+    <row r="35" ht="532" customHeight="1">
       <c r="A35" s="5" t="n">
         <v>31</v>
       </c>
@@ -12162,21 +12133,36 @@
         <is>
           <t>class Solution {
     public int[] maxSlidingWindow(int[] nums, int k) {
+    // int[] result = new int[nums.length - k +1];
+    // Deque&lt;Integer&gt; dq = new ArrayDeque&lt;&gt;();
+    // for(int i=0;i&lt;nums.length;i++){
+    //     if(!dq.isEmpty() &amp;&amp; dq.peekFirst()&lt;=i-k){
+    //         dq.pollFirst();
+    //     }
+    //     while(!dq.isEmpty() &amp;&amp; nums[i] &gt;= nums[dq.peekLast()]){
+    //         dq.pollLast();
+    //     }
+    //      dq.offerLast(i);
+    //     if( i&gt;= k-1){
+    //         result[i-k+1] = nums[dq.peekFirst()];
+    //     }
+    // } 
+    // return result;   
     int[] result = new int[nums.length - k +1];
     Deque&lt;Integer&gt; dq = new ArrayDeque&lt;&gt;();
     for(int i=0;i&lt;nums.length;i++){
-        if(!dq.isEmpty() &amp;&amp; dq.peekFirst()&lt;=i-k){
-            dq.pollFirst();
-        }
-        while(!dq.isEmpty() &amp;&amp; nums[i] &gt;= nums[dq.peekLast()]){
-            dq.pollLast();
-        }
-         dq.offerLast(i);
-        if( i&gt;= k-1){
-            result[i-k+1] = nums[dq.peekFirst()];
-        }
-    } 
-    return result;   
+    while(!dq.isEmpty() &amp;&amp; dq.peekFirst() &lt;= i-k){
+      dq.pollFirst();
+    }
+    while(!dq.isEmpty() &amp;&amp; nums[i] &gt;= nums[dq.peekLast()] ){
+        dq.pollLast();
+    }
+    dq.offerLast(i);
+    if(i &gt;=k-1){
+        result[i - k + 1] = nums[dq.peekFirst()];
+    }
+    }
+    return result;
     }
 }</t>
         </is>
@@ -12232,7 +12218,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="182" customHeight="1">
+    <row r="37" ht="308" customHeight="1">
       <c r="A37" s="5" t="n">
         <v>33</v>
       </c>
@@ -12246,24 +12232,29 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E37" s="25" t="inlineStr">
         <is>
-          <t>class Solution {
-    public void moveZeroes(int[] nums) {
-    int numbers = 0;
-    for(int traverse = 0;traverse&lt;nums.length;traverse++){
-        if(nums[traverse] != 0){
-            int temp = nums[traverse];
-            nums[traverse] = nums[numbers];
-            nums[numbers] = temp;
-            numbers++;
-        }
-    }  
-    }
-}</t>
+          <t>&lt;h1&gt;283 - Move Zeroes&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/move-zeroes/"&gt;move-zeroes&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an integer array &lt;code&gt;nums&lt;/code&gt;, move all &lt;code&gt;0&lt;/code&gt;&amp;#39;s to the end of it while maintaining the relative order of the non-zero elements.&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt; that you must do this in-place without making a copy of the array.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0,1,0,3,12]
+&lt;strong&gt;Output:&lt;/strong&gt; [1,3,12,0,0]
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; nums = [0]
+&lt;strong&gt;Output:&lt;/strong&gt; [0]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-2&lt;sup&gt;31&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 2&lt;sup&gt;31&lt;/sup&gt; - 1&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow up:&lt;/strong&gt; Could you minimize the total number of operations done?</t>
         </is>
       </c>
     </row>
@@ -13098,29 +13089,32 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E55" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
-&lt;strong&gt;Output:&lt;/strong&gt; true
-&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
-&lt;strong&gt;Output:&lt;/strong&gt; false
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public boolean isBoomerang(int[][] points) {
+    int x1=0,x2=0,x3=0;
+    int y1=0,y2=0,y3=0;
+    for(int i =0;i&lt;points.length;i++){
+        for(int j=0;j&lt;points[i].length-1;j++){
+           if(i==0){
+            x1 = points[i][j];
+            y1 = points[i][j+1];
+           }else if(i == 1){
+             x2 = points[i][j];
+             y2 = points[i][j+1];
+           }else{
+            x3 = points[i][j];
+            y3 = points[i][j+1];
+           }
+        }
+    } 
+    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13569,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="266" customHeight="1">
+    <row r="66" ht="490" customHeight="1">
       <c r="A66" s="7" t="n">
         <v>62</v>
       </c>
@@ -13589,100 +13583,77 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E66" s="26" t="inlineStr">
         <is>
-          <t>class Solution {
-    public static int digits(int num){
-        int multiply =1;
-        while(num!=0){
-            int rem = num%10;
-            multiply *= rem;
-            num /= 10;
-        }
-        return multiply;
-    }
-    public int smallestNumber(int n, int t) {
-    while(true){
-        if(digits(n)%t == 0){
-          return n;
-        } 
-        n++;
-    }
-}
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="560" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="E67" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
-A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
+          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
+&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="308" customHeight="1">
+      <c r="A67" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E67" s="25" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int largestInteger(int[] nums, int k) {
+    int[] arr = new int[51];
+    for(int i = 0;i&lt;nums.length-k+1;i++){
+        boolean[] seen = new boolean[51];
+        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
+            if (!seen[nums[j]]){
+               arr[nums[j]]++;
+               seen[nums[j]] = true;
+            } 
+        }
+    } 
+    int high =-1;
+    for(int i=0;i&lt;arr.length;i++){
+        if(arr[i] == 1){
+           if(high&lt;i) high = i;
+        }
+    } 
+    return high;
+    }
+}</t>
         </is>
       </c>
     </row>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -859,7 +859,7 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Divide and Conquer, Dynamic Programming</t>
+          <t>Divide and Conquer, Design, Binary Indexed Tree, Segment Tree, Sqrt Decomposition</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -875,24 +875,24 @@
         <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>80.90000000000001</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Divide and Conquer, Dynamic Programming</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -904,21 +904,21 @@
         <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>94.8</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -930,73 +930,73 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>54.4</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Prefix Sum</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1544</v>
+        <v>18</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>48.6</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table, Prefix Sum</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -1005,24 +1005,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1031,24 +1031,24 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>57.9</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Stack, Monotonic Stack</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -1057,17 +1057,17 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>44.5</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Stack, Monotonic Stack</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -1083,24 +1083,24 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>46.3</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -1109,24 +1109,24 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1135,17 +1135,17 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -1161,17 +1161,17 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
@@ -1187,24 +1187,24 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -1213,24 +1213,24 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
@@ -1239,24 +1239,24 @@
         <v>1</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0</v>
@@ -1265,21 +1265,21 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>1</v>
@@ -1288,72 +1288,72 @@
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>65.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>143.4</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>46.7</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -1369,24 +1369,24 @@
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Sorting, Quicksort</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -1395,99 +1395,99 @@
         <v>1</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>48.9</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Stack, Monotonic Stack</t>
+          <t>Sorting, Quicksort</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>34.3</v>
+        <v>8</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>67.40000000000001</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Stack, Monotonic Stack, Range Minimum/Maximum Query</t>
+          <t>Stack, Monotonic Stack</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>19</v>
+        <v>34.3</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>76.5</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Stack, Monotonic Stack, Range Minimum/Maximum Query</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>47.2</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>0</v>
@@ -1496,10 +1496,10 @@
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H34" s="7" t="n">
         <v>47.2</v>
@@ -1509,33 +1509,33 @@
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>48.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+          <t>Two Pointers, Binary Search</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
@@ -1551,281 +1551,281 @@
         <v>1</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H38" s="7" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr"/>
-      <c r="C38" s="9" t="n">
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D39" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="F39" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Breadth-First Search, Graph Theory, Topological Sort</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
+      <c r="C40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H40" s="7" t="n">
         <v>46.9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>47.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>Breadth-First Search, Union-Find, Graph Theory</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G42" s="7" t="n">
         <v>2.5</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H42" s="7" t="n">
         <v>46</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Depth-First Search — TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr"/>
-      <c r="C42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="9" t="n">
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9" t="n">
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="5" t="n">
+      <c r="C44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr"/>
-      <c r="C44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Linked List</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Divide and Conquer, Heap (Priority Queue), Merge Sort, Tournament Sort</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="n">
+      <c r="C46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H46" s="7" t="n">
         <v>45.9</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>42.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" s="5" t="n">
         <v>1</v>
@@ -1834,30 +1834,30 @@
         <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>46.8</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Recursion</t>
+          <t>Hash Table, Two Pointers, Floyd's Cycle Finding Algorithm</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>2</v>
@@ -1866,229 +1866,229 @@
         <v>0</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>45.3</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
+          <t>Recursion</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="5" t="n">
+      <c r="C50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Linked List — TOTAL</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr"/>
-      <c r="C50" s="9" t="n">
+      <c r="B51" s="8" t="inlineStr"/>
+      <c r="C51" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D50" s="9" t="n">
+      <c r="D51" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="9" t="n">
+      <c r="E51" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="9" t="n">
+      <c r="F51" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="5" t="n">
+      <c r="C52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="5" t="n">
+      <c r="H52" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr"/>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C54" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
+      <c r="D54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="G54" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H54" s="7" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr"/>
-      <c r="C54" s="9" t="n">
+      <c r="B55" s="8" t="inlineStr"/>
+      <c r="C55" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D54" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="9" t="n">
+      <c r="D55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G54" s="9" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr"/>
+      <c r="H55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="5" t="n">
+      <c r="C56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr"/>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H56" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0</v>
@@ -2097,17 +2097,17 @@
         <v>1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
@@ -2123,17 +2123,17 @@
         <v>1</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>44.1</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr"/>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
@@ -2149,237 +2149,263 @@
         <v>1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>45.3</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr"/>
       <c r="B60" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="7" t="n">
+      <c r="C61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H60" s="7" t="n">
+      <c r="H61" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr"/>
-      <c r="C61" s="9" t="n">
+      <c r="B62" s="8" t="inlineStr"/>
+      <c r="C62" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D61" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="9" t="n">
+      <c r="D62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="G61" s="9" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+      <c r="G62" s="9" t="inlineStr"/>
+      <c r="H62" s="9" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="7" t="n">
+      <c r="C63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr"/>
       <c r="B64" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="7" t="n">
+      <c r="C65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr"/>
-      <c r="C65" s="9" t="n">
+      <c r="B66" s="8" t="inlineStr"/>
+      <c r="C66" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="9" t="n">
+      <c r="D66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G65" s="9" t="inlineStr"/>
-      <c r="H65" s="9" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
+      <c r="G66" s="9" t="inlineStr"/>
+      <c r="H66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="7" t="n">
+      <c r="C67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H67" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr"/>
-      <c r="C67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="9" t="inlineStr"/>
-      <c r="H67" s="9" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr"/>
+      <c r="C68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="9" t="inlineStr"/>
+      <c r="H68" s="9" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr"/>
-      <c r="C68" s="11" t="n">
+      <c r="B69" s="10" t="inlineStr"/>
+      <c r="C69" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="D68" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="E68" s="11" t="n">
+      <c r="D69" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E69" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F68" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="G68" s="11" t="inlineStr"/>
-      <c r="H68" s="11" t="inlineStr"/>
+      <c r="F69" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="G69" s="11" t="inlineStr"/>
+      <c r="H69" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2395,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5956,11 +5982,61 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>307</v>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Range Sum Query - Mutable</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Divide and Conquer, Design, Binary Indexed Tree, Segment Tree, Sqrt Decomposition</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>95</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="J74" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" s="14" t="n">
+        <v>46289.03825231481</v>
+      </c>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F73">
+  <conditionalFormatting sqref="F5:F74">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -6041,6 +6117,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6052,7 +6129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6095,7 +6172,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   41 solved   (Low: 19 · Medium: 19 · High: 3)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   42 solved   (Low: 19 · Medium: 20 · High: 3)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -6520,7 +6597,7 @@
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Dynamic Programming   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Design, Binary Indexed Tree, Segment Tree, Sqrt Decomposition   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B23" s="18" t="n"/>
@@ -6551,11 +6628,11 @@
       <c r="A25" s="5" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Maximum Subarray</t>
+          <t>Range Sum Query - Mutable</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
@@ -6563,10 +6640,10 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>80.90000000000001</v>
+        <v>133.5</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -6574,7 +6651,7 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>46263.45222222222</v>
+        <v>46289.03825231481</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -6585,7 +6662,7 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Dynamic Programming   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Dynamic Programming   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B26" s="18" t="n"/>
@@ -6598,40 +6675,40 @@
       <c r="I26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n"/>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="21" t="n"/>
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Best Time to Buy and Sell Stock</t>
+          <t>Maximum Subarray</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>94.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -6639,7 +6716,7 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>46287.52454861111</v>
+        <v>46263.45222222222</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -6650,7 +6727,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Dynamic Programming   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B29" s="18" t="n"/>
@@ -6663,40 +6740,40 @@
       <c r="I29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Best Time to Buy and Sell Stock</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>4003</v>
+        <v>121</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>98</v>
+        <v>94.8</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -6704,7 +6781,7 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46247.80789351852</v>
+        <v>46287.52454861111</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -6715,7 +6792,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table   —   3 solved   (Low: 2 · Medium: 0 · High: 1)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -6728,40 +6805,40 @@
       <c r="I32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n"/>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Two Sum</t>
+          <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>1</v>
+        <v>4003</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -6769,7 +6846,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46251.8174537037</v>
+        <v>46247.80789351852</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -6778,75 +6855,55 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr"/>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="n">
-        <v>46252.95966435185</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table   —   3 solved   (Low: 2 · Medium: 0 · High: 1)</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="18" t="n"/>
+      <c r="I35" s="18" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="n"/>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="n"/>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="n"/>
-      <c r="H36" s="23" t="n"/>
-      <c r="I36" s="23" t="n"/>
+      <c r="A36" s="21" t="n"/>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>First Missing Positive</t>
+          <t>Two Sum</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>71.09999999999999</v>
+        <v>47</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -6854,7 +6911,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46273.670625</v>
+        <v>46251.8174537037</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -6863,55 +6920,75 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="18" t="n"/>
-      <c r="I38" s="18" t="n"/>
+      <c r="A38" s="7" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>46252.95966435185</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
+      <c r="A39" s="23" t="n"/>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="23" t="n"/>
+      <c r="I39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Subarray Sum Equals K</t>
+          <t>First Missing Positive</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>560</v>
+        <v>41</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1544</v>
+        <v>1</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>48.6</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -6919,7 +6996,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46263.40873842593</v>
+        <v>46273.670625</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -6930,7 +7007,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -6943,40 +7020,40 @@
       <c r="I41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="n"/>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Contains Duplicate II</t>
+          <t>Subarray Sum Equals K</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>219</v>
+        <v>560</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -6984,7 +7061,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46258.98878472222</v>
+        <v>46263.40873842593</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -6995,7 +7072,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -7008,40 +7085,40 @@
       <c r="I44" s="18" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="n"/>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="21" t="n"/>
+      <c r="I45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Find All Duplicates in an Array</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>442</v>
+        <v>219</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>57.9</v>
+        <v>104.8</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -7049,7 +7126,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46273.57508101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -7060,7 +7137,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Stack, Monotonic Stack   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -7073,40 +7150,40 @@
       <c r="I47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="n"/>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
+      <c r="A48" s="19" t="n"/>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="19" t="n"/>
+      <c r="H48" s="19" t="n"/>
+      <c r="I48" s="19" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Next Greater Element I</t>
+          <t>Find All Duplicates in an Array</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>496</v>
+        <v>442</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>44.5</v>
+        <v>57.9</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -7114,7 +7191,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46288.95560185185</v>
+        <v>46273.57508101852</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -7125,7 +7202,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Stack, Monotonic Stack   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -7156,11 +7233,11 @@
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Next Greater Element I</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1353</v>
+        <v>496</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
@@ -7168,10 +7245,10 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>46.3</v>
+        <v>44.5</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -7179,7 +7256,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46288.95560185185</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -7190,7 +7267,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -7203,40 +7280,40 @@
       <c r="I53" s="18" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="n"/>
-      <c r="B54" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="19" t="n"/>
-      <c r="E54" s="19" t="n"/>
-      <c r="F54" s="19" t="n"/>
-      <c r="G54" s="19" t="n"/>
-      <c r="H54" s="19" t="n"/>
-      <c r="I54" s="19" t="n"/>
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="21" t="n"/>
+      <c r="I54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -7244,7 +7321,7 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -7255,7 +7332,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -7268,40 +7345,40 @@
       <c r="I56" s="18" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="n"/>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="n"/>
-      <c r="D57" s="21" t="n"/>
-      <c r="E57" s="21" t="n"/>
-      <c r="F57" s="21" t="n"/>
-      <c r="G57" s="21" t="n"/>
-      <c r="H57" s="21" t="n"/>
-      <c r="I57" s="21" t="n"/>
+      <c r="A57" s="19" t="n"/>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="19" t="n"/>
+      <c r="G57" s="19" t="n"/>
+      <c r="H57" s="19" t="n"/>
+      <c r="I57" s="19" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -7309,7 +7386,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -7320,7 +7397,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -7351,11 +7428,11 @@
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
@@ -7363,10 +7440,10 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
@@ -7374,7 +7451,7 @@
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -7385,7 +7462,7 @@
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -7416,11 +7493,11 @@
       <c r="A64" s="5" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
@@ -7428,10 +7505,10 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -7439,7 +7516,7 @@
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -7450,7 +7527,7 @@
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -7463,40 +7540,40 @@
       <c r="I65" s="18" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="19" t="n"/>
-      <c r="B66" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
-      <c r="G66" s="19" t="n"/>
-      <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
+      <c r="A66" s="21" t="n"/>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="21" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -7504,7 +7581,7 @@
         </is>
       </c>
       <c r="H67" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -7515,7 +7592,7 @@
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B68" s="18" t="n"/>
@@ -7528,40 +7605,40 @@
       <c r="I68" s="18" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="21" t="n"/>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
+      <c r="A69" s="19" t="n"/>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="19" t="n"/>
+      <c r="H69" s="19" t="n"/>
+      <c r="I69" s="19" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -7569,7 +7646,7 @@
         </is>
       </c>
       <c r="H70" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -7580,7 +7657,7 @@
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B71" s="18" t="n"/>
@@ -7593,40 +7670,40 @@
       <c r="I71" s="18" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="19" t="n"/>
-      <c r="B72" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C72" s="19" t="n"/>
-      <c r="D72" s="19" t="n"/>
-      <c r="E72" s="19" t="n"/>
-      <c r="F72" s="19" t="n"/>
-      <c r="G72" s="19" t="n"/>
-      <c r="H72" s="19" t="n"/>
-      <c r="I72" s="19" t="n"/>
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
@@ -7634,7 +7711,7 @@
         </is>
       </c>
       <c r="H73" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -7645,7 +7722,7 @@
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B74" s="18" t="n"/>
@@ -7658,155 +7735,155 @@
       <c r="I74" s="18" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="21" t="n"/>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C75" s="21" t="n"/>
-      <c r="D75" s="21" t="n"/>
-      <c r="E75" s="21" t="n"/>
-      <c r="F75" s="21" t="n"/>
-      <c r="G75" s="21" t="n"/>
-      <c r="H75" s="21" t="n"/>
-      <c r="I75" s="21" t="n"/>
+      <c r="A75" s="19" t="n"/>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="19" t="n"/>
+      <c r="G75" s="19" t="n"/>
+      <c r="H75" s="19" t="n"/>
+      <c r="I75" s="19" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
+          <t>Matrix Block Sum</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>46262.8983912037</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="21" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="21" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr"/>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C79" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="5" t="n">
+      <c r="E79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="n">
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n">
         <v>46270.61052083333</v>
       </c>
-      <c r="I76" s="13" t="inlineStr">
+      <c r="I79" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="19" t="n"/>
-      <c r="B77" s="20" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="19" t="n"/>
+      <c r="B80" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C77" s="19" t="n"/>
-      <c r="D77" s="19" t="n"/>
-      <c r="E77" s="19" t="n"/>
-      <c r="F77" s="19" t="n"/>
-      <c r="G77" s="19" t="n"/>
-      <c r="H77" s="19" t="n"/>
-      <c r="I77" s="19" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Flight Bookings</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="n">
-        <v>46262.6837962963</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B79" s="18" t="n"/>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="18" t="n"/>
-      <c r="E79" s="18" t="n"/>
-      <c r="F79" s="18" t="n"/>
-      <c r="G79" s="18" t="n"/>
-      <c r="H79" s="18" t="n"/>
-      <c r="I79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="23" t="n"/>
-      <c r="B80" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="23" t="n"/>
-      <c r="E80" s="23" t="n"/>
-      <c r="F80" s="23" t="n"/>
-      <c r="G80" s="23" t="n"/>
-      <c r="H80" s="23" t="n"/>
-      <c r="I80" s="23" t="n"/>
+      <c r="C80" s="19" t="n"/>
+      <c r="D80" s="19" t="n"/>
+      <c r="E80" s="19" t="n"/>
+      <c r="F80" s="19" t="n"/>
+      <c r="G80" s="19" t="n"/>
+      <c r="H80" s="19" t="n"/>
+      <c r="I80" s="19" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window Maximum</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C81" s="5" t="n">
-        <v>239</v>
+        <v>1206</v>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>143.4</v>
+        <v>85</v>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
@@ -7814,7 +7891,7 @@
         </is>
       </c>
       <c r="H81" s="12" t="n">
-        <v>46276.50631944444</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -7825,7 +7902,7 @@
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Queue, Sliding Window, Heap (Priority Queue), Monotonic Queue, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B82" s="18" t="n"/>
@@ -7838,40 +7915,40 @@
       <c r="I82" s="18" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="21" t="n"/>
-      <c r="B83" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C83" s="21" t="n"/>
-      <c r="D83" s="21" t="n"/>
-      <c r="E83" s="21" t="n"/>
-      <c r="F83" s="21" t="n"/>
-      <c r="G83" s="21" t="n"/>
-      <c r="H83" s="21" t="n"/>
-      <c r="I83" s="21" t="n"/>
+      <c r="A83" s="23" t="n"/>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C83" s="23" t="n"/>
+      <c r="D83" s="23" t="n"/>
+      <c r="E83" s="23" t="n"/>
+      <c r="F83" s="23" t="n"/>
+      <c r="G83" s="23" t="n"/>
+      <c r="H83" s="23" t="n"/>
+      <c r="I83" s="23" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Sliding Window Maximum</t>
         </is>
       </c>
       <c r="C84" s="5" t="n">
-        <v>3347</v>
+        <v>239</v>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>46.7</v>
+        <v>143.4</v>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
@@ -7879,7 +7956,7 @@
         </is>
       </c>
       <c r="H84" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46276.50631944444</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -7890,7 +7967,7 @@
     <row r="85">
       <c r="A85" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B85" s="18" t="n"/>
@@ -7921,11 +7998,11 @@
       <c r="A87" s="5" t="inlineStr"/>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C87" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
@@ -7933,10 +8010,10 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
@@ -7944,7 +8021,7 @@
         </is>
       </c>
       <c r="H87" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -7955,7 +8032,7 @@
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sorting, Quicksort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B88" s="18" t="n"/>
@@ -7968,40 +8045,40 @@
       <c r="I88" s="18" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="19" t="n"/>
-      <c r="B89" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="n"/>
-      <c r="D89" s="19" t="n"/>
-      <c r="E89" s="19" t="n"/>
-      <c r="F89" s="19" t="n"/>
-      <c r="G89" s="19" t="n"/>
-      <c r="H89" s="19" t="n"/>
-      <c r="I89" s="19" t="n"/>
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="21" t="n"/>
+      <c r="E89" s="21" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="21" t="n"/>
+      <c r="I89" s="21" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Merge Intervals</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>56</v>
+        <v>643</v>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>48.9</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
@@ -8009,7 +8086,7 @@
         </is>
       </c>
       <c r="H90" s="12" t="n">
-        <v>46273.68709490741</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -8020,7 +8097,7 @@
     <row r="91">
       <c r="A91" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack   —   3 solved   (Low: 1 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sorting, Quicksort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B91" s="18" t="n"/>
@@ -8033,200 +8110,200 @@
       <c r="I91" s="18" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="21" t="n"/>
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="n"/>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
+      <c r="A92" s="19" t="n"/>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="n"/>
+      <c r="D92" s="19" t="n"/>
+      <c r="E92" s="19" t="n"/>
+      <c r="F92" s="19" t="n"/>
+      <c r="G92" s="19" t="n"/>
+      <c r="H92" s="19" t="n"/>
+      <c r="I92" s="19" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
+          <t>Merge Intervals</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>46273.68709490741</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack   —   3 solved   (Low: 1 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="n"/>
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+      <c r="G94" s="18" t="n"/>
+      <c r="H94" s="18" t="n"/>
+      <c r="I94" s="18" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="n"/>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="n"/>
+      <c r="D95" s="21" t="n"/>
+      <c r="E95" s="21" t="n"/>
+      <c r="F95" s="21" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr"/>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
           <t>Final Prices With a Special Discount in a Shop</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C96" s="5" t="n">
         <v>1570</v>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E96" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F96" s="5" t="n">
         <v>45.6</v>
       </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="n">
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n">
         <v>46275.51596064815</v>
       </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I96" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="19" t="n"/>
-      <c r="B94" s="20" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="19" t="n"/>
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C94" s="19" t="n"/>
-      <c r="D94" s="19" t="n"/>
-      <c r="E94" s="19" t="n"/>
-      <c r="F94" s="19" t="n"/>
-      <c r="G94" s="19" t="n"/>
-      <c r="H94" s="19" t="n"/>
-      <c r="I94" s="19" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="C97" s="19" t="n"/>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="19" t="n"/>
+      <c r="G97" s="19" t="n"/>
+      <c r="H97" s="19" t="n"/>
+      <c r="I97" s="19" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr"/>
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>Next Greater Element II</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C98" s="5" t="n">
         <v>503</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E98" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F98" s="5" t="n">
         <v>48.5</v>
       </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H95" s="12" t="n">
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="n">
         <v>46275.6128125</v>
       </c>
-      <c r="I95" s="13" t="inlineStr">
+      <c r="I98" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr"/>
-      <c r="B96" s="6" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr"/>
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Daily Temperatures</t>
         </is>
       </c>
-      <c r="C96" s="7" t="n">
+      <c r="C99" s="7" t="n">
         <v>739</v>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="7" t="n">
+      <c r="E99" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F96" s="7" t="n">
+      <c r="F99" s="7" t="n">
         <v>108.1</v>
       </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H96" s="14" t="n">
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="n">
         <v>46275.62596064815</v>
       </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
-        </is>
-      </c>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="23" t="n"/>
-      <c r="B98" s="24" t="inlineStr">
-        <is>
-          <t>High (Hard) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C98" s="23" t="n"/>
-      <c r="D98" s="23" t="n"/>
-      <c r="E98" s="23" t="n"/>
-      <c r="F98" s="23" t="n"/>
-      <c r="G98" s="23" t="n"/>
-      <c r="H98" s="23" t="n"/>
-      <c r="I98" s="23" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr"/>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Largest Rectangle in Histogram</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>46288.97087962963</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
+      <c r="I99" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8235,7 +8312,7 @@
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Stack, Monotonic Stack, Range Minimum/Maximum Query   —   1 solved   (Low: 0 · Medium: 0 · High: 1)</t>
         </is>
       </c>
       <c r="B100" s="18" t="n"/>
@@ -8248,40 +8325,40 @@
       <c r="I100" s="18" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="21" t="n"/>
-      <c r="B101" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C101" s="21" t="n"/>
-      <c r="D101" s="21" t="n"/>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
+      <c r="A101" s="23" t="n"/>
+      <c r="B101" s="24" t="inlineStr">
+        <is>
+          <t>High (Hard) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C101" s="23" t="n"/>
+      <c r="D101" s="23" t="n"/>
+      <c r="E101" s="23" t="n"/>
+      <c r="F101" s="23" t="n"/>
+      <c r="G101" s="23" t="n"/>
+      <c r="H101" s="23" t="n"/>
+      <c r="I101" s="23" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr"/>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Largest Rectangle in Histogram</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
-        <v>4281</v>
+        <v>84</v>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Hard</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>47.2</v>
+        <v>76.5</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
@@ -8289,7 +8366,7 @@
         </is>
       </c>
       <c r="H102" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46288.97087962963</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -8300,7 +8377,7 @@
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B103" s="18" t="n"/>
@@ -8316,7 +8393,7 @@
       <c r="A104" s="21" t="n"/>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C104" s="21" t="n"/>
@@ -8331,132 +8408,132 @@
       <c r="A105" s="5" t="inlineStr"/>
       <c r="B105" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="n"/>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="n"/>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="n"/>
+      <c r="D107" s="21" t="n"/>
+      <c r="E107" s="21" t="n"/>
+      <c r="F107" s="21" t="n"/>
+      <c r="G107" s="21" t="n"/>
+      <c r="H107" s="21" t="n"/>
+      <c r="I107" s="21" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr"/>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C108" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E105" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F105" s="5" t="n">
+      <c r="E108" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G105" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H105" s="12" t="n">
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I105" s="13" t="inlineStr">
+      <c r="I108" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="7" t="inlineStr"/>
-      <c r="B106" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr"/>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C106" s="7" t="n">
+      <c r="C109" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D109" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E106" s="7" t="n">
+      <c r="E109" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F106" s="7" t="n">
+      <c r="F109" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G106" s="7" t="inlineStr">
+      <c r="G109" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H106" s="14" t="n">
+      <c r="H109" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I106" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B107" s="18" t="n"/>
-      <c r="C107" s="18" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="19" t="n"/>
-      <c r="B108" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C108" s="19" t="n"/>
-      <c r="D108" s="19" t="n"/>
-      <c r="E108" s="19" t="n"/>
-      <c r="F108" s="19" t="n"/>
-      <c r="G108" s="19" t="n"/>
-      <c r="H108" s="19" t="n"/>
-      <c r="I108" s="19" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr"/>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Two Sum II - Input Array Is Sorted</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>46272.93130787037</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
+      <c r="I109" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -8465,7 +8542,7 @@
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B110" s="18" t="n"/>
@@ -8496,11 +8573,11 @@
       <c r="A112" s="5" t="inlineStr"/>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Find the Duplicate Number</t>
+          <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
       <c r="C112" s="5" t="n">
-        <v>287</v>
+        <v>167</v>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
@@ -8508,10 +8585,10 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
@@ -8519,7 +8596,7 @@
         </is>
       </c>
       <c r="H112" s="12" t="n">
-        <v>46274.9421875</v>
+        <v>46272.93130787037</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -8530,7 +8607,7 @@
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search, Bit Manipulation, Pigeonhole Principle, Floyd's Cycle Finding Algorithm   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B113" s="18" t="n"/>
@@ -8561,121 +8638,121 @@
       <c r="A115" s="5" t="inlineStr"/>
       <c r="B115" s="4" t="inlineStr">
         <is>
+          <t>Find the Duplicate Number</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>46274.9421875</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="19" t="n"/>
+      <c r="B117" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C117" s="19" t="n"/>
+      <c r="D117" s="19" t="n"/>
+      <c r="E117" s="19" t="n"/>
+      <c r="F117" s="19" t="n"/>
+      <c r="G117" s="19" t="n"/>
+      <c r="H117" s="19" t="n"/>
+      <c r="I117" s="19" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr"/>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C115" s="5" t="n">
+      <c r="C118" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E115" s="5" t="n">
+      <c r="E118" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F115" s="5" t="n">
+      <c r="F118" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H115" s="12" t="n">
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I115" s="13" t="inlineStr">
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="16" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DEPTH-FIRST SEARCH   —   4 solved   (Low: 0 · Medium: 4 · High: 0)</t>
         </is>
       </c>
-      <c r="B116" s="2" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="n"/>
-      <c r="H116" s="2" t="n"/>
-      <c r="I116" s="2" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B117" s="18" t="n"/>
-      <c r="C117" s="18" t="n"/>
-      <c r="D117" s="18" t="n"/>
-      <c r="E117" s="18" t="n"/>
-      <c r="F117" s="18" t="n"/>
-      <c r="G117" s="18" t="n"/>
-      <c r="H117" s="18" t="n"/>
-      <c r="I117" s="18" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="19" t="n"/>
-      <c r="B118" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C118" s="19" t="n"/>
-      <c r="D118" s="19" t="n"/>
-      <c r="E118" s="19" t="n"/>
-      <c r="F118" s="19" t="n"/>
-      <c r="G118" s="19" t="n"/>
-      <c r="H118" s="19" t="n"/>
-      <c r="I118" s="19" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr"/>
-      <c r="B119" s="4" t="inlineStr">
-        <is>
-          <t>Course Schedule II</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="G119" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H119" s="12" t="n">
-        <v>46288.67247685185</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B120" s="18" t="n"/>
@@ -8706,11 +8783,11 @@
       <c r="A122" s="5" t="inlineStr"/>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Course Schedule</t>
+          <t>Course Schedule II</t>
         </is>
       </c>
       <c r="C122" s="5" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
@@ -8718,10 +8795,10 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
@@ -8729,7 +8806,7 @@
         </is>
       </c>
       <c r="H122" s="12" t="n">
-        <v>46288.65751157407</v>
+        <v>46288.67247685185</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -8740,7 +8817,7 @@
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Graph Theory, Topological Sort, Directed Acyclic Graph   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B123" s="18" t="n"/>
@@ -8756,7 +8833,7 @@
       <c r="A124" s="19" t="n"/>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Medium (Medium) — 2 problem(s)</t>
+          <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C124" s="19" t="n"/>
@@ -8771,236 +8848,236 @@
       <c r="A125" s="5" t="inlineStr"/>
       <c r="B125" s="4" t="inlineStr">
         <is>
+          <t>Course Schedule</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>46288.65751157407</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Breadth-First Search, Union-Find, Graph Theory   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="n"/>
+      <c r="C126" s="18" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="18" t="n"/>
+      <c r="G126" s="18" t="n"/>
+      <c r="H126" s="18" t="n"/>
+      <c r="I126" s="18" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="19" t="n"/>
+      <c r="B127" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="n"/>
+      <c r="D127" s="19" t="n"/>
+      <c r="E127" s="19" t="n"/>
+      <c r="F127" s="19" t="n"/>
+      <c r="G127" s="19" t="n"/>
+      <c r="H127" s="19" t="n"/>
+      <c r="I127" s="19" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr"/>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
           <t>Number of Provinces</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C128" s="5" t="n">
         <v>547</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="5" t="n">
+      <c r="E128" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F125" s="5" t="n">
+      <c r="F128" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="n">
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H128" s="12" t="n">
         <v>46287.65729166667</v>
       </c>
-      <c r="I125" s="13" t="inlineStr">
+      <c r="I128" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="7" t="inlineStr"/>
-      <c r="B126" s="6" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="7" t="inlineStr"/>
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>Redundant Connection</t>
         </is>
       </c>
-      <c r="C126" s="7" t="n">
+      <c r="C129" s="7" t="n">
         <v>684</v>
       </c>
-      <c r="D126" s="7" t="inlineStr">
+      <c r="D129" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="7" t="n">
+      <c r="E129" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="7" t="n">
         <v>44.9</v>
       </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="n">
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H129" s="14" t="n">
         <v>46287.51434027778</v>
       </c>
-      <c r="I126" s="15" t="inlineStr">
+      <c r="I129" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="16" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B127" s="2" t="n"/>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n"/>
-      <c r="E127" s="2" t="n"/>
-      <c r="F127" s="2" t="n"/>
-      <c r="G127" s="2" t="n"/>
-      <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="17" t="inlineStr">
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B128" s="18" t="n"/>
-      <c r="C128" s="18" t="n"/>
-      <c r="D128" s="18" t="n"/>
-      <c r="E128" s="18" t="n"/>
-      <c r="F128" s="18" t="n"/>
-      <c r="G128" s="18" t="n"/>
-      <c r="H128" s="18" t="n"/>
-      <c r="I128" s="18" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="21" t="n"/>
-      <c r="B129" s="22" t="inlineStr">
+      <c r="B131" s="18" t="n"/>
+      <c r="C131" s="18" t="n"/>
+      <c r="D131" s="18" t="n"/>
+      <c r="E131" s="18" t="n"/>
+      <c r="F131" s="18" t="n"/>
+      <c r="G131" s="18" t="n"/>
+      <c r="H131" s="18" t="n"/>
+      <c r="I131" s="18" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="21" t="n"/>
+      <c r="B132" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C129" s="21" t="n"/>
-      <c r="D129" s="21" t="n"/>
-      <c r="E129" s="21" t="n"/>
-      <c r="F129" s="21" t="n"/>
-      <c r="G129" s="21" t="n"/>
-      <c r="H129" s="21" t="n"/>
-      <c r="I129" s="21" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr"/>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="C132" s="21" t="n"/>
+      <c r="D132" s="21" t="n"/>
+      <c r="E132" s="21" t="n"/>
+      <c r="F132" s="21" t="n"/>
+      <c r="G132" s="21" t="n"/>
+      <c r="H132" s="21" t="n"/>
+      <c r="I132" s="21" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr"/>
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C130" s="5" t="n">
+      <c r="C133" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E130" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="5" t="n">
+      <c r="E133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G130" s="5" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H130" s="12" t="n">
+      <c r="H133" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I130" s="13" t="inlineStr">
+      <c r="I133" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="16" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: LINKED LIST   —   7 solved   (Low: 3 · Medium: 2 · High: 2)</t>
         </is>
       </c>
-      <c r="B131" s="2" t="n"/>
-      <c r="C131" s="2" t="n"/>
-